--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1581,22 +1581,22 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
@@ -2162,97 +2162,97 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" s="19" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" s="19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" s="19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" s="19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" s="19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -2427,7 +2427,7 @@
         <v>7</v>
       </c>
       <c r="U5" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2496,7 +2496,7 @@
         <v>79.70999999999999</v>
       </c>
       <c r="U6" s="36" t="n">
-        <v>104.6</v>
+        <v>106.33</v>
       </c>
     </row>
     <row r="7">
@@ -2565,7 +2565,7 @@
         <v>92.14</v>
       </c>
       <c r="U7" s="36" t="n">
-        <v>88</v>
+        <v>91.17</v>
       </c>
     </row>
     <row r="8">
@@ -2634,7 +2634,7 @@
         <v>64.43000000000001</v>
       </c>
       <c r="U8" s="36" t="n">
-        <v>69.8</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="9">
@@ -2703,7 +2703,7 @@
         <v>60.71</v>
       </c>
       <c r="U9" s="36" t="n">
-        <v>67.2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -2772,7 +2772,7 @@
         <v>44.57</v>
       </c>
       <c r="U10" s="36" t="n">
-        <v>52.8</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="11">
@@ -2841,7 +2841,7 @@
         <v>50.14</v>
       </c>
       <c r="U11" s="36" t="n">
-        <v>48.6</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="12">
@@ -2910,7 +2910,7 @@
         <v>37</v>
       </c>
       <c r="U12" s="36" t="n">
-        <v>45.8</v>
+        <v>46.17</v>
       </c>
     </row>
     <row r="13">
@@ -2979,145 +2979,145 @@
         <v>37.71</v>
       </c>
       <c r="U13" s="36" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>6.67</v>
+        <v>9.43</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>11.29</v>
+        <v>12.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>10.57</v>
+        <v>13.29</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>11.14</v>
+        <v>14.71</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>13.86</v>
+        <v>17</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>18</v>
+        <v>19.71</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>18</v>
+        <v>17.71</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>17.43</v>
+        <v>19.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>15.29</v>
+        <v>24.14</v>
       </c>
       <c r="M14" s="36" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="N14" s="36" t="n">
         <v>24.43</v>
       </c>
-      <c r="N14" s="36" t="n">
-        <v>24.71</v>
-      </c>
       <c r="O14" s="36" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="P14" s="36" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="Q14" s="36" t="n">
         <v>25.57</v>
       </c>
-      <c r="P14" s="36" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="Q14" s="36" t="n">
-        <v>25.43</v>
-      </c>
       <c r="R14" s="36" t="n">
-        <v>22.57</v>
+        <v>29</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>21.29</v>
+        <v>27.71</v>
       </c>
       <c r="T14" s="36" t="n">
-        <v>29.14</v>
+        <v>32.57</v>
       </c>
       <c r="U14" s="36" t="n">
-        <v>33.2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.43</v>
+        <v>6.67</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>12.43</v>
+        <v>11.29</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13.29</v>
+        <v>10.57</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>14.71</v>
+        <v>11.14</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>17</v>
+        <v>13.86</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.71</v>
+        <v>18</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>17.71</v>
+        <v>18</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>19.57</v>
+        <v>17.43</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>24.14</v>
+        <v>15.29</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>27.57</v>
+        <v>24.43</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>24.43</v>
+        <v>24.71</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>27.29</v>
+        <v>25.57</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>26.57</v>
+        <v>19.29</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>25.57</v>
+        <v>25.43</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>29</v>
+        <v>22.57</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>27.71</v>
+        <v>21.29</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>32.57</v>
+        <v>29.14</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>32.4</v>
+        <v>30.83</v>
       </c>
     </row>
     <row r="16">
@@ -3186,7 +3186,7 @@
         <v>25</v>
       </c>
       <c r="U16" s="36" t="n">
-        <v>30</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="17">
@@ -3255,7 +3255,7 @@
         <v>25.29</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>28.4</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="18">
@@ -3324,7 +3324,7 @@
         <v>27.57</v>
       </c>
       <c r="U18" s="36" t="n">
-        <v>27.4</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="19">
@@ -3393,7 +3393,7 @@
         <v>21.29</v>
       </c>
       <c r="U19" s="36" t="n">
-        <v>26.6</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="20">
@@ -3462,7 +3462,7 @@
         <v>25.29</v>
       </c>
       <c r="U20" s="36" t="n">
-        <v>26.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -3531,7 +3531,7 @@
         <v>29.43</v>
       </c>
       <c r="U21" s="36" t="n">
-        <v>19.8</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="22">
@@ -3600,7 +3600,7 @@
         <v>9.289999999999999</v>
       </c>
       <c r="U22" s="36" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="23">
@@ -3669,7 +3669,7 @@
         <v>6.86</v>
       </c>
       <c r="U23" s="36" t="n">
-        <v>10.2</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="24">
@@ -3808,97 +3808,97 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" s="19" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" s="19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" s="19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" s="19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" s="19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -4073,7 +4073,7 @@
         <v>7</v>
       </c>
       <c r="U5" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -4142,7 +4142,7 @@
         <v>86540625</v>
       </c>
       <c r="U6" s="40" t="n">
-        <v>78702548</v>
+        <v>93068237</v>
       </c>
     </row>
     <row r="7">
@@ -4211,7 +4211,7 @@
         <v>89918146</v>
       </c>
       <c r="U7" s="40" t="n">
-        <v>68870796</v>
+        <v>82314782</v>
       </c>
     </row>
     <row r="8">
@@ -4280,7 +4280,7 @@
         <v>80004937</v>
       </c>
       <c r="U8" s="40" t="n">
-        <v>49458011</v>
+        <v>58515439</v>
       </c>
     </row>
     <row r="9">
@@ -4349,7 +4349,7 @@
         <v>59241681</v>
       </c>
       <c r="U9" s="40" t="n">
-        <v>46107234</v>
+        <v>55219336</v>
       </c>
     </row>
     <row r="10">
@@ -4418,7 +4418,7 @@
         <v>72064876</v>
       </c>
       <c r="U10" s="40" t="n">
-        <v>40087644</v>
+        <v>51253164</v>
       </c>
     </row>
     <row r="11">
@@ -4487,7 +4487,7 @@
         <v>50993465</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>49659321</v>
+        <v>54814925</v>
       </c>
     </row>
     <row r="12">
@@ -4556,7 +4556,7 @@
         <v>39637968</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>38621290</v>
+        <v>46715830</v>
       </c>
     </row>
     <row r="13">
@@ -4625,145 +4625,145 @@
         <v>58966944</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>26596750</v>
+        <v>33902796</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>5092853</v>
+        <v>11884771</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>11100161</v>
+        <v>10651216</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>14612055</v>
+        <v>13882033</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>20638987</v>
+        <v>17812948</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>14061352</v>
+        <v>17331854</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>31599148</v>
+        <v>26294756</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>18747614</v>
+        <v>24196222</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>19576415</v>
+        <v>22122847</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>14226838</v>
+        <v>31914115</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>23197145</v>
+        <v>32069521</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>25790711</v>
+        <v>38287475</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>27856115</v>
+        <v>28283704</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>20981901</v>
+        <v>27334091</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>25433123</v>
+        <v>36312415</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>19355230</v>
+        <v>39333565</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>24713836</v>
+        <v>28566119</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>20195634</v>
+        <v>40387845</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>24428723</v>
+        <v>34428781</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>11884771</v>
+        <v>5092853</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>10651216</v>
+        <v>11100161</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>13882033</v>
+        <v>14612055</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>17812948</v>
+        <v>20638987</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>17331854</v>
+        <v>14061352</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>26294756</v>
+        <v>31599148</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>24196222</v>
+        <v>18747614</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>22122847</v>
+        <v>19576415</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>31914115</v>
+        <v>14226838</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>32069521</v>
+        <v>23197145</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>38287475</v>
+        <v>25790711</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>28283704</v>
+        <v>27856115</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>27334091</v>
+        <v>20981901</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>36312415</v>
+        <v>25433123</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>39333565</v>
+        <v>19355230</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>28566119</v>
+        <v>24713836</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>40387845</v>
+        <v>20195634</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>28912581</v>
+        <v>26616042</v>
       </c>
     </row>
     <row r="16">
@@ -4832,7 +4832,7 @@
         <v>34209889</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>25565150</v>
+        <v>31392750</v>
       </c>
     </row>
     <row r="17">
@@ -4901,7 +4901,7 @@
         <v>21412810</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>24123071</v>
+        <v>29845918</v>
       </c>
     </row>
     <row r="18">
@@ -4970,7 +4970,7 @@
         <v>24608772</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>19125590</v>
+        <v>22962973</v>
       </c>
     </row>
     <row r="19">
@@ -5039,7 +5039,7 @@
         <v>25377166</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>20435991</v>
+        <v>22836881</v>
       </c>
     </row>
     <row r="20">
@@ -5108,7 +5108,7 @@
         <v>31150016</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>30786850</v>
+        <v>35208916</v>
       </c>
     </row>
     <row r="21">
@@ -5177,7 +5177,7 @@
         <v>25969876</v>
       </c>
       <c r="U21" s="40" t="n">
-        <v>16068026</v>
+        <v>20237866</v>
       </c>
     </row>
     <row r="22">
@@ -5246,7 +5246,7 @@
         <v>6880660</v>
       </c>
       <c r="U22" s="40" t="n">
-        <v>6507050</v>
+        <v>9242280</v>
       </c>
     </row>
     <row r="23">
@@ -5315,7 +5315,7 @@
         <v>6048269</v>
       </c>
       <c r="U23" s="40" t="n">
-        <v>6510130</v>
+        <v>8424030</v>
       </c>
     </row>
     <row r="24">
@@ -5454,97 +5454,97 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" s="19" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" s="19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" s="19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" s="19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" s="19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -5719,7 +5719,7 @@
         <v>7</v>
       </c>
       <c r="U5" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -5788,7 +5788,7 @@
         <v>7</v>
       </c>
       <c r="U6" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -5857,7 +5857,7 @@
         <v>7</v>
       </c>
       <c r="U7" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -5926,7 +5926,7 @@
         <v>7</v>
       </c>
       <c r="U8" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -5995,7 +5995,7 @@
         <v>7</v>
       </c>
       <c r="U9" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -6064,7 +6064,7 @@
         <v>7</v>
       </c>
       <c r="U10" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -6133,7 +6133,7 @@
         <v>7</v>
       </c>
       <c r="U11" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -6202,7 +6202,7 @@
         <v>7</v>
       </c>
       <c r="U12" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -6271,94 +6271,94 @@
         <v>7</v>
       </c>
       <c r="U13" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" s="42" t="n">
         <v>6</v>
-      </c>
-      <c r="E14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U14" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -6409,7 +6409,7 @@
         <v>7</v>
       </c>
       <c r="U15" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -6478,7 +6478,7 @@
         <v>7</v>
       </c>
       <c r="U16" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -6547,7 +6547,7 @@
         <v>7</v>
       </c>
       <c r="U17" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -6616,7 +6616,7 @@
         <v>7</v>
       </c>
       <c r="U18" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -6685,7 +6685,7 @@
         <v>7</v>
       </c>
       <c r="U19" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -6754,7 +6754,7 @@
         <v>7</v>
       </c>
       <c r="U20" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6823,7 +6823,7 @@
         <v>7</v>
       </c>
       <c r="U21" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -6892,7 +6892,7 @@
         <v>7</v>
       </c>
       <c r="U22" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -6961,7 +6961,7 @@
         <v>7</v>
       </c>
       <c r="U23" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2361,7 +2361,7 @@
       </c>
       <c r="U4" s="31" t="inlineStr">
         <is>
-          <t>31.08–06.09*</t>
+          <t>31.08–06.09</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
         <v>7</v>
       </c>
       <c r="U5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2496,7 +2496,7 @@
         <v>79.70999999999999</v>
       </c>
       <c r="U6" s="36" t="n">
-        <v>106.33</v>
+        <v>105.86</v>
       </c>
     </row>
     <row r="7">
@@ -2565,7 +2565,7 @@
         <v>92.14</v>
       </c>
       <c r="U7" s="36" t="n">
-        <v>91.17</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
@@ -2634,7 +2634,7 @@
         <v>64.43000000000001</v>
       </c>
       <c r="U8" s="36" t="n">
-        <v>68.5</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
@@ -2703,7 +2703,7 @@
         <v>60.71</v>
       </c>
       <c r="U9" s="36" t="n">
-        <v>65</v>
+        <v>66.86</v>
       </c>
     </row>
     <row r="10">
@@ -2772,7 +2772,7 @@
         <v>44.57</v>
       </c>
       <c r="U10" s="36" t="n">
-        <v>54.33</v>
+        <v>55.29</v>
       </c>
     </row>
     <row r="11">
@@ -2841,7 +2841,7 @@
         <v>50.14</v>
       </c>
       <c r="U11" s="36" t="n">
-        <v>47.83</v>
+        <v>48.86</v>
       </c>
     </row>
     <row r="12">
@@ -2910,7 +2910,7 @@
         <v>37</v>
       </c>
       <c r="U12" s="36" t="n">
-        <v>46.17</v>
+        <v>46.29</v>
       </c>
     </row>
     <row r="13">
@@ -2979,7 +2979,7 @@
         <v>37.71</v>
       </c>
       <c r="U13" s="36" t="n">
-        <v>39</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="14">
@@ -3048,7 +3048,7 @@
         <v>32.57</v>
       </c>
       <c r="U14" s="36" t="n">
-        <v>32</v>
+        <v>31.57</v>
       </c>
     </row>
     <row r="15">
@@ -3117,76 +3117,76 @@
         <v>29.14</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>30.83</v>
+        <v>31.43</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>3.25</v>
+        <v>14.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>8</v>
+        <v>11.86</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>9.43</v>
+        <v>18</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>12.71</v>
+        <v>19.14</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>11.57</v>
+        <v>21</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>23.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>11.86</v>
+        <v>20.43</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>24.57</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>19</v>
+        <v>24.14</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>19.57</v>
+        <v>24.43</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>16.86</v>
+        <v>22</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>14.71</v>
+        <v>18.43</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>15.86</v>
+        <v>24.71</v>
       </c>
       <c r="T16" s="36" t="n">
-        <v>25</v>
+        <v>27.57</v>
       </c>
       <c r="U16" s="36" t="n">
-        <v>29.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -3255,214 +3255,214 @@
         <v>25.29</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>29.33</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>0</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>14.43</v>
+        <v>3.25</v>
       </c>
       <c r="G18" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I18" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="J18" s="36" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="K18" s="36" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L18" s="36" t="n">
         <v>11.86</v>
       </c>
-      <c r="H18" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="I18" s="36" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="J18" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="K18" s="36" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="L18" s="36" t="n">
-        <v>20.43</v>
-      </c>
       <c r="M18" s="36" t="n">
-        <v>24.57</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>24.14</v>
+        <v>19</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>24.43</v>
+        <v>19.57</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>22</v>
+        <v>16.86</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>18.43</v>
+        <v>14.71</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>24.71</v>
+        <v>15.86</v>
       </c>
       <c r="T18" s="36" t="n">
-        <v>27.57</v>
+        <v>25</v>
       </c>
       <c r="U18" s="36" t="n">
-        <v>28.5</v>
+        <v>27.29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>0.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>3.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>11.71</v>
+        <v>14</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.57</v>
+        <v>17.14</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>20.43</v>
+        <v>16.14</v>
       </c>
       <c r="K19" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L19" s="36" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="M19" s="36" t="n">
         <v>21.71</v>
       </c>
-      <c r="L19" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="M19" s="36" t="n">
-        <v>22.71</v>
-      </c>
       <c r="N19" s="36" t="n">
-        <v>22.43</v>
+        <v>20.86</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>20.14</v>
+        <v>20.86</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>15.71</v>
+        <v>21.86</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>19.43</v>
+        <v>28.71</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>20.29</v>
+        <v>24.71</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>22.29</v>
+        <v>24.57</v>
       </c>
       <c r="T19" s="36" t="n">
-        <v>21.29</v>
+        <v>25.29</v>
       </c>
       <c r="U19" s="36" t="n">
-        <v>26.83</v>
+        <v>26.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="36" t="n">
         <v>3.33</v>
       </c>
-      <c r="E20" s="36" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F20" s="36" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="G20" s="36" t="n">
-        <v>9.140000000000001</v>
-      </c>
       <c r="H20" s="36" t="n">
-        <v>14</v>
+        <v>11.71</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>17.14</v>
+        <v>17.57</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>16.14</v>
+        <v>20.43</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>18.57</v>
+        <v>21.71</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>16.14</v>
+        <v>15</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>21.71</v>
+        <v>22.71</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>20.86</v>
+        <v>22.43</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>20.86</v>
+        <v>20.14</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>21.86</v>
+        <v>15.71</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>28.71</v>
+        <v>19.43</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>24.71</v>
+        <v>20.29</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>24.57</v>
+        <v>22.29</v>
       </c>
       <c r="T20" s="36" t="n">
-        <v>25.29</v>
+        <v>21.29</v>
       </c>
       <c r="U20" s="36" t="n">
-        <v>25</v>
+        <v>25.14</v>
       </c>
     </row>
     <row r="21">
@@ -3531,7 +3531,7 @@
         <v>29.43</v>
       </c>
       <c r="U21" s="36" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -3600,7 +3600,7 @@
         <v>9.289999999999999</v>
       </c>
       <c r="U22" s="36" t="n">
-        <v>13.5</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="23">
@@ -3669,7 +3669,7 @@
         <v>6.86</v>
       </c>
       <c r="U23" s="36" t="n">
-        <v>10.33</v>
+        <v>12.14</v>
       </c>
     </row>
     <row r="24">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="U4" s="31" t="inlineStr">
         <is>
-          <t>31.08–06.09*</t>
+          <t>31.08–06.09</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>7</v>
       </c>
       <c r="U5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -4142,7 +4142,7 @@
         <v>86540625</v>
       </c>
       <c r="U6" s="40" t="n">
-        <v>93068237</v>
+        <v>123494931</v>
       </c>
     </row>
     <row r="7">
@@ -4211,7 +4211,7 @@
         <v>89918146</v>
       </c>
       <c r="U7" s="40" t="n">
-        <v>82314782</v>
+        <v>94534230</v>
       </c>
     </row>
     <row r="8">
@@ -4280,7 +4280,7 @@
         <v>80004937</v>
       </c>
       <c r="U8" s="40" t="n">
-        <v>58515439</v>
+        <v>67225139</v>
       </c>
     </row>
     <row r="9">
@@ -4349,7 +4349,7 @@
         <v>59241681</v>
       </c>
       <c r="U9" s="40" t="n">
-        <v>55219336</v>
+        <v>65321829</v>
       </c>
     </row>
     <row r="10">
@@ -4418,7 +4418,7 @@
         <v>72064876</v>
       </c>
       <c r="U10" s="40" t="n">
-        <v>51253164</v>
+        <v>59606189</v>
       </c>
     </row>
     <row r="11">
@@ -4487,7 +4487,7 @@
         <v>50993465</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>54814925</v>
+        <v>62193580</v>
       </c>
     </row>
     <row r="12">
@@ -4556,7 +4556,7 @@
         <v>39637968</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>46715830</v>
+        <v>55199920</v>
       </c>
     </row>
     <row r="13">
@@ -4625,7 +4625,7 @@
         <v>58966944</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>33902796</v>
+        <v>43378746</v>
       </c>
     </row>
     <row r="14">
@@ -4694,7 +4694,7 @@
         <v>40387845</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>34428781</v>
+        <v>39744111</v>
       </c>
     </row>
     <row r="15">
@@ -4763,76 +4763,76 @@
         <v>20195634</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>26616042</v>
+        <v>32414171</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>0</v>
+        <v>8544625</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>0</v>
+        <v>8387478</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>1324510</v>
+        <v>10570508</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>10311989</v>
+        <v>11896580</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>19934535</v>
+        <v>19614352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>13536614</v>
+        <v>20966317</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>22187720</v>
+        <v>20073400</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>11732010</v>
+        <v>23801493</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>21143100</v>
+        <v>27940611</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>14330970</v>
+        <v>27893929</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>38267409</v>
+        <v>29635773</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>46351274</v>
+        <v>19554230</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>37105387</v>
+        <v>23848495</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>19868191</v>
+        <v>24194638</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>15153480</v>
+        <v>20330094</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>19277087</v>
+        <v>26044199</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>34209889</v>
+        <v>24608772</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>31392750</v>
+        <v>28079726</v>
       </c>
     </row>
     <row r="17">
@@ -4901,214 +4901,214 @@
         <v>21412810</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>29845918</v>
+        <v>34881782</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>8544625</v>
+        <v>0</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>8387478</v>
+        <v>0</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>10570508</v>
+        <v>1324510</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>11896580</v>
+        <v>10311989</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>19614352</v>
+        <v>19934535</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>20966317</v>
+        <v>13536614</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>20073400</v>
+        <v>22187720</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>23801493</v>
+        <v>11732010</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>27940611</v>
+        <v>21143100</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>27893929</v>
+        <v>14330970</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>29635773</v>
+        <v>38267409</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>19554230</v>
+        <v>46351274</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>23848495</v>
+        <v>37105387</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>24194638</v>
+        <v>19868191</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>20330094</v>
+        <v>15153480</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>26044199</v>
+        <v>19277087</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>24608772</v>
+        <v>34209889</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>22962973</v>
+        <v>33260760</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>3249588</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0</v>
+        <v>7305524</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>363900</v>
+        <v>9575225</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>3736700</v>
+        <v>9264589</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>17796776</v>
+        <v>20692424</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>42724228</v>
+        <v>27565767</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>33036620</v>
+        <v>19138015</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>29649130</v>
+        <v>24912292</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>13949368</v>
+        <v>19068954</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>24539413</v>
+        <v>25387051</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>19087217</v>
+        <v>21008637</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>17139440</v>
+        <v>30862574</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>17746930</v>
+        <v>31820447</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>21437830</v>
+        <v>31875986</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>17616397</v>
+        <v>48358034</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>19360848</v>
+        <v>30000524</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>25377166</v>
+        <v>31150016</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>22836881</v>
+        <v>40688796</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>7305524</v>
+        <v>0</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>9575225</v>
+        <v>363900</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>9264589</v>
+        <v>3736700</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>20692424</v>
+        <v>17796776</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>27565767</v>
+        <v>42724228</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>19138015</v>
+        <v>33036620</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>24912292</v>
+        <v>29649130</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>19068954</v>
+        <v>13949368</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>25387051</v>
+        <v>24539413</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>21008637</v>
+        <v>19087217</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>30862574</v>
+        <v>17139440</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>31820447</v>
+        <v>17746930</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>31875986</v>
+        <v>21437830</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>48358034</v>
+        <v>17616397</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>30000524</v>
+        <v>19360848</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>31150016</v>
+        <v>25377166</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>35208916</v>
+        <v>24702051</v>
       </c>
     </row>
     <row r="21">
@@ -5177,7 +5177,7 @@
         <v>25969876</v>
       </c>
       <c r="U21" s="40" t="n">
-        <v>20237866</v>
+        <v>23835106</v>
       </c>
     </row>
     <row r="22">
@@ -5246,7 +5246,7 @@
         <v>6880660</v>
       </c>
       <c r="U22" s="40" t="n">
-        <v>9242280</v>
+        <v>10209080</v>
       </c>
     </row>
     <row r="23">
@@ -5315,7 +5315,7 @@
         <v>6048269</v>
       </c>
       <c r="U23" s="40" t="n">
-        <v>8424030</v>
+        <v>9823030</v>
       </c>
     </row>
     <row r="24">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="U4" s="31" t="inlineStr">
         <is>
-          <t>31.08–06.09*</t>
+          <t>31.08–06.09</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5719,7 @@
         <v>7</v>
       </c>
       <c r="U5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -5788,7 +5788,7 @@
         <v>7</v>
       </c>
       <c r="U6" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -5857,7 +5857,7 @@
         <v>7</v>
       </c>
       <c r="U7" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -5926,7 +5926,7 @@
         <v>7</v>
       </c>
       <c r="U8" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -5995,7 +5995,7 @@
         <v>7</v>
       </c>
       <c r="U9" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -6064,7 +6064,7 @@
         <v>7</v>
       </c>
       <c r="U10" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -6133,7 +6133,7 @@
         <v>7</v>
       </c>
       <c r="U11" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -6202,7 +6202,7 @@
         <v>7</v>
       </c>
       <c r="U12" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -6271,7 +6271,7 @@
         <v>7</v>
       </c>
       <c r="U13" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -6340,7 +6340,7 @@
         <v>7</v>
       </c>
       <c r="U14" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -6409,31 +6409,31 @@
         <v>7</v>
       </c>
       <c r="U15" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E16" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F16" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G16" s="42" t="n">
         <v>7</v>
@@ -6478,7 +6478,7 @@
         <v>7</v>
       </c>
       <c r="U16" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -6547,31 +6547,31 @@
         <v>7</v>
       </c>
       <c r="U17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G18" s="42" t="n">
         <v>7</v>
@@ -6616,34 +6616,34 @@
         <v>7</v>
       </c>
       <c r="U18" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -6685,34 +6685,34 @@
         <v>7</v>
       </c>
       <c r="U19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20" s="42" t="n">
         <v>7</v>
@@ -6754,7 +6754,7 @@
         <v>7</v>
       </c>
       <c r="U20" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -6823,7 +6823,7 @@
         <v>7</v>
       </c>
       <c r="U21" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -6892,7 +6892,7 @@
         <v>7</v>
       </c>
       <c r="U22" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -6961,7 +6961,7 @@
         <v>7</v>
       </c>
       <c r="U23" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -686,7 +686,7 @@
         <v>6500000</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>9920000</v>
+        <v>7440000</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>320</v>
@@ -735,7 +735,7 @@
         <v>9000000</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>9920000</v>
+        <v>7440000</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>320</v>
@@ -784,7 +784,7 @@
         <v>11909091</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>9920000</v>
+        <v>7440000</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>320</v>
@@ -833,7 +833,7 @@
         <v>3647160</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>9920000</v>
+        <v>7440000</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>320</v>
@@ -882,7 +882,7 @@
         <v>4431000</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>8680000</v>
+        <v>6212400</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>320</v>
@@ -931,7 +931,7 @@
         <v>10420455</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>9920000</v>
+        <v>7440000</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>320</v>
@@ -980,7 +980,7 @@
         <v>7112000</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>9920000</v>
+        <v>7440000</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>320</v>
@@ -1029,7 +1029,7 @@
         <v>5800000</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>9920000</v>
+        <v>7440000</v>
       </c>
       <c r="H12" s="27" t="n">
         <v>320</v>
@@ -1078,7 +1078,7 @@
         <v>5818182</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>8680000</v>
+        <v>6212400</v>
       </c>
       <c r="H13" s="27" t="n">
         <v>320</v>
@@ -1127,7 +1127,7 @@
         <v>2954545</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>7440000</v>
+        <v>6212400</v>
       </c>
       <c r="H14" s="27" t="n">
         <v>320</v>
@@ -1176,7 +1176,7 @@
         <v>7386364</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>9920000</v>
+        <v>7440000</v>
       </c>
       <c r="H15" s="27" t="n">
         <v>320</v>
@@ -1225,7 +1225,7 @@
         <v>2954545</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>7440000</v>
+        <v>6212400</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>320</v>
@@ -1274,7 +1274,7 @@
         <v>7329545</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>8680000</v>
+        <v>6212400</v>
       </c>
       <c r="H17" s="27" t="n">
         <v>320</v>
@@ -1323,7 +1323,7 @@
         <v>3409091</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>8680000</v>
+        <v>6212400</v>
       </c>
       <c r="H18" s="27" t="n">
         <v>320</v>
@@ -1372,7 +1372,7 @@
         <v>4435000</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>7440000</v>
+        <v>6212400</v>
       </c>
       <c r="H19" s="27" t="n">
         <v>320</v>
@@ -1421,7 +1421,7 @@
         <v>7216000</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>9920000</v>
+        <v>7440000</v>
       </c>
       <c r="H20" s="27" t="n">
         <v>320</v>
@@ -1470,7 +1470,7 @@
         <v>2912000</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>8680000</v>
+        <v>6212400</v>
       </c>
       <c r="H21" s="27" t="n">
         <v>320</v>
@@ -1519,7 +1519,7 @@
         <v>5864000</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>8680000</v>
+        <v>6212400</v>
       </c>
       <c r="H22" s="27" t="n">
         <v>320</v>
@@ -2162,97 +2162,97 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="19" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="19" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="19" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="19" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="19" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="19" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="19" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -3808,97 +3808,97 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="19" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="19" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="19" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="19" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="19" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="19" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="19" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
@@ -5454,97 +5454,97 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="19" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="19" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="19" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="19" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="19" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="19" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="19" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2121,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2145,6 +2145,7 @@
     <col width="13" customWidth="1" style="20" min="19" max="19"/>
     <col width="13" customWidth="1" style="20" min="20" max="20"/>
     <col width="13" customWidth="1" style="20" min="21" max="21"/>
+    <col width="13" customWidth="1" style="20" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2162,99 +2163,104 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" s="19" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" s="19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" s="19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" s="19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" s="19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -2362,6 +2368,11 @@
       <c r="U4" s="31" t="inlineStr">
         <is>
           <t>31.08–06.09</t>
+        </is>
+      </c>
+      <c r="V4" s="31" t="inlineStr">
+        <is>
+          <t>07.09–13.09*</t>
         </is>
       </c>
     </row>
@@ -2429,6 +2440,9 @@
       <c r="U5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="V5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -2498,74 +2512,80 @@
       <c r="U6" s="36" t="n">
         <v>105.86</v>
       </c>
+      <c r="V6" s="36" t="n">
+        <v>116</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>11</v>
+        <v>14.29</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>29.43</v>
+        <v>19.14</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>38</v>
+        <v>26.71</v>
       </c>
       <c r="G7" s="36" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="H7" s="36" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="I7" s="36" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="J7" s="36" t="n">
+        <v>33</v>
+      </c>
+      <c r="K7" s="36" t="n">
+        <v>34.86</v>
+      </c>
+      <c r="L7" s="36" t="n">
         <v>41.29</v>
       </c>
-      <c r="H7" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I7" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J7" s="36" t="n">
-        <v>63</v>
-      </c>
-      <c r="K7" s="36" t="n">
-        <v>55.43</v>
-      </c>
-      <c r="L7" s="36" t="n">
-        <v>69.56999999999999</v>
-      </c>
       <c r="M7" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>41.43</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>76.86</v>
+        <v>46.14</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>41.57</v>
       </c>
       <c r="P7" s="36" t="n">
-        <v>71.43000000000001</v>
+        <v>51.86</v>
       </c>
       <c r="Q7" s="36" t="n">
-        <v>78.86</v>
+        <v>48.71</v>
       </c>
       <c r="R7" s="36" t="n">
-        <v>78.43000000000001</v>
+        <v>45.14</v>
       </c>
       <c r="S7" s="36" t="n">
-        <v>72.43000000000001</v>
+        <v>50.71</v>
       </c>
       <c r="T7" s="36" t="n">
-        <v>92.14</v>
+        <v>60.71</v>
       </c>
       <c r="U7" s="36" t="n">
-        <v>91</v>
+        <v>66.86</v>
+      </c>
+      <c r="V7" s="36" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="8">
@@ -2636,143 +2656,152 @@
       <c r="U8" s="36" t="n">
         <v>68</v>
       </c>
+      <c r="V8" s="36" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>14.29</v>
+        <v>11</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>19.14</v>
+        <v>29.43</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>26.71</v>
+        <v>38</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>28.14</v>
+        <v>41.29</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>28.57</v>
+        <v>51.43</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>31.57</v>
+        <v>58.29</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>34.86</v>
+        <v>55.43</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>41.29</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>41.43</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>46.14</v>
+        <v>76.86</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>41.57</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>51.86</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="Q9" s="36" t="n">
-        <v>48.71</v>
+        <v>78.86</v>
       </c>
       <c r="R9" s="36" t="n">
-        <v>45.14</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="S9" s="36" t="n">
-        <v>50.71</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="T9" s="36" t="n">
-        <v>60.71</v>
+        <v>92.14</v>
       </c>
       <c r="U9" s="36" t="n">
-        <v>66.86</v>
+        <v>91</v>
+      </c>
+      <c r="V9" s="36" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>8</v>
+        <v>12.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>13.14</v>
+        <v>16.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>19.43</v>
+        <v>21</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>26.43</v>
+        <v>20.29</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>32.29</v>
+        <v>28.57</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>31.29</v>
+        <v>24.14</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>33.57</v>
+        <v>27.57</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>40</v>
+        <v>28.14</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>42.43</v>
+        <v>28.86</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>38.57</v>
+        <v>33.14</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>34.29</v>
+        <v>30.71</v>
       </c>
       <c r="P10" s="36" t="n">
-        <v>37.86</v>
+        <v>31.14</v>
       </c>
       <c r="Q10" s="36" t="n">
-        <v>42.86</v>
+        <v>40.29</v>
       </c>
       <c r="R10" s="36" t="n">
-        <v>40.71</v>
+        <v>38.71</v>
       </c>
       <c r="S10" s="36" t="n">
-        <v>45.43</v>
+        <v>43.14</v>
       </c>
       <c r="T10" s="36" t="n">
-        <v>44.57</v>
+        <v>37</v>
       </c>
       <c r="U10" s="36" t="n">
-        <v>55.29</v>
+        <v>46.29</v>
+      </c>
+      <c r="V10" s="36" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -2843,833 +2872,872 @@
       <c r="U11" s="36" t="n">
         <v>48.86</v>
       </c>
+      <c r="V11" s="36" t="n">
+        <v>52</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>33.14</v>
+        <v>38.57</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>30.71</v>
+        <v>34.29</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>31.14</v>
+        <v>37.86</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>40.29</v>
+        <v>42.86</v>
       </c>
       <c r="R12" s="36" t="n">
-        <v>38.71</v>
+        <v>40.71</v>
       </c>
       <c r="S12" s="36" t="n">
-        <v>43.14</v>
+        <v>45.43</v>
       </c>
       <c r="T12" s="36" t="n">
-        <v>37</v>
+        <v>44.57</v>
       </c>
       <c r="U12" s="36" t="n">
-        <v>46.29</v>
+        <v>55.29</v>
+      </c>
+      <c r="V12" s="36" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>8.43</v>
+        <v>0</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>13.43</v>
+        <v>0</v>
       </c>
       <c r="F13" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G13" s="36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H13" s="36" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="I13" s="36" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="J13" s="36" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="K13" s="36" t="n">
         <v>21.71</v>
       </c>
-      <c r="G13" s="36" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="H13" s="36" t="n">
+      <c r="L13" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="M13" s="36" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="N13" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="O13" s="36" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="P13" s="36" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="Q13" s="36" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="R13" s="36" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="S13" s="36" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="T13" s="36" t="n">
         <v>21.29</v>
       </c>
-      <c r="I13" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="J13" s="36" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="K13" s="36" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="L13" s="36" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="M13" s="36" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="N13" s="36" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="O13" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="P13" s="36" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="Q13" s="36" t="n">
-        <v>31.29</v>
-      </c>
-      <c r="R13" s="36" t="n">
-        <v>36.14</v>
-      </c>
-      <c r="S13" s="36" t="n">
-        <v>31</v>
-      </c>
-      <c r="T13" s="36" t="n">
-        <v>37.71</v>
-      </c>
       <c r="U13" s="36" t="n">
-        <v>39.29</v>
+        <v>25.14</v>
+      </c>
+      <c r="V13" s="36" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>9.43</v>
+        <v>8.43</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.43</v>
+        <v>13.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>13.29</v>
+        <v>21.71</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>14.71</v>
+        <v>16.57</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>17</v>
+        <v>21.29</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>19.71</v>
+        <v>21.14</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>17.71</v>
+        <v>23.29</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>19.57</v>
+        <v>22.43</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>24.14</v>
+        <v>22.43</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>27.57</v>
+        <v>28.14</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>24.43</v>
+        <v>31.14</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>27.29</v>
+        <v>30</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>26.57</v>
+        <v>30.43</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>25.57</v>
+        <v>31.29</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>29</v>
+        <v>36.14</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>27.71</v>
+        <v>31</v>
       </c>
       <c r="T14" s="36" t="n">
-        <v>32.57</v>
+        <v>37.71</v>
       </c>
       <c r="U14" s="36" t="n">
-        <v>31.57</v>
+        <v>39.29</v>
+      </c>
+      <c r="V14" s="36" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>6.67</v>
+        <v>3.33</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>11.29</v>
+        <v>6.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>10.57</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>11.14</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>18</v>
+        <v>17.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>18</v>
+        <v>16.14</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>17.43</v>
+        <v>18.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>15.29</v>
+        <v>16.14</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>24.43</v>
+        <v>21.71</v>
       </c>
       <c r="N15" s="36" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="O15" s="36" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="P15" s="36" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="Q15" s="36" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="R15" s="36" t="n">
         <v>24.71</v>
       </c>
-      <c r="O15" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="P15" s="36" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="Q15" s="36" t="n">
-        <v>25.43</v>
-      </c>
-      <c r="R15" s="36" t="n">
-        <v>22.57</v>
-      </c>
       <c r="S15" s="36" t="n">
-        <v>21.29</v>
+        <v>24.57</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>29.14</v>
+        <v>25.29</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>31.43</v>
+        <v>26.71</v>
+      </c>
+      <c r="V15" s="36" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11</v>
+        <v>12.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>14.43</v>
+        <v>13.29</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>11.86</v>
+        <v>14.71</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>19.14</v>
+        <v>19.71</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>21</v>
+        <v>17.71</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>23.43</v>
+        <v>19.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>20.43</v>
+        <v>24.14</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>24.57</v>
+        <v>27.57</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>24.14</v>
+        <v>24.43</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>24.43</v>
+        <v>27.29</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>22</v>
+        <v>26.57</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>23</v>
+        <v>25.57</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>18.43</v>
+        <v>29</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>24.71</v>
+        <v>27.71</v>
       </c>
       <c r="T16" s="36" t="n">
-        <v>27.57</v>
+        <v>32.57</v>
       </c>
       <c r="U16" s="36" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="V16" s="36" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3</v>
+        <v>6.67</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>7.14</v>
+        <v>11.29</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.43</v>
+        <v>10.57</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>12.71</v>
+        <v>11.14</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.43</v>
+        <v>13.86</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21.14</v>
+        <v>18</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>18.57</v>
+        <v>17.43</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.57</v>
+        <v>15.29</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>14.71</v>
+        <v>24.43</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>19.14</v>
+        <v>24.71</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>18</v>
+        <v>25.57</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>15.29</v>
+        <v>19.29</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>15.29</v>
+        <v>25.43</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>18.71</v>
+        <v>22.57</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>18</v>
+        <v>21.29</v>
       </c>
       <c r="T17" s="36" t="n">
-        <v>25.29</v>
+        <v>29.14</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>28.86</v>
+        <v>31.43</v>
+      </c>
+      <c r="V17" s="36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>3.25</v>
+        <v>19.43</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>8</v>
+        <v>15.86</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>9.43</v>
+        <v>14.86</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>12.71</v>
+        <v>16.71</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>11.57</v>
+        <v>19.71</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>16.86</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>11.86</v>
+        <v>24.86</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>23.43</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>19</v>
+        <v>19.43</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>19.57</v>
+        <v>25.57</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>16.86</v>
+        <v>27.43</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>15</v>
+        <v>29.14</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>14.71</v>
+        <v>25</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>15.86</v>
+        <v>29.57</v>
       </c>
       <c r="T18" s="36" t="n">
-        <v>25</v>
+        <v>29.43</v>
       </c>
       <c r="U18" s="36" t="n">
-        <v>27.29</v>
+        <v>21</v>
+      </c>
+      <c r="V18" s="36" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>6.43</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>14</v>
+        <v>9.43</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.14</v>
+        <v>12.71</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>16.14</v>
+        <v>11.57</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>18.57</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>16.14</v>
+        <v>11.86</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>21.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>20.86</v>
+        <v>19</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>20.86</v>
+        <v>19.57</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>21.86</v>
+        <v>16.86</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>28.71</v>
+        <v>15</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>24.71</v>
+        <v>14.71</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>24.57</v>
+        <v>15.86</v>
       </c>
       <c r="T19" s="36" t="n">
-        <v>25.29</v>
+        <v>25</v>
       </c>
       <c r="U19" s="36" t="n">
-        <v>26.71</v>
+        <v>27.29</v>
+      </c>
+      <c r="V19" s="36" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>0.5</v>
+        <v>14.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>3.33</v>
+        <v>11.86</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>11.71</v>
+        <v>18</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>17.57</v>
+        <v>19.14</v>
       </c>
       <c r="J20" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="K20" s="36" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="L20" s="36" t="n">
         <v>20.43</v>
       </c>
-      <c r="K20" s="36" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="L20" s="36" t="n">
-        <v>15</v>
-      </c>
       <c r="M20" s="36" t="n">
-        <v>22.71</v>
+        <v>24.57</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>22.43</v>
+        <v>24.14</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>20.14</v>
+        <v>24.43</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>15.71</v>
+        <v>22</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>19.43</v>
+        <v>23</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>20.29</v>
+        <v>18.43</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>22.29</v>
+        <v>24.71</v>
       </c>
       <c r="T20" s="36" t="n">
-        <v>21.29</v>
+        <v>27.57</v>
       </c>
       <c r="U20" s="36" t="n">
-        <v>25.14</v>
+        <v>30</v>
+      </c>
+      <c r="V20" s="36" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E21" s="36" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="F21" s="36" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="G21" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="H21" s="36" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="I21" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="J21" s="36" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K21" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L21" s="36" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="M21" s="36" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="N21" s="36" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="O21" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="P21" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="Q21" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="R21" s="36" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="S21" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="T21" s="36" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="U21" s="36" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="V21" s="36" t="n">
         <v>16</v>
-      </c>
-      <c r="F21" s="36" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="G21" s="36" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="H21" s="36" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="I21" s="36" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="J21" s="36" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="K21" s="36" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="L21" s="36" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="M21" s="36" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="N21" s="36" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="O21" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="P21" s="36" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="Q21" s="36" t="n">
-        <v>29.14</v>
-      </c>
-      <c r="R21" s="36" t="n">
-        <v>25</v>
-      </c>
-      <c r="S21" s="36" t="n">
-        <v>29.57</v>
-      </c>
-      <c r="T21" s="36" t="n">
-        <v>29.43</v>
-      </c>
-      <c r="U21" s="36" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>2.8</v>
+        <v>5.14</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>4</v>
+        <v>5.29</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>6</v>
+        <v>7.86</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>4.43</v>
+        <v>7.14</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>3.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>5.86</v>
+        <v>7.14</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>5.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>7.43</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O22" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P22" s="36" t="n">
-        <v>7.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q22" s="36" t="n">
-        <v>10.29</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="R22" s="36" t="n">
-        <v>7</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S22" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="T22" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>6.86</v>
       </c>
       <c r="U22" s="36" t="n">
-        <v>12.71</v>
+        <v>12.14</v>
+      </c>
+      <c r="V22" s="36" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G23" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="36" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G23" s="36" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H23" s="36" t="n">
-        <v>7.86</v>
+        <v>6</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>7.14</v>
+        <v>4.43</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>7.14</v>
+        <v>5.86</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>6</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>8.710000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="O23" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="Q23" s="36" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="R23" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="R23" s="36" t="n">
+      <c r="T23" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="S23" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="T23" s="36" t="n">
-        <v>6.86</v>
-      </c>
       <c r="U23" s="36" t="n">
-        <v>12.14</v>
+        <v>12.71</v>
+      </c>
+      <c r="V23" s="36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -3753,6 +3821,10 @@
       </c>
       <c r="U24" s="39">
         <f>AVERAGE(U6:U23)</f>
+        <v/>
+      </c>
+      <c r="V24" s="39">
+        <f>AVERAGE(V6:V23)</f>
         <v/>
       </c>
     </row>
@@ -3767,7 +3839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3791,6 +3863,7 @@
     <col width="13" customWidth="1" style="20" min="19" max="19"/>
     <col width="13" customWidth="1" style="20" min="20" max="20"/>
     <col width="13" customWidth="1" style="20" min="21" max="21"/>
+    <col width="13" customWidth="1" style="20" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3808,99 +3881,104 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" s="19" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" s="19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" s="19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" s="19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" s="19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -4008,6 +4086,11 @@
       <c r="U4" s="31" t="inlineStr">
         <is>
           <t>31.08–06.09</t>
+        </is>
+      </c>
+      <c r="V4" s="31" t="inlineStr">
+        <is>
+          <t>07.09–13.09*</t>
         </is>
       </c>
     </row>
@@ -4075,6 +4158,9 @@
       <c r="U5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="V5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -4144,74 +4230,80 @@
       <c r="U6" s="40" t="n">
         <v>123494931</v>
       </c>
+      <c r="V6" s="40" t="n">
+        <v>13397457</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>6122227</v>
+        <v>15808893</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>31792625</v>
+        <v>14209578</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>49374899</v>
+        <v>30449860</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>38585414</v>
+        <v>32603120</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>51458725</v>
+        <v>35552907</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>61835892</v>
+        <v>31069118</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>80551167</v>
+        <v>40525338</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>61490143</v>
+        <v>42402722</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>68619843</v>
+        <v>42012092</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>81742671</v>
+        <v>58722069</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>69757179</v>
+        <v>48135084</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>68198708</v>
+        <v>44293878</v>
       </c>
       <c r="P7" s="40" t="n">
-        <v>67906121</v>
+        <v>41613311</v>
       </c>
       <c r="Q7" s="40" t="n">
-        <v>84229530</v>
+        <v>43739350</v>
       </c>
       <c r="R7" s="40" t="n">
-        <v>92096471</v>
+        <v>78234960</v>
       </c>
       <c r="S7" s="40" t="n">
-        <v>78023476</v>
+        <v>47535640</v>
       </c>
       <c r="T7" s="40" t="n">
-        <v>89918146</v>
+        <v>59241681</v>
       </c>
       <c r="U7" s="40" t="n">
-        <v>94534230</v>
+        <v>65321829</v>
+      </c>
+      <c r="V7" s="40" t="n">
+        <v>8061073</v>
       </c>
     </row>
     <row r="8">
@@ -4282,143 +4374,152 @@
       <c r="U8" s="40" t="n">
         <v>67225139</v>
       </c>
+      <c r="V8" s="40" t="n">
+        <v>9493950</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>15808893</v>
+        <v>6122227</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>14209578</v>
+        <v>31792625</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>30449860</v>
+        <v>49374899</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>32603120</v>
+        <v>38585414</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>35552907</v>
+        <v>51458725</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>31069118</v>
+        <v>61835892</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>40525338</v>
+        <v>80551167</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>42402722</v>
+        <v>61490143</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>42012092</v>
+        <v>68619843</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>58722069</v>
+        <v>81742671</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>48135084</v>
+        <v>69757179</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>44293878</v>
+        <v>68198708</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>41613311</v>
+        <v>67906121</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>43739350</v>
+        <v>84229530</v>
       </c>
       <c r="R9" s="40" t="n">
-        <v>78234960</v>
+        <v>92096471</v>
       </c>
       <c r="S9" s="40" t="n">
-        <v>47535640</v>
+        <v>78023476</v>
       </c>
       <c r="T9" s="40" t="n">
-        <v>59241681</v>
+        <v>89918146</v>
       </c>
       <c r="U9" s="40" t="n">
-        <v>65321829</v>
+        <v>94534230</v>
+      </c>
+      <c r="V9" s="40" t="n">
+        <v>8159022</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>0</v>
+        <v>536260</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>8972650</v>
+        <v>14403556</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>18100396</v>
+        <v>16216832</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>23988817</v>
+        <v>32622053</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>22409732</v>
+        <v>23929705</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>37715520</v>
+        <v>37214538</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>35926824</v>
+        <v>25375430</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>39462393</v>
+        <v>31500087</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>51983942</v>
+        <v>28078687</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>58935844</v>
+        <v>34472458</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>38454971</v>
+        <v>35343350</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>42939312</v>
+        <v>51225290</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>43650420</v>
+        <v>36142612</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>53954095</v>
+        <v>47488940</v>
       </c>
       <c r="R10" s="40" t="n">
-        <v>48898463</v>
+        <v>44805002</v>
       </c>
       <c r="S10" s="40" t="n">
-        <v>48011655</v>
+        <v>43327432</v>
       </c>
       <c r="T10" s="40" t="n">
-        <v>72064876</v>
+        <v>39637968</v>
       </c>
       <c r="U10" s="40" t="n">
-        <v>59606189</v>
+        <v>55199920</v>
+      </c>
+      <c r="V10" s="40" t="n">
+        <v>9084932</v>
       </c>
     </row>
     <row r="11">
@@ -4489,833 +4590,872 @@
       <c r="U11" s="40" t="n">
         <v>62193580</v>
       </c>
+      <c r="V11" s="40" t="n">
+        <v>6258124</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>35343350</v>
+        <v>38454971</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>51225290</v>
+        <v>42939312</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>36142612</v>
+        <v>43650420</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>47488940</v>
+        <v>53954095</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>44805002</v>
+        <v>48898463</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>43327432</v>
+        <v>48011655</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>39637968</v>
+        <v>72064876</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>55199920</v>
+        <v>59606189</v>
+      </c>
+      <c r="V12" s="40" t="n">
+        <v>6499760</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>10351067</v>
+        <v>0</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>21091580</v>
+        <v>0</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>24243567</v>
+        <v>363900</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>16381412</v>
+        <v>3736700</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>21591272</v>
+        <v>17796776</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>21904190</v>
+        <v>42724228</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25438080</v>
+        <v>33036620</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>24614280</v>
+        <v>29649130</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28889771</v>
+        <v>13949368</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>44250621</v>
+        <v>24539413</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>29608597</v>
+        <v>19087217</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>25219748</v>
+        <v>17139440</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>28515437</v>
+        <v>17746930</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>35235670</v>
+        <v>21437830</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>38511490</v>
+        <v>17616397</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>40935998</v>
+        <v>19360848</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>58966944</v>
+        <v>25377166</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>43378746</v>
+        <v>24702051</v>
+      </c>
+      <c r="V13" s="40" t="n">
+        <v>7538980</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>475871</v>
+        <v>251520</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>11884771</v>
+        <v>10351067</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>10651216</v>
+        <v>21091580</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>13882033</v>
+        <v>24243567</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>17812948</v>
+        <v>16381412</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>17331854</v>
+        <v>21591272</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>26294756</v>
+        <v>21904190</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>24196222</v>
+        <v>25438080</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>22122847</v>
+        <v>24614280</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>31914115</v>
+        <v>28889771</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>32069521</v>
+        <v>44250621</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>38287475</v>
+        <v>29608597</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>28283704</v>
+        <v>25219748</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>27334091</v>
+        <v>28515437</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>36312415</v>
+        <v>35235670</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>39333565</v>
+        <v>38511490</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>28566119</v>
+        <v>40935998</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>40387845</v>
+        <v>58966944</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>39744111</v>
+        <v>43378746</v>
+      </c>
+      <c r="V14" s="40" t="n">
+        <v>12960399</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>5092853</v>
+        <v>3249588</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>11100161</v>
+        <v>7305524</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>14612055</v>
+        <v>9575225</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>20638987</v>
+        <v>9264589</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>14061352</v>
+        <v>20692424</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>31599148</v>
+        <v>27565767</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>18747614</v>
+        <v>19138015</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>19576415</v>
+        <v>24912292</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>14226838</v>
+        <v>19068954</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>23197145</v>
+        <v>25387051</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>25790711</v>
+        <v>21008637</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>27856115</v>
+        <v>30862574</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>20981901</v>
+        <v>31820447</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>25433123</v>
+        <v>31875986</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>19355230</v>
+        <v>48358034</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>24713836</v>
+        <v>30000524</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>20195634</v>
+        <v>31150016</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>32414171</v>
+        <v>40688796</v>
+      </c>
+      <c r="V15" s="40" t="n">
+        <v>5649727</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>530238</v>
+        <v>475871</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>8544625</v>
+        <v>11884771</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>8387478</v>
+        <v>10651216</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>10570508</v>
+        <v>13882033</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>11896580</v>
+        <v>17812948</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>19614352</v>
+        <v>17331854</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>20966317</v>
+        <v>26294756</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>20073400</v>
+        <v>24196222</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>23801493</v>
+        <v>22122847</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>27940611</v>
+        <v>31914115</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>27893929</v>
+        <v>32069521</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>29635773</v>
+        <v>38287475</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>19554230</v>
+        <v>28283704</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>23848495</v>
+        <v>27334091</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>24194638</v>
+        <v>36312415</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>20330094</v>
+        <v>39333565</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>26044199</v>
+        <v>28566119</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>24608772</v>
+        <v>40387845</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>28079726</v>
+        <v>39744111</v>
+      </c>
+      <c r="V16" s="40" t="n">
+        <v>3756818</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3337146</v>
+        <v>5092853</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10420206</v>
+        <v>11100161</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>21387685</v>
+        <v>14612055</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>16050448</v>
+        <v>20638987</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>21568794</v>
+        <v>14061352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>30845816</v>
+        <v>31599148</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>45285935</v>
+        <v>18747614</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>28941455</v>
+        <v>19576415</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>21801828</v>
+        <v>14226838</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>19628570</v>
+        <v>23197145</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>23276090</v>
+        <v>25790711</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>27906254</v>
+        <v>27856115</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>20822247</v>
+        <v>20981901</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>20014322</v>
+        <v>25433123</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>19159625</v>
+        <v>19355230</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>22535696</v>
+        <v>24713836</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>21412810</v>
+        <v>20195634</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>34881782</v>
+        <v>32414171</v>
+      </c>
+      <c r="V17" s="40" t="n">
+        <v>6485364</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>0</v>
+        <v>6239584</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>0</v>
+        <v>13803407</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>1324510</v>
+        <v>28572076</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>10311989</v>
+        <v>15282581</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>19934535</v>
+        <v>16594572</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>13536614</v>
+        <v>15223898</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>22187720</v>
+        <v>27696695</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>11732010</v>
+        <v>17717888</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>21143100</v>
+        <v>24163432</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>14330970</v>
+        <v>23623477</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>38267409</v>
+        <v>19145601</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>46351274</v>
+        <v>30157601</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>37105387</v>
+        <v>41172333</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>19868191</v>
+        <v>34303423</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>15153480</v>
+        <v>35044850</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>19277087</v>
+        <v>33519824</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>34209889</v>
+        <v>25969876</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>33260760</v>
+        <v>23835106</v>
+      </c>
+      <c r="V18" s="40" t="n">
+        <v>4841761</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>7305524</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>9575225</v>
+        <v>1324510</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>9264589</v>
+        <v>10311989</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>20692424</v>
+        <v>19934535</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>27565767</v>
+        <v>13536614</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>19138015</v>
+        <v>22187720</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>24912292</v>
+        <v>11732010</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>19068954</v>
+        <v>21143100</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>25387051</v>
+        <v>14330970</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>21008637</v>
+        <v>38267409</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>30862574</v>
+        <v>46351274</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>31820447</v>
+        <v>37105387</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>31875986</v>
+        <v>19868191</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>48358034</v>
+        <v>15153480</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>30000524</v>
+        <v>19277087</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>31150016</v>
+        <v>34209889</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>40688796</v>
+        <v>33260760</v>
+      </c>
+      <c r="V19" s="40" t="n">
+        <v>10036079</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>0</v>
+        <v>8544625</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>0</v>
+        <v>8387478</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>363900</v>
+        <v>10570508</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>3736700</v>
+        <v>11896580</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>17796776</v>
+        <v>19614352</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>42724228</v>
+        <v>20966317</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>33036620</v>
+        <v>20073400</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>29649130</v>
+        <v>23801493</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>13949368</v>
+        <v>27940611</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>24539413</v>
+        <v>27893929</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>19087217</v>
+        <v>29635773</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>17139440</v>
+        <v>19554230</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>17746930</v>
+        <v>23848495</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>21437830</v>
+        <v>24194638</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>17616397</v>
+        <v>20330094</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>19360848</v>
+        <v>26044199</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>25377166</v>
+        <v>24608772</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>24702051</v>
+        <v>28079726</v>
+      </c>
+      <c r="V20" s="40" t="n">
+        <v>2703785</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>6239584</v>
+        <v>3337146</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>13803407</v>
+        <v>10420206</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>28572076</v>
+        <v>21387685</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>15282581</v>
+        <v>16050448</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>16594572</v>
+        <v>21568794</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>15223898</v>
+        <v>30845816</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>27696695</v>
+        <v>45285935</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>17717888</v>
+        <v>28941455</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>24163432</v>
+        <v>21801828</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>23623477</v>
+        <v>19628570</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>19145601</v>
+        <v>23276090</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>30157601</v>
+        <v>27906254</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>41172333</v>
+        <v>20822247</v>
       </c>
       <c r="Q21" s="40" t="n">
-        <v>34303423</v>
+        <v>20014322</v>
       </c>
       <c r="R21" s="40" t="n">
-        <v>35044850</v>
+        <v>19159625</v>
       </c>
       <c r="S21" s="40" t="n">
-        <v>33519824</v>
+        <v>22535696</v>
       </c>
       <c r="T21" s="40" t="n">
-        <v>25969876</v>
+        <v>21412810</v>
       </c>
       <c r="U21" s="40" t="n">
-        <v>23835106</v>
+        <v>34881782</v>
+      </c>
+      <c r="V21" s="40" t="n">
+        <v>2138453</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>0</v>
+        <v>2474409</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>0</v>
+        <v>4696696</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>1339100</v>
+        <v>6991878</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>5579340</v>
+        <v>4060163</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>9518200</v>
+        <v>7685466</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>11747640</v>
+        <v>10141286</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>3885270</v>
+        <v>6393871</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>8765870</v>
+        <v>4534503</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>4571680</v>
+        <v>7579040</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>3911995</v>
+        <v>9679437</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>9234090</v>
+        <v>6102368</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>5390260</v>
+        <v>4294070</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>4645370</v>
+        <v>5589419</v>
       </c>
       <c r="Q22" s="40" t="n">
-        <v>10400980</v>
+        <v>10264941</v>
       </c>
       <c r="R22" s="40" t="n">
-        <v>6123322</v>
+        <v>6114083</v>
       </c>
       <c r="S22" s="40" t="n">
-        <v>5648770</v>
+        <v>10758755</v>
       </c>
       <c r="T22" s="40" t="n">
-        <v>6880660</v>
+        <v>6048269</v>
       </c>
       <c r="U22" s="40" t="n">
-        <v>10209080</v>
+        <v>9823030</v>
+      </c>
+      <c r="V22" s="40" t="n">
+        <v>547770</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>2474409</v>
+        <v>0</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>4696696</v>
+        <v>0</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>6991878</v>
+        <v>1339100</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>4060163</v>
+        <v>5579340</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>7685466</v>
+        <v>9518200</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>10141286</v>
+        <v>11747640</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>6393871</v>
+        <v>3885270</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>4534503</v>
+        <v>8765870</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>7579040</v>
+        <v>4571680</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>9679437</v>
+        <v>3911995</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>6102368</v>
+        <v>9234090</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>4294070</v>
+        <v>5390260</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>5589419</v>
+        <v>4645370</v>
       </c>
       <c r="Q23" s="40" t="n">
-        <v>10264941</v>
+        <v>10400980</v>
       </c>
       <c r="R23" s="40" t="n">
-        <v>6114083</v>
+        <v>6123322</v>
       </c>
       <c r="S23" s="40" t="n">
-        <v>10758755</v>
+        <v>5648770</v>
       </c>
       <c r="T23" s="40" t="n">
-        <v>6048269</v>
+        <v>6880660</v>
       </c>
       <c r="U23" s="40" t="n">
-        <v>9823030</v>
+        <v>10209080</v>
+      </c>
+      <c r="V23" s="40" t="n">
+        <v>547780</v>
       </c>
     </row>
     <row r="24">
@@ -5399,6 +5539,10 @@
       </c>
       <c r="U24" s="41">
         <f>AVERAGE(U6:U23)</f>
+        <v/>
+      </c>
+      <c r="V24" s="41">
+        <f>AVERAGE(V6:V23)</f>
         <v/>
       </c>
     </row>
@@ -5413,7 +5557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -5437,6 +5581,7 @@
     <col width="13" customWidth="1" style="20" min="19" max="19"/>
     <col width="13" customWidth="1" style="20" min="20" max="20"/>
     <col width="13" customWidth="1" style="20" min="21" max="21"/>
+    <col width="13" customWidth="1" style="20" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5454,99 +5599,104 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" s="19" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" s="19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" s="19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" s="19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" s="19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -5654,6 +5804,11 @@
       <c r="U4" s="31" t="inlineStr">
         <is>
           <t>31.08–06.09</t>
+        </is>
+      </c>
+      <c r="V4" s="31" t="inlineStr">
+        <is>
+          <t>07.09–13.09*</t>
         </is>
       </c>
     </row>
@@ -5721,6 +5876,9 @@
       <c r="U5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="V5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -5790,23 +5948,26 @@
       <c r="U6" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="V6" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" s="42" t="n">
         <v>7</v>
@@ -5858,6 +6019,9 @@
       </c>
       <c r="U7" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V7" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -5928,23 +6092,26 @@
       <c r="U8" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="V8" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
@@ -5996,27 +6163,30 @@
       </c>
       <c r="U9" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V9" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" s="42" t="n">
         <v>7</v>
@@ -6065,6 +6235,9 @@
       </c>
       <c r="U10" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V10" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -6135,26 +6308,29 @@
       <c r="U11" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="V11" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>7</v>
@@ -6203,90 +6379,96 @@
       </c>
       <c r="U12" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V12" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" s="42" t="n">
         <v>1</v>
-      </c>
-      <c r="D13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="42" t="n">
         <v>7</v>
@@ -6341,24 +6523,27 @@
       </c>
       <c r="U14" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V14" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -6410,17 +6595,20 @@
       </c>
       <c r="U15" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V15" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -6480,23 +6668,26 @@
       <c r="U16" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="V16" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -6548,30 +6739,33 @@
       </c>
       <c r="U17" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V17" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G18" s="42" t="n">
         <v>7</v>
@@ -6617,30 +6811,33 @@
       </c>
       <c r="U18" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V18" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G19" s="42" t="n">
         <v>7</v>
@@ -6686,33 +6883,36 @@
       </c>
       <c r="U19" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V19" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="42" t="n">
         <v>7</v>
@@ -6755,24 +6955,27 @@
       </c>
       <c r="U20" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V20" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E21" s="42" t="n">
         <v>7</v>
@@ -6824,30 +7027,33 @@
       </c>
       <c r="U21" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V21" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F22" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G22" s="42" t="n">
         <v>7</v>
@@ -6868,7 +7074,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N22" s="42" t="n">
         <v>7</v>
@@ -6893,30 +7099,33 @@
       </c>
       <c r="U22" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V22" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F23" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G23" s="42" t="n">
         <v>7</v>
@@ -6937,7 +7146,7 @@
         <v>7</v>
       </c>
       <c r="M23" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N23" s="42" t="n">
         <v>7</v>
@@ -6962,6 +7171,9 @@
       </c>
       <c r="U23" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="V23" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -7047,6 +7259,10 @@
         <f>AVERAGE(U6:U23)</f>
         <v/>
       </c>
+      <c r="V24" s="43">
+        <f>AVERAGE(V6:V23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2441,7 +2441,7 @@
         <v>7</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2513,1087 +2513,1087 @@
         <v>105.86</v>
       </c>
       <c r="V6" s="36" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>14.29</v>
+        <v>11</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>19.14</v>
+        <v>29.43</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>26.71</v>
+        <v>38</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>28.14</v>
+        <v>41.29</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>28.57</v>
+        <v>51.43</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>31.57</v>
+        <v>58.29</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>34.86</v>
+        <v>55.43</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>41.29</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>41.43</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>46.14</v>
+        <v>76.86</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>41.57</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="P7" s="36" t="n">
-        <v>51.86</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="Q7" s="36" t="n">
-        <v>48.71</v>
+        <v>78.86</v>
       </c>
       <c r="R7" s="36" t="n">
-        <v>45.14</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="S7" s="36" t="n">
-        <v>50.71</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="T7" s="36" t="n">
-        <v>60.71</v>
+        <v>92.14</v>
       </c>
       <c r="U7" s="36" t="n">
-        <v>66.86</v>
+        <v>91</v>
       </c>
       <c r="V7" s="36" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>7.33</v>
+        <v>19.14</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>17.86</v>
+        <v>26.71</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>22.14</v>
+        <v>28.14</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>24.86</v>
+        <v>28.57</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>36.57</v>
+        <v>31.57</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>43.86</v>
+        <v>34.86</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>50.14</v>
+        <v>41.29</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>59</v>
+        <v>41.43</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>53.71</v>
+        <v>46.14</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>46.57</v>
+        <v>41.57</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>49.29</v>
+        <v>51.86</v>
       </c>
       <c r="Q8" s="36" t="n">
-        <v>65.56999999999999</v>
+        <v>48.71</v>
       </c>
       <c r="R8" s="36" t="n">
-        <v>67.29000000000001</v>
+        <v>45.14</v>
       </c>
       <c r="S8" s="36" t="n">
-        <v>61</v>
+        <v>50.71</v>
       </c>
       <c r="T8" s="36" t="n">
-        <v>64.43000000000001</v>
+        <v>60.71</v>
       </c>
       <c r="U8" s="36" t="n">
-        <v>68</v>
+        <v>66.86</v>
       </c>
       <c r="V8" s="36" t="n">
-        <v>61</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>29.43</v>
+        <v>7.33</v>
       </c>
       <c r="F9" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G9" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H9" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I9" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J9" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="G9" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="H9" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I9" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J9" s="36" t="n">
-        <v>63</v>
-      </c>
       <c r="K9" s="36" t="n">
-        <v>55.43</v>
+        <v>43.86</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>69.56999999999999</v>
+        <v>50.14</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>59</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>76.86</v>
+        <v>53.71</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>46.57</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>71.43000000000001</v>
+        <v>49.29</v>
       </c>
       <c r="Q9" s="36" t="n">
-        <v>78.86</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R9" s="36" t="n">
-        <v>78.43000000000001</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="S9" s="36" t="n">
-        <v>72.43000000000001</v>
+        <v>61</v>
       </c>
       <c r="T9" s="36" t="n">
-        <v>92.14</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="U9" s="36" t="n">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="V9" s="36" t="n">
-        <v>60</v>
+        <v>68.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>1.67</v>
+        <v>7.25</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>12.14</v>
+        <v>18.71</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>16.57</v>
+        <v>21.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>21</v>
+        <v>30.29</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>20.29</v>
+        <v>38</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>28.57</v>
+        <v>39.71</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>24.14</v>
+        <v>41.71</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>27.57</v>
+        <v>35.14</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>28.14</v>
+        <v>41</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>28.86</v>
+        <v>48</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>33.14</v>
+        <v>49.43</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>30.71</v>
+        <v>45.57</v>
       </c>
       <c r="P10" s="36" t="n">
-        <v>31.14</v>
+        <v>43</v>
       </c>
       <c r="Q10" s="36" t="n">
-        <v>40.29</v>
+        <v>46.57</v>
       </c>
       <c r="R10" s="36" t="n">
-        <v>38.71</v>
+        <v>48.43</v>
       </c>
       <c r="S10" s="36" t="n">
-        <v>43.14</v>
+        <v>38.29</v>
       </c>
       <c r="T10" s="36" t="n">
-        <v>37</v>
+        <v>50.14</v>
       </c>
       <c r="U10" s="36" t="n">
-        <v>46.29</v>
+        <v>48.86</v>
       </c>
       <c r="V10" s="36" t="n">
-        <v>53</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>18.71</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>21.57</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>30.29</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>38</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>39.71</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>41.71</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>35.14</v>
+        <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>48</v>
+        <v>42.43</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>49.43</v>
+        <v>38.57</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>45.57</v>
+        <v>34.29</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>43</v>
+        <v>37.86</v>
       </c>
       <c r="Q11" s="36" t="n">
-        <v>46.57</v>
+        <v>42.86</v>
       </c>
       <c r="R11" s="36" t="n">
-        <v>48.43</v>
+        <v>40.71</v>
       </c>
       <c r="S11" s="36" t="n">
-        <v>38.29</v>
+        <v>45.43</v>
       </c>
       <c r="T11" s="36" t="n">
-        <v>50.14</v>
+        <v>44.57</v>
       </c>
       <c r="U11" s="36" t="n">
-        <v>48.86</v>
+        <v>55.29</v>
       </c>
       <c r="V11" s="36" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>8</v>
+        <v>12.14</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>13.14</v>
+        <v>16.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>19.43</v>
+        <v>21</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>26.43</v>
+        <v>20.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>32.29</v>
+        <v>28.57</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>31.29</v>
+        <v>24.14</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>33.57</v>
+        <v>27.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>40</v>
+        <v>28.14</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>42.43</v>
+        <v>28.86</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>38.57</v>
+        <v>33.14</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>34.29</v>
+        <v>30.71</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>37.86</v>
+        <v>31.14</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>42.86</v>
+        <v>40.29</v>
       </c>
       <c r="R12" s="36" t="n">
-        <v>40.71</v>
+        <v>38.71</v>
       </c>
       <c r="S12" s="36" t="n">
-        <v>45.43</v>
+        <v>43.14</v>
       </c>
       <c r="T12" s="36" t="n">
-        <v>44.57</v>
+        <v>37</v>
       </c>
       <c r="U12" s="36" t="n">
-        <v>55.29</v>
+        <v>46.29</v>
       </c>
       <c r="V12" s="36" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>0</v>
+        <v>8.43</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>0</v>
+        <v>13.43</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>0.5</v>
+        <v>21.71</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>3.33</v>
+        <v>16.57</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>11.71</v>
+        <v>21.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>17.57</v>
+        <v>21.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>20.43</v>
+        <v>23.29</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>21.71</v>
+        <v>22.43</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>15</v>
+        <v>22.43</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>22.71</v>
+        <v>28.14</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>22.43</v>
+        <v>31.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>20.14</v>
+        <v>30</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>15.71</v>
+        <v>30.43</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>19.43</v>
+        <v>31.29</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>20.29</v>
+        <v>36.14</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>22.29</v>
+        <v>31</v>
       </c>
       <c r="T13" s="36" t="n">
-        <v>21.29</v>
+        <v>37.71</v>
       </c>
       <c r="U13" s="36" t="n">
-        <v>25.14</v>
+        <v>39.29</v>
       </c>
       <c r="V13" s="36" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>8.43</v>
+        <v>6.67</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>13.43</v>
+        <v>11.29</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>21.71</v>
+        <v>10.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>16.57</v>
+        <v>11.14</v>
       </c>
       <c r="H14" s="36" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="I14" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="J14" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="K14" s="36" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="L14" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="M14" s="36" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="N14" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="O14" s="36" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="P14" s="36" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="Q14" s="36" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="R14" s="36" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="S14" s="36" t="n">
         <v>21.29</v>
       </c>
-      <c r="I14" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="J14" s="36" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="K14" s="36" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="L14" s="36" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="M14" s="36" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="N14" s="36" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="O14" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="P14" s="36" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="Q14" s="36" t="n">
-        <v>31.29</v>
-      </c>
-      <c r="R14" s="36" t="n">
-        <v>36.14</v>
-      </c>
-      <c r="S14" s="36" t="n">
-        <v>31</v>
-      </c>
       <c r="T14" s="36" t="n">
-        <v>37.71</v>
+        <v>29.14</v>
       </c>
       <c r="U14" s="36" t="n">
-        <v>39.29</v>
+        <v>31.43</v>
       </c>
       <c r="V14" s="36" t="n">
-        <v>38</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>3.33</v>
+        <v>7</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>6.43</v>
+        <v>16</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>19.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>15.86</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>14</v>
+        <v>14.86</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>17.14</v>
+        <v>16.71</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>16.14</v>
+        <v>19.71</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>18.57</v>
+        <v>16.86</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>16.14</v>
+        <v>24.86</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>21.71</v>
+        <v>23.43</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>20.86</v>
+        <v>19.43</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>20.86</v>
+        <v>25.57</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>21.86</v>
+        <v>27.43</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>28.71</v>
+        <v>29.14</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>24.71</v>
+        <v>25</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>24.57</v>
+        <v>29.57</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>25.29</v>
+        <v>29.43</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>26.71</v>
+        <v>21</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>34</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.43</v>
+        <v>3.33</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>12.43</v>
+        <v>6.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.29</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>14.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>19.71</v>
+        <v>17.14</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>17.71</v>
+        <v>16.14</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>19.57</v>
+        <v>18.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>24.14</v>
+        <v>16.14</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>27.57</v>
+        <v>21.71</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>24.43</v>
+        <v>20.86</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>27.29</v>
+        <v>20.86</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>26.57</v>
+        <v>21.86</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>25.57</v>
+        <v>28.71</v>
       </c>
       <c r="R16" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="S16" s="36" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="T16" s="36" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="U16" s="36" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="V16" s="36" t="n">
         <v>29</v>
-      </c>
-      <c r="S16" s="36" t="n">
-        <v>27.71</v>
-      </c>
-      <c r="T16" s="36" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="U16" s="36" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="V16" s="36" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11.29</v>
+        <v>0</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>10.57</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>11.14</v>
+        <v>3.33</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>13.86</v>
+        <v>11.71</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>18</v>
+        <v>17.57</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>18</v>
+        <v>20.43</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>17.43</v>
+        <v>21.71</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15.29</v>
+        <v>15</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>24.43</v>
+        <v>22.71</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>24.71</v>
+        <v>22.43</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>25.57</v>
+        <v>20.14</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>19.29</v>
+        <v>15.71</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>25.43</v>
+        <v>19.43</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>22.57</v>
+        <v>20.29</v>
       </c>
       <c r="S17" s="36" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="T17" s="36" t="n">
         <v>21.29</v>
       </c>
-      <c r="T17" s="36" t="n">
-        <v>29.14</v>
-      </c>
       <c r="U17" s="36" t="n">
-        <v>31.43</v>
+        <v>25.14</v>
       </c>
       <c r="V17" s="36" t="n">
-        <v>30</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>7</v>
+        <v>9.43</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>16</v>
+        <v>12.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>19.43</v>
+        <v>13.29</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>15.86</v>
+        <v>14.71</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>14.86</v>
+        <v>17</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>16.71</v>
+        <v>19.71</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>19.71</v>
+        <v>17.71</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>16.86</v>
+        <v>19.57</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>24.86</v>
+        <v>24.14</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>23.43</v>
+        <v>27.57</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>19.43</v>
+        <v>24.43</v>
       </c>
       <c r="O18" s="36" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="P18" s="36" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="Q18" s="36" t="n">
         <v>25.57</v>
       </c>
-      <c r="P18" s="36" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="Q18" s="36" t="n">
-        <v>29.14</v>
-      </c>
       <c r="R18" s="36" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>29.57</v>
+        <v>27.71</v>
       </c>
       <c r="T18" s="36" t="n">
-        <v>29.43</v>
+        <v>32.57</v>
       </c>
       <c r="U18" s="36" t="n">
-        <v>21</v>
+        <v>31.57</v>
       </c>
       <c r="V18" s="36" t="n">
-        <v>28</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>3.25</v>
+        <v>14.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>8</v>
+        <v>11.86</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>9.43</v>
+        <v>18</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>12.71</v>
+        <v>19.14</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>11.57</v>
+        <v>21</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>23.43</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>11.86</v>
+        <v>20.43</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>24.57</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>19</v>
+        <v>24.14</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>19.57</v>
+        <v>24.43</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>16.86</v>
+        <v>22</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>14.71</v>
+        <v>18.43</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>15.86</v>
+        <v>24.71</v>
       </c>
       <c r="T19" s="36" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="U19" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="V19" s="36" t="n">
         <v>25</v>
-      </c>
-      <c r="U19" s="36" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="V19" s="36" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>3</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>11</v>
+        <v>7.14</v>
       </c>
       <c r="F20" s="36" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="G20" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="H20" s="36" t="n">
         <v>14.43</v>
       </c>
-      <c r="G20" s="36" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="H20" s="36" t="n">
+      <c r="I20" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="J20" s="36" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K20" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L20" s="36" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="M20" s="36" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="N20" s="36" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="O20" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="I20" s="36" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="J20" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="K20" s="36" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="L20" s="36" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="M20" s="36" t="n">
-        <v>24.57</v>
-      </c>
-      <c r="N20" s="36" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="O20" s="36" t="n">
-        <v>24.43</v>
-      </c>
       <c r="P20" s="36" t="n">
-        <v>22</v>
+        <v>15.29</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>23</v>
+        <v>15.29</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>18.43</v>
+        <v>18.71</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>24.71</v>
+        <v>18</v>
       </c>
       <c r="T20" s="36" t="n">
-        <v>27.57</v>
+        <v>25.29</v>
       </c>
       <c r="U20" s="36" t="n">
-        <v>30</v>
+        <v>28.86</v>
       </c>
       <c r="V20" s="36" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>13.43</v>
+        <v>3.25</v>
       </c>
       <c r="G21" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I21" s="36" t="n">
         <v>12.71</v>
       </c>
-      <c r="H21" s="36" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="I21" s="36" t="n">
+      <c r="J21" s="36" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="K21" s="36" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L21" s="36" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="M21" s="36" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N21" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="J21" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="K21" s="36" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="L21" s="36" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="M21" s="36" t="n">
+      <c r="O21" s="36" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="P21" s="36" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="Q21" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="R21" s="36" t="n">
         <v>14.71</v>
       </c>
-      <c r="N21" s="36" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="O21" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="P21" s="36" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="Q21" s="36" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="R21" s="36" t="n">
-        <v>18.71</v>
-      </c>
       <c r="S21" s="36" t="n">
-        <v>18</v>
+        <v>15.86</v>
       </c>
       <c r="T21" s="36" t="n">
-        <v>25.29</v>
+        <v>25</v>
       </c>
       <c r="U21" s="36" t="n">
-        <v>28.86</v>
+        <v>27.29</v>
       </c>
       <c r="V21" s="36" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="22">
@@ -3665,7 +3665,7 @@
         <v>12.14</v>
       </c>
       <c r="V22" s="36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -3737,7 +3737,7 @@
         <v>12.71</v>
       </c>
       <c r="V23" s="36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -4159,7 +4159,7 @@
         <v>7</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4231,1087 +4231,1087 @@
         <v>123494931</v>
       </c>
       <c r="V6" s="40" t="n">
-        <v>13397457</v>
+        <v>30897634</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>15808893</v>
+        <v>6122227</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>14209578</v>
+        <v>31792625</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>30449860</v>
+        <v>49374899</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>32603120</v>
+        <v>38585414</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>35552907</v>
+        <v>51458725</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>31069118</v>
+        <v>61835892</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>40525338</v>
+        <v>80551167</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>42402722</v>
+        <v>61490143</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>42012092</v>
+        <v>68619843</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>58722069</v>
+        <v>81742671</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>48135084</v>
+        <v>69757179</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>44293878</v>
+        <v>68198708</v>
       </c>
       <c r="P7" s="40" t="n">
-        <v>41613311</v>
+        <v>67906121</v>
       </c>
       <c r="Q7" s="40" t="n">
-        <v>43739350</v>
+        <v>84229530</v>
       </c>
       <c r="R7" s="40" t="n">
-        <v>78234960</v>
+        <v>92096471</v>
       </c>
       <c r="S7" s="40" t="n">
-        <v>47535640</v>
+        <v>78023476</v>
       </c>
       <c r="T7" s="40" t="n">
-        <v>59241681</v>
+        <v>89918146</v>
       </c>
       <c r="U7" s="40" t="n">
-        <v>65321829</v>
+        <v>94534230</v>
       </c>
       <c r="V7" s="40" t="n">
-        <v>8061073</v>
+        <v>21726028</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>2886450</v>
+        <v>14209578</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>22932586</v>
+        <v>30449860</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>24764259</v>
+        <v>32603120</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>32268886</v>
+        <v>35552907</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>42977335</v>
+        <v>31069118</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>44364359</v>
+        <v>40525338</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>53225819</v>
+        <v>42402722</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>51621207</v>
+        <v>42012092</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>58204066</v>
+        <v>58722069</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>58190202</v>
+        <v>48135084</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>46275213</v>
+        <v>44293878</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>51530060</v>
+        <v>41613311</v>
       </c>
       <c r="Q8" s="40" t="n">
-        <v>85043089</v>
+        <v>43739350</v>
       </c>
       <c r="R8" s="40" t="n">
-        <v>67469168</v>
+        <v>78234960</v>
       </c>
       <c r="S8" s="40" t="n">
-        <v>66040134</v>
+        <v>47535640</v>
       </c>
       <c r="T8" s="40" t="n">
-        <v>80004937</v>
+        <v>59241681</v>
       </c>
       <c r="U8" s="40" t="n">
-        <v>67225139</v>
+        <v>65321829</v>
       </c>
       <c r="V8" s="40" t="n">
-        <v>9493950</v>
+        <v>19224013</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>6122227</v>
+        <v>0</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>31792625</v>
+        <v>2886450</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>49374899</v>
+        <v>22932586</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>38585414</v>
+        <v>24764259</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>51458725</v>
+        <v>32268886</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>61835892</v>
+        <v>42977335</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>80551167</v>
+        <v>44364359</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>61490143</v>
+        <v>53225819</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>68619843</v>
+        <v>51621207</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>81742671</v>
+        <v>58204066</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>69757179</v>
+        <v>58190202</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>68198708</v>
+        <v>46275213</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>67906121</v>
+        <v>51530060</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>84229530</v>
+        <v>85043089</v>
       </c>
       <c r="R9" s="40" t="n">
-        <v>92096471</v>
+        <v>67469168</v>
       </c>
       <c r="S9" s="40" t="n">
-        <v>78023476</v>
+        <v>66040134</v>
       </c>
       <c r="T9" s="40" t="n">
-        <v>89918146</v>
+        <v>80004937</v>
       </c>
       <c r="U9" s="40" t="n">
-        <v>94534230</v>
+        <v>67225139</v>
       </c>
       <c r="V9" s="40" t="n">
-        <v>8159022</v>
+        <v>21692188</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>536260</v>
+        <v>3771593</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>14403556</v>
+        <v>17664217</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>16216832</v>
+        <v>21748722</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>32622053</v>
+        <v>38313932</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>23929705</v>
+        <v>49313727</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>37214538</v>
+        <v>41788221</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>25375430</v>
+        <v>36755638</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>31500087</v>
+        <v>43259404</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>28078687</v>
+        <v>68694825</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>34472458</v>
+        <v>48824266</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>35343350</v>
+        <v>57556194</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>51225290</v>
+        <v>38323101</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>36142612</v>
+        <v>40276838</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>47488940</v>
+        <v>45419704</v>
       </c>
       <c r="R10" s="40" t="n">
-        <v>44805002</v>
+        <v>55923182</v>
       </c>
       <c r="S10" s="40" t="n">
-        <v>43327432</v>
+        <v>40248814</v>
       </c>
       <c r="T10" s="40" t="n">
-        <v>39637968</v>
+        <v>50993465</v>
       </c>
       <c r="U10" s="40" t="n">
-        <v>55199920</v>
+        <v>62193580</v>
       </c>
       <c r="V10" s="40" t="n">
-        <v>9084932</v>
+        <v>14276700</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>3771593</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>17664217</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>21748722</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>38313932</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>49313727</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>41788221</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>36755638</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>43259404</v>
+        <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>68694825</v>
+        <v>51983942</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>48824266</v>
+        <v>58935844</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>57556194</v>
+        <v>38454971</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>38323101</v>
+        <v>42939312</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>40276838</v>
+        <v>43650420</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>45419704</v>
+        <v>53954095</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>55923182</v>
+        <v>48898463</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>40248814</v>
+        <v>48011655</v>
       </c>
       <c r="T11" s="40" t="n">
-        <v>50993465</v>
+        <v>72064876</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>62193580</v>
+        <v>59606189</v>
       </c>
       <c r="V11" s="40" t="n">
-        <v>6258124</v>
+        <v>14567286</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>0</v>
+        <v>536260</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>8972650</v>
+        <v>14403556</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>18100396</v>
+        <v>16216832</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>23988817</v>
+        <v>32622053</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>22409732</v>
+        <v>23929705</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37715520</v>
+        <v>37214538</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>35926824</v>
+        <v>25375430</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>39462393</v>
+        <v>31500087</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>51983942</v>
+        <v>28078687</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>58935844</v>
+        <v>34472458</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>38454971</v>
+        <v>35343350</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>42939312</v>
+        <v>51225290</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>43650420</v>
+        <v>36142612</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>53954095</v>
+        <v>47488940</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>48898463</v>
+        <v>44805002</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>48011655</v>
+        <v>43327432</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>72064876</v>
+        <v>39637968</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>59606189</v>
+        <v>55199920</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>6499760</v>
+        <v>15995228</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>0</v>
+        <v>10351067</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>0</v>
+        <v>21091580</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>363900</v>
+        <v>24243567</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>3736700</v>
+        <v>16381412</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>17796776</v>
+        <v>21591272</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>42724228</v>
+        <v>21904190</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>33036620</v>
+        <v>25438080</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>29649130</v>
+        <v>24614280</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>13949368</v>
+        <v>28889771</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>24539413</v>
+        <v>44250621</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>19087217</v>
+        <v>29608597</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>17139440</v>
+        <v>25219748</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>17746930</v>
+        <v>28515437</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>21437830</v>
+        <v>35235670</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>17616397</v>
+        <v>38511490</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>19360848</v>
+        <v>40935998</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>25377166</v>
+        <v>58966944</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>24702051</v>
+        <v>43378746</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>7538980</v>
+        <v>23435581</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>10351067</v>
+        <v>5092853</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>21091580</v>
+        <v>11100161</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>24243567</v>
+        <v>14612055</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>16381412</v>
+        <v>20638987</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>21591272</v>
+        <v>14061352</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>21904190</v>
+        <v>31599148</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>25438080</v>
+        <v>18747614</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>24614280</v>
+        <v>19576415</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>28889771</v>
+        <v>14226838</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>44250621</v>
+        <v>23197145</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>29608597</v>
+        <v>25790711</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>25219748</v>
+        <v>27856115</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>28515437</v>
+        <v>20981901</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>35235670</v>
+        <v>25433123</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>38511490</v>
+        <v>19355230</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>40935998</v>
+        <v>24713836</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>58966944</v>
+        <v>20195634</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>43378746</v>
+        <v>32414171</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>12960399</v>
+        <v>12129515</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>3249588</v>
+        <v>6239584</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>7305524</v>
+        <v>13803407</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>9575225</v>
+        <v>28572076</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>9264589</v>
+        <v>15282581</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>20692424</v>
+        <v>16594572</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>27565767</v>
+        <v>15223898</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>19138015</v>
+        <v>27696695</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>24912292</v>
+        <v>17717888</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>19068954</v>
+        <v>24163432</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>25387051</v>
+        <v>23623477</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>21008637</v>
+        <v>19145601</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>30862574</v>
+        <v>30157601</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>31820447</v>
+        <v>41172333</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>31875986</v>
+        <v>34303423</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>48358034</v>
+        <v>35044850</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>30000524</v>
+        <v>33519824</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>31150016</v>
+        <v>25969876</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>40688796</v>
+        <v>23835106</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>5649727</v>
+        <v>9222250</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>11884771</v>
+        <v>3249588</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>10651216</v>
+        <v>7305524</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>13882033</v>
+        <v>9575225</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>17812948</v>
+        <v>9264589</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>17331854</v>
+        <v>20692424</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>26294756</v>
+        <v>27565767</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>24196222</v>
+        <v>19138015</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>22122847</v>
+        <v>24912292</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>31914115</v>
+        <v>19068954</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>32069521</v>
+        <v>25387051</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>38287475</v>
+        <v>21008637</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>28283704</v>
+        <v>30862574</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>27334091</v>
+        <v>31820447</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>36312415</v>
+        <v>31875986</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>39333565</v>
+        <v>48358034</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>28566119</v>
+        <v>30000524</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>40387845</v>
+        <v>31150016</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>39744111</v>
+        <v>40688796</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>3756818</v>
+        <v>11483697</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>5092853</v>
+        <v>0</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>11100161</v>
+        <v>0</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>14612055</v>
+        <v>363900</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>20638987</v>
+        <v>3736700</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>14061352</v>
+        <v>17796776</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>31599148</v>
+        <v>42724228</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>18747614</v>
+        <v>33036620</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>19576415</v>
+        <v>29649130</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>14226838</v>
+        <v>13949368</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>23197145</v>
+        <v>24539413</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>25790711</v>
+        <v>19087217</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>27856115</v>
+        <v>17139440</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>20981901</v>
+        <v>17746930</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>25433123</v>
+        <v>21437830</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>19355230</v>
+        <v>17616397</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>24713836</v>
+        <v>19360848</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>20195634</v>
+        <v>25377166</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>32414171</v>
+        <v>24702051</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>6485364</v>
+        <v>9849990</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>6239584</v>
+        <v>11884771</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>13803407</v>
+        <v>10651216</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>28572076</v>
+        <v>13882033</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>15282581</v>
+        <v>17812948</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>16594572</v>
+        <v>17331854</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>15223898</v>
+        <v>26294756</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>27696695</v>
+        <v>24196222</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>17717888</v>
+        <v>22122847</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>24163432</v>
+        <v>31914115</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>23623477</v>
+        <v>32069521</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>19145601</v>
+        <v>38287475</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>30157601</v>
+        <v>28283704</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>41172333</v>
+        <v>27334091</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>34303423</v>
+        <v>36312415</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>35044850</v>
+        <v>39333565</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>33519824</v>
+        <v>28566119</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>25969876</v>
+        <v>40387845</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>23835106</v>
+        <v>39744111</v>
       </c>
       <c r="V18" s="40" t="n">
-        <v>4841761</v>
+        <v>7963668</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>8544625</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0</v>
+        <v>8387478</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>1324510</v>
+        <v>10570508</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>10311989</v>
+        <v>11896580</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>19934535</v>
+        <v>19614352</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>13536614</v>
+        <v>20966317</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>22187720</v>
+        <v>20073400</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>11732010</v>
+        <v>23801493</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>21143100</v>
+        <v>27940611</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>14330970</v>
+        <v>27893929</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>38267409</v>
+        <v>29635773</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>46351274</v>
+        <v>19554230</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>37105387</v>
+        <v>23848495</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>19868191</v>
+        <v>24194638</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>15153480</v>
+        <v>20330094</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>19277087</v>
+        <v>26044199</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>34209889</v>
+        <v>24608772</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>33260760</v>
+        <v>28079726</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>10036079</v>
+        <v>5134615</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>8544625</v>
+        <v>3337146</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>8387478</v>
+        <v>10420206</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>10570508</v>
+        <v>21387685</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>11896580</v>
+        <v>16050448</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>19614352</v>
+        <v>21568794</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>20966317</v>
+        <v>30845816</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>20073400</v>
+        <v>45285935</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>23801493</v>
+        <v>28941455</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>27940611</v>
+        <v>21801828</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>27893929</v>
+        <v>19628570</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>29635773</v>
+        <v>23276090</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>19554230</v>
+        <v>27906254</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>23848495</v>
+        <v>20822247</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>24194638</v>
+        <v>20014322</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>20330094</v>
+        <v>19159625</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>26044199</v>
+        <v>22535696</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>24608772</v>
+        <v>21412810</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>28079726</v>
+        <v>34881782</v>
       </c>
       <c r="V20" s="40" t="n">
-        <v>2703785</v>
+        <v>6468218</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>3337146</v>
+        <v>0</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>10420206</v>
+        <v>0</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>21387685</v>
+        <v>1324510</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>16050448</v>
+        <v>10311989</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>21568794</v>
+        <v>19934535</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>30845816</v>
+        <v>13536614</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>45285935</v>
+        <v>22187720</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>28941455</v>
+        <v>11732010</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>21801828</v>
+        <v>21143100</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>19628570</v>
+        <v>14330970</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>23276090</v>
+        <v>38267409</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>27906254</v>
+        <v>46351274</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>20822247</v>
+        <v>37105387</v>
       </c>
       <c r="Q21" s="40" t="n">
-        <v>20014322</v>
+        <v>19868191</v>
       </c>
       <c r="R21" s="40" t="n">
-        <v>19159625</v>
+        <v>15153480</v>
       </c>
       <c r="S21" s="40" t="n">
-        <v>22535696</v>
+        <v>19277087</v>
       </c>
       <c r="T21" s="40" t="n">
-        <v>21412810</v>
+        <v>34209889</v>
       </c>
       <c r="U21" s="40" t="n">
-        <v>34881782</v>
+        <v>33260760</v>
       </c>
       <c r="V21" s="40" t="n">
-        <v>2138453</v>
+        <v>12037629</v>
       </c>
     </row>
     <row r="22">
@@ -5383,7 +5383,7 @@
         <v>9823030</v>
       </c>
       <c r="V22" s="40" t="n">
-        <v>547770</v>
+        <v>1944810</v>
       </c>
     </row>
     <row r="23">
@@ -5455,7 +5455,7 @@
         <v>10209080</v>
       </c>
       <c r="V23" s="40" t="n">
-        <v>547780</v>
+        <v>1759870</v>
       </c>
     </row>
     <row r="24">
@@ -5877,7 +5877,7 @@
         <v>7</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -5949,25 +5949,25 @@
         <v>7</v>
       </c>
       <c r="V6" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E7" s="42" t="n">
         <v>7</v>
@@ -6021,28 +6021,28 @@
         <v>7</v>
       </c>
       <c r="V7" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -6093,28 +6093,28 @@
         <v>7</v>
       </c>
       <c r="V8" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E9" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F9" s="42" t="n">
         <v>7</v>
@@ -6165,25 +6165,25 @@
         <v>7</v>
       </c>
       <c r="V9" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>7</v>
@@ -6237,28 +6237,28 @@
         <v>7</v>
       </c>
       <c r="V10" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -6309,28 +6309,28 @@
         <v>7</v>
       </c>
       <c r="V11" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>7</v>
@@ -6381,97 +6381,97 @@
         <v>7</v>
       </c>
       <c r="V12" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E13" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V13" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -6525,25 +6525,25 @@
         <v>7</v>
       </c>
       <c r="V14" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -6597,107 +6597,107 @@
         <v>7</v>
       </c>
       <c r="V15" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="D16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="H17" s="42" t="n">
         <v>7</v>
       </c>
@@ -6741,25 +6741,25 @@
         <v>7</v>
       </c>
       <c r="V17" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -6813,31 +6813,31 @@
         <v>7</v>
       </c>
       <c r="V18" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
         <v>7</v>
@@ -6885,103 +6885,103 @@
         <v>7</v>
       </c>
       <c r="V19" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V20" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="D20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V20" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G21" s="42" t="n">
         <v>7</v>
@@ -7029,7 +7029,7 @@
         <v>7</v>
       </c>
       <c r="V21" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -7101,7 +7101,7 @@
         <v>7</v>
       </c>
       <c r="V22" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -7173,7 +7173,7 @@
         <v>7</v>
       </c>
       <c r="V23" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2441,7 +2441,7 @@
         <v>7</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2513,7 +2513,7 @@
         <v>105.86</v>
       </c>
       <c r="V6" s="36" t="n">
-        <v>117</v>
+        <v>116.33</v>
       </c>
     </row>
     <row r="7">
@@ -2585,151 +2585,151 @@
         <v>91</v>
       </c>
       <c r="V7" s="36" t="n">
-        <v>79</v>
+        <v>82.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>19.14</v>
+        <v>7.33</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>26.71</v>
+        <v>17.86</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>28.14</v>
+        <v>22.14</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>28.57</v>
+        <v>24.86</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>31.57</v>
+        <v>36.57</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>34.86</v>
+        <v>43.86</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>41.29</v>
+        <v>50.14</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>41.43</v>
+        <v>59</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>46.14</v>
+        <v>53.71</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>41.57</v>
+        <v>46.57</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>51.86</v>
+        <v>49.29</v>
       </c>
       <c r="Q8" s="36" t="n">
-        <v>48.71</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R8" s="36" t="n">
-        <v>45.14</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="S8" s="36" t="n">
-        <v>50.71</v>
+        <v>61</v>
       </c>
       <c r="T8" s="36" t="n">
-        <v>60.71</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="U8" s="36" t="n">
-        <v>66.86</v>
+        <v>68</v>
       </c>
       <c r="V8" s="36" t="n">
-        <v>69.5</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>7.33</v>
+        <v>19.14</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>17.86</v>
+        <v>26.71</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>22.14</v>
+        <v>28.14</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>24.86</v>
+        <v>28.57</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>36.57</v>
+        <v>31.57</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>43.86</v>
+        <v>34.86</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>50.14</v>
+        <v>41.29</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>59</v>
+        <v>41.43</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>53.71</v>
+        <v>46.14</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>46.57</v>
+        <v>41.57</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>49.29</v>
+        <v>51.86</v>
       </c>
       <c r="Q9" s="36" t="n">
-        <v>65.56999999999999</v>
+        <v>48.71</v>
       </c>
       <c r="R9" s="36" t="n">
-        <v>67.29000000000001</v>
+        <v>45.14</v>
       </c>
       <c r="S9" s="36" t="n">
-        <v>61</v>
+        <v>50.71</v>
       </c>
       <c r="T9" s="36" t="n">
-        <v>64.43000000000001</v>
+        <v>60.71</v>
       </c>
       <c r="U9" s="36" t="n">
-        <v>68</v>
+        <v>66.86</v>
       </c>
       <c r="V9" s="36" t="n">
-        <v>68.5</v>
+        <v>68.67</v>
       </c>
     </row>
     <row r="10">
@@ -2801,223 +2801,223 @@
         <v>48.86</v>
       </c>
       <c r="V10" s="36" t="n">
-        <v>56.5</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>8.43</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>13.43</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>21.71</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>16.57</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>21.29</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>21.14</v>
       </c>
       <c r="J11" s="36" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="K11" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="L11" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="M11" s="36" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="N11" s="36" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="O11" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="P11" s="36" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="Q11" s="36" t="n">
         <v>31.29</v>
       </c>
-      <c r="K11" s="36" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="L11" s="36" t="n">
-        <v>40</v>
-      </c>
-      <c r="M11" s="36" t="n">
-        <v>42.43</v>
-      </c>
-      <c r="N11" s="36" t="n">
-        <v>38.57</v>
-      </c>
-      <c r="O11" s="36" t="n">
-        <v>34.29</v>
-      </c>
-      <c r="P11" s="36" t="n">
-        <v>37.86</v>
-      </c>
-      <c r="Q11" s="36" t="n">
-        <v>42.86</v>
-      </c>
       <c r="R11" s="36" t="n">
-        <v>40.71</v>
+        <v>36.14</v>
       </c>
       <c r="S11" s="36" t="n">
-        <v>45.43</v>
+        <v>31</v>
       </c>
       <c r="T11" s="36" t="n">
-        <v>44.57</v>
+        <v>37.71</v>
       </c>
       <c r="U11" s="36" t="n">
-        <v>55.29</v>
+        <v>39.29</v>
       </c>
       <c r="V11" s="36" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>33.14</v>
+        <v>38.57</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>30.71</v>
+        <v>34.29</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>31.14</v>
+        <v>37.86</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>40.29</v>
+        <v>42.86</v>
       </c>
       <c r="R12" s="36" t="n">
-        <v>38.71</v>
+        <v>40.71</v>
       </c>
       <c r="S12" s="36" t="n">
-        <v>43.14</v>
+        <v>45.43</v>
       </c>
       <c r="T12" s="36" t="n">
-        <v>37</v>
+        <v>44.57</v>
       </c>
       <c r="U12" s="36" t="n">
-        <v>46.29</v>
+        <v>55.29</v>
       </c>
       <c r="V12" s="36" t="n">
-        <v>44</v>
+        <v>45.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>8.43</v>
+        <v>1.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>13.43</v>
+        <v>12.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>21.71</v>
+        <v>16.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>16.57</v>
+        <v>21</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>21.29</v>
+        <v>20.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>21.14</v>
+        <v>28.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>23.29</v>
+        <v>24.14</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>22.43</v>
+        <v>27.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>22.43</v>
+        <v>28.14</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.14</v>
+        <v>28.86</v>
       </c>
       <c r="N13" s="36" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="O13" s="36" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="P13" s="36" t="n">
         <v>31.14</v>
       </c>
-      <c r="O13" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="P13" s="36" t="n">
-        <v>30.43</v>
-      </c>
       <c r="Q13" s="36" t="n">
-        <v>31.29</v>
+        <v>40.29</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>36.14</v>
+        <v>38.71</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>31</v>
+        <v>43.14</v>
       </c>
       <c r="T13" s="36" t="n">
-        <v>37.71</v>
+        <v>37</v>
       </c>
       <c r="U13" s="36" t="n">
-        <v>39.29</v>
+        <v>46.29</v>
       </c>
       <c r="V13" s="36" t="n">
-        <v>42</v>
+        <v>41.33</v>
       </c>
     </row>
     <row r="14">
@@ -3089,367 +3089,367 @@
         <v>31.43</v>
       </c>
       <c r="V14" s="36" t="n">
-        <v>31.5</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>7</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>19.43</v>
+        <v>14.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>15.86</v>
+        <v>11.86</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>14.86</v>
+        <v>18</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>16.71</v>
+        <v>19.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>19.71</v>
+        <v>21</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>16.86</v>
+        <v>23.43</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>24.86</v>
+        <v>20.43</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>23.43</v>
+        <v>24.57</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>19.43</v>
+        <v>24.14</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>25.57</v>
+        <v>24.43</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>27.43</v>
+        <v>22</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>29.14</v>
+        <v>23</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>25</v>
+        <v>18.43</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>29.57</v>
+        <v>24.71</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>29.43</v>
+        <v>27.57</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>30.5</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>3.33</v>
+        <v>9.43</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>6.43</v>
+        <v>12.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>17.14</v>
+        <v>19.71</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>16.14</v>
+        <v>17.71</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>18.57</v>
+        <v>19.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>16.14</v>
+        <v>24.14</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>21.71</v>
+        <v>27.57</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>20.86</v>
+        <v>24.43</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>20.86</v>
+        <v>27.29</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>21.86</v>
+        <v>26.57</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>28.71</v>
+        <v>25.57</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>24.71</v>
+        <v>29</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>24.57</v>
+        <v>27.71</v>
       </c>
       <c r="T16" s="36" t="n">
-        <v>25.29</v>
+        <v>32.57</v>
       </c>
       <c r="U16" s="36" t="n">
-        <v>26.71</v>
+        <v>31.57</v>
       </c>
       <c r="V16" s="36" t="n">
-        <v>29</v>
+        <v>28.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>0.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>3.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>11.71</v>
+        <v>14</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.57</v>
+        <v>17.14</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>20.43</v>
+        <v>16.14</v>
       </c>
       <c r="K17" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L17" s="36" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="M17" s="36" t="n">
         <v>21.71</v>
       </c>
-      <c r="L17" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="M17" s="36" t="n">
-        <v>22.71</v>
-      </c>
       <c r="N17" s="36" t="n">
-        <v>22.43</v>
+        <v>20.86</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>20.14</v>
+        <v>20.86</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>15.71</v>
+        <v>21.86</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>19.43</v>
+        <v>28.71</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>20.29</v>
+        <v>24.71</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>22.29</v>
+        <v>24.57</v>
       </c>
       <c r="T17" s="36" t="n">
-        <v>21.29</v>
+        <v>25.29</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>25.14</v>
+        <v>26.71</v>
       </c>
       <c r="V17" s="36" t="n">
-        <v>28.5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>9.43</v>
+        <v>7</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>12.43</v>
+        <v>16</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>13.29</v>
+        <v>19.43</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>14.71</v>
+        <v>15.86</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>17</v>
+        <v>14.86</v>
       </c>
       <c r="I18" s="36" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="J18" s="36" t="n">
         <v>19.71</v>
       </c>
-      <c r="J18" s="36" t="n">
-        <v>17.71</v>
-      </c>
       <c r="K18" s="36" t="n">
-        <v>19.57</v>
+        <v>16.86</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>24.14</v>
+        <v>24.86</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>27.57</v>
+        <v>23.43</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>24.43</v>
+        <v>19.43</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>27.29</v>
+        <v>25.57</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>26.57</v>
+        <v>27.43</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>25.57</v>
+        <v>29.14</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>27.71</v>
+        <v>29.57</v>
       </c>
       <c r="T18" s="36" t="n">
-        <v>32.57</v>
+        <v>29.43</v>
       </c>
       <c r="U18" s="36" t="n">
-        <v>31.57</v>
+        <v>21</v>
       </c>
       <c r="V18" s="36" t="n">
-        <v>25.5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>14.43</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>11.86</v>
+        <v>3.33</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>18</v>
+        <v>11.71</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>19.14</v>
+        <v>17.57</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>21</v>
+        <v>20.43</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>23.43</v>
+        <v>21.71</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>20.43</v>
+        <v>15</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>24.57</v>
+        <v>22.71</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>24.14</v>
+        <v>22.43</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>24.43</v>
+        <v>20.14</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>22</v>
+        <v>15.71</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>23</v>
+        <v>19.43</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>18.43</v>
+        <v>20.29</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>24.71</v>
+        <v>22.29</v>
       </c>
       <c r="T19" s="36" t="n">
-        <v>27.57</v>
+        <v>21.29</v>
       </c>
       <c r="U19" s="36" t="n">
-        <v>30</v>
+        <v>25.14</v>
       </c>
       <c r="V19" s="36" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -3521,7 +3521,7 @@
         <v>28.86</v>
       </c>
       <c r="V20" s="36" t="n">
-        <v>19.5</v>
+        <v>22.67</v>
       </c>
     </row>
     <row r="21">
@@ -3593,7 +3593,7 @@
         <v>27.29</v>
       </c>
       <c r="V21" s="36" t="n">
-        <v>19.5</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="22">
@@ -3737,7 +3737,7 @@
         <v>12.71</v>
       </c>
       <c r="V23" s="36" t="n">
-        <v>7</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="24">
@@ -4159,7 +4159,7 @@
         <v>7</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4231,7 +4231,7 @@
         <v>123494931</v>
       </c>
       <c r="V6" s="40" t="n">
-        <v>30897634</v>
+        <v>50393648</v>
       </c>
     </row>
     <row r="7">
@@ -4303,151 +4303,151 @@
         <v>94534230</v>
       </c>
       <c r="V7" s="40" t="n">
-        <v>21726028</v>
+        <v>33703288</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>15808893</v>
+        <v>0</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>14209578</v>
+        <v>2886450</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>30449860</v>
+        <v>22932586</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>32603120</v>
+        <v>24764259</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>35552907</v>
+        <v>32268886</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>31069118</v>
+        <v>42977335</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>40525338</v>
+        <v>44364359</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>42402722</v>
+        <v>53225819</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>42012092</v>
+        <v>51621207</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>58722069</v>
+        <v>58204066</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>48135084</v>
+        <v>58190202</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>44293878</v>
+        <v>46275213</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>41613311</v>
+        <v>51530060</v>
       </c>
       <c r="Q8" s="40" t="n">
-        <v>43739350</v>
+        <v>85043089</v>
       </c>
       <c r="R8" s="40" t="n">
-        <v>78234960</v>
+        <v>67469168</v>
       </c>
       <c r="S8" s="40" t="n">
-        <v>47535640</v>
+        <v>66040134</v>
       </c>
       <c r="T8" s="40" t="n">
-        <v>59241681</v>
+        <v>80004937</v>
       </c>
       <c r="U8" s="40" t="n">
-        <v>65321829</v>
+        <v>67225139</v>
       </c>
       <c r="V8" s="40" t="n">
-        <v>19224013</v>
+        <v>33208704</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>0</v>
+        <v>15808893</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>2886450</v>
+        <v>14209578</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>22932586</v>
+        <v>30449860</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>24764259</v>
+        <v>32603120</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>32268886</v>
+        <v>35552907</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>42977335</v>
+        <v>31069118</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>44364359</v>
+        <v>40525338</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>53225819</v>
+        <v>42402722</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>51621207</v>
+        <v>42012092</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>58204066</v>
+        <v>58722069</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>58190202</v>
+        <v>48135084</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>46275213</v>
+        <v>44293878</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>51530060</v>
+        <v>41613311</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>85043089</v>
+        <v>43739350</v>
       </c>
       <c r="R9" s="40" t="n">
-        <v>67469168</v>
+        <v>78234960</v>
       </c>
       <c r="S9" s="40" t="n">
-        <v>66040134</v>
+        <v>47535640</v>
       </c>
       <c r="T9" s="40" t="n">
-        <v>80004937</v>
+        <v>59241681</v>
       </c>
       <c r="U9" s="40" t="n">
-        <v>67225139</v>
+        <v>65321829</v>
       </c>
       <c r="V9" s="40" t="n">
-        <v>21692188</v>
+        <v>28211873</v>
       </c>
     </row>
     <row r="10">
@@ -4519,223 +4519,223 @@
         <v>62193580</v>
       </c>
       <c r="V10" s="40" t="n">
-        <v>14276700</v>
+        <v>20295930</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>10351067</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>21091580</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>24243567</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>16381412</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>21591272</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>21904190</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>25438080</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>24614280</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>51983942</v>
+        <v>28889771</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>58935844</v>
+        <v>44250621</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>38454971</v>
+        <v>29608597</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>42939312</v>
+        <v>25219748</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>43650420</v>
+        <v>28515437</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>53954095</v>
+        <v>35235670</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>48898463</v>
+        <v>38511490</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>48011655</v>
+        <v>40935998</v>
       </c>
       <c r="T11" s="40" t="n">
-        <v>72064876</v>
+        <v>58966944</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>59606189</v>
+        <v>43378746</v>
       </c>
       <c r="V11" s="40" t="n">
-        <v>14567286</v>
+        <v>38896921</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>35343350</v>
+        <v>38454971</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>51225290</v>
+        <v>42939312</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>36142612</v>
+        <v>43650420</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>47488940</v>
+        <v>53954095</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>44805002</v>
+        <v>48898463</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>43327432</v>
+        <v>48011655</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>39637968</v>
+        <v>72064876</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>55199920</v>
+        <v>59606189</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>15995228</v>
+        <v>18870804</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>10351067</v>
+        <v>536260</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>21091580</v>
+        <v>14403556</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>24243567</v>
+        <v>16216832</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>16381412</v>
+        <v>32622053</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>21591272</v>
+        <v>23929705</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>21904190</v>
+        <v>37214538</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25438080</v>
+        <v>25375430</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>24614280</v>
+        <v>31500087</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28889771</v>
+        <v>28078687</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>44250621</v>
+        <v>34472458</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>29608597</v>
+        <v>35343350</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>25219748</v>
+        <v>51225290</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>28515437</v>
+        <v>36142612</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>35235670</v>
+        <v>47488940</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>38511490</v>
+        <v>44805002</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>40935998</v>
+        <v>43327432</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>58966944</v>
+        <v>39637968</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>43378746</v>
+        <v>55199920</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>23435581</v>
+        <v>22754071</v>
       </c>
     </row>
     <row r="14">
@@ -4807,367 +4807,367 @@
         <v>32414171</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>12129515</v>
+        <v>18308005</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>6239584</v>
+        <v>8544625</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>13803407</v>
+        <v>8387478</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>28572076</v>
+        <v>10570508</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>15282581</v>
+        <v>11896580</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>16594572</v>
+        <v>19614352</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>15223898</v>
+        <v>20966317</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>27696695</v>
+        <v>20073400</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>17717888</v>
+        <v>23801493</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>24163432</v>
+        <v>27940611</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>23623477</v>
+        <v>27893929</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>19145601</v>
+        <v>29635773</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>30157601</v>
+        <v>19554230</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>41172333</v>
+        <v>23848495</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>34303423</v>
+        <v>24194638</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>35044850</v>
+        <v>20330094</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>33519824</v>
+        <v>26044199</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>25969876</v>
+        <v>24608772</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>23835106</v>
+        <v>28079726</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>9222250</v>
+        <v>9739595</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>3249588</v>
+        <v>11884771</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>7305524</v>
+        <v>10651216</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>9575225</v>
+        <v>13882033</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>9264589</v>
+        <v>17812948</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>20692424</v>
+        <v>17331854</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>27565767</v>
+        <v>26294756</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>19138015</v>
+        <v>24196222</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>24912292</v>
+        <v>22122847</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>19068954</v>
+        <v>31914115</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>25387051</v>
+        <v>32069521</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>21008637</v>
+        <v>38287475</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>30862574</v>
+        <v>28283704</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>31820447</v>
+        <v>27334091</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>31875986</v>
+        <v>36312415</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>48358034</v>
+        <v>39333565</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>30000524</v>
+        <v>28566119</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>31150016</v>
+        <v>40387845</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>40688796</v>
+        <v>39744111</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>11483697</v>
+        <v>12971308</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>0</v>
+        <v>3249588</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>0</v>
+        <v>7305524</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>363900</v>
+        <v>9575225</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>3736700</v>
+        <v>9264589</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>17796776</v>
+        <v>20692424</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>42724228</v>
+        <v>27565767</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>33036620</v>
+        <v>19138015</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>29649130</v>
+        <v>24912292</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>13949368</v>
+        <v>19068954</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>24539413</v>
+        <v>25387051</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>19087217</v>
+        <v>21008637</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>17139440</v>
+        <v>30862574</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>17746930</v>
+        <v>31820447</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>21437830</v>
+        <v>31875986</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>17616397</v>
+        <v>48358034</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>19360848</v>
+        <v>30000524</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>25377166</v>
+        <v>31150016</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>24702051</v>
+        <v>40688796</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>9849990</v>
+        <v>15593994</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>11884771</v>
+        <v>6239584</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>10651216</v>
+        <v>13803407</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>13882033</v>
+        <v>28572076</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>17812948</v>
+        <v>15282581</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>17331854</v>
+        <v>16594572</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>26294756</v>
+        <v>15223898</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>24196222</v>
+        <v>27696695</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>22122847</v>
+        <v>17717888</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>31914115</v>
+        <v>24163432</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>32069521</v>
+        <v>23623477</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>38287475</v>
+        <v>19145601</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>28283704</v>
+        <v>30157601</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>27334091</v>
+        <v>41172333</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>36312415</v>
+        <v>34303423</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>39333565</v>
+        <v>35044850</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>28566119</v>
+        <v>33519824</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>40387845</v>
+        <v>25969876</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>39744111</v>
+        <v>23835106</v>
       </c>
       <c r="V18" s="40" t="n">
-        <v>7963668</v>
+        <v>12017920</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>8544625</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>8387478</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>10570508</v>
+        <v>363900</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>11896580</v>
+        <v>3736700</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>19614352</v>
+        <v>17796776</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>20966317</v>
+        <v>42724228</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>20073400</v>
+        <v>33036620</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>23801493</v>
+        <v>29649130</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>27940611</v>
+        <v>13949368</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>27893929</v>
+        <v>24539413</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>29635773</v>
+        <v>19087217</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>19554230</v>
+        <v>17139440</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>23848495</v>
+        <v>17746930</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>24194638</v>
+        <v>21437830</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>20330094</v>
+        <v>17616397</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>26044199</v>
+        <v>19360848</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>24608772</v>
+        <v>25377166</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>28079726</v>
+        <v>24702051</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>5134615</v>
+        <v>11947180</v>
       </c>
     </row>
     <row r="20">
@@ -5239,7 +5239,7 @@
         <v>34881782</v>
       </c>
       <c r="V20" s="40" t="n">
-        <v>6468218</v>
+        <v>12177618</v>
       </c>
     </row>
     <row r="21">
@@ -5311,7 +5311,7 @@
         <v>33260760</v>
       </c>
       <c r="V21" s="40" t="n">
-        <v>12037629</v>
+        <v>12878799</v>
       </c>
     </row>
     <row r="22">
@@ -5383,7 +5383,7 @@
         <v>9823030</v>
       </c>
       <c r="V22" s="40" t="n">
-        <v>1944810</v>
+        <v>3383440</v>
       </c>
     </row>
     <row r="23">
@@ -5455,7 +5455,7 @@
         <v>10209080</v>
       </c>
       <c r="V23" s="40" t="n">
-        <v>1759870</v>
+        <v>4013700</v>
       </c>
     </row>
     <row r="24">
@@ -5877,7 +5877,7 @@
         <v>7</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -5949,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="V6" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6021,29 +6021,29 @@
         <v>7</v>
       </c>
       <c r="V7" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="42" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
       </c>
@@ -6093,79 +6093,79 @@
         <v>7</v>
       </c>
       <c r="V8" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V9" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="F9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U9" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V9" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -6237,28 +6237,28 @@
         <v>7</v>
       </c>
       <c r="V10" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -6309,97 +6309,97 @@
         <v>7</v>
       </c>
       <c r="V11" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V12" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V12" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -6453,7 +6453,7 @@
         <v>7</v>
       </c>
       <c r="V13" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -6525,25 +6525,25 @@
         <v>7</v>
       </c>
       <c r="V14" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -6597,106 +6597,106 @@
         <v>7</v>
       </c>
       <c r="V15" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F17" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17" s="42" t="n">
         <v>7</v>
@@ -6741,25 +6741,25 @@
         <v>7</v>
       </c>
       <c r="V17" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -6813,34 +6813,34 @@
         <v>7</v>
       </c>
       <c r="V18" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F19" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="G19" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -6885,7 +6885,7 @@
         <v>7</v>
       </c>
       <c r="V19" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -6957,7 +6957,7 @@
         <v>7</v>
       </c>
       <c r="V20" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -7029,7 +7029,7 @@
         <v>7</v>
       </c>
       <c r="V21" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -7101,7 +7101,7 @@
         <v>7</v>
       </c>
       <c r="V22" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -7173,7 +7173,7 @@
         <v>7</v>
       </c>
       <c r="V23" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2441,7 +2441,7 @@
         <v>7</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2513,7 +2513,7 @@
         <v>105.86</v>
       </c>
       <c r="V6" s="36" t="n">
-        <v>116.33</v>
+        <v>115.6</v>
       </c>
     </row>
     <row r="7">
@@ -2585,7 +2585,7 @@
         <v>91</v>
       </c>
       <c r="V7" s="36" t="n">
-        <v>82.33</v>
+        <v>85.2</v>
       </c>
     </row>
     <row r="8">
@@ -2657,7 +2657,7 @@
         <v>68</v>
       </c>
       <c r="V8" s="36" t="n">
-        <v>72.33</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="9">
@@ -2729,7 +2729,7 @@
         <v>66.86</v>
       </c>
       <c r="V9" s="36" t="n">
-        <v>68.67</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="10">
@@ -2801,7 +2801,7 @@
         <v>48.86</v>
       </c>
       <c r="V10" s="36" t="n">
-        <v>54</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="11">
@@ -2873,7 +2873,7 @@
         <v>39.29</v>
       </c>
       <c r="V11" s="36" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="12">
@@ -2945,7 +2945,7 @@
         <v>55.29</v>
       </c>
       <c r="V12" s="36" t="n">
-        <v>45.67</v>
+        <v>47.4</v>
       </c>
     </row>
     <row r="13">
@@ -3017,7 +3017,7 @@
         <v>46.29</v>
       </c>
       <c r="V13" s="36" t="n">
-        <v>41.33</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="14">
@@ -3089,151 +3089,151 @@
         <v>31.43</v>
       </c>
       <c r="V14" s="36" t="n">
-        <v>32.67</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>11</v>
+        <v>12.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>14.43</v>
+        <v>13.29</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>11.86</v>
+        <v>14.71</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.14</v>
+        <v>19.71</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>21</v>
+        <v>17.71</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>23.43</v>
+        <v>19.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>20.43</v>
+        <v>24.14</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>24.57</v>
+        <v>27.57</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>24.14</v>
+        <v>24.43</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>24.43</v>
+        <v>27.29</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>22</v>
+        <v>26.57</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>23</v>
+        <v>25.57</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>18.43</v>
+        <v>29</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>24.71</v>
+        <v>27.71</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>27.57</v>
+        <v>32.57</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>30</v>
+        <v>31.57</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>28.67</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.43</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>12.43</v>
+        <v>11</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.29</v>
+        <v>14.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>14.71</v>
+        <v>11.86</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>19.71</v>
+        <v>19.14</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>17.71</v>
+        <v>21</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>19.57</v>
+        <v>23.43</v>
       </c>
       <c r="L16" s="36" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="M16" s="36" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="N16" s="36" t="n">
         <v>24.14</v>
       </c>
-      <c r="M16" s="36" t="n">
+      <c r="O16" s="36" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="P16" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q16" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="R16" s="36" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="S16" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="T16" s="36" t="n">
         <v>27.57</v>
       </c>
-      <c r="N16" s="36" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="O16" s="36" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="P16" s="36" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="Q16" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="R16" s="36" t="n">
-        <v>29</v>
-      </c>
-      <c r="S16" s="36" t="n">
-        <v>27.71</v>
-      </c>
-      <c r="T16" s="36" t="n">
-        <v>32.57</v>
-      </c>
       <c r="U16" s="36" t="n">
-        <v>31.57</v>
+        <v>30</v>
       </c>
       <c r="V16" s="36" t="n">
-        <v>28.33</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="17">
@@ -3305,7 +3305,7 @@
         <v>26.71</v>
       </c>
       <c r="V17" s="36" t="n">
-        <v>28</v>
+        <v>29.8</v>
       </c>
     </row>
     <row r="18">
@@ -3377,7 +3377,7 @@
         <v>21</v>
       </c>
       <c r="V18" s="36" t="n">
-        <v>27</v>
+        <v>27.8</v>
       </c>
     </row>
     <row r="19">
@@ -3449,7 +3449,7 @@
         <v>25.14</v>
       </c>
       <c r="V19" s="36" t="n">
-        <v>26</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="20">
@@ -3521,7 +3521,7 @@
         <v>28.86</v>
       </c>
       <c r="V20" s="36" t="n">
-        <v>22.67</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="21">
@@ -3593,151 +3593,151 @@
         <v>27.29</v>
       </c>
       <c r="V21" s="36" t="n">
-        <v>16.67</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G22" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="36" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G22" s="36" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H22" s="36" t="n">
-        <v>7.86</v>
+        <v>6</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>7.14</v>
+        <v>4.43</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>7.14</v>
+        <v>5.86</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>6</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>8.710000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="O22" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P22" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="Q22" s="36" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="R22" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="S22" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="R22" s="36" t="n">
+      <c r="T22" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="S22" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="T22" s="36" t="n">
-        <v>6.86</v>
-      </c>
       <c r="U22" s="36" t="n">
-        <v>12.14</v>
+        <v>12.71</v>
       </c>
       <c r="V22" s="36" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23" s="36" t="n">
-        <v>2.8</v>
+        <v>5.14</v>
       </c>
       <c r="G23" s="36" t="n">
-        <v>4</v>
+        <v>5.29</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>6</v>
+        <v>7.86</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>4.43</v>
+        <v>7.14</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>3.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>5.86</v>
+        <v>7.14</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>5.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>7.43</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O23" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>7.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q23" s="36" t="n">
-        <v>10.29</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="R23" s="36" t="n">
-        <v>7</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S23" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="T23" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>6.86</v>
       </c>
       <c r="U23" s="36" t="n">
-        <v>12.71</v>
+        <v>12.14</v>
       </c>
       <c r="V23" s="36" t="n">
-        <v>9.67</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="24">
@@ -4159,7 +4159,7 @@
         <v>7</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -4231,7 +4231,7 @@
         <v>123494931</v>
       </c>
       <c r="V6" s="40" t="n">
-        <v>50393648</v>
+        <v>86658775</v>
       </c>
     </row>
     <row r="7">
@@ -4303,7 +4303,7 @@
         <v>94534230</v>
       </c>
       <c r="V7" s="40" t="n">
-        <v>33703288</v>
+        <v>56815805</v>
       </c>
     </row>
     <row r="8">
@@ -4375,7 +4375,7 @@
         <v>67225139</v>
       </c>
       <c r="V8" s="40" t="n">
-        <v>33208704</v>
+        <v>58429601</v>
       </c>
     </row>
     <row r="9">
@@ -4447,7 +4447,7 @@
         <v>65321829</v>
       </c>
       <c r="V9" s="40" t="n">
-        <v>28211873</v>
+        <v>41433332</v>
       </c>
     </row>
     <row r="10">
@@ -4519,7 +4519,7 @@
         <v>62193580</v>
       </c>
       <c r="V10" s="40" t="n">
-        <v>20295930</v>
+        <v>31336303</v>
       </c>
     </row>
     <row r="11">
@@ -4591,7 +4591,7 @@
         <v>43378746</v>
       </c>
       <c r="V11" s="40" t="n">
-        <v>38896921</v>
+        <v>51117522</v>
       </c>
     </row>
     <row r="12">
@@ -4663,7 +4663,7 @@
         <v>59606189</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>18870804</v>
+        <v>33591231</v>
       </c>
     </row>
     <row r="13">
@@ -4735,7 +4735,7 @@
         <v>55199920</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>22754071</v>
+        <v>35604413</v>
       </c>
     </row>
     <row r="14">
@@ -4807,151 +4807,151 @@
         <v>32414171</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>18308005</v>
+        <v>28822727</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>530238</v>
+        <v>475871</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>8544625</v>
+        <v>11884771</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>8387478</v>
+        <v>10651216</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>10570508</v>
+        <v>13882033</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>11896580</v>
+        <v>17812948</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>19614352</v>
+        <v>17331854</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>20966317</v>
+        <v>26294756</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>20073400</v>
+        <v>24196222</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>23801493</v>
+        <v>22122847</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>27940611</v>
+        <v>31914115</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>27893929</v>
+        <v>32069521</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>29635773</v>
+        <v>38287475</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>19554230</v>
+        <v>28283704</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>23848495</v>
+        <v>27334091</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>24194638</v>
+        <v>36312415</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>20330094</v>
+        <v>39333565</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>26044199</v>
+        <v>28566119</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>24608772</v>
+        <v>40387845</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>28079726</v>
+        <v>39744111</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>9739595</v>
+        <v>22781810</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>475871</v>
+        <v>530238</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>11884771</v>
+        <v>8544625</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>10651216</v>
+        <v>8387478</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>13882033</v>
+        <v>10570508</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>17812948</v>
+        <v>11896580</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>17331854</v>
+        <v>19614352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>26294756</v>
+        <v>20966317</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>24196222</v>
+        <v>20073400</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>22122847</v>
+        <v>23801493</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>31914115</v>
+        <v>27940611</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>32069521</v>
+        <v>27893929</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>38287475</v>
+        <v>29635773</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>28283704</v>
+        <v>19554230</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>27334091</v>
+        <v>23848495</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>36312415</v>
+        <v>24194638</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>39333565</v>
+        <v>20330094</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>28566119</v>
+        <v>26044199</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>40387845</v>
+        <v>24608772</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>39744111</v>
+        <v>28079726</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>12971308</v>
+        <v>16109324</v>
       </c>
     </row>
     <row r="17">
@@ -5023,7 +5023,7 @@
         <v>40688796</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>15593994</v>
+        <v>22740490</v>
       </c>
     </row>
     <row r="18">
@@ -5095,7 +5095,7 @@
         <v>23835106</v>
       </c>
       <c r="V18" s="40" t="n">
-        <v>12017920</v>
+        <v>20638044</v>
       </c>
     </row>
     <row r="19">
@@ -5167,7 +5167,7 @@
         <v>24702051</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>11947180</v>
+        <v>18566429</v>
       </c>
     </row>
     <row r="20">
@@ -5239,7 +5239,7 @@
         <v>34881782</v>
       </c>
       <c r="V20" s="40" t="n">
-        <v>12177618</v>
+        <v>17556284</v>
       </c>
     </row>
     <row r="21">
@@ -5311,151 +5311,151 @@
         <v>33260760</v>
       </c>
       <c r="V21" s="40" t="n">
-        <v>12878799</v>
+        <v>18662552</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>2474409</v>
+        <v>0</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>4696696</v>
+        <v>0</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>6991878</v>
+        <v>1339100</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>4060163</v>
+        <v>5579340</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>7685466</v>
+        <v>9518200</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>10141286</v>
+        <v>11747640</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>6393871</v>
+        <v>3885270</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>4534503</v>
+        <v>8765870</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>7579040</v>
+        <v>4571680</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>9679437</v>
+        <v>3911995</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>6102368</v>
+        <v>9234090</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>4294070</v>
+        <v>5390260</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>5589419</v>
+        <v>4645370</v>
       </c>
       <c r="Q22" s="40" t="n">
-        <v>10264941</v>
+        <v>10400980</v>
       </c>
       <c r="R22" s="40" t="n">
-        <v>6114083</v>
+        <v>6123322</v>
       </c>
       <c r="S22" s="40" t="n">
-        <v>10758755</v>
+        <v>5648770</v>
       </c>
       <c r="T22" s="40" t="n">
-        <v>6048269</v>
+        <v>6880660</v>
       </c>
       <c r="U22" s="40" t="n">
-        <v>9823030</v>
+        <v>10209080</v>
       </c>
       <c r="V22" s="40" t="n">
-        <v>3383440</v>
+        <v>14739190</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>0</v>
+        <v>2474409</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>0</v>
+        <v>4696696</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>1339100</v>
+        <v>6991878</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>5579340</v>
+        <v>4060163</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>9518200</v>
+        <v>7685466</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>11747640</v>
+        <v>10141286</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>3885270</v>
+        <v>6393871</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>8765870</v>
+        <v>4534503</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>4571680</v>
+        <v>7579040</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>3911995</v>
+        <v>9679437</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>9234090</v>
+        <v>6102368</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>5390260</v>
+        <v>4294070</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>4645370</v>
+        <v>5589419</v>
       </c>
       <c r="Q23" s="40" t="n">
-        <v>10400980</v>
+        <v>10264941</v>
       </c>
       <c r="R23" s="40" t="n">
-        <v>6123322</v>
+        <v>6114083</v>
       </c>
       <c r="S23" s="40" t="n">
-        <v>5648770</v>
+        <v>10758755</v>
       </c>
       <c r="T23" s="40" t="n">
-        <v>6880660</v>
+        <v>6048269</v>
       </c>
       <c r="U23" s="40" t="n">
-        <v>10209080</v>
+        <v>9823030</v>
       </c>
       <c r="V23" s="40" t="n">
-        <v>4013700</v>
+        <v>5365390</v>
       </c>
     </row>
     <row r="24">
@@ -5877,7 +5877,7 @@
         <v>7</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -5949,7 +5949,7 @@
         <v>7</v>
       </c>
       <c r="V6" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -6021,7 +6021,7 @@
         <v>7</v>
       </c>
       <c r="V7" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -6093,7 +6093,7 @@
         <v>7</v>
       </c>
       <c r="V8" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -6165,7 +6165,7 @@
         <v>7</v>
       </c>
       <c r="V9" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -6237,7 +6237,7 @@
         <v>7</v>
       </c>
       <c r="V10" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -6309,7 +6309,7 @@
         <v>7</v>
       </c>
       <c r="V11" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -6381,7 +6381,7 @@
         <v>7</v>
       </c>
       <c r="V12" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -6453,7 +6453,7 @@
         <v>7</v>
       </c>
       <c r="V13" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -6525,18 +6525,18 @@
         <v>7</v>
       </c>
       <c r="V14" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
@@ -6597,18 +6597,18 @@
         <v>7</v>
       </c>
       <c r="V15" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -6669,7 +6669,7 @@
         <v>7</v>
       </c>
       <c r="V16" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -6741,7 +6741,7 @@
         <v>7</v>
       </c>
       <c r="V17" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -6813,7 +6813,7 @@
         <v>7</v>
       </c>
       <c r="V18" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -6885,7 +6885,7 @@
         <v>7</v>
       </c>
       <c r="V19" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -6957,7 +6957,7 @@
         <v>7</v>
       </c>
       <c r="V20" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -7029,31 +7029,31 @@
         <v>7</v>
       </c>
       <c r="V21" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F22" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" s="42" t="n">
         <v>7</v>
@@ -7074,7 +7074,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N22" s="42" t="n">
         <v>7</v>
@@ -7101,79 +7101,79 @@
         <v>7</v>
       </c>
       <c r="V22" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V23" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="G23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M23" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="N23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V23" s="42" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2121,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2146,6 +2146,7 @@
     <col width="13" customWidth="1" style="20" min="20" max="20"/>
     <col width="13" customWidth="1" style="20" min="21" max="21"/>
     <col width="13" customWidth="1" style="20" min="22" max="22"/>
+    <col width="13" customWidth="1" style="20" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2263,6 +2264,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2372,7 +2378,12 @@
       </c>
       <c r="V4" s="31" t="inlineStr">
         <is>
-          <t>07.09–13.09*</t>
+          <t>07.09–13.09</t>
+        </is>
+      </c>
+      <c r="W4" s="31" t="inlineStr">
+        <is>
+          <t>14.09–20.09</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2452,10 @@
         <v>7</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W5" s="34" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2513,7 +2527,10 @@
         <v>105.86</v>
       </c>
       <c r="V6" s="36" t="n">
-        <v>115.6</v>
+        <v>116</v>
+      </c>
+      <c r="W6" s="36" t="n">
+        <v>125.14</v>
       </c>
     </row>
     <row r="7">
@@ -2585,7 +2602,10 @@
         <v>91</v>
       </c>
       <c r="V7" s="36" t="n">
-        <v>85.2</v>
+        <v>85.43000000000001</v>
+      </c>
+      <c r="W7" s="36" t="n">
+        <v>88.56999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2657,7 +2677,10 @@
         <v>68</v>
       </c>
       <c r="V8" s="36" t="n">
-        <v>78.2</v>
+        <v>77.56999999999999</v>
+      </c>
+      <c r="W8" s="36" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -2729,7 +2752,10 @@
         <v>66.86</v>
       </c>
       <c r="V9" s="36" t="n">
-        <v>63.6</v>
+        <v>63.29</v>
+      </c>
+      <c r="W9" s="36" t="n">
+        <v>65.29000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2801,7 +2827,10 @@
         <v>48.86</v>
       </c>
       <c r="V10" s="36" t="n">
-        <v>48.6</v>
+        <v>49.57</v>
+      </c>
+      <c r="W10" s="36" t="n">
+        <v>49.86</v>
       </c>
     </row>
     <row r="11">
@@ -2873,7 +2902,10 @@
         <v>39.29</v>
       </c>
       <c r="V11" s="36" t="n">
-        <v>47.8</v>
+        <v>45.86</v>
+      </c>
+      <c r="W11" s="36" t="n">
+        <v>45.14</v>
       </c>
     </row>
     <row r="12">
@@ -2945,439 +2977,460 @@
         <v>55.29</v>
       </c>
       <c r="V12" s="36" t="n">
-        <v>47.4</v>
+        <v>46.29</v>
+      </c>
+      <c r="W12" s="36" t="n">
+        <v>43.71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>1.67</v>
+        <v>6.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>12.14</v>
+        <v>11.29</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>16.57</v>
+        <v>10.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>21</v>
+        <v>11.14</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>20.29</v>
+        <v>13.86</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>28.57</v>
+        <v>18</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>24.14</v>
+        <v>18</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>27.57</v>
+        <v>17.43</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>28.14</v>
+        <v>15.29</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.86</v>
+        <v>24.43</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>33.14</v>
+        <v>24.71</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>30.71</v>
+        <v>25.57</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>31.14</v>
+        <v>19.29</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>40.29</v>
+        <v>25.43</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>38.71</v>
+        <v>22.57</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>43.14</v>
+        <v>21.29</v>
       </c>
       <c r="T13" s="36" t="n">
-        <v>37</v>
+        <v>29.14</v>
       </c>
       <c r="U13" s="36" t="n">
-        <v>46.29</v>
+        <v>31.43</v>
       </c>
       <c r="V13" s="36" t="n">
-        <v>42.4</v>
+        <v>35.71</v>
+      </c>
+      <c r="W13" s="36" t="n">
+        <v>40.71</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>6.67</v>
+        <v>1.67</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>11.29</v>
+        <v>12.14</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>10.57</v>
+        <v>16.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>11.14</v>
+        <v>21</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>13.86</v>
+        <v>20.29</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>18</v>
+        <v>28.57</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>18</v>
+        <v>24.14</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>17.43</v>
+        <v>27.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>15.29</v>
+        <v>28.14</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>24.43</v>
+        <v>28.86</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>24.71</v>
+        <v>33.14</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>25.57</v>
+        <v>30.71</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>19.29</v>
+        <v>31.14</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>25.43</v>
+        <v>40.29</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>22.57</v>
+        <v>38.71</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>21.29</v>
+        <v>43.14</v>
       </c>
       <c r="T14" s="36" t="n">
-        <v>29.14</v>
+        <v>37</v>
       </c>
       <c r="U14" s="36" t="n">
-        <v>31.43</v>
+        <v>46.29</v>
       </c>
       <c r="V14" s="36" t="n">
-        <v>33.6</v>
+        <v>43.14</v>
+      </c>
+      <c r="W14" s="36" t="n">
+        <v>36.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.43</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>12.43</v>
+        <v>11</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13.29</v>
+        <v>14.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>14.71</v>
+        <v>11.86</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.71</v>
+        <v>19.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>17.71</v>
+        <v>21</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>19.57</v>
+        <v>23.43</v>
       </c>
       <c r="L15" s="36" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="M15" s="36" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="N15" s="36" t="n">
         <v>24.14</v>
       </c>
-      <c r="M15" s="36" t="n">
+      <c r="O15" s="36" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="P15" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q15" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="R15" s="36" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="S15" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="T15" s="36" t="n">
         <v>27.57</v>
       </c>
-      <c r="N15" s="36" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="O15" s="36" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="P15" s="36" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="Q15" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="R15" s="36" t="n">
-        <v>29</v>
-      </c>
-      <c r="S15" s="36" t="n">
-        <v>27.71</v>
-      </c>
-      <c r="T15" s="36" t="n">
-        <v>32.57</v>
-      </c>
       <c r="U15" s="36" t="n">
-        <v>31.57</v>
+        <v>30</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>30.6</v>
+        <v>28.57</v>
+      </c>
+      <c r="W15" s="36" t="n">
+        <v>30.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11</v>
+        <v>12.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>14.43</v>
+        <v>13.29</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>11.86</v>
+        <v>14.71</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>19.14</v>
+        <v>19.71</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>21</v>
+        <v>17.71</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>23.43</v>
+        <v>19.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>20.43</v>
+        <v>24.14</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>24.57</v>
+        <v>27.57</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>24.14</v>
+        <v>24.43</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>24.43</v>
+        <v>27.29</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>22</v>
+        <v>26.57</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>23</v>
+        <v>25.57</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>18.43</v>
+        <v>29</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>24.71</v>
+        <v>27.71</v>
       </c>
       <c r="T16" s="36" t="n">
-        <v>27.57</v>
+        <v>32.57</v>
       </c>
       <c r="U16" s="36" t="n">
-        <v>30</v>
+        <v>31.57</v>
       </c>
       <c r="V16" s="36" t="n">
-        <v>30.6</v>
+        <v>29.57</v>
+      </c>
+      <c r="W16" s="36" t="n">
+        <v>29.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>6.43</v>
+        <v>7.14</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>13.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>12.71</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14</v>
+        <v>14.43</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.14</v>
+        <v>19</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>16.14</v>
+        <v>21.14</v>
       </c>
       <c r="K17" s="36" t="n">
         <v>18.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.14</v>
+        <v>16.57</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>21.71</v>
+        <v>14.71</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>20.86</v>
+        <v>19.14</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>20.86</v>
+        <v>18</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>21.86</v>
+        <v>15.29</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>28.71</v>
+        <v>15.29</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>24.71</v>
+        <v>18.71</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>24.57</v>
+        <v>18</v>
       </c>
       <c r="T17" s="36" t="n">
         <v>25.29</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>26.71</v>
+        <v>28.86</v>
       </c>
       <c r="V17" s="36" t="n">
-        <v>29.8</v>
+        <v>24</v>
+      </c>
+      <c r="W17" s="36" t="n">
+        <v>29.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>7</v>
+        <v>3.33</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>16</v>
+        <v>6.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>19.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>15.86</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>14.86</v>
+        <v>14</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>16.71</v>
+        <v>17.14</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>19.71</v>
+        <v>16.14</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>16.86</v>
+        <v>18.57</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>24.86</v>
+        <v>16.14</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>23.43</v>
+        <v>21.71</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>19.43</v>
+        <v>20.86</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>25.57</v>
+        <v>20.86</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>27.43</v>
+        <v>21.86</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>29.14</v>
+        <v>28.71</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>25</v>
+        <v>24.71</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>29.57</v>
+        <v>24.57</v>
       </c>
       <c r="T18" s="36" t="n">
-        <v>29.43</v>
+        <v>25.29</v>
       </c>
       <c r="U18" s="36" t="n">
-        <v>21</v>
+        <v>26.71</v>
       </c>
       <c r="V18" s="36" t="n">
-        <v>27.8</v>
+        <v>27.57</v>
+      </c>
+      <c r="W18" s="36" t="n">
+        <v>28.29</v>
       </c>
     </row>
     <row r="19">
@@ -3449,79 +3502,85 @@
         <v>25.14</v>
       </c>
       <c r="V19" s="36" t="n">
-        <v>24.4</v>
+        <v>23.57</v>
+      </c>
+      <c r="W19" s="36" t="n">
+        <v>26.29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>7.14</v>
+        <v>16</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>13.43</v>
+        <v>19.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>12.71</v>
+        <v>15.86</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>14.43</v>
+        <v>14.86</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>19</v>
+        <v>16.71</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>21.14</v>
+        <v>19.71</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>18.57</v>
+        <v>16.86</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>16.57</v>
+        <v>24.86</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>14.71</v>
+        <v>23.43</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>19.14</v>
+        <v>19.43</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>18</v>
+        <v>25.57</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>15.29</v>
+        <v>27.43</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>15.29</v>
+        <v>29.14</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>18.71</v>
+        <v>25</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>18</v>
+        <v>29.57</v>
       </c>
       <c r="T20" s="36" t="n">
-        <v>25.29</v>
+        <v>29.43</v>
       </c>
       <c r="U20" s="36" t="n">
-        <v>28.86</v>
+        <v>21</v>
       </c>
       <c r="V20" s="36" t="n">
-        <v>21.8</v>
+        <v>27.14</v>
+      </c>
+      <c r="W20" s="36" t="n">
+        <v>25.57</v>
       </c>
     </row>
     <row r="21">
@@ -3593,151 +3652,160 @@
         <v>27.29</v>
       </c>
       <c r="V21" s="36" t="n">
-        <v>16.6</v>
+        <v>17.14</v>
+      </c>
+      <c r="W21" s="36" t="n">
+        <v>22.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>2.8</v>
+        <v>5.14</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>4</v>
+        <v>5.29</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>6</v>
+        <v>7.86</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>4.43</v>
+        <v>7.14</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>3.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>5.86</v>
+        <v>7.14</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>5.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>7.43</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O22" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P22" s="36" t="n">
-        <v>7.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q22" s="36" t="n">
-        <v>10.29</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="R22" s="36" t="n">
-        <v>7</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S22" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="T22" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>6.86</v>
       </c>
       <c r="U22" s="36" t="n">
-        <v>12.71</v>
+        <v>12.14</v>
       </c>
       <c r="V22" s="36" t="n">
-        <v>9.800000000000001</v>
+        <v>8.140000000000001</v>
+      </c>
+      <c r="W22" s="36" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G23" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="36" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G23" s="36" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H23" s="36" t="n">
-        <v>7.86</v>
+        <v>6</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>7.14</v>
+        <v>4.43</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>7.14</v>
+        <v>5.86</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>6</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>8.710000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="O23" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="Q23" s="36" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="R23" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="R23" s="36" t="n">
+      <c r="T23" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="S23" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="T23" s="36" t="n">
-        <v>6.86</v>
-      </c>
       <c r="U23" s="36" t="n">
-        <v>12.14</v>
+        <v>12.71</v>
       </c>
       <c r="V23" s="36" t="n">
-        <v>8.6</v>
+        <v>9.57</v>
+      </c>
+      <c r="W23" s="36" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -3825,6 +3893,10 @@
       </c>
       <c r="V24" s="39">
         <f>AVERAGE(V6:V23)</f>
+        <v/>
+      </c>
+      <c r="W24" s="39">
+        <f>AVERAGE(W6:W23)</f>
         <v/>
       </c>
     </row>
@@ -3839,7 +3911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3864,6 +3936,7 @@
     <col width="13" customWidth="1" style="20" min="20" max="20"/>
     <col width="13" customWidth="1" style="20" min="21" max="21"/>
     <col width="13" customWidth="1" style="20" min="22" max="22"/>
+    <col width="13" customWidth="1" style="20" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3981,6 +4054,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -4090,7 +4168,12 @@
       </c>
       <c r="V4" s="31" t="inlineStr">
         <is>
-          <t>07.09–13.09*</t>
+          <t>07.09–13.09</t>
+        </is>
+      </c>
+      <c r="W4" s="31" t="inlineStr">
+        <is>
+          <t>14.09–20.09</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4242,10 @@
         <v>7</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W5" s="34" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -4231,7 +4317,10 @@
         <v>123494931</v>
       </c>
       <c r="V6" s="40" t="n">
-        <v>86658775</v>
+        <v>117613634</v>
+      </c>
+      <c r="W6" s="40" t="n">
+        <v>129454842</v>
       </c>
     </row>
     <row r="7">
@@ -4303,7 +4392,10 @@
         <v>94534230</v>
       </c>
       <c r="V7" s="40" t="n">
-        <v>56815805</v>
+        <v>81100625</v>
+      </c>
+      <c r="W7" s="40" t="n">
+        <v>109654171</v>
       </c>
     </row>
     <row r="8">
@@ -4375,7 +4467,10 @@
         <v>67225139</v>
       </c>
       <c r="V8" s="40" t="n">
-        <v>58429601</v>
+        <v>80820230</v>
+      </c>
+      <c r="W8" s="40" t="n">
+        <v>73904849</v>
       </c>
     </row>
     <row r="9">
@@ -4447,7 +4542,10 @@
         <v>65321829</v>
       </c>
       <c r="V9" s="40" t="n">
-        <v>41433332</v>
+        <v>57895664</v>
+      </c>
+      <c r="W9" s="40" t="n">
+        <v>63196973</v>
       </c>
     </row>
     <row r="10">
@@ -4519,7 +4617,10 @@
         <v>62193580</v>
       </c>
       <c r="V10" s="40" t="n">
-        <v>31336303</v>
+        <v>45202354</v>
+      </c>
+      <c r="W10" s="40" t="n">
+        <v>45317128</v>
       </c>
     </row>
     <row r="11">
@@ -4591,7 +4692,10 @@
         <v>43378746</v>
       </c>
       <c r="V11" s="40" t="n">
-        <v>51117522</v>
+        <v>67522298</v>
+      </c>
+      <c r="W11" s="40" t="n">
+        <v>44905121</v>
       </c>
     </row>
     <row r="12">
@@ -4663,439 +4767,460 @@
         <v>59606189</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>33591231</v>
+        <v>50164748</v>
+      </c>
+      <c r="W12" s="40" t="n">
+        <v>46095774</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>536260</v>
+        <v>5092853</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>14403556</v>
+        <v>11100161</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>16216832</v>
+        <v>14612055</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>32622053</v>
+        <v>20638987</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>23929705</v>
+        <v>14061352</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37214538</v>
+        <v>31599148</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25375430</v>
+        <v>18747614</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>31500087</v>
+        <v>19576415</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28078687</v>
+        <v>14226838</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>34472458</v>
+        <v>23197145</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>35343350</v>
+        <v>25790711</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>51225290</v>
+        <v>27856115</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>36142612</v>
+        <v>20981901</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>47488940</v>
+        <v>25433123</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>44805002</v>
+        <v>19355230</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>43327432</v>
+        <v>24713836</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>39637968</v>
+        <v>20195634</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>55199920</v>
+        <v>32414171</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>35604413</v>
+        <v>42780769</v>
+      </c>
+      <c r="W13" s="40" t="n">
+        <v>36755122</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>5092853</v>
+        <v>536260</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>11100161</v>
+        <v>14403556</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>14612055</v>
+        <v>16216832</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>20638987</v>
+        <v>32622053</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>14061352</v>
+        <v>23929705</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>31599148</v>
+        <v>37214538</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>18747614</v>
+        <v>25375430</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>19576415</v>
+        <v>31500087</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>14226838</v>
+        <v>28078687</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>23197145</v>
+        <v>34472458</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>25790711</v>
+        <v>35343350</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>27856115</v>
+        <v>51225290</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>20981901</v>
+        <v>36142612</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>25433123</v>
+        <v>47488940</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>19355230</v>
+        <v>44805002</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>24713836</v>
+        <v>43327432</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>20195634</v>
+        <v>39637968</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>32414171</v>
+        <v>55199920</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>28822727</v>
+        <v>50680631</v>
+      </c>
+      <c r="W14" s="40" t="n">
+        <v>50163008</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>475871</v>
+        <v>530238</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>11884771</v>
+        <v>8544625</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>10651216</v>
+        <v>8387478</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>13882033</v>
+        <v>10570508</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>17812948</v>
+        <v>11896580</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>17331854</v>
+        <v>19614352</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>26294756</v>
+        <v>20966317</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>24196222</v>
+        <v>20073400</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>22122847</v>
+        <v>23801493</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>31914115</v>
+        <v>27940611</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>32069521</v>
+        <v>27893929</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>38287475</v>
+        <v>29635773</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>28283704</v>
+        <v>19554230</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>27334091</v>
+        <v>23848495</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>36312415</v>
+        <v>24194638</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>39333565</v>
+        <v>20330094</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>28566119</v>
+        <v>26044199</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>40387845</v>
+        <v>24608772</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>39744111</v>
+        <v>28079726</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>22781810</v>
+        <v>20968052</v>
+      </c>
+      <c r="W15" s="40" t="n">
+        <v>29501132</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>530238</v>
+        <v>475871</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>8544625</v>
+        <v>11884771</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>8387478</v>
+        <v>10651216</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>10570508</v>
+        <v>13882033</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>11896580</v>
+        <v>17812948</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>19614352</v>
+        <v>17331854</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>20966317</v>
+        <v>26294756</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>20073400</v>
+        <v>24196222</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>23801493</v>
+        <v>22122847</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>27940611</v>
+        <v>31914115</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>27893929</v>
+        <v>32069521</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>29635773</v>
+        <v>38287475</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>19554230</v>
+        <v>28283704</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>23848495</v>
+        <v>27334091</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>24194638</v>
+        <v>36312415</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>20330094</v>
+        <v>39333565</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>26044199</v>
+        <v>28566119</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>24608772</v>
+        <v>40387845</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>28079726</v>
+        <v>39744111</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>16109324</v>
+        <v>31477917</v>
+      </c>
+      <c r="W16" s="40" t="n">
+        <v>29910767</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3249588</v>
+        <v>3337146</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>7305524</v>
+        <v>10420206</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>9575225</v>
+        <v>21387685</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>9264589</v>
+        <v>16050448</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>20692424</v>
+        <v>21568794</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>27565767</v>
+        <v>30845816</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>19138015</v>
+        <v>45285935</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>24912292</v>
+        <v>28941455</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>19068954</v>
+        <v>21801828</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>25387051</v>
+        <v>19628570</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>21008637</v>
+        <v>23276090</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>30862574</v>
+        <v>27906254</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>31820447</v>
+        <v>20822247</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>31875986</v>
+        <v>20014322</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>48358034</v>
+        <v>19159625</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>30000524</v>
+        <v>22535696</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>31150016</v>
+        <v>21412810</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>40688796</v>
+        <v>34881782</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>22740490</v>
+        <v>25904024</v>
+      </c>
+      <c r="W17" s="40" t="n">
+        <v>46961904</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>6239584</v>
+        <v>3249588</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>13803407</v>
+        <v>7305524</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>28572076</v>
+        <v>9575225</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>15282581</v>
+        <v>9264589</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>16594572</v>
+        <v>20692424</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>15223898</v>
+        <v>27565767</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>27696695</v>
+        <v>19138015</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>17717888</v>
+        <v>24912292</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>24163432</v>
+        <v>19068954</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>23623477</v>
+        <v>25387051</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>19145601</v>
+        <v>21008637</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>30157601</v>
+        <v>30862574</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>41172333</v>
+        <v>31820447</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>34303423</v>
+        <v>31875986</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>35044850</v>
+        <v>48358034</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>33519824</v>
+        <v>30000524</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>25969876</v>
+        <v>31150016</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>23835106</v>
+        <v>40688796</v>
       </c>
       <c r="V18" s="40" t="n">
-        <v>20638044</v>
+        <v>31752550</v>
+      </c>
+      <c r="W18" s="40" t="n">
+        <v>32778027</v>
       </c>
     </row>
     <row r="19">
@@ -5167,79 +5292,85 @@
         <v>24702051</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>18566429</v>
+        <v>26856647</v>
+      </c>
+      <c r="W19" s="40" t="n">
+        <v>27122255</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>3337146</v>
+        <v>6239584</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>10420206</v>
+        <v>13803407</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>21387685</v>
+        <v>28572076</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>16050448</v>
+        <v>15282581</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>21568794</v>
+        <v>16594572</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>30845816</v>
+        <v>15223898</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>45285935</v>
+        <v>27696695</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>28941455</v>
+        <v>17717888</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>21801828</v>
+        <v>24163432</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>19628570</v>
+        <v>23623477</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>23276090</v>
+        <v>19145601</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>27906254</v>
+        <v>30157601</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>20822247</v>
+        <v>41172333</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>20014322</v>
+        <v>34303423</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>19159625</v>
+        <v>35044850</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>22535696</v>
+        <v>33519824</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>21412810</v>
+        <v>25969876</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>34881782</v>
+        <v>23835106</v>
       </c>
       <c r="V20" s="40" t="n">
-        <v>17556284</v>
+        <v>27833047</v>
+      </c>
+      <c r="W20" s="40" t="n">
+        <v>22815382</v>
       </c>
     </row>
     <row r="21">
@@ -5311,151 +5442,160 @@
         <v>33260760</v>
       </c>
       <c r="V21" s="40" t="n">
-        <v>18662552</v>
+        <v>23559262</v>
+      </c>
+      <c r="W21" s="40" t="n">
+        <v>29206004</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>0</v>
+        <v>2474409</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>0</v>
+        <v>4696696</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>1339100</v>
+        <v>6991878</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>5579340</v>
+        <v>4060163</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>9518200</v>
+        <v>7685466</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>11747640</v>
+        <v>10141286</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>3885270</v>
+        <v>6393871</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>8765870</v>
+        <v>4534503</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>4571680</v>
+        <v>7579040</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>3911995</v>
+        <v>9679437</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>9234090</v>
+        <v>6102368</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>5390260</v>
+        <v>4294070</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>4645370</v>
+        <v>5589419</v>
       </c>
       <c r="Q22" s="40" t="n">
-        <v>10400980</v>
+        <v>10264941</v>
       </c>
       <c r="R22" s="40" t="n">
-        <v>6123322</v>
+        <v>6114083</v>
       </c>
       <c r="S22" s="40" t="n">
-        <v>5648770</v>
+        <v>10758755</v>
       </c>
       <c r="T22" s="40" t="n">
-        <v>6880660</v>
+        <v>6048269</v>
       </c>
       <c r="U22" s="40" t="n">
-        <v>10209080</v>
+        <v>9823030</v>
       </c>
       <c r="V22" s="40" t="n">
-        <v>14739190</v>
+        <v>7263590</v>
+      </c>
+      <c r="W22" s="40" t="n">
+        <v>14940492</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>2474409</v>
+        <v>0</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>4696696</v>
+        <v>0</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>6991878</v>
+        <v>1339100</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>4060163</v>
+        <v>5579340</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>7685466</v>
+        <v>9518200</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>10141286</v>
+        <v>11747640</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>6393871</v>
+        <v>3885270</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>4534503</v>
+        <v>8765870</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>7579040</v>
+        <v>4571680</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>9679437</v>
+        <v>3911995</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>6102368</v>
+        <v>9234090</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>4294070</v>
+        <v>5390260</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>5589419</v>
+        <v>4645370</v>
       </c>
       <c r="Q23" s="40" t="n">
-        <v>10264941</v>
+        <v>10400980</v>
       </c>
       <c r="R23" s="40" t="n">
-        <v>6114083</v>
+        <v>6123322</v>
       </c>
       <c r="S23" s="40" t="n">
-        <v>10758755</v>
+        <v>5648770</v>
       </c>
       <c r="T23" s="40" t="n">
-        <v>6048269</v>
+        <v>6880660</v>
       </c>
       <c r="U23" s="40" t="n">
-        <v>9823030</v>
+        <v>10209080</v>
       </c>
       <c r="V23" s="40" t="n">
-        <v>5365390</v>
+        <v>17909229</v>
+      </c>
+      <c r="W23" s="40" t="n">
+        <v>9500343</v>
       </c>
     </row>
     <row r="24">
@@ -5543,6 +5683,10 @@
       </c>
       <c r="V24" s="41">
         <f>AVERAGE(V6:V23)</f>
+        <v/>
+      </c>
+      <c r="W24" s="41">
+        <f>AVERAGE(W6:W23)</f>
         <v/>
       </c>
     </row>
@@ -5557,7 +5701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -5582,6 +5726,7 @@
     <col width="13" customWidth="1" style="20" min="20" max="20"/>
     <col width="13" customWidth="1" style="20" min="21" max="21"/>
     <col width="13" customWidth="1" style="20" min="22" max="22"/>
+    <col width="13" customWidth="1" style="20" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5699,6 +5844,11 @@
           <t>2026-09-07</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -5808,7 +5958,12 @@
       </c>
       <c r="V4" s="31" t="inlineStr">
         <is>
-          <t>07.09–13.09*</t>
+          <t>07.09–13.09</t>
+        </is>
+      </c>
+      <c r="W4" s="31" t="inlineStr">
+        <is>
+          <t>14.09–20.09</t>
         </is>
       </c>
     </row>
@@ -5877,7 +6032,10 @@
         <v>7</v>
       </c>
       <c r="V5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W5" s="34" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -5949,7 +6107,10 @@
         <v>7</v>
       </c>
       <c r="V6" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W6" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -6021,7 +6182,10 @@
         <v>7</v>
       </c>
       <c r="V7" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W7" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -6093,7 +6257,10 @@
         <v>7</v>
       </c>
       <c r="V8" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W8" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -6165,7 +6332,10 @@
         <v>7</v>
       </c>
       <c r="V9" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W9" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -6237,7 +6407,10 @@
         <v>7</v>
       </c>
       <c r="V10" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W10" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -6309,7 +6482,10 @@
         <v>7</v>
       </c>
       <c r="V11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W11" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -6381,25 +6557,28 @@
         <v>7</v>
       </c>
       <c r="V12" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W12" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -6453,25 +6632,28 @@
         <v>7</v>
       </c>
       <c r="V13" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W13" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -6525,18 +6707,21 @@
         <v>7</v>
       </c>
       <c r="V14" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W14" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
@@ -6597,18 +6782,21 @@
         <v>7</v>
       </c>
       <c r="V15" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W15" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -6669,25 +6857,28 @@
         <v>7</v>
       </c>
       <c r="V16" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W16" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -6741,25 +6932,28 @@
         <v>7</v>
       </c>
       <c r="V17" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W17" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -6813,7 +7007,10 @@
         <v>7</v>
       </c>
       <c r="V18" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W18" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -6885,25 +7082,28 @@
         <v>7</v>
       </c>
       <c r="V19" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W19" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>7</v>
@@ -6957,7 +7157,10 @@
         <v>7</v>
       </c>
       <c r="V20" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W20" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -7029,31 +7232,34 @@
         <v>7</v>
       </c>
       <c r="V21" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W21" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F22" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G22" s="42" t="n">
         <v>7</v>
@@ -7074,7 +7280,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N22" s="42" t="n">
         <v>7</v>
@@ -7101,31 +7307,34 @@
         <v>7</v>
       </c>
       <c r="V22" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W22" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F23" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G23" s="42" t="n">
         <v>7</v>
@@ -7146,7 +7355,7 @@
         <v>7</v>
       </c>
       <c r="M23" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N23" s="42" t="n">
         <v>7</v>
@@ -7173,7 +7382,10 @@
         <v>7</v>
       </c>
       <c r="V23" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
+      </c>
+      <c r="W23" s="42" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -7263,6 +7475,10 @@
         <f>AVERAGE(V6:V23)</f>
         <v/>
       </c>
+      <c r="W24" s="43">
+        <f>AVERAGE(W6:W23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2121,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2147,6 +2147,7 @@
     <col width="13" customWidth="1" style="20" min="21" max="21"/>
     <col width="13" customWidth="1" style="20" min="22" max="22"/>
     <col width="13" customWidth="1" style="20" min="23" max="23"/>
+    <col width="13" customWidth="1" style="20" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2269,6 +2270,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2384,6 +2390,11 @@
       <c r="W4" s="31" t="inlineStr">
         <is>
           <t>14.09–20.09</t>
+        </is>
+      </c>
+      <c r="X4" s="31" t="inlineStr">
+        <is>
+          <t>21.09–27.09*</t>
         </is>
       </c>
     </row>
@@ -2457,6 +2468,9 @@
       <c r="W5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="X5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -2532,6 +2546,9 @@
       <c r="W6" s="36" t="n">
         <v>125.14</v>
       </c>
+      <c r="X6" s="36" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -2607,6 +2624,9 @@
       <c r="W7" s="36" t="n">
         <v>88.56999999999999</v>
       </c>
+      <c r="X7" s="36" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -2682,6 +2702,9 @@
       <c r="W8" s="36" t="n">
         <v>71</v>
       </c>
+      <c r="X8" s="36" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -2757,6 +2780,9 @@
       <c r="W9" s="36" t="n">
         <v>65.29000000000001</v>
       </c>
+      <c r="X9" s="36" t="n">
+        <v>77</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -2832,230 +2858,242 @@
       <c r="W10" s="36" t="n">
         <v>49.86</v>
       </c>
+      <c r="X10" s="36" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>8.43</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>13.43</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>21.71</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>16.57</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>21.29</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>21.14</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>23.29</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>22.43</v>
+        <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>22.43</v>
+        <v>40</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>28.14</v>
+        <v>42.43</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>31.14</v>
+        <v>38.57</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>30</v>
+        <v>34.29</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>30.43</v>
+        <v>37.86</v>
       </c>
       <c r="Q11" s="36" t="n">
-        <v>31.29</v>
+        <v>42.86</v>
       </c>
       <c r="R11" s="36" t="n">
-        <v>36.14</v>
+        <v>40.71</v>
       </c>
       <c r="S11" s="36" t="n">
-        <v>31</v>
+        <v>45.43</v>
       </c>
       <c r="T11" s="36" t="n">
-        <v>37.71</v>
+        <v>44.57</v>
       </c>
       <c r="U11" s="36" t="n">
-        <v>39.29</v>
+        <v>55.29</v>
       </c>
       <c r="V11" s="36" t="n">
-        <v>45.86</v>
+        <v>46.29</v>
       </c>
       <c r="W11" s="36" t="n">
-        <v>45.14</v>
+        <v>43.71</v>
+      </c>
+      <c r="X11" s="36" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>8</v>
+        <v>11.29</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>13.14</v>
+        <v>10.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>19.43</v>
+        <v>11.14</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>26.43</v>
+        <v>13.86</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>32.29</v>
+        <v>18</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>31.29</v>
+        <v>18</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>33.57</v>
+        <v>17.43</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>40</v>
+        <v>15.29</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>42.43</v>
+        <v>24.43</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>38.57</v>
+        <v>24.71</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>34.29</v>
+        <v>25.57</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>37.86</v>
+        <v>19.29</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>42.86</v>
+        <v>25.43</v>
       </c>
       <c r="R12" s="36" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="S12" s="36" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="T12" s="36" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="U12" s="36" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="V12" s="36" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="W12" s="36" t="n">
         <v>40.71</v>
       </c>
-      <c r="S12" s="36" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="T12" s="36" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="U12" s="36" t="n">
-        <v>55.29</v>
-      </c>
-      <c r="V12" s="36" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="W12" s="36" t="n">
-        <v>43.71</v>
+      <c r="X12" s="36" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>6.67</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>11.29</v>
+        <v>11</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>10.57</v>
+        <v>14.43</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>11.14</v>
+        <v>11.86</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>13.86</v>
+        <v>18</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>18</v>
+        <v>19.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>17.43</v>
+        <v>23.43</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>15.29</v>
+        <v>20.43</v>
       </c>
       <c r="M13" s="36" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="N13" s="36" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="O13" s="36" t="n">
         <v>24.43</v>
       </c>
-      <c r="N13" s="36" t="n">
+      <c r="P13" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q13" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="R13" s="36" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="S13" s="36" t="n">
         <v>24.71</v>
       </c>
-      <c r="O13" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="P13" s="36" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="Q13" s="36" t="n">
-        <v>25.43</v>
-      </c>
-      <c r="R13" s="36" t="n">
-        <v>22.57</v>
-      </c>
-      <c r="S13" s="36" t="n">
-        <v>21.29</v>
-      </c>
       <c r="T13" s="36" t="n">
-        <v>29.14</v>
+        <v>27.57</v>
       </c>
       <c r="U13" s="36" t="n">
-        <v>31.43</v>
+        <v>30</v>
       </c>
       <c r="V13" s="36" t="n">
-        <v>35.71</v>
+        <v>28.57</v>
       </c>
       <c r="W13" s="36" t="n">
-        <v>40.71</v>
+        <v>30.14</v>
+      </c>
+      <c r="X13" s="36" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -3132,455 +3170,476 @@
       <c r="W14" s="36" t="n">
         <v>36.86</v>
       </c>
+      <c r="X14" s="36" t="n">
+        <v>48</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>11</v>
+        <v>13.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>14.43</v>
+        <v>21.71</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>11.86</v>
+        <v>16.57</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>18</v>
+        <v>21.29</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.14</v>
+        <v>21.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>21</v>
+        <v>23.29</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>23.43</v>
+        <v>22.43</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>20.43</v>
+        <v>22.43</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>24.57</v>
+        <v>28.14</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>24.14</v>
+        <v>31.14</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>24.43</v>
+        <v>30</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>22</v>
+        <v>30.43</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>23</v>
+        <v>31.29</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>18.43</v>
+        <v>36.14</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>24.71</v>
+        <v>31</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>27.57</v>
+        <v>37.71</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>30</v>
+        <v>39.29</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>28.57</v>
+        <v>45.86</v>
       </c>
       <c r="W15" s="36" t="n">
-        <v>30.14</v>
+        <v>45.14</v>
+      </c>
+      <c r="X15" s="36" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.43</v>
+        <v>7</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>12.43</v>
+        <v>16</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.29</v>
+        <v>19.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>14.71</v>
+        <v>15.86</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>17</v>
+        <v>14.86</v>
       </c>
       <c r="I16" s="36" t="n">
+        <v>16.71</v>
+      </c>
+      <c r="J16" s="36" t="n">
         <v>19.71</v>
       </c>
-      <c r="J16" s="36" t="n">
-        <v>17.71</v>
-      </c>
       <c r="K16" s="36" t="n">
-        <v>19.57</v>
+        <v>16.86</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>24.14</v>
+        <v>24.86</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>27.57</v>
+        <v>23.43</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>24.43</v>
+        <v>19.43</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>27.29</v>
+        <v>25.57</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>26.57</v>
+        <v>27.43</v>
       </c>
       <c r="Q16" s="36" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="R16" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="S16" s="36" t="n">
+        <v>29.57</v>
+      </c>
+      <c r="T16" s="36" t="n">
+        <v>29.43</v>
+      </c>
+      <c r="U16" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="V16" s="36" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="W16" s="36" t="n">
         <v>25.57</v>
       </c>
-      <c r="R16" s="36" t="n">
-        <v>29</v>
-      </c>
-      <c r="S16" s="36" t="n">
-        <v>27.71</v>
-      </c>
-      <c r="T16" s="36" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="U16" s="36" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="V16" s="36" t="n">
-        <v>29.57</v>
-      </c>
-      <c r="W16" s="36" t="n">
-        <v>29.86</v>
+      <c r="X16" s="36" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.43</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>12.71</v>
+        <v>3.33</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.43</v>
+        <v>11.71</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19</v>
+        <v>17.57</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21.14</v>
+        <v>20.43</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>18.57</v>
+        <v>21.71</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.57</v>
+        <v>15</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>14.71</v>
+        <v>22.71</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>19.14</v>
+        <v>22.43</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>18</v>
+        <v>20.14</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>15.29</v>
+        <v>15.71</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>15.29</v>
+        <v>19.43</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>18.71</v>
+        <v>20.29</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>18</v>
+        <v>22.29</v>
       </c>
       <c r="T17" s="36" t="n">
-        <v>25.29</v>
+        <v>21.29</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>28.86</v>
+        <v>25.14</v>
       </c>
       <c r="V17" s="36" t="n">
-        <v>24</v>
+        <v>23.57</v>
       </c>
       <c r="W17" s="36" t="n">
-        <v>29.29</v>
+        <v>26.29</v>
+      </c>
+      <c r="X17" s="36" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>3.33</v>
+        <v>9.43</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>6.43</v>
+        <v>12.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.14</v>
+        <v>19.71</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>16.14</v>
+        <v>17.71</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>18.57</v>
+        <v>19.57</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>16.14</v>
+        <v>24.14</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>21.71</v>
+        <v>27.57</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>20.86</v>
+        <v>24.43</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>20.86</v>
+        <v>27.29</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>21.86</v>
+        <v>26.57</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>28.71</v>
+        <v>25.57</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>24.71</v>
+        <v>29</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>24.57</v>
+        <v>27.71</v>
       </c>
       <c r="T18" s="36" t="n">
-        <v>25.29</v>
+        <v>32.57</v>
       </c>
       <c r="U18" s="36" t="n">
-        <v>26.71</v>
+        <v>31.57</v>
       </c>
       <c r="V18" s="36" t="n">
-        <v>27.57</v>
+        <v>29.57</v>
       </c>
       <c r="W18" s="36" t="n">
-        <v>28.29</v>
+        <v>29.86</v>
+      </c>
+      <c r="X18" s="36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>0.5</v>
+        <v>13.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>3.33</v>
+        <v>12.71</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>11.71</v>
+        <v>14.43</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.57</v>
+        <v>19</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>20.43</v>
+        <v>21.14</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>21.71</v>
+        <v>18.57</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>15</v>
+        <v>16.57</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>22.71</v>
+        <v>14.71</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>22.43</v>
+        <v>19.14</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>20.14</v>
+        <v>18</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>15.71</v>
+        <v>15.29</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>19.43</v>
+        <v>15.29</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>20.29</v>
+        <v>18.71</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>22.29</v>
+        <v>18</v>
       </c>
       <c r="T19" s="36" t="n">
-        <v>21.29</v>
+        <v>25.29</v>
       </c>
       <c r="U19" s="36" t="n">
-        <v>25.14</v>
+        <v>28.86</v>
       </c>
       <c r="V19" s="36" t="n">
-        <v>23.57</v>
+        <v>24</v>
       </c>
       <c r="W19" s="36" t="n">
-        <v>26.29</v>
+        <v>29.29</v>
+      </c>
+      <c r="X19" s="36" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>7</v>
+        <v>3.33</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>16</v>
+        <v>6.43</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>19.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>15.86</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>14.86</v>
+        <v>14</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>16.71</v>
+        <v>17.14</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>19.71</v>
+        <v>16.14</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>16.86</v>
+        <v>18.57</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>24.86</v>
+        <v>16.14</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>23.43</v>
+        <v>21.71</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>19.43</v>
+        <v>20.86</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>25.57</v>
+        <v>20.86</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>27.43</v>
+        <v>21.86</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>29.14</v>
+        <v>28.71</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>25</v>
+        <v>24.71</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>29.57</v>
+        <v>24.57</v>
       </c>
       <c r="T20" s="36" t="n">
-        <v>29.43</v>
+        <v>25.29</v>
       </c>
       <c r="U20" s="36" t="n">
-        <v>21</v>
+        <v>26.71</v>
       </c>
       <c r="V20" s="36" t="n">
-        <v>27.14</v>
+        <v>27.57</v>
       </c>
       <c r="W20" s="36" t="n">
-        <v>25.57</v>
+        <v>28.29</v>
+      </c>
+      <c r="X20" s="36" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -3657,6 +3716,9 @@
       <c r="W21" s="36" t="n">
         <v>22.14</v>
       </c>
+      <c r="X21" s="36" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -3732,6 +3794,9 @@
       <c r="W22" s="36" t="n">
         <v>13</v>
       </c>
+      <c r="X22" s="36" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -3806,6 +3871,9 @@
       </c>
       <c r="W23" s="36" t="n">
         <v>11</v>
+      </c>
+      <c r="X23" s="36" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -3897,6 +3965,10 @@
       </c>
       <c r="W24" s="39">
         <f>AVERAGE(W6:W23)</f>
+        <v/>
+      </c>
+      <c r="X24" s="39">
+        <f>AVERAGE(X6:X23)</f>
         <v/>
       </c>
     </row>
@@ -3911,7 +3983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -3937,6 +4009,7 @@
     <col width="13" customWidth="1" style="20" min="21" max="21"/>
     <col width="13" customWidth="1" style="20" min="22" max="22"/>
     <col width="13" customWidth="1" style="20" min="23" max="23"/>
+    <col width="13" customWidth="1" style="20" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4059,6 +4132,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -4174,6 +4252,11 @@
       <c r="W4" s="31" t="inlineStr">
         <is>
           <t>14.09–20.09</t>
+        </is>
+      </c>
+      <c r="X4" s="31" t="inlineStr">
+        <is>
+          <t>21.09–27.09*</t>
         </is>
       </c>
     </row>
@@ -4247,6 +4330,9 @@
       <c r="W5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="X5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -4322,6 +4408,9 @@
       <c r="W6" s="40" t="n">
         <v>129454842</v>
       </c>
+      <c r="X6" s="40" t="n">
+        <v>15718036</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -4397,6 +4486,9 @@
       <c r="W7" s="40" t="n">
         <v>109654171</v>
       </c>
+      <c r="X7" s="40" t="n">
+        <v>14231521</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -4472,6 +4564,9 @@
       <c r="W8" s="40" t="n">
         <v>73904849</v>
       </c>
+      <c r="X8" s="40" t="n">
+        <v>13707680</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -4547,6 +4642,9 @@
       <c r="W9" s="40" t="n">
         <v>63196973</v>
       </c>
+      <c r="X9" s="40" t="n">
+        <v>9481297</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -4622,230 +4720,242 @@
       <c r="W10" s="40" t="n">
         <v>45317128</v>
       </c>
+      <c r="X10" s="40" t="n">
+        <v>8088824</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>10351067</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>21091580</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>24243567</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>16381412</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>21591272</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>21904190</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>25438080</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>24614280</v>
+        <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>28889771</v>
+        <v>51983942</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>44250621</v>
+        <v>58935844</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>29608597</v>
+        <v>38454971</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>25219748</v>
+        <v>42939312</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>28515437</v>
+        <v>43650420</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>35235670</v>
+        <v>53954095</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>38511490</v>
+        <v>48898463</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>40935998</v>
+        <v>48011655</v>
       </c>
       <c r="T11" s="40" t="n">
-        <v>58966944</v>
+        <v>72064876</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>43378746</v>
+        <v>59606189</v>
       </c>
       <c r="V11" s="40" t="n">
-        <v>67522298</v>
+        <v>50164748</v>
       </c>
       <c r="W11" s="40" t="n">
-        <v>44905121</v>
+        <v>46095774</v>
+      </c>
+      <c r="X11" s="40" t="n">
+        <v>9023140</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>0</v>
+        <v>5092853</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>8972650</v>
+        <v>11100161</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>18100396</v>
+        <v>14612055</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>23988817</v>
+        <v>20638987</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>22409732</v>
+        <v>14061352</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37715520</v>
+        <v>31599148</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>35926824</v>
+        <v>18747614</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>39462393</v>
+        <v>19576415</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>51983942</v>
+        <v>14226838</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>58935844</v>
+        <v>23197145</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>38454971</v>
+        <v>25790711</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>42939312</v>
+        <v>27856115</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>43650420</v>
+        <v>20981901</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>53954095</v>
+        <v>25433123</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>48898463</v>
+        <v>19355230</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>48011655</v>
+        <v>24713836</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>72064876</v>
+        <v>20195634</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>59606189</v>
+        <v>32414171</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>50164748</v>
+        <v>42780769</v>
       </c>
       <c r="W12" s="40" t="n">
-        <v>46095774</v>
+        <v>36755122</v>
+      </c>
+      <c r="X12" s="40" t="n">
+        <v>5515983</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>5092853</v>
+        <v>8544625</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>11100161</v>
+        <v>8387478</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>14612055</v>
+        <v>10570508</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>20638987</v>
+        <v>11896580</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>14061352</v>
+        <v>19614352</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>31599148</v>
+        <v>20966317</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>18747614</v>
+        <v>20073400</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>19576415</v>
+        <v>23801493</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>14226838</v>
+        <v>27940611</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>23197145</v>
+        <v>27893929</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>25790711</v>
+        <v>29635773</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>27856115</v>
+        <v>19554230</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>20981901</v>
+        <v>23848495</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>25433123</v>
+        <v>24194638</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>19355230</v>
+        <v>20330094</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>24713836</v>
+        <v>26044199</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>20195634</v>
+        <v>24608772</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>32414171</v>
+        <v>28079726</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>42780769</v>
+        <v>20968052</v>
       </c>
       <c r="W13" s="40" t="n">
-        <v>36755122</v>
+        <v>29501132</v>
+      </c>
+      <c r="X13" s="40" t="n">
+        <v>6010680</v>
       </c>
     </row>
     <row r="14">
@@ -4922,455 +5032,476 @@
       <c r="W14" s="40" t="n">
         <v>50163008</v>
       </c>
+      <c r="X14" s="40" t="n">
+        <v>9471126</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>530238</v>
+        <v>251520</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>8544625</v>
+        <v>10351067</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>8387478</v>
+        <v>21091580</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>10570508</v>
+        <v>24243567</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>11896580</v>
+        <v>16381412</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>19614352</v>
+        <v>21591272</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>20966317</v>
+        <v>21904190</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>20073400</v>
+        <v>25438080</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>23801493</v>
+        <v>24614280</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>27940611</v>
+        <v>28889771</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>27893929</v>
+        <v>44250621</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>29635773</v>
+        <v>29608597</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>19554230</v>
+        <v>25219748</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>23848495</v>
+        <v>28515437</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>24194638</v>
+        <v>35235670</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>20330094</v>
+        <v>38511490</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>26044199</v>
+        <v>40935998</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>24608772</v>
+        <v>58966944</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>28079726</v>
+        <v>43378746</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>20968052</v>
+        <v>67522298</v>
       </c>
       <c r="W15" s="40" t="n">
-        <v>29501132</v>
+        <v>44905121</v>
+      </c>
+      <c r="X15" s="40" t="n">
+        <v>6219236</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>11884771</v>
+        <v>6239584</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>10651216</v>
+        <v>13803407</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>13882033</v>
+        <v>28572076</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>17812948</v>
+        <v>15282581</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>17331854</v>
+        <v>16594572</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>26294756</v>
+        <v>15223898</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>24196222</v>
+        <v>27696695</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>22122847</v>
+        <v>17717888</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>31914115</v>
+        <v>24163432</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>32069521</v>
+        <v>23623477</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>38287475</v>
+        <v>19145601</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>28283704</v>
+        <v>30157601</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>27334091</v>
+        <v>41172333</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>36312415</v>
+        <v>34303423</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>39333565</v>
+        <v>35044850</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>28566119</v>
+        <v>33519824</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>40387845</v>
+        <v>25969876</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>39744111</v>
+        <v>23835106</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>31477917</v>
+        <v>27833047</v>
       </c>
       <c r="W16" s="40" t="n">
-        <v>29910767</v>
+        <v>22815382</v>
+      </c>
+      <c r="X16" s="40" t="n">
+        <v>6854510</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3337146</v>
+        <v>0</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10420206</v>
+        <v>0</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>21387685</v>
+        <v>363900</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>16050448</v>
+        <v>3736700</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>21568794</v>
+        <v>17796776</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>30845816</v>
+        <v>42724228</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>45285935</v>
+        <v>33036620</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>28941455</v>
+        <v>29649130</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>21801828</v>
+        <v>13949368</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>19628570</v>
+        <v>24539413</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>23276090</v>
+        <v>19087217</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>27906254</v>
+        <v>17139440</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>20822247</v>
+        <v>17746930</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>20014322</v>
+        <v>21437830</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>19159625</v>
+        <v>17616397</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>22535696</v>
+        <v>19360848</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>21412810</v>
+        <v>25377166</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>34881782</v>
+        <v>24702051</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>25904024</v>
+        <v>26856647</v>
       </c>
       <c r="W17" s="40" t="n">
-        <v>46961904</v>
+        <v>27122255</v>
+      </c>
+      <c r="X17" s="40" t="n">
+        <v>3848490</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>3249588</v>
+        <v>11884771</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>7305524</v>
+        <v>10651216</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>9575225</v>
+        <v>13882033</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>9264589</v>
+        <v>17812948</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>20692424</v>
+        <v>17331854</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>27565767</v>
+        <v>26294756</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>19138015</v>
+        <v>24196222</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>24912292</v>
+        <v>22122847</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>19068954</v>
+        <v>31914115</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>25387051</v>
+        <v>32069521</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>21008637</v>
+        <v>38287475</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>30862574</v>
+        <v>28283704</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>31820447</v>
+        <v>27334091</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>31875986</v>
+        <v>36312415</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>48358034</v>
+        <v>39333565</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>30000524</v>
+        <v>28566119</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>31150016</v>
+        <v>40387845</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>40688796</v>
+        <v>39744111</v>
       </c>
       <c r="V18" s="40" t="n">
-        <v>31752550</v>
+        <v>31477917</v>
       </c>
       <c r="W18" s="40" t="n">
-        <v>32778027</v>
+        <v>29910767</v>
+      </c>
+      <c r="X18" s="40" t="n">
+        <v>5016090</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>363900</v>
+        <v>21387685</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>3736700</v>
+        <v>16050448</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>17796776</v>
+        <v>21568794</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>42724228</v>
+        <v>30845816</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>33036620</v>
+        <v>45285935</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>29649130</v>
+        <v>28941455</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>13949368</v>
+        <v>21801828</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>24539413</v>
+        <v>19628570</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>19087217</v>
+        <v>23276090</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>17139440</v>
+        <v>27906254</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>17746930</v>
+        <v>20822247</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>21437830</v>
+        <v>20014322</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>17616397</v>
+        <v>19159625</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>19360848</v>
+        <v>22535696</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>25377166</v>
+        <v>21412810</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>24702051</v>
+        <v>34881782</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>26856647</v>
+        <v>25904024</v>
       </c>
       <c r="W19" s="40" t="n">
-        <v>27122255</v>
+        <v>46961904</v>
+      </c>
+      <c r="X19" s="40" t="n">
+        <v>6203657</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>6239584</v>
+        <v>3249588</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>13803407</v>
+        <v>7305524</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>28572076</v>
+        <v>9575225</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>15282581</v>
+        <v>9264589</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>16594572</v>
+        <v>20692424</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>15223898</v>
+        <v>27565767</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>27696695</v>
+        <v>19138015</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>17717888</v>
+        <v>24912292</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>24163432</v>
+        <v>19068954</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>23623477</v>
+        <v>25387051</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>19145601</v>
+        <v>21008637</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>30157601</v>
+        <v>30862574</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>41172333</v>
+        <v>31820447</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>34303423</v>
+        <v>31875986</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>35044850</v>
+        <v>48358034</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>33519824</v>
+        <v>30000524</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>25969876</v>
+        <v>31150016</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>23835106</v>
+        <v>40688796</v>
       </c>
       <c r="V20" s="40" t="n">
-        <v>27833047</v>
+        <v>31752550</v>
       </c>
       <c r="W20" s="40" t="n">
-        <v>22815382</v>
+        <v>32778027</v>
+      </c>
+      <c r="X20" s="40" t="n">
+        <v>2452990</v>
       </c>
     </row>
     <row r="21">
@@ -5447,6 +5578,9 @@
       <c r="W21" s="40" t="n">
         <v>29206004</v>
       </c>
+      <c r="X21" s="40" t="n">
+        <v>2293950</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -5522,6 +5656,9 @@
       <c r="W22" s="40" t="n">
         <v>14940492</v>
       </c>
+      <c r="X22" s="40" t="n">
+        <v>2132920</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -5596,6 +5733,9 @@
       </c>
       <c r="W23" s="40" t="n">
         <v>9500343</v>
+      </c>
+      <c r="X23" s="40" t="n">
+        <v>4497780</v>
       </c>
     </row>
     <row r="24">
@@ -5687,6 +5827,10 @@
       </c>
       <c r="W24" s="41">
         <f>AVERAGE(W6:W23)</f>
+        <v/>
+      </c>
+      <c r="X24" s="41">
+        <f>AVERAGE(X6:X23)</f>
         <v/>
       </c>
     </row>
@@ -5701,7 +5845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -5727,6 +5871,7 @@
     <col width="13" customWidth="1" style="20" min="21" max="21"/>
     <col width="13" customWidth="1" style="20" min="22" max="22"/>
     <col width="13" customWidth="1" style="20" min="23" max="23"/>
+    <col width="13" customWidth="1" style="20" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5849,6 +5994,11 @@
           <t>2026-09-14</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -5964,6 +6114,11 @@
       <c r="W4" s="31" t="inlineStr">
         <is>
           <t>14.09–20.09</t>
+        </is>
+      </c>
+      <c r="X4" s="31" t="inlineStr">
+        <is>
+          <t>21.09–27.09*</t>
         </is>
       </c>
     </row>
@@ -6037,6 +6192,9 @@
       <c r="W5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="X5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -6112,6 +6270,9 @@
       <c r="W6" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="X6" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -6187,6 +6348,9 @@
       <c r="W7" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="X7" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -6262,6 +6426,9 @@
       <c r="W8" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="X8" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -6337,6 +6504,9 @@
       <c r="W9" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="X9" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -6412,101 +6582,107 @@
       <c r="W10" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="X10" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X11" s="42" t="n">
         <v>1</v>
-      </c>
-      <c r="D11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V11" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W11" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>7</v>
@@ -6561,24 +6737,27 @@
       </c>
       <c r="W12" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="X12" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -6636,6 +6815,9 @@
       </c>
       <c r="W13" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="X13" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -6712,20 +6894,23 @@
       <c r="W14" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="X14" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="42" t="n">
         <v>7</v>
@@ -6786,24 +6971,27 @@
       </c>
       <c r="W15" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="X15" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -6861,33 +7049,36 @@
       </c>
       <c r="W16" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="X16" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F17" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G17" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" s="42" t="n">
         <v>7</v>
@@ -6936,24 +7127,27 @@
       </c>
       <c r="W17" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="X17" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -7011,33 +7205,36 @@
       </c>
       <c r="W18" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="X18" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -7086,24 +7283,27 @@
       </c>
       <c r="W19" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="X19" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="42" t="n">
         <v>7</v>
@@ -7161,6 +7361,9 @@
       </c>
       <c r="W20" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="X20" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -7237,6 +7440,9 @@
       <c r="W21" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="X21" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -7312,6 +7518,9 @@
       <c r="W22" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="X22" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -7386,6 +7595,9 @@
       </c>
       <c r="W23" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="X23" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -7479,6 +7691,10 @@
         <f>AVERAGE(W6:W23)</f>
         <v/>
       </c>
+      <c r="X24" s="43">
+        <f>AVERAGE(X6:X23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2469,7 +2469,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2547,7 +2547,7 @@
         <v>125.14</v>
       </c>
       <c r="X6" s="36" t="n">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
@@ -2625,7 +2625,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="X7" s="36" t="n">
-        <v>102</v>
+        <v>93.5</v>
       </c>
     </row>
     <row r="8">
@@ -2703,7 +2703,7 @@
         <v>71</v>
       </c>
       <c r="X8" s="36" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9">
@@ -2781,7 +2781,7 @@
         <v>65.29000000000001</v>
       </c>
       <c r="X9" s="36" t="n">
-        <v>77</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="10">
@@ -2859,865 +2859,865 @@
         <v>49.86</v>
       </c>
       <c r="X10" s="36" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>11.29</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>10.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>11.14</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>13.86</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>18</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>31.29</v>
+        <v>18</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>33.57</v>
+        <v>17.43</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>40</v>
+        <v>15.29</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>42.43</v>
+        <v>24.43</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>38.57</v>
+        <v>24.71</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>34.29</v>
+        <v>25.57</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>37.86</v>
+        <v>19.29</v>
       </c>
       <c r="Q11" s="36" t="n">
-        <v>42.86</v>
+        <v>25.43</v>
       </c>
       <c r="R11" s="36" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="S11" s="36" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="T11" s="36" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="U11" s="36" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="V11" s="36" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="W11" s="36" t="n">
         <v>40.71</v>
       </c>
-      <c r="S11" s="36" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="T11" s="36" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="U11" s="36" t="n">
-        <v>55.29</v>
-      </c>
-      <c r="V11" s="36" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="W11" s="36" t="n">
-        <v>43.71</v>
-      </c>
       <c r="X11" s="36" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>11.29</v>
+        <v>8</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>10.57</v>
+        <v>13.14</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>11.14</v>
+        <v>19.43</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>13.86</v>
+        <v>26.43</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>18</v>
+        <v>32.29</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>18</v>
+        <v>31.29</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>17.43</v>
+        <v>33.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>15.29</v>
+        <v>40</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>24.43</v>
+        <v>42.43</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>24.71</v>
+        <v>38.57</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>25.57</v>
+        <v>34.29</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>19.29</v>
+        <v>37.86</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>25.43</v>
+        <v>42.86</v>
       </c>
       <c r="R12" s="36" t="n">
-        <v>22.57</v>
+        <v>40.71</v>
       </c>
       <c r="S12" s="36" t="n">
-        <v>21.29</v>
+        <v>45.43</v>
       </c>
       <c r="T12" s="36" t="n">
-        <v>29.14</v>
+        <v>44.57</v>
       </c>
       <c r="U12" s="36" t="n">
-        <v>31.43</v>
+        <v>55.29</v>
       </c>
       <c r="V12" s="36" t="n">
-        <v>35.71</v>
+        <v>46.29</v>
       </c>
       <c r="W12" s="36" t="n">
-        <v>40.71</v>
+        <v>43.71</v>
       </c>
       <c r="X12" s="36" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>1.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>11</v>
+        <v>12.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>14.43</v>
+        <v>16.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>11.86</v>
+        <v>21</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>18</v>
+        <v>20.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>19.14</v>
+        <v>28.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>21</v>
+        <v>24.14</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>23.43</v>
+        <v>27.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>20.43</v>
+        <v>28.14</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>24.57</v>
+        <v>28.86</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>24.14</v>
+        <v>33.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>24.43</v>
+        <v>30.71</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>22</v>
+        <v>31.14</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>23</v>
+        <v>40.29</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>18.43</v>
+        <v>38.71</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>24.71</v>
+        <v>43.14</v>
       </c>
       <c r="T13" s="36" t="n">
-        <v>27.57</v>
+        <v>37</v>
       </c>
       <c r="U13" s="36" t="n">
-        <v>30</v>
+        <v>46.29</v>
       </c>
       <c r="V13" s="36" t="n">
-        <v>28.57</v>
+        <v>43.14</v>
       </c>
       <c r="W13" s="36" t="n">
-        <v>30.14</v>
+        <v>36.86</v>
       </c>
       <c r="X13" s="36" t="n">
-        <v>49</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>1.67</v>
+        <v>8.43</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.14</v>
+        <v>13.43</v>
       </c>
       <c r="F14" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="G14" s="36" t="n">
         <v>16.57</v>
       </c>
-      <c r="G14" s="36" t="n">
-        <v>21</v>
-      </c>
       <c r="H14" s="36" t="n">
-        <v>20.29</v>
+        <v>21.29</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>28.57</v>
+        <v>21.14</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>24.14</v>
+        <v>23.29</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>27.57</v>
+        <v>22.43</v>
       </c>
       <c r="L14" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="M14" s="36" t="n">
         <v>28.14</v>
       </c>
-      <c r="M14" s="36" t="n">
-        <v>28.86</v>
-      </c>
       <c r="N14" s="36" t="n">
-        <v>33.14</v>
+        <v>31.14</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>30.71</v>
+        <v>30</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>31.14</v>
+        <v>30.43</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>40.29</v>
+        <v>31.29</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>38.71</v>
+        <v>36.14</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>43.14</v>
+        <v>31</v>
       </c>
       <c r="T14" s="36" t="n">
-        <v>37</v>
+        <v>37.71</v>
       </c>
       <c r="U14" s="36" t="n">
-        <v>46.29</v>
+        <v>39.29</v>
       </c>
       <c r="V14" s="36" t="n">
-        <v>43.14</v>
+        <v>45.86</v>
       </c>
       <c r="W14" s="36" t="n">
-        <v>36.86</v>
+        <v>45.14</v>
       </c>
       <c r="X14" s="36" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>8.43</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>13.43</v>
+        <v>11</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>21.71</v>
+        <v>14.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>16.57</v>
+        <v>11.86</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>21.29</v>
+        <v>18</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>21.14</v>
+        <v>19.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>23.29</v>
+        <v>21</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>22.43</v>
+        <v>23.43</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>22.43</v>
+        <v>20.43</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>28.14</v>
+        <v>24.57</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>31.14</v>
+        <v>24.14</v>
       </c>
       <c r="O15" s="36" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="P15" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q15" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="R15" s="36" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="S15" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="T15" s="36" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="U15" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="P15" s="36" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="Q15" s="36" t="n">
-        <v>31.29</v>
-      </c>
-      <c r="R15" s="36" t="n">
-        <v>36.14</v>
-      </c>
-      <c r="S15" s="36" t="n">
-        <v>31</v>
-      </c>
-      <c r="T15" s="36" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="U15" s="36" t="n">
-        <v>39.29</v>
-      </c>
       <c r="V15" s="36" t="n">
-        <v>45.86</v>
+        <v>28.57</v>
       </c>
       <c r="W15" s="36" t="n">
-        <v>45.14</v>
+        <v>30.14</v>
       </c>
       <c r="X15" s="36" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>7</v>
+        <v>9.43</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>16</v>
+        <v>12.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>19.43</v>
+        <v>13.29</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>15.86</v>
+        <v>14.71</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>14.86</v>
+        <v>17</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>16.71</v>
+        <v>19.71</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>19.71</v>
+        <v>17.71</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>16.86</v>
+        <v>19.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>24.86</v>
+        <v>24.14</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>23.43</v>
+        <v>27.57</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>19.43</v>
+        <v>24.43</v>
       </c>
       <c r="O16" s="36" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="P16" s="36" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="Q16" s="36" t="n">
         <v>25.57</v>
       </c>
-      <c r="P16" s="36" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="Q16" s="36" t="n">
-        <v>29.14</v>
-      </c>
       <c r="R16" s="36" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S16" s="36" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="T16" s="36" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="U16" s="36" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="V16" s="36" t="n">
         <v>29.57</v>
       </c>
-      <c r="T16" s="36" t="n">
-        <v>29.43</v>
-      </c>
-      <c r="U16" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="V16" s="36" t="n">
-        <v>27.14</v>
-      </c>
       <c r="W16" s="36" t="n">
-        <v>25.57</v>
+        <v>29.86</v>
       </c>
       <c r="X16" s="36" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>0.5</v>
+        <v>19.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>3.33</v>
+        <v>15.86</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>11.71</v>
+        <v>14.86</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.57</v>
+        <v>16.71</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>20.43</v>
+        <v>19.71</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>21.71</v>
+        <v>16.86</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15</v>
+        <v>24.86</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>22.71</v>
+        <v>23.43</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>22.43</v>
+        <v>19.43</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>20.14</v>
+        <v>25.57</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>15.71</v>
+        <v>27.43</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>19.43</v>
+        <v>29.14</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>20.29</v>
+        <v>25</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>22.29</v>
+        <v>29.57</v>
       </c>
       <c r="T17" s="36" t="n">
-        <v>21.29</v>
+        <v>29.43</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>25.14</v>
+        <v>21</v>
       </c>
       <c r="V17" s="36" t="n">
-        <v>23.57</v>
+        <v>27.14</v>
       </c>
       <c r="W17" s="36" t="n">
-        <v>26.29</v>
+        <v>25.57</v>
       </c>
       <c r="X17" s="36" t="n">
-        <v>33</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>9.43</v>
+        <v>3</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>12.43</v>
+        <v>7.14</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>13.29</v>
+        <v>13.43</v>
       </c>
       <c r="G18" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="H18" s="36" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="I18" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="J18" s="36" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K18" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L18" s="36" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="M18" s="36" t="n">
         <v>14.71</v>
       </c>
-      <c r="H18" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="I18" s="36" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="J18" s="36" t="n">
-        <v>17.71</v>
-      </c>
-      <c r="K18" s="36" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="L18" s="36" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="M18" s="36" t="n">
-        <v>27.57</v>
-      </c>
       <c r="N18" s="36" t="n">
-        <v>24.43</v>
+        <v>19.14</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>27.29</v>
+        <v>18</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>26.57</v>
+        <v>15.29</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>25.57</v>
+        <v>15.29</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>29</v>
+        <v>18.71</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>27.71</v>
+        <v>18</v>
       </c>
       <c r="T18" s="36" t="n">
-        <v>32.57</v>
+        <v>25.29</v>
       </c>
       <c r="U18" s="36" t="n">
-        <v>31.57</v>
+        <v>28.86</v>
       </c>
       <c r="V18" s="36" t="n">
-        <v>29.57</v>
+        <v>24</v>
       </c>
       <c r="W18" s="36" t="n">
-        <v>29.86</v>
+        <v>29.29</v>
       </c>
       <c r="X18" s="36" t="n">
-        <v>30</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>13.43</v>
+        <v>3.25</v>
       </c>
       <c r="G19" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I19" s="36" t="n">
         <v>12.71</v>
       </c>
-      <c r="H19" s="36" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="I19" s="36" t="n">
+      <c r="J19" s="36" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="K19" s="36" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L19" s="36" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="M19" s="36" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N19" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="J19" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="K19" s="36" t="n">
-        <v>18.57</v>
-      </c>
-      <c r="L19" s="36" t="n">
-        <v>16.57</v>
-      </c>
-      <c r="M19" s="36" t="n">
+      <c r="O19" s="36" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="P19" s="36" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="Q19" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="R19" s="36" t="n">
         <v>14.71</v>
       </c>
-      <c r="N19" s="36" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="O19" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="P19" s="36" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="Q19" s="36" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="R19" s="36" t="n">
-        <v>18.71</v>
-      </c>
       <c r="S19" s="36" t="n">
-        <v>18</v>
+        <v>15.86</v>
       </c>
       <c r="T19" s="36" t="n">
-        <v>25.29</v>
+        <v>25</v>
       </c>
       <c r="U19" s="36" t="n">
-        <v>28.86</v>
+        <v>27.29</v>
       </c>
       <c r="V19" s="36" t="n">
-        <v>24</v>
+        <v>17.14</v>
       </c>
       <c r="W19" s="36" t="n">
-        <v>29.29</v>
+        <v>22.14</v>
       </c>
       <c r="X19" s="36" t="n">
-        <v>28</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G20" s="36" t="n">
         <v>3.33</v>
       </c>
-      <c r="E20" s="36" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F20" s="36" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="G20" s="36" t="n">
-        <v>9.140000000000001</v>
-      </c>
       <c r="H20" s="36" t="n">
-        <v>14</v>
+        <v>11.71</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>17.14</v>
+        <v>17.57</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>16.14</v>
+        <v>20.43</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>18.57</v>
+        <v>21.71</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>16.14</v>
+        <v>15</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>21.71</v>
+        <v>22.71</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>20.86</v>
+        <v>22.43</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>20.86</v>
+        <v>20.14</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>21.86</v>
+        <v>15.71</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>28.71</v>
+        <v>19.43</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>24.71</v>
+        <v>20.29</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>24.57</v>
+        <v>22.29</v>
       </c>
       <c r="T20" s="36" t="n">
-        <v>25.29</v>
+        <v>21.29</v>
       </c>
       <c r="U20" s="36" t="n">
-        <v>26.71</v>
+        <v>25.14</v>
       </c>
       <c r="V20" s="36" t="n">
-        <v>27.57</v>
+        <v>23.57</v>
       </c>
       <c r="W20" s="36" t="n">
-        <v>28.29</v>
+        <v>26.29</v>
       </c>
       <c r="X20" s="36" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>3.25</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>8</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>9.43</v>
+        <v>14</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>12.71</v>
+        <v>17.14</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>11.57</v>
+        <v>16.14</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>18.57</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>11.86</v>
+        <v>16.14</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>21.71</v>
       </c>
       <c r="N21" s="36" t="n">
-        <v>19</v>
+        <v>20.86</v>
       </c>
       <c r="O21" s="36" t="n">
-        <v>19.57</v>
+        <v>20.86</v>
       </c>
       <c r="P21" s="36" t="n">
-        <v>16.86</v>
+        <v>21.86</v>
       </c>
       <c r="Q21" s="36" t="n">
-        <v>15</v>
+        <v>28.71</v>
       </c>
       <c r="R21" s="36" t="n">
-        <v>14.71</v>
+        <v>24.71</v>
       </c>
       <c r="S21" s="36" t="n">
-        <v>15.86</v>
+        <v>24.57</v>
       </c>
       <c r="T21" s="36" t="n">
-        <v>25</v>
+        <v>25.29</v>
       </c>
       <c r="U21" s="36" t="n">
-        <v>27.29</v>
+        <v>26.71</v>
       </c>
       <c r="V21" s="36" t="n">
-        <v>17.14</v>
+        <v>27.57</v>
       </c>
       <c r="W21" s="36" t="n">
-        <v>22.14</v>
+        <v>28.29</v>
       </c>
       <c r="X21" s="36" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="22">
@@ -3795,7 +3795,7 @@
         <v>13</v>
       </c>
       <c r="X22" s="36" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="23">
@@ -3873,7 +3873,7 @@
         <v>11</v>
       </c>
       <c r="X23" s="36" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="24">
@@ -4331,7 +4331,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4409,7 +4409,7 @@
         <v>129454842</v>
       </c>
       <c r="X6" s="40" t="n">
-        <v>15718036</v>
+        <v>32748695</v>
       </c>
     </row>
     <row r="7">
@@ -4487,7 +4487,7 @@
         <v>109654171</v>
       </c>
       <c r="X7" s="40" t="n">
-        <v>14231521</v>
+        <v>28982423</v>
       </c>
     </row>
     <row r="8">
@@ -4565,7 +4565,7 @@
         <v>73904849</v>
       </c>
       <c r="X8" s="40" t="n">
-        <v>13707680</v>
+        <v>21750030</v>
       </c>
     </row>
     <row r="9">
@@ -4643,7 +4643,7 @@
         <v>63196973</v>
       </c>
       <c r="X9" s="40" t="n">
-        <v>9481297</v>
+        <v>16980917</v>
       </c>
     </row>
     <row r="10">
@@ -4721,865 +4721,865 @@
         <v>45317128</v>
       </c>
       <c r="X10" s="40" t="n">
-        <v>8088824</v>
+        <v>15044114</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>5092853</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>11100161</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>14612055</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>20638987</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>14061352</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>31599148</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>18747614</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>19576415</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>51983942</v>
+        <v>14226838</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>58935844</v>
+        <v>23197145</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>38454971</v>
+        <v>25790711</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>42939312</v>
+        <v>27856115</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>43650420</v>
+        <v>20981901</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>53954095</v>
+        <v>25433123</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>48898463</v>
+        <v>19355230</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>48011655</v>
+        <v>24713836</v>
       </c>
       <c r="T11" s="40" t="n">
-        <v>72064876</v>
+        <v>20195634</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>59606189</v>
+        <v>32414171</v>
       </c>
       <c r="V11" s="40" t="n">
-        <v>50164748</v>
+        <v>42780769</v>
       </c>
       <c r="W11" s="40" t="n">
-        <v>46095774</v>
+        <v>36755122</v>
       </c>
       <c r="X11" s="40" t="n">
-        <v>9023140</v>
+        <v>12824148</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>5092853</v>
+        <v>0</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>11100161</v>
+        <v>8972650</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>14612055</v>
+        <v>18100396</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>20638987</v>
+        <v>23988817</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>14061352</v>
+        <v>22409732</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>31599148</v>
+        <v>37715520</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>18747614</v>
+        <v>35926824</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>19576415</v>
+        <v>39462393</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>14226838</v>
+        <v>51983942</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>23197145</v>
+        <v>58935844</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>25790711</v>
+        <v>38454971</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>27856115</v>
+        <v>42939312</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>20981901</v>
+        <v>43650420</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>25433123</v>
+        <v>53954095</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>19355230</v>
+        <v>48898463</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>24713836</v>
+        <v>48011655</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>20195634</v>
+        <v>72064876</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>32414171</v>
+        <v>59606189</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>42780769</v>
+        <v>50164748</v>
       </c>
       <c r="W12" s="40" t="n">
-        <v>36755122</v>
+        <v>46095774</v>
       </c>
       <c r="X12" s="40" t="n">
-        <v>5515983</v>
+        <v>16027020</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>8544625</v>
+        <v>536260</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>8387478</v>
+        <v>14403556</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>10570508</v>
+        <v>16216832</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>11896580</v>
+        <v>32622053</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>19614352</v>
+        <v>23929705</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>20966317</v>
+        <v>37214538</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>20073400</v>
+        <v>25375430</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>23801493</v>
+        <v>31500087</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>27940611</v>
+        <v>28078687</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>27893929</v>
+        <v>34472458</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>29635773</v>
+        <v>35343350</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>19554230</v>
+        <v>51225290</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>23848495</v>
+        <v>36142612</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>24194638</v>
+        <v>47488940</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>20330094</v>
+        <v>44805002</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>26044199</v>
+        <v>43327432</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>24608772</v>
+        <v>39637968</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>28079726</v>
+        <v>55199920</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>20968052</v>
+        <v>50680631</v>
       </c>
       <c r="W13" s="40" t="n">
-        <v>29501132</v>
+        <v>50163008</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>6010680</v>
+        <v>16305491</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>536260</v>
+        <v>10351067</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>14403556</v>
+        <v>21091580</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>16216832</v>
+        <v>24243567</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>32622053</v>
+        <v>16381412</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>23929705</v>
+        <v>21591272</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>37214538</v>
+        <v>21904190</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>25375430</v>
+        <v>25438080</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>31500087</v>
+        <v>24614280</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>28078687</v>
+        <v>28889771</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>34472458</v>
+        <v>44250621</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>35343350</v>
+        <v>29608597</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>51225290</v>
+        <v>25219748</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>36142612</v>
+        <v>28515437</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>47488940</v>
+        <v>35235670</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>44805002</v>
+        <v>38511490</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>43327432</v>
+        <v>40935998</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>39637968</v>
+        <v>58966944</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>55199920</v>
+        <v>43378746</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>50680631</v>
+        <v>67522298</v>
       </c>
       <c r="W14" s="40" t="n">
-        <v>50163008</v>
+        <v>44905121</v>
       </c>
       <c r="X14" s="40" t="n">
-        <v>9471126</v>
+        <v>12048035</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>251520</v>
+        <v>530238</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>10351067</v>
+        <v>8544625</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>21091580</v>
+        <v>8387478</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>24243567</v>
+        <v>10570508</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>16381412</v>
+        <v>11896580</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>21591272</v>
+        <v>19614352</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>21904190</v>
+        <v>20966317</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>25438080</v>
+        <v>20073400</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>24614280</v>
+        <v>23801493</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>28889771</v>
+        <v>27940611</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>44250621</v>
+        <v>27893929</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>29608597</v>
+        <v>29635773</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>25219748</v>
+        <v>19554230</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>28515437</v>
+        <v>23848495</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>35235670</v>
+        <v>24194638</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>38511490</v>
+        <v>20330094</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>40935998</v>
+        <v>26044199</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>58966944</v>
+        <v>24608772</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>43378746</v>
+        <v>28079726</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>67522298</v>
+        <v>20968052</v>
       </c>
       <c r="W15" s="40" t="n">
-        <v>44905121</v>
+        <v>29501132</v>
       </c>
       <c r="X15" s="40" t="n">
-        <v>6219236</v>
+        <v>9875680</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>6239584</v>
+        <v>11884771</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>13803407</v>
+        <v>10651216</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>28572076</v>
+        <v>13882033</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>15282581</v>
+        <v>17812948</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>16594572</v>
+        <v>17331854</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>15223898</v>
+        <v>26294756</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>27696695</v>
+        <v>24196222</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>17717888</v>
+        <v>22122847</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>24163432</v>
+        <v>31914115</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>23623477</v>
+        <v>32069521</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>19145601</v>
+        <v>38287475</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>30157601</v>
+        <v>28283704</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>41172333</v>
+        <v>27334091</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>34303423</v>
+        <v>36312415</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>35044850</v>
+        <v>39333565</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>33519824</v>
+        <v>28566119</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>25969876</v>
+        <v>40387845</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>23835106</v>
+        <v>39744111</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>27833047</v>
+        <v>31477917</v>
       </c>
       <c r="W16" s="40" t="n">
-        <v>22815382</v>
+        <v>29910767</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>6854510</v>
+        <v>11821237</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>0</v>
+        <v>6239584</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>0</v>
+        <v>13803407</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>363900</v>
+        <v>28572076</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>3736700</v>
+        <v>15282581</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>17796776</v>
+        <v>16594572</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>42724228</v>
+        <v>15223898</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>33036620</v>
+        <v>27696695</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>29649130</v>
+        <v>17717888</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>13949368</v>
+        <v>24163432</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>24539413</v>
+        <v>23623477</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>19087217</v>
+        <v>19145601</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>17139440</v>
+        <v>30157601</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>17746930</v>
+        <v>41172333</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>21437830</v>
+        <v>34303423</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>17616397</v>
+        <v>35044850</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>19360848</v>
+        <v>33519824</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>25377166</v>
+        <v>25969876</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>24702051</v>
+        <v>23835106</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>26856647</v>
+        <v>27833047</v>
       </c>
       <c r="W17" s="40" t="n">
-        <v>27122255</v>
+        <v>22815382</v>
       </c>
       <c r="X17" s="40" t="n">
-        <v>3848490</v>
+        <v>9264470</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>11884771</v>
+        <v>3337146</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>10651216</v>
+        <v>10420206</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>13882033</v>
+        <v>21387685</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>17812948</v>
+        <v>16050448</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>17331854</v>
+        <v>21568794</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>26294756</v>
+        <v>30845816</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>24196222</v>
+        <v>45285935</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>22122847</v>
+        <v>28941455</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>31914115</v>
+        <v>21801828</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>32069521</v>
+        <v>19628570</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>38287475</v>
+        <v>23276090</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>28283704</v>
+        <v>27906254</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>27334091</v>
+        <v>20822247</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>36312415</v>
+        <v>20014322</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>39333565</v>
+        <v>19159625</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>28566119</v>
+        <v>22535696</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>40387845</v>
+        <v>21412810</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>39744111</v>
+        <v>34881782</v>
       </c>
       <c r="V18" s="40" t="n">
-        <v>31477917</v>
+        <v>25904024</v>
       </c>
       <c r="W18" s="40" t="n">
-        <v>29910767</v>
+        <v>46961904</v>
       </c>
       <c r="X18" s="40" t="n">
-        <v>5016090</v>
+        <v>9758897</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>3337146</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>10420206</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>21387685</v>
+        <v>1324510</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>16050448</v>
+        <v>10311989</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>21568794</v>
+        <v>19934535</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>30845816</v>
+        <v>13536614</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>45285935</v>
+        <v>22187720</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>28941455</v>
+        <v>11732010</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>21801828</v>
+        <v>21143100</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>19628570</v>
+        <v>14330970</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>23276090</v>
+        <v>38267409</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>27906254</v>
+        <v>46351274</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>20822247</v>
+        <v>37105387</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>20014322</v>
+        <v>19868191</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>19159625</v>
+        <v>15153480</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>22535696</v>
+        <v>19277087</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>21412810</v>
+        <v>34209889</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>34881782</v>
+        <v>33260760</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>25904024</v>
+        <v>23559262</v>
       </c>
       <c r="W19" s="40" t="n">
-        <v>46961904</v>
+        <v>29206004</v>
       </c>
       <c r="X19" s="40" t="n">
-        <v>6203657</v>
+        <v>7751290</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>7305524</v>
+        <v>0</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>9575225</v>
+        <v>363900</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>9264589</v>
+        <v>3736700</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>20692424</v>
+        <v>17796776</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>27565767</v>
+        <v>42724228</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>19138015</v>
+        <v>33036620</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>24912292</v>
+        <v>29649130</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>19068954</v>
+        <v>13949368</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>25387051</v>
+        <v>24539413</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>21008637</v>
+        <v>19087217</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>30862574</v>
+        <v>17139440</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>31820447</v>
+        <v>17746930</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>31875986</v>
+        <v>21437830</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>48358034</v>
+        <v>17616397</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>30000524</v>
+        <v>19360848</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>31150016</v>
+        <v>25377166</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>40688796</v>
+        <v>24702051</v>
       </c>
       <c r="V20" s="40" t="n">
-        <v>31752550</v>
+        <v>26856647</v>
       </c>
       <c r="W20" s="40" t="n">
-        <v>32778027</v>
+        <v>27122255</v>
       </c>
       <c r="X20" s="40" t="n">
-        <v>2452990</v>
+        <v>6230104</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>0</v>
+        <v>3249588</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>0</v>
+        <v>7305524</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>1324510</v>
+        <v>9575225</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>10311989</v>
+        <v>9264589</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>19934535</v>
+        <v>20692424</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>13536614</v>
+        <v>27565767</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>22187720</v>
+        <v>19138015</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>11732010</v>
+        <v>24912292</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>21143100</v>
+        <v>19068954</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>14330970</v>
+        <v>25387051</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>38267409</v>
+        <v>21008637</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>46351274</v>
+        <v>30862574</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>37105387</v>
+        <v>31820447</v>
       </c>
       <c r="Q21" s="40" t="n">
-        <v>19868191</v>
+        <v>31875986</v>
       </c>
       <c r="R21" s="40" t="n">
-        <v>15153480</v>
+        <v>48358034</v>
       </c>
       <c r="S21" s="40" t="n">
-        <v>19277087</v>
+        <v>30000524</v>
       </c>
       <c r="T21" s="40" t="n">
-        <v>34209889</v>
+        <v>31150016</v>
       </c>
       <c r="U21" s="40" t="n">
-        <v>33260760</v>
+        <v>40688796</v>
       </c>
       <c r="V21" s="40" t="n">
-        <v>23559262</v>
+        <v>31752550</v>
       </c>
       <c r="W21" s="40" t="n">
-        <v>29206004</v>
+        <v>32778027</v>
       </c>
       <c r="X21" s="40" t="n">
-        <v>2293950</v>
+        <v>3707800</v>
       </c>
     </row>
     <row r="22">
@@ -5657,7 +5657,7 @@
         <v>14940492</v>
       </c>
       <c r="X22" s="40" t="n">
-        <v>2132920</v>
+        <v>4020890</v>
       </c>
     </row>
     <row r="23">
@@ -5735,7 +5735,7 @@
         <v>9500343</v>
       </c>
       <c r="X23" s="40" t="n">
-        <v>4497780</v>
+        <v>7035661</v>
       </c>
     </row>
     <row r="24">
@@ -6193,7 +6193,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -6271,7 +6271,7 @@
         <v>7</v>
       </c>
       <c r="X6" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -6349,7 +6349,7 @@
         <v>7</v>
       </c>
       <c r="X7" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -6427,7 +6427,7 @@
         <v>7</v>
       </c>
       <c r="X8" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6505,7 +6505,7 @@
         <v>7</v>
       </c>
       <c r="X9" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -6583,28 +6583,28 @@
         <v>7</v>
       </c>
       <c r="X10" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -6661,28 +6661,28 @@
         <v>7</v>
       </c>
       <c r="X11" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>7</v>
@@ -6739,103 +6739,103 @@
         <v>7</v>
       </c>
       <c r="X12" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X13" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="D13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X13" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -6895,22 +6895,22 @@
         <v>7</v>
       </c>
       <c r="X14" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="42" t="n">
         <v>7</v>
@@ -6973,25 +6973,25 @@
         <v>7</v>
       </c>
       <c r="X15" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -7051,187 +7051,187 @@
         <v>7</v>
       </c>
       <c r="X16" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X17" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="G17" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="H17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X17" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X18" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="D18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W18" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X18" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G19" s="42" t="n">
         <v>7</v>
@@ -7285,34 +7285,34 @@
         <v>7</v>
       </c>
       <c r="X19" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20" s="42" t="n">
         <v>7</v>
@@ -7363,31 +7363,31 @@
         <v>7</v>
       </c>
       <c r="X20" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G21" s="42" t="n">
         <v>7</v>
@@ -7441,7 +7441,7 @@
         <v>7</v>
       </c>
       <c r="X21" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -7519,7 +7519,7 @@
         <v>7</v>
       </c>
       <c r="X22" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -7597,7 +7597,7 @@
         <v>7</v>
       </c>
       <c r="X23" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2469,7 +2469,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2547,7 +2547,7 @@
         <v>125.14</v>
       </c>
       <c r="X6" s="36" t="n">
-        <v>116</v>
+        <v>111.67</v>
       </c>
     </row>
     <row r="7">
@@ -2625,7 +2625,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="X7" s="36" t="n">
-        <v>93.5</v>
+        <v>90.33</v>
       </c>
     </row>
     <row r="8">
@@ -2703,7 +2703,7 @@
         <v>71</v>
       </c>
       <c r="X8" s="36" t="n">
-        <v>77</v>
+        <v>79.33</v>
       </c>
     </row>
     <row r="9">
@@ -2781,7 +2781,7 @@
         <v>65.29000000000001</v>
       </c>
       <c r="X9" s="36" t="n">
-        <v>65.5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -2859,7 +2859,7 @@
         <v>49.86</v>
       </c>
       <c r="X10" s="36" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -2937,7 +2937,7 @@
         <v>40.71</v>
       </c>
       <c r="X11" s="36" t="n">
-        <v>58</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="12">
@@ -3015,241 +3015,241 @@
         <v>43.71</v>
       </c>
       <c r="X12" s="36" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>1.67</v>
+        <v>8.43</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>12.14</v>
+        <v>13.43</v>
       </c>
       <c r="F13" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="G13" s="36" t="n">
         <v>16.57</v>
       </c>
-      <c r="G13" s="36" t="n">
-        <v>21</v>
-      </c>
       <c r="H13" s="36" t="n">
-        <v>20.29</v>
+        <v>21.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>28.57</v>
+        <v>21.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>24.14</v>
+        <v>23.29</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>27.57</v>
+        <v>22.43</v>
       </c>
       <c r="L13" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="M13" s="36" t="n">
         <v>28.14</v>
       </c>
-      <c r="M13" s="36" t="n">
-        <v>28.86</v>
-      </c>
       <c r="N13" s="36" t="n">
-        <v>33.14</v>
+        <v>31.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>30.71</v>
+        <v>30</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>31.14</v>
+        <v>30.43</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>40.29</v>
+        <v>31.29</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>38.71</v>
+        <v>36.14</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>43.14</v>
+        <v>31</v>
       </c>
       <c r="T13" s="36" t="n">
-        <v>37</v>
+        <v>37.71</v>
       </c>
       <c r="U13" s="36" t="n">
-        <v>46.29</v>
+        <v>39.29</v>
       </c>
       <c r="V13" s="36" t="n">
-        <v>43.14</v>
+        <v>45.86</v>
       </c>
       <c r="W13" s="36" t="n">
-        <v>36.86</v>
+        <v>45.14</v>
       </c>
       <c r="X13" s="36" t="n">
-        <v>47.5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>8.43</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>13.43</v>
+        <v>11</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>21.71</v>
+        <v>14.43</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>16.57</v>
+        <v>11.86</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>21.29</v>
+        <v>18</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>21.14</v>
+        <v>19.14</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>23.29</v>
+        <v>21</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>22.43</v>
+        <v>23.43</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>22.43</v>
+        <v>20.43</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>28.14</v>
+        <v>24.57</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>31.14</v>
+        <v>24.14</v>
       </c>
       <c r="O14" s="36" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="P14" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q14" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="R14" s="36" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="S14" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="T14" s="36" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="U14" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="P14" s="36" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="Q14" s="36" t="n">
-        <v>31.29</v>
-      </c>
-      <c r="R14" s="36" t="n">
-        <v>36.14</v>
-      </c>
-      <c r="S14" s="36" t="n">
-        <v>31</v>
-      </c>
-      <c r="T14" s="36" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="U14" s="36" t="n">
-        <v>39.29</v>
-      </c>
       <c r="V14" s="36" t="n">
-        <v>45.86</v>
+        <v>28.57</v>
       </c>
       <c r="W14" s="36" t="n">
-        <v>45.14</v>
+        <v>30.14</v>
       </c>
       <c r="X14" s="36" t="n">
-        <v>47.5</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>1.67</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>11</v>
+        <v>12.14</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>14.43</v>
+        <v>16.57</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>11.86</v>
+        <v>21</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>18</v>
+        <v>20.29</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.14</v>
+        <v>28.57</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>21</v>
+        <v>24.14</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>23.43</v>
+        <v>27.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>20.43</v>
+        <v>28.14</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>24.57</v>
+        <v>28.86</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>24.14</v>
+        <v>33.14</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>24.43</v>
+        <v>30.71</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>22</v>
+        <v>31.14</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>23</v>
+        <v>40.29</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>18.43</v>
+        <v>38.71</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>24.71</v>
+        <v>43.14</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>27.57</v>
+        <v>37</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>30</v>
+        <v>46.29</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>28.57</v>
+        <v>43.14</v>
       </c>
       <c r="W15" s="36" t="n">
-        <v>30.14</v>
+        <v>36.86</v>
       </c>
       <c r="X15" s="36" t="n">
-        <v>44</v>
+        <v>39.33</v>
       </c>
     </row>
     <row r="16">
@@ -3327,7 +3327,7 @@
         <v>29.86</v>
       </c>
       <c r="X16" s="36" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -3405,7 +3405,7 @@
         <v>25.57</v>
       </c>
       <c r="X17" s="36" t="n">
-        <v>31.5</v>
+        <v>30.33</v>
       </c>
     </row>
     <row r="18">
@@ -3483,18 +3483,18 @@
         <v>29.29</v>
       </c>
       <c r="X18" s="36" t="n">
-        <v>28.5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
@@ -3507,72 +3507,72 @@
         <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>3.25</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>8</v>
+        <v>3.33</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>9.43</v>
+        <v>11.71</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>12.71</v>
+        <v>17.57</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>11.57</v>
+        <v>20.43</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>21.71</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>11.86</v>
+        <v>15</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>22.71</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>19</v>
+        <v>22.43</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>19.57</v>
+        <v>20.14</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>16.86</v>
+        <v>15.71</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>15</v>
+        <v>19.43</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>14.71</v>
+        <v>20.29</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>15.86</v>
+        <v>22.29</v>
       </c>
       <c r="T19" s="36" t="n">
-        <v>25</v>
+        <v>21.29</v>
       </c>
       <c r="U19" s="36" t="n">
-        <v>27.29</v>
+        <v>25.14</v>
       </c>
       <c r="V19" s="36" t="n">
-        <v>17.14</v>
+        <v>23.57</v>
       </c>
       <c r="W19" s="36" t="n">
-        <v>22.14</v>
+        <v>26.29</v>
       </c>
       <c r="X19" s="36" t="n">
-        <v>26.5</v>
+        <v>24.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
@@ -3585,61 +3585,61 @@
         <v>0</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>0.5</v>
+        <v>3.25</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>3.33</v>
+        <v>8</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>11.71</v>
+        <v>9.43</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>17.57</v>
+        <v>12.71</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>20.43</v>
+        <v>11.57</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>21.71</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L20" s="36" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="M20" s="36" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N20" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="O20" s="36" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="P20" s="36" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="Q20" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="M20" s="36" t="n">
-        <v>22.71</v>
-      </c>
-      <c r="N20" s="36" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="O20" s="36" t="n">
-        <v>20.14</v>
-      </c>
-      <c r="P20" s="36" t="n">
-        <v>15.71</v>
-      </c>
-      <c r="Q20" s="36" t="n">
-        <v>19.43</v>
-      </c>
       <c r="R20" s="36" t="n">
-        <v>20.29</v>
+        <v>14.71</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>22.29</v>
+        <v>15.86</v>
       </c>
       <c r="T20" s="36" t="n">
-        <v>21.29</v>
+        <v>25</v>
       </c>
       <c r="U20" s="36" t="n">
-        <v>25.14</v>
+        <v>27.29</v>
       </c>
       <c r="V20" s="36" t="n">
-        <v>23.57</v>
+        <v>17.14</v>
       </c>
       <c r="W20" s="36" t="n">
-        <v>26.29</v>
+        <v>22.14</v>
       </c>
       <c r="X20" s="36" t="n">
-        <v>26</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="21">
@@ -3717,163 +3717,163 @@
         <v>28.29</v>
       </c>
       <c r="X21" s="36" t="n">
-        <v>18.5</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G22" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="36" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G22" s="36" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H22" s="36" t="n">
-        <v>7.86</v>
+        <v>6</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>7.14</v>
+        <v>4.43</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>7.14</v>
+        <v>5.86</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>6</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>8.710000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="O22" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P22" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="Q22" s="36" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="R22" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="S22" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="R22" s="36" t="n">
+      <c r="T22" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="S22" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="T22" s="36" t="n">
-        <v>6.86</v>
-      </c>
       <c r="U22" s="36" t="n">
-        <v>12.14</v>
+        <v>12.71</v>
       </c>
       <c r="V22" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="W22" s="36" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X22" s="36" t="n">
-        <v>13.5</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23" s="36" t="n">
-        <v>2.8</v>
+        <v>5.14</v>
       </c>
       <c r="G23" s="36" t="n">
-        <v>4</v>
+        <v>5.29</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>6</v>
+        <v>7.86</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>4.43</v>
+        <v>7.14</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>3.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>5.86</v>
+        <v>7.14</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>5.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>7.43</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O23" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>7.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q23" s="36" t="n">
-        <v>10.29</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="R23" s="36" t="n">
-        <v>7</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S23" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="T23" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>6.86</v>
       </c>
       <c r="U23" s="36" t="n">
-        <v>12.71</v>
+        <v>12.14</v>
       </c>
       <c r="V23" s="36" t="n">
-        <v>9.57</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="W23" s="36" t="n">
+        <v>13</v>
+      </c>
+      <c r="X23" s="36" t="n">
         <v>11</v>
-      </c>
-      <c r="X23" s="36" t="n">
-        <v>12.5</v>
       </c>
     </row>
     <row r="24">
@@ -4331,7 +4331,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4409,7 +4409,7 @@
         <v>129454842</v>
       </c>
       <c r="X6" s="40" t="n">
-        <v>32748695</v>
+        <v>44873353</v>
       </c>
     </row>
     <row r="7">
@@ -4487,7 +4487,7 @@
         <v>109654171</v>
       </c>
       <c r="X7" s="40" t="n">
-        <v>28982423</v>
+        <v>40696582</v>
       </c>
     </row>
     <row r="8">
@@ -4565,7 +4565,7 @@
         <v>73904849</v>
       </c>
       <c r="X8" s="40" t="n">
-        <v>21750030</v>
+        <v>36203549</v>
       </c>
     </row>
     <row r="9">
@@ -4643,7 +4643,7 @@
         <v>63196973</v>
       </c>
       <c r="X9" s="40" t="n">
-        <v>16980917</v>
+        <v>23239367</v>
       </c>
     </row>
     <row r="10">
@@ -4721,7 +4721,7 @@
         <v>45317128</v>
       </c>
       <c r="X10" s="40" t="n">
-        <v>15044114</v>
+        <v>22730834</v>
       </c>
     </row>
     <row r="11">
@@ -4799,7 +4799,7 @@
         <v>36755122</v>
       </c>
       <c r="X11" s="40" t="n">
-        <v>12824148</v>
+        <v>17293678</v>
       </c>
     </row>
     <row r="12">
@@ -4877,241 +4877,241 @@
         <v>46095774</v>
       </c>
       <c r="X12" s="40" t="n">
-        <v>16027020</v>
+        <v>22831058</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>536260</v>
+        <v>10351067</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>14403556</v>
+        <v>21091580</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>16216832</v>
+        <v>24243567</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>32622053</v>
+        <v>16381412</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>23929705</v>
+        <v>21591272</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37214538</v>
+        <v>21904190</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25375430</v>
+        <v>25438080</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>31500087</v>
+        <v>24614280</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28078687</v>
+        <v>28889771</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>34472458</v>
+        <v>44250621</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>35343350</v>
+        <v>29608597</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>51225290</v>
+        <v>25219748</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>36142612</v>
+        <v>28515437</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>47488940</v>
+        <v>35235670</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>44805002</v>
+        <v>38511490</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>43327432</v>
+        <v>40935998</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>39637968</v>
+        <v>58966944</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>55199920</v>
+        <v>43378746</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>50680631</v>
+        <v>67522298</v>
       </c>
       <c r="W13" s="40" t="n">
-        <v>50163008</v>
+        <v>44905121</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>16305491</v>
+        <v>15705441</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>251520</v>
+        <v>530238</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>10351067</v>
+        <v>8544625</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>21091580</v>
+        <v>8387478</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>24243567</v>
+        <v>10570508</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>16381412</v>
+        <v>11896580</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>21591272</v>
+        <v>19614352</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>21904190</v>
+        <v>20966317</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>25438080</v>
+        <v>20073400</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>24614280</v>
+        <v>23801493</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>28889771</v>
+        <v>27940611</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>44250621</v>
+        <v>27893929</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>29608597</v>
+        <v>29635773</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>25219748</v>
+        <v>19554230</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>28515437</v>
+        <v>23848495</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>35235670</v>
+        <v>24194638</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>38511490</v>
+        <v>20330094</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>40935998</v>
+        <v>26044199</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>58966944</v>
+        <v>24608772</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>43378746</v>
+        <v>28079726</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>67522298</v>
+        <v>20968052</v>
       </c>
       <c r="W14" s="40" t="n">
-        <v>44905121</v>
+        <v>29501132</v>
       </c>
       <c r="X14" s="40" t="n">
-        <v>12048035</v>
+        <v>13915169</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>8544625</v>
+        <v>536260</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>8387478</v>
+        <v>14403556</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>10570508</v>
+        <v>16216832</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>11896580</v>
+        <v>32622053</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>19614352</v>
+        <v>23929705</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>20966317</v>
+        <v>37214538</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>20073400</v>
+        <v>25375430</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>23801493</v>
+        <v>31500087</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>27940611</v>
+        <v>28078687</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>27893929</v>
+        <v>34472458</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>29635773</v>
+        <v>35343350</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>19554230</v>
+        <v>51225290</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>23848495</v>
+        <v>36142612</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>24194638</v>
+        <v>47488940</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>20330094</v>
+        <v>44805002</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>26044199</v>
+        <v>43327432</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>24608772</v>
+        <v>39637968</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>28079726</v>
+        <v>55199920</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>20968052</v>
+        <v>50680631</v>
       </c>
       <c r="W15" s="40" t="n">
-        <v>29501132</v>
+        <v>50163008</v>
       </c>
       <c r="X15" s="40" t="n">
-        <v>9875680</v>
+        <v>19671451</v>
       </c>
     </row>
     <row r="16">
@@ -5189,7 +5189,7 @@
         <v>29910767</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>11821237</v>
+        <v>15898878</v>
       </c>
     </row>
     <row r="17">
@@ -5267,7 +5267,7 @@
         <v>22815382</v>
       </c>
       <c r="X17" s="40" t="n">
-        <v>9264470</v>
+        <v>12845840</v>
       </c>
     </row>
     <row r="18">
@@ -5345,18 +5345,18 @@
         <v>46961904</v>
       </c>
       <c r="X18" s="40" t="n">
-        <v>9758897</v>
+        <v>16467227</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
@@ -5369,72 +5369,72 @@
         <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>1324510</v>
+        <v>363900</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>10311989</v>
+        <v>3736700</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>19934535</v>
+        <v>17796776</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>13536614</v>
+        <v>42724228</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>22187720</v>
+        <v>33036620</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>11732010</v>
+        <v>29649130</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>21143100</v>
+        <v>13949368</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>14330970</v>
+        <v>24539413</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>38267409</v>
+        <v>19087217</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>46351274</v>
+        <v>17139440</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>37105387</v>
+        <v>17746930</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>19868191</v>
+        <v>21437830</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>15153480</v>
+        <v>17616397</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>19277087</v>
+        <v>19360848</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>34209889</v>
+        <v>25377166</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>33260760</v>
+        <v>24702051</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>23559262</v>
+        <v>26856647</v>
       </c>
       <c r="W19" s="40" t="n">
-        <v>29206004</v>
+        <v>27122255</v>
       </c>
       <c r="X19" s="40" t="n">
-        <v>7751290</v>
+        <v>9117774</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
@@ -5447,61 +5447,61 @@
         <v>0</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>363900</v>
+        <v>1324510</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>3736700</v>
+        <v>10311989</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>17796776</v>
+        <v>19934535</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>42724228</v>
+        <v>13536614</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>33036620</v>
+        <v>22187720</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>29649130</v>
+        <v>11732010</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>13949368</v>
+        <v>21143100</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>24539413</v>
+        <v>14330970</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>19087217</v>
+        <v>38267409</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>17139440</v>
+        <v>46351274</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>17746930</v>
+        <v>37105387</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>21437830</v>
+        <v>19868191</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>17616397</v>
+        <v>15153480</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>19360848</v>
+        <v>19277087</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>25377166</v>
+        <v>34209889</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>24702051</v>
+        <v>33260760</v>
       </c>
       <c r="V20" s="40" t="n">
-        <v>26856647</v>
+        <v>23559262</v>
       </c>
       <c r="W20" s="40" t="n">
-        <v>27122255</v>
+        <v>29206004</v>
       </c>
       <c r="X20" s="40" t="n">
-        <v>6230104</v>
+        <v>12133950</v>
       </c>
     </row>
     <row r="21">
@@ -5579,163 +5579,163 @@
         <v>32778027</v>
       </c>
       <c r="X21" s="40" t="n">
-        <v>3707800</v>
+        <v>8059440</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>2474409</v>
+        <v>0</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>4696696</v>
+        <v>0</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>6991878</v>
+        <v>1339100</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>4060163</v>
+        <v>5579340</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>7685466</v>
+        <v>9518200</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>10141286</v>
+        <v>11747640</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>6393871</v>
+        <v>3885270</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>4534503</v>
+        <v>8765870</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>7579040</v>
+        <v>4571680</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>9679437</v>
+        <v>3911995</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>6102368</v>
+        <v>9234090</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>4294070</v>
+        <v>5390260</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>5589419</v>
+        <v>4645370</v>
       </c>
       <c r="Q22" s="40" t="n">
-        <v>10264941</v>
+        <v>10400980</v>
       </c>
       <c r="R22" s="40" t="n">
-        <v>6114083</v>
+        <v>6123322</v>
       </c>
       <c r="S22" s="40" t="n">
-        <v>10758755</v>
+        <v>5648770</v>
       </c>
       <c r="T22" s="40" t="n">
-        <v>6048269</v>
+        <v>6880660</v>
       </c>
       <c r="U22" s="40" t="n">
-        <v>9823030</v>
+        <v>10209080</v>
       </c>
       <c r="V22" s="40" t="n">
-        <v>7263590</v>
+        <v>17909229</v>
       </c>
       <c r="W22" s="40" t="n">
-        <v>14940492</v>
+        <v>9500343</v>
       </c>
       <c r="X22" s="40" t="n">
-        <v>4020890</v>
+        <v>10687851</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>0</v>
+        <v>2474409</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>0</v>
+        <v>4696696</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>1339100</v>
+        <v>6991878</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>5579340</v>
+        <v>4060163</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>9518200</v>
+        <v>7685466</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>11747640</v>
+        <v>10141286</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>3885270</v>
+        <v>6393871</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>8765870</v>
+        <v>4534503</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>4571680</v>
+        <v>7579040</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>3911995</v>
+        <v>9679437</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>9234090</v>
+        <v>6102368</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>5390260</v>
+        <v>4294070</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>4645370</v>
+        <v>5589419</v>
       </c>
       <c r="Q23" s="40" t="n">
-        <v>10400980</v>
+        <v>10264941</v>
       </c>
       <c r="R23" s="40" t="n">
-        <v>6123322</v>
+        <v>6114083</v>
       </c>
       <c r="S23" s="40" t="n">
-        <v>5648770</v>
+        <v>10758755</v>
       </c>
       <c r="T23" s="40" t="n">
-        <v>6880660</v>
+        <v>6048269</v>
       </c>
       <c r="U23" s="40" t="n">
-        <v>10209080</v>
+        <v>9823030</v>
       </c>
       <c r="V23" s="40" t="n">
-        <v>17909229</v>
+        <v>7263590</v>
       </c>
       <c r="W23" s="40" t="n">
-        <v>9500343</v>
+        <v>14940492</v>
       </c>
       <c r="X23" s="40" t="n">
-        <v>7035661</v>
+        <v>4579290</v>
       </c>
     </row>
     <row r="24">
@@ -6193,7 +6193,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -6271,7 +6271,7 @@
         <v>7</v>
       </c>
       <c r="X6" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6349,7 +6349,7 @@
         <v>7</v>
       </c>
       <c r="X7" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6427,7 +6427,7 @@
         <v>7</v>
       </c>
       <c r="X8" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6505,7 +6505,7 @@
         <v>7</v>
       </c>
       <c r="X9" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -6583,7 +6583,7 @@
         <v>7</v>
       </c>
       <c r="X10" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -6661,7 +6661,7 @@
         <v>7</v>
       </c>
       <c r="X11" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6739,100 +6739,100 @@
         <v>7</v>
       </c>
       <c r="X12" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X13" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X13" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="42" t="n">
         <v>7</v>
@@ -6895,25 +6895,25 @@
         <v>7</v>
       </c>
       <c r="X14" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -6973,7 +6973,7 @@
         <v>7</v>
       </c>
       <c r="X15" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -7051,7 +7051,7 @@
         <v>7</v>
       </c>
       <c r="X16" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -7129,7 +7129,7 @@
         <v>7</v>
       </c>
       <c r="X17" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -7207,18 +7207,18 @@
         <v>7</v>
       </c>
       <c r="X18" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
@@ -7231,10 +7231,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -7285,18 +7285,18 @@
         <v>7</v>
       </c>
       <c r="X19" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="42" t="n">
         <v>7</v>
@@ -7363,7 +7363,7 @@
         <v>7</v>
       </c>
       <c r="X20" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -7441,109 +7441,109 @@
         <v>7</v>
       </c>
       <c r="X21" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M22" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="N22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X22" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="D22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W22" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X22" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F23" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G23" s="42" t="n">
         <v>7</v>
@@ -7564,7 +7564,7 @@
         <v>7</v>
       </c>
       <c r="M23" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N23" s="42" t="n">
         <v>7</v>
@@ -7597,7 +7597,7 @@
         <v>7</v>
       </c>
       <c r="X23" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2469,7 +2469,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2547,7 +2547,7 @@
         <v>125.14</v>
       </c>
       <c r="X6" s="36" t="n">
-        <v>111.67</v>
+        <v>114.5</v>
       </c>
     </row>
     <row r="7">
@@ -2625,7 +2625,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="X7" s="36" t="n">
-        <v>90.33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -2703,7 +2703,7 @@
         <v>71</v>
       </c>
       <c r="X8" s="36" t="n">
-        <v>79.33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
@@ -2781,7 +2781,7 @@
         <v>65.29000000000001</v>
       </c>
       <c r="X9" s="36" t="n">
-        <v>58</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="10">
@@ -2859,163 +2859,163 @@
         <v>49.86</v>
       </c>
       <c r="X10" s="36" t="n">
-        <v>54</v>
+        <v>55.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>11.29</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>10.57</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>11.14</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>13.86</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>18</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>18</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>17.43</v>
+        <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>15.29</v>
+        <v>40</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>24.43</v>
+        <v>42.43</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>24.71</v>
+        <v>38.57</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>25.57</v>
+        <v>34.29</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>19.29</v>
+        <v>37.86</v>
       </c>
       <c r="Q11" s="36" t="n">
-        <v>25.43</v>
+        <v>42.86</v>
       </c>
       <c r="R11" s="36" t="n">
-        <v>22.57</v>
+        <v>40.71</v>
       </c>
       <c r="S11" s="36" t="n">
-        <v>21.29</v>
+        <v>45.43</v>
       </c>
       <c r="T11" s="36" t="n">
-        <v>29.14</v>
+        <v>44.57</v>
       </c>
       <c r="U11" s="36" t="n">
-        <v>31.43</v>
+        <v>55.29</v>
       </c>
       <c r="V11" s="36" t="n">
-        <v>35.71</v>
+        <v>46.29</v>
       </c>
       <c r="W11" s="36" t="n">
-        <v>40.71</v>
+        <v>43.71</v>
       </c>
       <c r="X11" s="36" t="n">
-        <v>52.33</v>
+        <v>54.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>8</v>
+        <v>11.29</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>13.14</v>
+        <v>10.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>19.43</v>
+        <v>11.14</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>26.43</v>
+        <v>13.86</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>32.29</v>
+        <v>18</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>31.29</v>
+        <v>18</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>33.57</v>
+        <v>17.43</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>40</v>
+        <v>15.29</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>42.43</v>
+        <v>24.43</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>38.57</v>
+        <v>24.71</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>34.29</v>
+        <v>25.57</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>37.86</v>
+        <v>19.29</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>42.86</v>
+        <v>25.43</v>
       </c>
       <c r="R12" s="36" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="S12" s="36" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="T12" s="36" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="U12" s="36" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="V12" s="36" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="W12" s="36" t="n">
         <v>40.71</v>
       </c>
-      <c r="S12" s="36" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="T12" s="36" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="U12" s="36" t="n">
-        <v>55.29</v>
-      </c>
-      <c r="V12" s="36" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="W12" s="36" t="n">
-        <v>43.71</v>
-      </c>
       <c r="X12" s="36" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="13">
@@ -3093,7 +3093,7 @@
         <v>45.14</v>
       </c>
       <c r="X13" s="36" t="n">
-        <v>43</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="14">
@@ -3171,7 +3171,7 @@
         <v>30.14</v>
       </c>
       <c r="X14" s="36" t="n">
-        <v>42</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="15">
@@ -3249,7 +3249,7 @@
         <v>36.86</v>
       </c>
       <c r="X15" s="36" t="n">
-        <v>39.33</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="16">
@@ -3327,7 +3327,7 @@
         <v>29.86</v>
       </c>
       <c r="X16" s="36" t="n">
-        <v>34</v>
+        <v>32.25</v>
       </c>
     </row>
     <row r="17">
@@ -3405,7 +3405,7 @@
         <v>25.57</v>
       </c>
       <c r="X17" s="36" t="n">
-        <v>30.33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18">
@@ -3483,7 +3483,7 @@
         <v>29.29</v>
       </c>
       <c r="X18" s="36" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -3561,7 +3561,7 @@
         <v>26.29</v>
       </c>
       <c r="X19" s="36" t="n">
-        <v>24.33</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="20">
@@ -3639,7 +3639,7 @@
         <v>22.14</v>
       </c>
       <c r="X20" s="36" t="n">
-        <v>23.67</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="21">
@@ -3717,7 +3717,7 @@
         <v>28.29</v>
       </c>
       <c r="X21" s="36" t="n">
-        <v>23.33</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="22">
@@ -3795,7 +3795,7 @@
         <v>11</v>
       </c>
       <c r="X22" s="36" t="n">
-        <v>13.67</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="23">
@@ -3873,7 +3873,7 @@
         <v>13</v>
       </c>
       <c r="X23" s="36" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="24">
@@ -4331,7 +4331,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -4409,7 +4409,7 @@
         <v>129454842</v>
       </c>
       <c r="X6" s="40" t="n">
-        <v>44873353</v>
+        <v>59250996</v>
       </c>
     </row>
     <row r="7">
@@ -4487,7 +4487,7 @@
         <v>109654171</v>
       </c>
       <c r="X7" s="40" t="n">
-        <v>40696582</v>
+        <v>50680089</v>
       </c>
     </row>
     <row r="8">
@@ -4565,7 +4565,7 @@
         <v>73904849</v>
       </c>
       <c r="X8" s="40" t="n">
-        <v>36203549</v>
+        <v>46809869</v>
       </c>
     </row>
     <row r="9">
@@ -4643,7 +4643,7 @@
         <v>63196973</v>
       </c>
       <c r="X9" s="40" t="n">
-        <v>23239367</v>
+        <v>30165449</v>
       </c>
     </row>
     <row r="10">
@@ -4721,163 +4721,163 @@
         <v>45317128</v>
       </c>
       <c r="X10" s="40" t="n">
-        <v>22730834</v>
+        <v>31203079</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>5092853</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>11100161</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>14612055</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>20638987</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>14061352</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>31599148</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>18747614</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>19576415</v>
+        <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>14226838</v>
+        <v>51983942</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>23197145</v>
+        <v>58935844</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>25790711</v>
+        <v>38454971</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>27856115</v>
+        <v>42939312</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>20981901</v>
+        <v>43650420</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>25433123</v>
+        <v>53954095</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>19355230</v>
+        <v>48898463</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>24713836</v>
+        <v>48011655</v>
       </c>
       <c r="T11" s="40" t="n">
-        <v>20195634</v>
+        <v>72064876</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>32414171</v>
+        <v>59606189</v>
       </c>
       <c r="V11" s="40" t="n">
-        <v>42780769</v>
+        <v>50164748</v>
       </c>
       <c r="W11" s="40" t="n">
-        <v>36755122</v>
+        <v>46095774</v>
       </c>
       <c r="X11" s="40" t="n">
-        <v>17293678</v>
+        <v>34955680</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>0</v>
+        <v>5092853</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>8972650</v>
+        <v>11100161</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>18100396</v>
+        <v>14612055</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>23988817</v>
+        <v>20638987</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>22409732</v>
+        <v>14061352</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37715520</v>
+        <v>31599148</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>35926824</v>
+        <v>18747614</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>39462393</v>
+        <v>19576415</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>51983942</v>
+        <v>14226838</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>58935844</v>
+        <v>23197145</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>38454971</v>
+        <v>25790711</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>42939312</v>
+        <v>27856115</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>43650420</v>
+        <v>20981901</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>53954095</v>
+        <v>25433123</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>48898463</v>
+        <v>19355230</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>48011655</v>
+        <v>24713836</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>72064876</v>
+        <v>20195634</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>59606189</v>
+        <v>32414171</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>50164748</v>
+        <v>42780769</v>
       </c>
       <c r="W12" s="40" t="n">
-        <v>46095774</v>
+        <v>36755122</v>
       </c>
       <c r="X12" s="40" t="n">
-        <v>22831058</v>
+        <v>23897488</v>
       </c>
     </row>
     <row r="13">
@@ -4955,7 +4955,7 @@
         <v>44905121</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>15705441</v>
+        <v>26038183</v>
       </c>
     </row>
     <row r="14">
@@ -5033,7 +5033,7 @@
         <v>29501132</v>
       </c>
       <c r="X14" s="40" t="n">
-        <v>13915169</v>
+        <v>17832959</v>
       </c>
     </row>
     <row r="15">
@@ -5111,7 +5111,7 @@
         <v>50163008</v>
       </c>
       <c r="X15" s="40" t="n">
-        <v>19671451</v>
+        <v>23947147</v>
       </c>
     </row>
     <row r="16">
@@ -5189,7 +5189,7 @@
         <v>29910767</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>15898878</v>
+        <v>20499607</v>
       </c>
     </row>
     <row r="17">
@@ -5267,7 +5267,7 @@
         <v>22815382</v>
       </c>
       <c r="X17" s="40" t="n">
-        <v>12845840</v>
+        <v>19633943</v>
       </c>
     </row>
     <row r="18">
@@ -5345,7 +5345,7 @@
         <v>46961904</v>
       </c>
       <c r="X18" s="40" t="n">
-        <v>16467227</v>
+        <v>21304309</v>
       </c>
     </row>
     <row r="19">
@@ -5423,7 +5423,7 @@
         <v>27122255</v>
       </c>
       <c r="X19" s="40" t="n">
-        <v>9117774</v>
+        <v>13822534</v>
       </c>
     </row>
     <row r="20">
@@ -5501,7 +5501,7 @@
         <v>29206004</v>
       </c>
       <c r="X20" s="40" t="n">
-        <v>12133950</v>
+        <v>15884040</v>
       </c>
     </row>
     <row r="21">
@@ -5579,7 +5579,7 @@
         <v>32778027</v>
       </c>
       <c r="X21" s="40" t="n">
-        <v>8059440</v>
+        <v>12258548</v>
       </c>
     </row>
     <row r="22">
@@ -5657,7 +5657,7 @@
         <v>9500343</v>
       </c>
       <c r="X22" s="40" t="n">
-        <v>10687851</v>
+        <v>12691311</v>
       </c>
     </row>
     <row r="23">
@@ -5735,7 +5735,7 @@
         <v>14940492</v>
       </c>
       <c r="X23" s="40" t="n">
-        <v>4579290</v>
+        <v>6051645</v>
       </c>
     </row>
     <row r="24">
@@ -6193,7 +6193,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -6271,7 +6271,7 @@
         <v>7</v>
       </c>
       <c r="X6" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -6349,7 +6349,7 @@
         <v>7</v>
       </c>
       <c r="X7" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -6427,7 +6427,7 @@
         <v>7</v>
       </c>
       <c r="X8" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6505,7 +6505,7 @@
         <v>7</v>
       </c>
       <c r="X9" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -6583,28 +6583,28 @@
         <v>7</v>
       </c>
       <c r="X10" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -6661,28 +6661,28 @@
         <v>7</v>
       </c>
       <c r="X11" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>7</v>
@@ -6739,7 +6739,7 @@
         <v>7</v>
       </c>
       <c r="X12" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -6817,7 +6817,7 @@
         <v>7</v>
       </c>
       <c r="X13" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -6895,7 +6895,7 @@
         <v>7</v>
       </c>
       <c r="X14" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -6973,7 +6973,7 @@
         <v>7</v>
       </c>
       <c r="X15" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -7051,7 +7051,7 @@
         <v>7</v>
       </c>
       <c r="X16" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -7129,7 +7129,7 @@
         <v>7</v>
       </c>
       <c r="X17" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="X18" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -7285,7 +7285,7 @@
         <v>7</v>
       </c>
       <c r="X19" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -7363,7 +7363,7 @@
         <v>7</v>
       </c>
       <c r="X20" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -7441,7 +7441,7 @@
         <v>7</v>
       </c>
       <c r="X21" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -7519,7 +7519,7 @@
         <v>7</v>
       </c>
       <c r="X22" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -7597,7 +7597,7 @@
         <v>7</v>
       </c>
       <c r="X23" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2469,7 +2469,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2547,7 +2547,7 @@
         <v>125.14</v>
       </c>
       <c r="X6" s="36" t="n">
-        <v>114.5</v>
+        <v>115.2</v>
       </c>
     </row>
     <row r="7">
@@ -2625,7 +2625,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="X7" s="36" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -2703,7 +2703,7 @@
         <v>71</v>
       </c>
       <c r="X8" s="36" t="n">
-        <v>73</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="9">
@@ -2781,7 +2781,7 @@
         <v>65.29000000000001</v>
       </c>
       <c r="X9" s="36" t="n">
-        <v>60.5</v>
+        <v>64.2</v>
       </c>
     </row>
     <row r="10">
@@ -2859,7 +2859,7 @@
         <v>49.86</v>
       </c>
       <c r="X10" s="36" t="n">
-        <v>55.25</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="11">
@@ -2937,7 +2937,7 @@
         <v>43.71</v>
       </c>
       <c r="X11" s="36" t="n">
-        <v>54.75</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="12">
@@ -3015,7 +3015,7 @@
         <v>40.71</v>
       </c>
       <c r="X12" s="36" t="n">
-        <v>50.5</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="13">
@@ -3093,7 +3093,7 @@
         <v>45.14</v>
       </c>
       <c r="X13" s="36" t="n">
-        <v>44.5</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="14">
@@ -3171,7 +3171,7 @@
         <v>30.14</v>
       </c>
       <c r="X14" s="36" t="n">
-        <v>37.5</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="15">
@@ -3249,7 +3249,7 @@
         <v>36.86</v>
       </c>
       <c r="X15" s="36" t="n">
-        <v>35.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -3327,7 +3327,7 @@
         <v>29.86</v>
       </c>
       <c r="X16" s="36" t="n">
-        <v>32.25</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="17">
@@ -3405,7 +3405,7 @@
         <v>25.57</v>
       </c>
       <c r="X17" s="36" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
     </row>
     <row r="18">
@@ -3483,7 +3483,7 @@
         <v>29.29</v>
       </c>
       <c r="X18" s="36" t="n">
-        <v>28</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="19">
@@ -3561,7 +3561,7 @@
         <v>26.29</v>
       </c>
       <c r="X19" s="36" t="n">
-        <v>27.75</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="20">
@@ -3639,7 +3639,7 @@
         <v>22.14</v>
       </c>
       <c r="X20" s="36" t="n">
-        <v>25.75</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -3717,7 +3717,7 @@
         <v>28.29</v>
       </c>
       <c r="X21" s="36" t="n">
-        <v>24.25</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="22">
@@ -3795,7 +3795,7 @@
         <v>11</v>
       </c>
       <c r="X22" s="36" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="23">
@@ -3873,7 +3873,7 @@
         <v>13</v>
       </c>
       <c r="X23" s="36" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -4331,7 +4331,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -4409,7 +4409,7 @@
         <v>129454842</v>
       </c>
       <c r="X6" s="40" t="n">
-        <v>59250996</v>
+        <v>73785828</v>
       </c>
     </row>
     <row r="7">
@@ -4487,7 +4487,7 @@
         <v>109654171</v>
       </c>
       <c r="X7" s="40" t="n">
-        <v>50680089</v>
+        <v>65259659</v>
       </c>
     </row>
     <row r="8">
@@ -4565,7 +4565,7 @@
         <v>73904849</v>
       </c>
       <c r="X8" s="40" t="n">
-        <v>46809869</v>
+        <v>56290129</v>
       </c>
     </row>
     <row r="9">
@@ -4643,7 +4643,7 @@
         <v>63196973</v>
       </c>
       <c r="X9" s="40" t="n">
-        <v>30165449</v>
+        <v>40655985</v>
       </c>
     </row>
     <row r="10">
@@ -4721,7 +4721,7 @@
         <v>45317128</v>
       </c>
       <c r="X10" s="40" t="n">
-        <v>31203079</v>
+        <v>36683099</v>
       </c>
     </row>
     <row r="11">
@@ -4799,7 +4799,7 @@
         <v>46095774</v>
       </c>
       <c r="X11" s="40" t="n">
-        <v>34955680</v>
+        <v>46091244</v>
       </c>
     </row>
     <row r="12">
@@ -4877,7 +4877,7 @@
         <v>36755122</v>
       </c>
       <c r="X12" s="40" t="n">
-        <v>23897488</v>
+        <v>29542068</v>
       </c>
     </row>
     <row r="13">
@@ -4955,7 +4955,7 @@
         <v>44905121</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>26038183</v>
+        <v>32737914</v>
       </c>
     </row>
     <row r="14">
@@ -5033,7 +5033,7 @@
         <v>29501132</v>
       </c>
       <c r="X14" s="40" t="n">
-        <v>17832959</v>
+        <v>25344709</v>
       </c>
     </row>
     <row r="15">
@@ -5111,7 +5111,7 @@
         <v>50163008</v>
       </c>
       <c r="X15" s="40" t="n">
-        <v>23947147</v>
+        <v>28550123</v>
       </c>
     </row>
     <row r="16">
@@ -5189,7 +5189,7 @@
         <v>29910767</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>20499607</v>
+        <v>25852337</v>
       </c>
     </row>
     <row r="17">
@@ -5267,7 +5267,7 @@
         <v>22815382</v>
       </c>
       <c r="X17" s="40" t="n">
-        <v>19633943</v>
+        <v>22766886</v>
       </c>
     </row>
     <row r="18">
@@ -5345,7 +5345,7 @@
         <v>46961904</v>
       </c>
       <c r="X18" s="40" t="n">
-        <v>21304309</v>
+        <v>26477189</v>
       </c>
     </row>
     <row r="19">
@@ -5423,7 +5423,7 @@
         <v>27122255</v>
       </c>
       <c r="X19" s="40" t="n">
-        <v>13822534</v>
+        <v>22011572</v>
       </c>
     </row>
     <row r="20">
@@ -5501,7 +5501,7 @@
         <v>29206004</v>
       </c>
       <c r="X20" s="40" t="n">
-        <v>15884040</v>
+        <v>18930150</v>
       </c>
     </row>
     <row r="21">
@@ -5579,7 +5579,7 @@
         <v>32778027</v>
       </c>
       <c r="X21" s="40" t="n">
-        <v>12258548</v>
+        <v>14421913</v>
       </c>
     </row>
     <row r="22">
@@ -5657,7 +5657,7 @@
         <v>9500343</v>
       </c>
       <c r="X22" s="40" t="n">
-        <v>12691311</v>
+        <v>14004715</v>
       </c>
     </row>
     <row r="23">
@@ -5735,7 +5735,7 @@
         <v>14940492</v>
       </c>
       <c r="X23" s="40" t="n">
-        <v>6051645</v>
+        <v>6298445</v>
       </c>
     </row>
     <row r="24">
@@ -6193,7 +6193,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -6271,7 +6271,7 @@
         <v>7</v>
       </c>
       <c r="X6" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -6349,7 +6349,7 @@
         <v>7</v>
       </c>
       <c r="X7" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -6427,7 +6427,7 @@
         <v>7</v>
       </c>
       <c r="X8" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -6505,7 +6505,7 @@
         <v>7</v>
       </c>
       <c r="X9" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -6583,7 +6583,7 @@
         <v>7</v>
       </c>
       <c r="X10" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -6661,7 +6661,7 @@
         <v>7</v>
       </c>
       <c r="X11" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -6739,7 +6739,7 @@
         <v>7</v>
       </c>
       <c r="X12" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -6817,7 +6817,7 @@
         <v>7</v>
       </c>
       <c r="X13" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -6895,7 +6895,7 @@
         <v>7</v>
       </c>
       <c r="X14" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -6973,7 +6973,7 @@
         <v>7</v>
       </c>
       <c r="X15" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -7051,7 +7051,7 @@
         <v>7</v>
       </c>
       <c r="X16" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -7129,7 +7129,7 @@
         <v>7</v>
       </c>
       <c r="X17" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="X18" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -7285,7 +7285,7 @@
         <v>7</v>
       </c>
       <c r="X19" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -7363,7 +7363,7 @@
         <v>7</v>
       </c>
       <c r="X20" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -7441,7 +7441,7 @@
         <v>7</v>
       </c>
       <c r="X21" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -7519,7 +7519,7 @@
         <v>7</v>
       </c>
       <c r="X22" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -7597,7 +7597,7 @@
         <v>7</v>
       </c>
       <c r="X23" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2394,7 +2394,7 @@
       </c>
       <c r="X4" s="31" t="inlineStr">
         <is>
-          <t>21.09–27.09*</t>
+          <t>21.09–27.09</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2547,7 +2547,7 @@
         <v>125.14</v>
       </c>
       <c r="X6" s="36" t="n">
-        <v>115.2</v>
+        <v>117.43</v>
       </c>
     </row>
     <row r="7">
@@ -2625,7 +2625,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="X7" s="36" t="n">
-        <v>79</v>
+        <v>80.70999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -2703,7 +2703,7 @@
         <v>71</v>
       </c>
       <c r="X8" s="36" t="n">
-        <v>71.8</v>
+        <v>68.43000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2781,7 +2781,7 @@
         <v>65.29000000000001</v>
       </c>
       <c r="X9" s="36" t="n">
-        <v>64.2</v>
+        <v>61.43</v>
       </c>
     </row>
     <row r="10">
@@ -2859,7 +2859,7 @@
         <v>49.86</v>
       </c>
       <c r="X10" s="36" t="n">
-        <v>52.6</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="11">
@@ -2937,7 +2937,7 @@
         <v>43.71</v>
       </c>
       <c r="X11" s="36" t="n">
-        <v>49.8</v>
+        <v>49.57</v>
       </c>
     </row>
     <row r="12">
@@ -3015,7 +3015,7 @@
         <v>40.71</v>
       </c>
       <c r="X12" s="36" t="n">
-        <v>49.2</v>
+        <v>46.86</v>
       </c>
     </row>
     <row r="13">
@@ -3093,7 +3093,7 @@
         <v>45.14</v>
       </c>
       <c r="X13" s="36" t="n">
-        <v>44.2</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="14">
@@ -3171,7 +3171,7 @@
         <v>30.14</v>
       </c>
       <c r="X14" s="36" t="n">
-        <v>36.2</v>
+        <v>34.43</v>
       </c>
     </row>
     <row r="15">
@@ -3249,7 +3249,7 @@
         <v>36.86</v>
       </c>
       <c r="X15" s="36" t="n">
-        <v>35</v>
+        <v>33.43</v>
       </c>
     </row>
     <row r="16">
@@ -3327,163 +3327,163 @@
         <v>29.86</v>
       </c>
       <c r="X16" s="36" t="n">
-        <v>33.2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>16</v>
+        <v>7.14</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>19.43</v>
+        <v>13.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>15.86</v>
+        <v>12.71</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.86</v>
+        <v>14.43</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>16.71</v>
+        <v>19</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>19.71</v>
+        <v>21.14</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>16.86</v>
+        <v>18.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>24.86</v>
+        <v>16.57</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>23.43</v>
+        <v>14.71</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>19.43</v>
+        <v>19.14</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>25.57</v>
+        <v>18</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>27.43</v>
+        <v>15.29</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>29.14</v>
+        <v>15.29</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>25</v>
+        <v>18.71</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>29.57</v>
+        <v>18</v>
       </c>
       <c r="T17" s="36" t="n">
-        <v>29.43</v>
+        <v>25.29</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>21</v>
+        <v>28.86</v>
       </c>
       <c r="V17" s="36" t="n">
-        <v>27.14</v>
+        <v>24</v>
       </c>
       <c r="W17" s="36" t="n">
-        <v>25.57</v>
+        <v>29.29</v>
       </c>
       <c r="X17" s="36" t="n">
-        <v>30.6</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>7.14</v>
+        <v>16</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>13.43</v>
+        <v>19.43</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>12.71</v>
+        <v>15.86</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>14.43</v>
+        <v>14.86</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>19</v>
+        <v>16.71</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>21.14</v>
+        <v>19.71</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>18.57</v>
+        <v>16.86</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>16.57</v>
+        <v>24.86</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>14.71</v>
+        <v>23.43</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>19.14</v>
+        <v>19.43</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>18</v>
+        <v>25.57</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>15.29</v>
+        <v>27.43</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>15.29</v>
+        <v>29.14</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>18.71</v>
+        <v>25</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>18</v>
+        <v>29.57</v>
       </c>
       <c r="T18" s="36" t="n">
-        <v>25.29</v>
+        <v>29.43</v>
       </c>
       <c r="U18" s="36" t="n">
-        <v>28.86</v>
+        <v>21</v>
       </c>
       <c r="V18" s="36" t="n">
-        <v>24</v>
+        <v>27.14</v>
       </c>
       <c r="W18" s="36" t="n">
-        <v>29.29</v>
+        <v>25.57</v>
       </c>
       <c r="X18" s="36" t="n">
-        <v>30.2</v>
+        <v>30.29</v>
       </c>
     </row>
     <row r="19">
@@ -3561,7 +3561,7 @@
         <v>26.29</v>
       </c>
       <c r="X19" s="36" t="n">
-        <v>27.4</v>
+        <v>26.43</v>
       </c>
     </row>
     <row r="20">
@@ -3639,7 +3639,7 @@
         <v>22.14</v>
       </c>
       <c r="X20" s="36" t="n">
-        <v>24</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="21">
@@ -3717,7 +3717,7 @@
         <v>28.29</v>
       </c>
       <c r="X21" s="36" t="n">
-        <v>23.4</v>
+        <v>21.29</v>
       </c>
     </row>
     <row r="22">
@@ -3795,7 +3795,7 @@
         <v>11</v>
       </c>
       <c r="X22" s="36" t="n">
-        <v>14.4</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="23">
@@ -3873,7 +3873,7 @@
         <v>13</v>
       </c>
       <c r="X23" s="36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.140000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="X4" s="31" t="inlineStr">
         <is>
-          <t>21.09–27.09*</t>
+          <t>21.09–27.09</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -4409,7 +4409,7 @@
         <v>129454842</v>
       </c>
       <c r="X6" s="40" t="n">
-        <v>73785828</v>
+        <v>114593094</v>
       </c>
     </row>
     <row r="7">
@@ -4487,7 +4487,7 @@
         <v>109654171</v>
       </c>
       <c r="X7" s="40" t="n">
-        <v>65259659</v>
+        <v>99375298</v>
       </c>
     </row>
     <row r="8">
@@ -4565,7 +4565,7 @@
         <v>73904849</v>
       </c>
       <c r="X8" s="40" t="n">
-        <v>56290129</v>
+        <v>73547034</v>
       </c>
     </row>
     <row r="9">
@@ -4643,7 +4643,7 @@
         <v>63196973</v>
       </c>
       <c r="X9" s="40" t="n">
-        <v>40655985</v>
+        <v>51807160</v>
       </c>
     </row>
     <row r="10">
@@ -4721,7 +4721,7 @@
         <v>45317128</v>
       </c>
       <c r="X10" s="40" t="n">
-        <v>36683099</v>
+        <v>48612400</v>
       </c>
     </row>
     <row r="11">
@@ -4799,7 +4799,7 @@
         <v>46095774</v>
       </c>
       <c r="X11" s="40" t="n">
-        <v>46091244</v>
+        <v>57645111</v>
       </c>
     </row>
     <row r="12">
@@ -4877,7 +4877,7 @@
         <v>36755122</v>
       </c>
       <c r="X12" s="40" t="n">
-        <v>29542068</v>
+        <v>38071365</v>
       </c>
     </row>
     <row r="13">
@@ -4955,7 +4955,7 @@
         <v>44905121</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>32737914</v>
+        <v>43314104</v>
       </c>
     </row>
     <row r="14">
@@ -5033,7 +5033,7 @@
         <v>29501132</v>
       </c>
       <c r="X14" s="40" t="n">
-        <v>25344709</v>
+        <v>30624981</v>
       </c>
     </row>
     <row r="15">
@@ -5111,7 +5111,7 @@
         <v>50163008</v>
       </c>
       <c r="X15" s="40" t="n">
-        <v>28550123</v>
+        <v>38778399</v>
       </c>
     </row>
     <row r="16">
@@ -5189,163 +5189,163 @@
         <v>29910767</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>25852337</v>
+        <v>44620606</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>6239584</v>
+        <v>3337146</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>13803407</v>
+        <v>10420206</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>28572076</v>
+        <v>21387685</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>15282581</v>
+        <v>16050448</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>16594572</v>
+        <v>21568794</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>15223898</v>
+        <v>30845816</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>27696695</v>
+        <v>45285935</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>17717888</v>
+        <v>28941455</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>24163432</v>
+        <v>21801828</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>23623477</v>
+        <v>19628570</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>19145601</v>
+        <v>23276090</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>30157601</v>
+        <v>27906254</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>41172333</v>
+        <v>20822247</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>34303423</v>
+        <v>20014322</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>35044850</v>
+        <v>19159625</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>33519824</v>
+        <v>22535696</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>25969876</v>
+        <v>21412810</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>23835106</v>
+        <v>34881782</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>27833047</v>
+        <v>25904024</v>
       </c>
       <c r="W17" s="40" t="n">
-        <v>22815382</v>
+        <v>46961904</v>
       </c>
       <c r="X17" s="40" t="n">
-        <v>22766886</v>
+        <v>42299644</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>3337146</v>
+        <v>6239584</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>10420206</v>
+        <v>13803407</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>21387685</v>
+        <v>28572076</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>16050448</v>
+        <v>15282581</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>21568794</v>
+        <v>16594572</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>30845816</v>
+        <v>15223898</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>45285935</v>
+        <v>27696695</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>28941455</v>
+        <v>17717888</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>21801828</v>
+        <v>24163432</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>19628570</v>
+        <v>23623477</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>23276090</v>
+        <v>19145601</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>27906254</v>
+        <v>30157601</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>20822247</v>
+        <v>41172333</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>20014322</v>
+        <v>34303423</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>19159625</v>
+        <v>35044850</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>22535696</v>
+        <v>33519824</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>21412810</v>
+        <v>25969876</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>34881782</v>
+        <v>23835106</v>
       </c>
       <c r="V18" s="40" t="n">
-        <v>25904024</v>
+        <v>27833047</v>
       </c>
       <c r="W18" s="40" t="n">
-        <v>46961904</v>
+        <v>22815382</v>
       </c>
       <c r="X18" s="40" t="n">
-        <v>26477189</v>
+        <v>28299644</v>
       </c>
     </row>
     <row r="19">
@@ -5423,7 +5423,7 @@
         <v>27122255</v>
       </c>
       <c r="X19" s="40" t="n">
-        <v>22011572</v>
+        <v>30650242</v>
       </c>
     </row>
     <row r="20">
@@ -5501,7 +5501,7 @@
         <v>29206004</v>
       </c>
       <c r="X20" s="40" t="n">
-        <v>18930150</v>
+        <v>26477239</v>
       </c>
     </row>
     <row r="21">
@@ -5579,7 +5579,7 @@
         <v>32778027</v>
       </c>
       <c r="X21" s="40" t="n">
-        <v>14421913</v>
+        <v>21331873</v>
       </c>
     </row>
     <row r="22">
@@ -5657,7 +5657,7 @@
         <v>9500343</v>
       </c>
       <c r="X22" s="40" t="n">
-        <v>14004715</v>
+        <v>19439125</v>
       </c>
     </row>
     <row r="23">
@@ -5735,7 +5735,7 @@
         <v>14940492</v>
       </c>
       <c r="X23" s="40" t="n">
-        <v>6298445</v>
+        <v>8868985</v>
       </c>
     </row>
     <row r="24">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="X4" s="31" t="inlineStr">
         <is>
-          <t>21.09–27.09*</t>
+          <t>21.09–27.09</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
         <v>7</v>
       </c>
       <c r="X5" s="34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -6271,7 +6271,7 @@
         <v>7</v>
       </c>
       <c r="X6" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -6349,7 +6349,7 @@
         <v>7</v>
       </c>
       <c r="X7" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -6427,7 +6427,7 @@
         <v>7</v>
       </c>
       <c r="X8" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -6505,7 +6505,7 @@
         <v>7</v>
       </c>
       <c r="X9" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -6583,7 +6583,7 @@
         <v>7</v>
       </c>
       <c r="X10" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -6661,7 +6661,7 @@
         <v>7</v>
       </c>
       <c r="X11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -6739,7 +6739,7 @@
         <v>7</v>
       </c>
       <c r="X12" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -6817,7 +6817,7 @@
         <v>7</v>
       </c>
       <c r="X13" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -6895,7 +6895,7 @@
         <v>7</v>
       </c>
       <c r="X14" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -6973,7 +6973,7 @@
         <v>7</v>
       </c>
       <c r="X15" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -7051,25 +7051,25 @@
         <v>7</v>
       </c>
       <c r="X16" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -7129,25 +7129,25 @@
         <v>7</v>
       </c>
       <c r="X17" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -7207,7 +7207,7 @@
         <v>7</v>
       </c>
       <c r="X18" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -7285,7 +7285,7 @@
         <v>7</v>
       </c>
       <c r="X19" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -7363,7 +7363,7 @@
         <v>7</v>
       </c>
       <c r="X20" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -7441,7 +7441,7 @@
         <v>7</v>
       </c>
       <c r="X21" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -7519,7 +7519,7 @@
         <v>7</v>
       </c>
       <c r="X22" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -7597,7 +7597,7 @@
         <v>7</v>
       </c>
       <c r="X23" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2121,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2148,6 +2148,10 @@
     <col width="13" customWidth="1" style="20" min="22" max="22"/>
     <col width="13" customWidth="1" style="20" min="23" max="23"/>
     <col width="13" customWidth="1" style="20" min="24" max="24"/>
+    <col width="13" customWidth="1" style="20" min="25" max="25"/>
+    <col width="13" customWidth="1" style="20" min="26" max="26"/>
+    <col width="13" customWidth="1" style="20" min="27" max="27"/>
+    <col width="13" customWidth="1" style="20" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2275,6 +2279,26 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2395,6 +2419,26 @@
       <c r="X4" s="31" t="inlineStr">
         <is>
           <t>21.09–27.09</t>
+        </is>
+      </c>
+      <c r="Y4" s="31" t="inlineStr">
+        <is>
+          <t>28.09–04.10</t>
+        </is>
+      </c>
+      <c r="Z4" s="31" t="inlineStr">
+        <is>
+          <t>05.10–11.10</t>
+        </is>
+      </c>
+      <c r="AA4" s="31" t="inlineStr">
+        <is>
+          <t>12.10–18.10</t>
+        </is>
+      </c>
+      <c r="AB4" s="31" t="inlineStr">
+        <is>
+          <t>19.10–25.10*</t>
         </is>
       </c>
     </row>
@@ -2471,6 +2515,18 @@
       <c r="X5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="Y5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -2549,6 +2605,18 @@
       <c r="X6" s="36" t="n">
         <v>117.43</v>
       </c>
+      <c r="Y6" s="36" t="n">
+        <v>128.86</v>
+      </c>
+      <c r="Z6" s="36" t="n">
+        <v>122</v>
+      </c>
+      <c r="AA6" s="36" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB6" s="36" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -2627,6 +2695,18 @@
       <c r="X7" s="36" t="n">
         <v>80.70999999999999</v>
       </c>
+      <c r="Y7" s="36" t="n">
+        <v>101.29</v>
+      </c>
+      <c r="Z7" s="36" t="n">
+        <v>76.14</v>
+      </c>
+      <c r="AA7" s="36" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="AB7" s="36" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -2705,161 +2785,197 @@
       <c r="X8" s="36" t="n">
         <v>68.43000000000001</v>
       </c>
+      <c r="Y8" s="36" t="n">
+        <v>78.43000000000001</v>
+      </c>
+      <c r="Z8" s="36" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="AA8" s="36" t="n">
+        <v>78.56999999999999</v>
+      </c>
+      <c r="AB8" s="36" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>14.29</v>
+        <v>7.25</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>19.14</v>
+        <v>18.71</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>26.71</v>
+        <v>21.57</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>28.14</v>
+        <v>30.29</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>28.57</v>
+        <v>38</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>31.57</v>
+        <v>39.71</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>33</v>
+        <v>41.71</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>34.86</v>
+        <v>35.14</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>41.29</v>
+        <v>41</v>
       </c>
       <c r="M9" s="36" t="n">
+        <v>48</v>
+      </c>
+      <c r="N9" s="36" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="O9" s="36" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="P9" s="36" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q9" s="36" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="R9" s="36" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="S9" s="36" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="T9" s="36" t="n">
+        <v>50.14</v>
+      </c>
+      <c r="U9" s="36" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="V9" s="36" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="W9" s="36" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="X9" s="36" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="Y9" s="36" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="Z9" s="36" t="n">
         <v>41.43</v>
       </c>
-      <c r="N9" s="36" t="n">
-        <v>46.14</v>
-      </c>
-      <c r="O9" s="36" t="n">
-        <v>41.57</v>
-      </c>
-      <c r="P9" s="36" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="Q9" s="36" t="n">
-        <v>48.71</v>
-      </c>
-      <c r="R9" s="36" t="n">
-        <v>45.14</v>
-      </c>
-      <c r="S9" s="36" t="n">
-        <v>50.71</v>
-      </c>
-      <c r="T9" s="36" t="n">
-        <v>60.71</v>
-      </c>
-      <c r="U9" s="36" t="n">
-        <v>66.86</v>
-      </c>
-      <c r="V9" s="36" t="n">
-        <v>63.29</v>
-      </c>
-      <c r="W9" s="36" t="n">
-        <v>65.29000000000001</v>
-      </c>
-      <c r="X9" s="36" t="n">
-        <v>61.43</v>
+      <c r="AA9" s="36" t="n">
+        <v>57.14</v>
+      </c>
+      <c r="AB9" s="36" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>7.25</v>
+        <v>1.67</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>18.71</v>
+        <v>12.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>21.57</v>
+        <v>16.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>30.29</v>
+        <v>21</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>38</v>
+        <v>20.29</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>39.71</v>
+        <v>28.57</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>41.71</v>
+        <v>24.14</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>35.14</v>
+        <v>27.57</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41</v>
+        <v>28.14</v>
       </c>
       <c r="M10" s="36" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="N10" s="36" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="O10" s="36" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="P10" s="36" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="Q10" s="36" t="n">
+        <v>40.29</v>
+      </c>
+      <c r="R10" s="36" t="n">
+        <v>38.71</v>
+      </c>
+      <c r="S10" s="36" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="T10" s="36" t="n">
+        <v>37</v>
+      </c>
+      <c r="U10" s="36" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="V10" s="36" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="W10" s="36" t="n">
+        <v>36.86</v>
+      </c>
+      <c r="X10" s="36" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="Y10" s="36" t="n">
         <v>48</v>
       </c>
-      <c r="N10" s="36" t="n">
-        <v>49.43</v>
-      </c>
-      <c r="O10" s="36" t="n">
-        <v>45.57</v>
-      </c>
-      <c r="P10" s="36" t="n">
-        <v>43</v>
-      </c>
-      <c r="Q10" s="36" t="n">
-        <v>46.57</v>
-      </c>
-      <c r="R10" s="36" t="n">
-        <v>48.43</v>
-      </c>
-      <c r="S10" s="36" t="n">
-        <v>38.29</v>
-      </c>
-      <c r="T10" s="36" t="n">
-        <v>50.14</v>
-      </c>
-      <c r="U10" s="36" t="n">
-        <v>48.86</v>
-      </c>
-      <c r="V10" s="36" t="n">
-        <v>49.57</v>
-      </c>
-      <c r="W10" s="36" t="n">
-        <v>49.86</v>
-      </c>
-      <c r="X10" s="36" t="n">
-        <v>50.86</v>
+      <c r="Z10" s="36" t="n">
+        <v>39.86</v>
+      </c>
+      <c r="AA10" s="36" t="n">
+        <v>37.14</v>
+      </c>
+      <c r="AB10" s="36" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -2939,629 +3055,737 @@
       <c r="X11" s="36" t="n">
         <v>49.57</v>
       </c>
+      <c r="Y11" s="36" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="Z11" s="36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA11" s="36" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="AB11" s="36" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>6.67</v>
+        <v>14.29</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>11.29</v>
+        <v>19.14</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>10.57</v>
+        <v>26.71</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>11.14</v>
+        <v>28.14</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>13.86</v>
+        <v>28.57</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>18</v>
+        <v>31.57</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>17.43</v>
+        <v>34.86</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>15.29</v>
+        <v>41.29</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>24.43</v>
+        <v>41.43</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>24.71</v>
+        <v>46.14</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>25.57</v>
+        <v>41.57</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>19.29</v>
+        <v>51.86</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>25.43</v>
+        <v>48.71</v>
       </c>
       <c r="R12" s="36" t="n">
-        <v>22.57</v>
+        <v>45.14</v>
       </c>
       <c r="S12" s="36" t="n">
-        <v>21.29</v>
+        <v>50.71</v>
       </c>
       <c r="T12" s="36" t="n">
-        <v>29.14</v>
+        <v>60.71</v>
       </c>
       <c r="U12" s="36" t="n">
-        <v>31.43</v>
+        <v>66.86</v>
       </c>
       <c r="V12" s="36" t="n">
-        <v>35.71</v>
+        <v>63.29</v>
       </c>
       <c r="W12" s="36" t="n">
-        <v>40.71</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="X12" s="36" t="n">
-        <v>46.86</v>
+        <v>61.43</v>
+      </c>
+      <c r="Y12" s="36" t="n">
+        <v>66.29000000000001</v>
+      </c>
+      <c r="Z12" s="36" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="AA12" s="36" t="n">
+        <v>63.71</v>
+      </c>
+      <c r="AB12" s="36" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>8.43</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>13.43</v>
+        <v>11</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>21.71</v>
+        <v>14.43</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>16.57</v>
+        <v>11.86</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>21.29</v>
+        <v>18</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>21.14</v>
+        <v>19.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>23.29</v>
+        <v>21</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>22.43</v>
+        <v>23.43</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>22.43</v>
+        <v>20.43</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.14</v>
+        <v>24.57</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>31.14</v>
+        <v>24.14</v>
       </c>
       <c r="O13" s="36" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="P13" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q13" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="R13" s="36" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="S13" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="T13" s="36" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="U13" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="P13" s="36" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="Q13" s="36" t="n">
+      <c r="V13" s="36" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="W13" s="36" t="n">
+        <v>30.14</v>
+      </c>
+      <c r="X13" s="36" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="Y13" s="36" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="Z13" s="36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA13" s="36" t="n">
         <v>31.29</v>
       </c>
-      <c r="R13" s="36" t="n">
-        <v>36.14</v>
-      </c>
-      <c r="S13" s="36" t="n">
-        <v>31</v>
-      </c>
-      <c r="T13" s="36" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="U13" s="36" t="n">
-        <v>39.29</v>
-      </c>
-      <c r="V13" s="36" t="n">
-        <v>45.86</v>
-      </c>
-      <c r="W13" s="36" t="n">
-        <v>45.14</v>
-      </c>
-      <c r="X13" s="36" t="n">
-        <v>41.86</v>
+      <c r="AB13" s="36" t="n">
+        <v>49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>11</v>
+        <v>13.43</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>14.43</v>
+        <v>21.71</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>11.86</v>
+        <v>16.57</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>18</v>
+        <v>21.29</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>19.14</v>
+        <v>21.14</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>21</v>
+        <v>23.29</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>23.43</v>
+        <v>22.43</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>20.43</v>
+        <v>22.43</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>24.57</v>
+        <v>28.14</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>24.14</v>
+        <v>31.14</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>24.43</v>
+        <v>30</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>22</v>
+        <v>30.43</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>23</v>
+        <v>31.29</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>18.43</v>
+        <v>36.14</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>24.71</v>
+        <v>31</v>
       </c>
       <c r="T14" s="36" t="n">
-        <v>27.57</v>
+        <v>37.71</v>
       </c>
       <c r="U14" s="36" t="n">
-        <v>30</v>
+        <v>39.29</v>
       </c>
       <c r="V14" s="36" t="n">
-        <v>28.57</v>
+        <v>45.86</v>
       </c>
       <c r="W14" s="36" t="n">
-        <v>30.14</v>
+        <v>45.14</v>
       </c>
       <c r="X14" s="36" t="n">
-        <v>34.43</v>
+        <v>41.86</v>
+      </c>
+      <c r="Y14" s="36" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z14" s="36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA14" s="36" t="n">
+        <v>51.14</v>
+      </c>
+      <c r="AB14" s="36" t="n">
+        <v>48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>12.14</v>
+        <v>7.14</v>
       </c>
       <c r="F15" s="36" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="G15" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="H15" s="36" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="I15" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="J15" s="36" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K15" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L15" s="36" t="n">
         <v>16.57</v>
       </c>
-      <c r="G15" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="H15" s="36" t="n">
-        <v>20.29</v>
-      </c>
-      <c r="I15" s="36" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="J15" s="36" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="K15" s="36" t="n">
-        <v>27.57</v>
-      </c>
-      <c r="L15" s="36" t="n">
-        <v>28.14</v>
-      </c>
       <c r="M15" s="36" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="N15" s="36" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="O15" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="P15" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="Q15" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="R15" s="36" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="S15" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="T15" s="36" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="U15" s="36" t="n">
         <v>28.86</v>
       </c>
-      <c r="N15" s="36" t="n">
-        <v>33.14</v>
-      </c>
-      <c r="O15" s="36" t="n">
-        <v>30.71</v>
-      </c>
-      <c r="P15" s="36" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="Q15" s="36" t="n">
-        <v>40.29</v>
-      </c>
-      <c r="R15" s="36" t="n">
-        <v>38.71</v>
-      </c>
-      <c r="S15" s="36" t="n">
-        <v>43.14</v>
-      </c>
-      <c r="T15" s="36" t="n">
-        <v>37</v>
-      </c>
-      <c r="U15" s="36" t="n">
-        <v>46.29</v>
-      </c>
       <c r="V15" s="36" t="n">
-        <v>43.14</v>
+        <v>24</v>
       </c>
       <c r="W15" s="36" t="n">
-        <v>36.86</v>
+        <v>29.29</v>
       </c>
       <c r="X15" s="36" t="n">
-        <v>33.43</v>
+        <v>31.71</v>
+      </c>
+      <c r="Y15" s="36" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z15" s="36" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="AA15" s="36" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="AB15" s="36" t="n">
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.43</v>
+        <v>6.67</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>12.43</v>
+        <v>11.29</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.29</v>
+        <v>10.57</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>14.71</v>
+        <v>11.14</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>17</v>
+        <v>13.86</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>19.71</v>
+        <v>18</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>17.71</v>
+        <v>18</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>19.57</v>
+        <v>17.43</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>24.14</v>
+        <v>15.29</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>27.57</v>
+        <v>24.43</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>24.43</v>
+        <v>24.71</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>27.29</v>
+        <v>25.57</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>26.57</v>
+        <v>19.29</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>25.57</v>
+        <v>25.43</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>29</v>
+        <v>22.57</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>27.71</v>
+        <v>21.29</v>
       </c>
       <c r="T16" s="36" t="n">
-        <v>32.57</v>
+        <v>29.14</v>
       </c>
       <c r="U16" s="36" t="n">
-        <v>31.57</v>
+        <v>31.43</v>
       </c>
       <c r="V16" s="36" t="n">
-        <v>29.57</v>
+        <v>35.71</v>
       </c>
       <c r="W16" s="36" t="n">
-        <v>29.86</v>
+        <v>40.71</v>
       </c>
       <c r="X16" s="36" t="n">
-        <v>32</v>
+        <v>46.86</v>
+      </c>
+      <c r="Y16" s="36" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="Z16" s="36" t="n">
+        <v>37</v>
+      </c>
+      <c r="AA16" s="36" t="n">
+        <v>52.57</v>
+      </c>
+      <c r="AB16" s="36" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>7.14</v>
+        <v>6.43</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>12.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.43</v>
+        <v>14</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19</v>
+        <v>17.14</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21.14</v>
+        <v>16.14</v>
       </c>
       <c r="K17" s="36" t="n">
         <v>18.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.57</v>
+        <v>16.14</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>14.71</v>
+        <v>21.71</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>19.14</v>
+        <v>20.86</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>18</v>
+        <v>20.86</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>15.29</v>
+        <v>21.86</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>15.29</v>
+        <v>28.71</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>18.71</v>
+        <v>24.71</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>18</v>
+        <v>24.57</v>
       </c>
       <c r="T17" s="36" t="n">
         <v>25.29</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>28.86</v>
+        <v>26.71</v>
       </c>
       <c r="V17" s="36" t="n">
-        <v>24</v>
+        <v>27.57</v>
       </c>
       <c r="W17" s="36" t="n">
-        <v>29.29</v>
+        <v>28.29</v>
       </c>
       <c r="X17" s="36" t="n">
-        <v>31.71</v>
+        <v>21.29</v>
+      </c>
+      <c r="Y17" s="36" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z17" s="36" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="AA17" s="36" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="AB17" s="36" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F18" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G18" s="36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H18" s="36" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="I18" s="36" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="J18" s="36" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="K18" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="L18" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="M18" s="36" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="N18" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="O18" s="36" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="P18" s="36" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="Q18" s="36" t="n">
         <v>19.43</v>
       </c>
-      <c r="G18" s="36" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="H18" s="36" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="I18" s="36" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="J18" s="36" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="K18" s="36" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="L18" s="36" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="M18" s="36" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="N18" s="36" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="O18" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="P18" s="36" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="Q18" s="36" t="n">
-        <v>29.14</v>
-      </c>
       <c r="R18" s="36" t="n">
-        <v>25</v>
+        <v>20.29</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>29.57</v>
+        <v>22.29</v>
       </c>
       <c r="T18" s="36" t="n">
-        <v>29.43</v>
+        <v>21.29</v>
       </c>
       <c r="U18" s="36" t="n">
-        <v>21</v>
+        <v>25.14</v>
       </c>
       <c r="V18" s="36" t="n">
-        <v>27.14</v>
+        <v>23.57</v>
       </c>
       <c r="W18" s="36" t="n">
-        <v>25.57</v>
+        <v>26.29</v>
       </c>
       <c r="X18" s="36" t="n">
-        <v>30.29</v>
+        <v>26.43</v>
+      </c>
+      <c r="Y18" s="36" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="Z18" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA18" s="36" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB18" s="36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>9.43</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>0</v>
+        <v>12.43</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>0.5</v>
+        <v>13.29</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>3.33</v>
+        <v>14.71</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>11.71</v>
+        <v>17</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.57</v>
+        <v>19.71</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>20.43</v>
+        <v>17.71</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>21.71</v>
+        <v>19.57</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>15</v>
+        <v>24.14</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>22.71</v>
+        <v>27.57</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>22.43</v>
+        <v>24.43</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>20.14</v>
+        <v>27.29</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>15.71</v>
+        <v>26.57</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>19.43</v>
+        <v>25.57</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>20.29</v>
+        <v>29</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>22.29</v>
+        <v>27.71</v>
       </c>
       <c r="T19" s="36" t="n">
-        <v>21.29</v>
+        <v>32.57</v>
       </c>
       <c r="U19" s="36" t="n">
-        <v>25.14</v>
+        <v>31.57</v>
       </c>
       <c r="V19" s="36" t="n">
-        <v>23.57</v>
+        <v>29.57</v>
       </c>
       <c r="W19" s="36" t="n">
-        <v>26.29</v>
+        <v>29.86</v>
       </c>
       <c r="X19" s="36" t="n">
-        <v>26.43</v>
+        <v>32</v>
+      </c>
+      <c r="Y19" s="36" t="n">
+        <v>32.14</v>
+      </c>
+      <c r="Z19" s="36" t="n">
+        <v>27.14</v>
+      </c>
+      <c r="AA19" s="36" t="n">
+        <v>36.43</v>
+      </c>
+      <c r="AB19" s="36" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -3641,239 +3865,287 @@
       <c r="X20" s="36" t="n">
         <v>23.43</v>
       </c>
+      <c r="Y20" s="36" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="Z20" s="36" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="AA20" s="36" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="AB20" s="36" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>3.33</v>
+        <v>7</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>6.43</v>
+        <v>16</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>19.43</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>15.86</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>14</v>
+        <v>14.86</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>17.14</v>
+        <v>16.71</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>16.14</v>
+        <v>19.71</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>18.57</v>
+        <v>16.86</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>16.14</v>
+        <v>24.86</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>21.71</v>
+        <v>23.43</v>
       </c>
       <c r="N21" s="36" t="n">
-        <v>20.86</v>
+        <v>19.43</v>
       </c>
       <c r="O21" s="36" t="n">
-        <v>20.86</v>
+        <v>25.57</v>
       </c>
       <c r="P21" s="36" t="n">
-        <v>21.86</v>
+        <v>27.43</v>
       </c>
       <c r="Q21" s="36" t="n">
-        <v>28.71</v>
+        <v>29.14</v>
       </c>
       <c r="R21" s="36" t="n">
-        <v>24.71</v>
+        <v>25</v>
       </c>
       <c r="S21" s="36" t="n">
-        <v>24.57</v>
+        <v>29.57</v>
       </c>
       <c r="T21" s="36" t="n">
-        <v>25.29</v>
+        <v>29.43</v>
       </c>
       <c r="U21" s="36" t="n">
-        <v>26.71</v>
+        <v>21</v>
       </c>
       <c r="V21" s="36" t="n">
-        <v>27.57</v>
+        <v>27.14</v>
       </c>
       <c r="W21" s="36" t="n">
-        <v>28.29</v>
+        <v>25.57</v>
       </c>
       <c r="X21" s="36" t="n">
-        <v>21.29</v>
+        <v>30.29</v>
+      </c>
+      <c r="Y21" s="36" t="n">
+        <v>26.57</v>
+      </c>
+      <c r="Z21" s="36" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="AA21" s="36" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="AB21" s="36" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F22" s="36" t="n">
-        <v>2.8</v>
+        <v>5.14</v>
       </c>
       <c r="G22" s="36" t="n">
-        <v>4</v>
+        <v>5.29</v>
       </c>
       <c r="H22" s="36" t="n">
-        <v>6</v>
+        <v>7.86</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>4.43</v>
+        <v>7.14</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>3.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>5.86</v>
+        <v>7.14</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>5.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>7.43</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O22" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P22" s="36" t="n">
-        <v>7.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q22" s="36" t="n">
-        <v>10.29</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="R22" s="36" t="n">
-        <v>7</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S22" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="T22" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>6.86</v>
       </c>
       <c r="U22" s="36" t="n">
-        <v>12.71</v>
+        <v>12.14</v>
       </c>
       <c r="V22" s="36" t="n">
-        <v>9.57</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="W22" s="36" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X22" s="36" t="n">
-        <v>14.86</v>
+        <v>9.140000000000001</v>
+      </c>
+      <c r="Y22" s="36" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="Z22" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="36" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G23" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F23" s="36" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G23" s="36" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H23" s="36" t="n">
-        <v>7.86</v>
+        <v>6</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>7.14</v>
+        <v>4.43</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>7.14</v>
+        <v>5.86</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>6</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>8.710000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="O23" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="Q23" s="36" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="R23" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="R23" s="36" t="n">
+      <c r="T23" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="S23" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="T23" s="36" t="n">
-        <v>6.86</v>
-      </c>
       <c r="U23" s="36" t="n">
-        <v>12.14</v>
+        <v>12.71</v>
       </c>
       <c r="V23" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="W23" s="36" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X23" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>14.86</v>
+      </c>
+      <c r="Y23" s="36" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z23" s="36" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="AA23" s="36" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="AB23" s="36" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -3969,6 +4241,22 @@
       </c>
       <c r="X24" s="39">
         <f>AVERAGE(X6:X23)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="39">
+        <f>AVERAGE(Y6:Y23)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="39">
+        <f>AVERAGE(Z6:Z23)</f>
+        <v/>
+      </c>
+      <c r="AA24" s="39">
+        <f>AVERAGE(AA6:AA23)</f>
+        <v/>
+      </c>
+      <c r="AB24" s="39">
+        <f>AVERAGE(AB6:AB23)</f>
         <v/>
       </c>
     </row>
@@ -3983,7 +4271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -4010,6 +4298,10 @@
     <col width="13" customWidth="1" style="20" min="22" max="22"/>
     <col width="13" customWidth="1" style="20" min="23" max="23"/>
     <col width="13" customWidth="1" style="20" min="24" max="24"/>
+    <col width="13" customWidth="1" style="20" min="25" max="25"/>
+    <col width="13" customWidth="1" style="20" min="26" max="26"/>
+    <col width="13" customWidth="1" style="20" min="27" max="27"/>
+    <col width="13" customWidth="1" style="20" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4137,6 +4429,26 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -4257,6 +4569,26 @@
       <c r="X4" s="31" t="inlineStr">
         <is>
           <t>21.09–27.09</t>
+        </is>
+      </c>
+      <c r="Y4" s="31" t="inlineStr">
+        <is>
+          <t>28.09–04.10</t>
+        </is>
+      </c>
+      <c r="Z4" s="31" t="inlineStr">
+        <is>
+          <t>05.10–11.10</t>
+        </is>
+      </c>
+      <c r="AA4" s="31" t="inlineStr">
+        <is>
+          <t>12.10–18.10</t>
+        </is>
+      </c>
+      <c r="AB4" s="31" t="inlineStr">
+        <is>
+          <t>19.10–25.10*</t>
         </is>
       </c>
     </row>
@@ -4333,6 +4665,18 @@
       <c r="X5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="Y5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -4411,6 +4755,18 @@
       <c r="X6" s="40" t="n">
         <v>114593094</v>
       </c>
+      <c r="Y6" s="40" t="n">
+        <v>118746212</v>
+      </c>
+      <c r="Z6" s="40" t="n">
+        <v>101974620</v>
+      </c>
+      <c r="AA6" s="40" t="n">
+        <v>121486853</v>
+      </c>
+      <c r="AB6" s="40" t="n">
+        <v>15825840</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -4489,6 +4845,18 @@
       <c r="X7" s="40" t="n">
         <v>99375298</v>
       </c>
+      <c r="Y7" s="40" t="n">
+        <v>105623451</v>
+      </c>
+      <c r="Z7" s="40" t="n">
+        <v>73957610</v>
+      </c>
+      <c r="AA7" s="40" t="n">
+        <v>96334193</v>
+      </c>
+      <c r="AB7" s="40" t="n">
+        <v>13660584</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -4567,161 +4935,197 @@
       <c r="X8" s="40" t="n">
         <v>73547034</v>
       </c>
+      <c r="Y8" s="40" t="n">
+        <v>84513482</v>
+      </c>
+      <c r="Z8" s="40" t="n">
+        <v>80572023</v>
+      </c>
+      <c r="AA8" s="40" t="n">
+        <v>88660521</v>
+      </c>
+      <c r="AB8" s="40" t="n">
+        <v>13233103</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>15808893</v>
+        <v>3771593</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>14209578</v>
+        <v>17664217</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>30449860</v>
+        <v>21748722</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>32603120</v>
+        <v>38313932</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>35552907</v>
+        <v>49313727</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>31069118</v>
+        <v>41788221</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>40525338</v>
+        <v>36755638</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>42402722</v>
+        <v>43259404</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>42012092</v>
+        <v>68694825</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>58722069</v>
+        <v>48824266</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>48135084</v>
+        <v>57556194</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>44293878</v>
+        <v>38323101</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>41613311</v>
+        <v>40276838</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>43739350</v>
+        <v>45419704</v>
       </c>
       <c r="R9" s="40" t="n">
-        <v>78234960</v>
+        <v>55923182</v>
       </c>
       <c r="S9" s="40" t="n">
-        <v>47535640</v>
+        <v>40248814</v>
       </c>
       <c r="T9" s="40" t="n">
-        <v>59241681</v>
+        <v>50993465</v>
       </c>
       <c r="U9" s="40" t="n">
-        <v>65321829</v>
+        <v>62193580</v>
       </c>
       <c r="V9" s="40" t="n">
-        <v>57895664</v>
+        <v>45202354</v>
       </c>
       <c r="W9" s="40" t="n">
-        <v>63196973</v>
+        <v>45317128</v>
       </c>
       <c r="X9" s="40" t="n">
-        <v>51807160</v>
+        <v>48612400</v>
+      </c>
+      <c r="Y9" s="40" t="n">
+        <v>64209970</v>
+      </c>
+      <c r="Z9" s="40" t="n">
+        <v>38948580</v>
+      </c>
+      <c r="AA9" s="40" t="n">
+        <v>60557072</v>
+      </c>
+      <c r="AB9" s="40" t="n">
+        <v>10905727</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>3771593</v>
+        <v>536260</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>17664217</v>
+        <v>14403556</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>21748722</v>
+        <v>16216832</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>38313932</v>
+        <v>32622053</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>49313727</v>
+        <v>23929705</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>41788221</v>
+        <v>37214538</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>36755638</v>
+        <v>25375430</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>43259404</v>
+        <v>31500087</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>68694825</v>
+        <v>28078687</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>48824266</v>
+        <v>34472458</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>57556194</v>
+        <v>35343350</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>38323101</v>
+        <v>51225290</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>40276838</v>
+        <v>36142612</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>45419704</v>
+        <v>47488940</v>
       </c>
       <c r="R10" s="40" t="n">
-        <v>55923182</v>
+        <v>44805002</v>
       </c>
       <c r="S10" s="40" t="n">
-        <v>40248814</v>
+        <v>43327432</v>
       </c>
       <c r="T10" s="40" t="n">
-        <v>50993465</v>
+        <v>39637968</v>
       </c>
       <c r="U10" s="40" t="n">
-        <v>62193580</v>
+        <v>55199920</v>
       </c>
       <c r="V10" s="40" t="n">
-        <v>45202354</v>
+        <v>50680631</v>
       </c>
       <c r="W10" s="40" t="n">
-        <v>45317128</v>
+        <v>50163008</v>
       </c>
       <c r="X10" s="40" t="n">
-        <v>48612400</v>
+        <v>38778399</v>
+      </c>
+      <c r="Y10" s="40" t="n">
+        <v>50996587</v>
+      </c>
+      <c r="Z10" s="40" t="n">
+        <v>42228986</v>
+      </c>
+      <c r="AA10" s="40" t="n">
+        <v>32767816</v>
+      </c>
+      <c r="AB10" s="40" t="n">
+        <v>9982520</v>
       </c>
     </row>
     <row r="11">
@@ -4801,629 +5205,737 @@
       <c r="X11" s="40" t="n">
         <v>57645111</v>
       </c>
+      <c r="Y11" s="40" t="n">
+        <v>55172528</v>
+      </c>
+      <c r="Z11" s="40" t="n">
+        <v>47962010</v>
+      </c>
+      <c r="AA11" s="40" t="n">
+        <v>43352139</v>
+      </c>
+      <c r="AB11" s="40" t="n">
+        <v>11340600</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>5092853</v>
+        <v>15808893</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>11100161</v>
+        <v>14209578</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>14612055</v>
+        <v>30449860</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>20638987</v>
+        <v>32603120</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>14061352</v>
+        <v>35552907</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>31599148</v>
+        <v>31069118</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>18747614</v>
+        <v>40525338</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>19576415</v>
+        <v>42402722</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>14226838</v>
+        <v>42012092</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>23197145</v>
+        <v>58722069</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>25790711</v>
+        <v>48135084</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>27856115</v>
+        <v>44293878</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>20981901</v>
+        <v>41613311</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>25433123</v>
+        <v>43739350</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>19355230</v>
+        <v>78234960</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>24713836</v>
+        <v>47535640</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>20195634</v>
+        <v>59241681</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>32414171</v>
+        <v>65321829</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>42780769</v>
+        <v>57895664</v>
       </c>
       <c r="W12" s="40" t="n">
-        <v>36755122</v>
+        <v>63196973</v>
       </c>
       <c r="X12" s="40" t="n">
-        <v>38071365</v>
+        <v>51807160</v>
+      </c>
+      <c r="Y12" s="40" t="n">
+        <v>67644051</v>
+      </c>
+      <c r="Z12" s="40" t="n">
+        <v>43897626</v>
+      </c>
+      <c r="AA12" s="40" t="n">
+        <v>68108471</v>
+      </c>
+      <c r="AB12" s="40" t="n">
+        <v>7568429</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>251520</v>
+        <v>530238</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>10351067</v>
+        <v>8544625</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>21091580</v>
+        <v>8387478</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>24243567</v>
+        <v>10570508</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>16381412</v>
+        <v>11896580</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>21591272</v>
+        <v>19614352</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>21904190</v>
+        <v>20966317</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25438080</v>
+        <v>20073400</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>24614280</v>
+        <v>23801493</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28889771</v>
+        <v>27940611</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>44250621</v>
+        <v>27893929</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>29608597</v>
+        <v>29635773</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>25219748</v>
+        <v>19554230</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>28515437</v>
+        <v>23848495</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>35235670</v>
+        <v>24194638</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>38511490</v>
+        <v>20330094</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>40935998</v>
+        <v>26044199</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>58966944</v>
+        <v>24608772</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>43378746</v>
+        <v>28079726</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>67522298</v>
+        <v>20968052</v>
       </c>
       <c r="W13" s="40" t="n">
-        <v>44905121</v>
+        <v>29501132</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>43314104</v>
+        <v>30624981</v>
+      </c>
+      <c r="Y13" s="40" t="n">
+        <v>28071639</v>
+      </c>
+      <c r="Z13" s="40" t="n">
+        <v>21021583</v>
+      </c>
+      <c r="AA13" s="40" t="n">
+        <v>29229414</v>
+      </c>
+      <c r="AB13" s="40" t="n">
+        <v>6457629</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>530238</v>
+        <v>251520</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>8544625</v>
+        <v>10351067</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>8387478</v>
+        <v>21091580</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>10570508</v>
+        <v>24243567</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>11896580</v>
+        <v>16381412</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>19614352</v>
+        <v>21591272</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>20966317</v>
+        <v>21904190</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>20073400</v>
+        <v>25438080</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>23801493</v>
+        <v>24614280</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>27940611</v>
+        <v>28889771</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>27893929</v>
+        <v>44250621</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>29635773</v>
+        <v>29608597</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>19554230</v>
+        <v>25219748</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>23848495</v>
+        <v>28515437</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>24194638</v>
+        <v>35235670</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>20330094</v>
+        <v>38511490</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>26044199</v>
+        <v>40935998</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>24608772</v>
+        <v>58966944</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>28079726</v>
+        <v>43378746</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>20968052</v>
+        <v>67522298</v>
       </c>
       <c r="W14" s="40" t="n">
-        <v>29501132</v>
+        <v>44905121</v>
       </c>
       <c r="X14" s="40" t="n">
-        <v>30624981</v>
+        <v>43314104</v>
+      </c>
+      <c r="Y14" s="40" t="n">
+        <v>45152620</v>
+      </c>
+      <c r="Z14" s="40" t="n">
+        <v>33695914</v>
+      </c>
+      <c r="AA14" s="40" t="n">
+        <v>56470370</v>
+      </c>
+      <c r="AB14" s="40" t="n">
+        <v>7316350</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>536260</v>
+        <v>3337146</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>14403556</v>
+        <v>10420206</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>16216832</v>
+        <v>21387685</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>32622053</v>
+        <v>16050448</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>23929705</v>
+        <v>21568794</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>37214538</v>
+        <v>30845816</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>25375430</v>
+        <v>45285935</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>31500087</v>
+        <v>28941455</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>28078687</v>
+        <v>21801828</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>34472458</v>
+        <v>19628570</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>35343350</v>
+        <v>23276090</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>51225290</v>
+        <v>27906254</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>36142612</v>
+        <v>20822247</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>47488940</v>
+        <v>20014322</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>44805002</v>
+        <v>19159625</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>43327432</v>
+        <v>22535696</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>39637968</v>
+        <v>21412810</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>55199920</v>
+        <v>34881782</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>50680631</v>
+        <v>25904024</v>
       </c>
       <c r="W15" s="40" t="n">
-        <v>50163008</v>
+        <v>46961904</v>
       </c>
       <c r="X15" s="40" t="n">
-        <v>38778399</v>
+        <v>42299644</v>
+      </c>
+      <c r="Y15" s="40" t="n">
+        <v>32109759</v>
+      </c>
+      <c r="Z15" s="40" t="n">
+        <v>22714393</v>
+      </c>
+      <c r="AA15" s="40" t="n">
+        <v>52198815</v>
+      </c>
+      <c r="AB15" s="40" t="n">
+        <v>10446420</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>11884771</v>
+        <v>5092853</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>10651216</v>
+        <v>11100161</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>13882033</v>
+        <v>14612055</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>17812948</v>
+        <v>20638987</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>17331854</v>
+        <v>14061352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>26294756</v>
+        <v>31599148</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>24196222</v>
+        <v>18747614</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>22122847</v>
+        <v>19576415</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>31914115</v>
+        <v>14226838</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>32069521</v>
+        <v>23197145</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>38287475</v>
+        <v>25790711</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>28283704</v>
+        <v>27856115</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>27334091</v>
+        <v>20981901</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>36312415</v>
+        <v>25433123</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>39333565</v>
+        <v>19355230</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>28566119</v>
+        <v>24713836</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>40387845</v>
+        <v>20195634</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>39744111</v>
+        <v>32414171</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>31477917</v>
+        <v>42780769</v>
       </c>
       <c r="W16" s="40" t="n">
-        <v>29910767</v>
+        <v>36755122</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>44620606</v>
+        <v>38071365</v>
+      </c>
+      <c r="Y16" s="40" t="n">
+        <v>34397222</v>
+      </c>
+      <c r="Z16" s="40" t="n">
+        <v>32536036</v>
+      </c>
+      <c r="AA16" s="40" t="n">
+        <v>43911137</v>
+      </c>
+      <c r="AB16" s="40" t="n">
+        <v>2335805</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3337146</v>
+        <v>3249588</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10420206</v>
+        <v>7305524</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>21387685</v>
+        <v>9575225</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>16050448</v>
+        <v>9264589</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>21568794</v>
+        <v>20692424</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>30845816</v>
+        <v>27565767</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>45285935</v>
+        <v>19138015</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>28941455</v>
+        <v>24912292</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>21801828</v>
+        <v>19068954</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>19628570</v>
+        <v>25387051</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>23276090</v>
+        <v>21008637</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>27906254</v>
+        <v>30862574</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>20822247</v>
+        <v>31820447</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>20014322</v>
+        <v>31875986</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>19159625</v>
+        <v>48358034</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>22535696</v>
+        <v>30000524</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>21412810</v>
+        <v>31150016</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>34881782</v>
+        <v>40688796</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>25904024</v>
+        <v>31752550</v>
       </c>
       <c r="W17" s="40" t="n">
-        <v>46961904</v>
+        <v>32778027</v>
       </c>
       <c r="X17" s="40" t="n">
-        <v>42299644</v>
+        <v>21331873</v>
+      </c>
+      <c r="Y17" s="40" t="n">
+        <v>28676177</v>
+      </c>
+      <c r="Z17" s="40" t="n">
+        <v>32596511</v>
+      </c>
+      <c r="AA17" s="40" t="n">
+        <v>53200913</v>
+      </c>
+      <c r="AB17" s="40" t="n">
+        <v>4088670</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>6239584</v>
+        <v>0</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>13803407</v>
+        <v>0</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>28572076</v>
+        <v>363900</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>15282581</v>
+        <v>3736700</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>16594572</v>
+        <v>17796776</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>15223898</v>
+        <v>42724228</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>27696695</v>
+        <v>33036620</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>17717888</v>
+        <v>29649130</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>24163432</v>
+        <v>13949368</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>23623477</v>
+        <v>24539413</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>19145601</v>
+        <v>19087217</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>30157601</v>
+        <v>17139440</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>41172333</v>
+        <v>17746930</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>34303423</v>
+        <v>21437830</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>35044850</v>
+        <v>17616397</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>33519824</v>
+        <v>19360848</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>25969876</v>
+        <v>25377166</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>23835106</v>
+        <v>24702051</v>
       </c>
       <c r="V18" s="40" t="n">
-        <v>27833047</v>
+        <v>26856647</v>
       </c>
       <c r="W18" s="40" t="n">
-        <v>22815382</v>
+        <v>27122255</v>
       </c>
       <c r="X18" s="40" t="n">
-        <v>28299644</v>
+        <v>30650242</v>
+      </c>
+      <c r="Y18" s="40" t="n">
+        <v>21101547</v>
+      </c>
+      <c r="Z18" s="40" t="n">
+        <v>30037062</v>
+      </c>
+      <c r="AA18" s="40" t="n">
+        <v>22123372</v>
+      </c>
+      <c r="AB18" s="40" t="n">
+        <v>4001630</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>11884771</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0</v>
+        <v>10651216</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>363900</v>
+        <v>13882033</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>3736700</v>
+        <v>17812948</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>17796776</v>
+        <v>17331854</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>42724228</v>
+        <v>26294756</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>33036620</v>
+        <v>24196222</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>29649130</v>
+        <v>22122847</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>13949368</v>
+        <v>31914115</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>24539413</v>
+        <v>32069521</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>19087217</v>
+        <v>38287475</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>17139440</v>
+        <v>28283704</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>17746930</v>
+        <v>27334091</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>21437830</v>
+        <v>36312415</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>17616397</v>
+        <v>39333565</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>19360848</v>
+        <v>28566119</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>25377166</v>
+        <v>40387845</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>24702051</v>
+        <v>39744111</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>26856647</v>
+        <v>31477917</v>
       </c>
       <c r="W19" s="40" t="n">
-        <v>27122255</v>
+        <v>29910767</v>
       </c>
       <c r="X19" s="40" t="n">
-        <v>30650242</v>
+        <v>44620606</v>
+      </c>
+      <c r="Y19" s="40" t="n">
+        <v>35679497</v>
+      </c>
+      <c r="Z19" s="40" t="n">
+        <v>25102609</v>
+      </c>
+      <c r="AA19" s="40" t="n">
+        <v>39000780</v>
+      </c>
+      <c r="AB19" s="40" t="n">
+        <v>2897220</v>
       </c>
     </row>
     <row r="20">
@@ -5503,239 +6015,287 @@
       <c r="X20" s="40" t="n">
         <v>26477239</v>
       </c>
+      <c r="Y20" s="40" t="n">
+        <v>31392938</v>
+      </c>
+      <c r="Z20" s="40" t="n">
+        <v>14752034</v>
+      </c>
+      <c r="AA20" s="40" t="n">
+        <v>27021110</v>
+      </c>
+      <c r="AB20" s="40" t="n">
+        <v>3193370</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>3249588</v>
+        <v>6239584</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>7305524</v>
+        <v>13803407</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>9575225</v>
+        <v>28572076</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>9264589</v>
+        <v>15282581</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>20692424</v>
+        <v>16594572</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>27565767</v>
+        <v>15223898</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>19138015</v>
+        <v>27696695</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>24912292</v>
+        <v>17717888</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>19068954</v>
+        <v>24163432</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>25387051</v>
+        <v>23623477</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>21008637</v>
+        <v>19145601</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>30862574</v>
+        <v>30157601</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>31820447</v>
+        <v>41172333</v>
       </c>
       <c r="Q21" s="40" t="n">
-        <v>31875986</v>
+        <v>34303423</v>
       </c>
       <c r="R21" s="40" t="n">
-        <v>48358034</v>
+        <v>35044850</v>
       </c>
       <c r="S21" s="40" t="n">
-        <v>30000524</v>
+        <v>33519824</v>
       </c>
       <c r="T21" s="40" t="n">
-        <v>31150016</v>
+        <v>25969876</v>
       </c>
       <c r="U21" s="40" t="n">
-        <v>40688796</v>
+        <v>23835106</v>
       </c>
       <c r="V21" s="40" t="n">
-        <v>31752550</v>
+        <v>27833047</v>
       </c>
       <c r="W21" s="40" t="n">
-        <v>32778027</v>
+        <v>22815382</v>
       </c>
       <c r="X21" s="40" t="n">
-        <v>21331873</v>
+        <v>28299644</v>
+      </c>
+      <c r="Y21" s="40" t="n">
+        <v>23130899</v>
+      </c>
+      <c r="Z21" s="40" t="n">
+        <v>20390472</v>
+      </c>
+      <c r="AA21" s="40" t="n">
+        <v>25564267</v>
+      </c>
+      <c r="AB21" s="40" t="n">
+        <v>2362507</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>0</v>
+        <v>2474409</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>0</v>
+        <v>4696696</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>1339100</v>
+        <v>6991878</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>5579340</v>
+        <v>4060163</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>9518200</v>
+        <v>7685466</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>11747640</v>
+        <v>10141286</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>3885270</v>
+        <v>6393871</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>8765870</v>
+        <v>4534503</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>4571680</v>
+        <v>7579040</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>3911995</v>
+        <v>9679437</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>9234090</v>
+        <v>6102368</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>5390260</v>
+        <v>4294070</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>4645370</v>
+        <v>5589419</v>
       </c>
       <c r="Q22" s="40" t="n">
-        <v>10400980</v>
+        <v>10264941</v>
       </c>
       <c r="R22" s="40" t="n">
-        <v>6123322</v>
+        <v>6114083</v>
       </c>
       <c r="S22" s="40" t="n">
-        <v>5648770</v>
+        <v>10758755</v>
       </c>
       <c r="T22" s="40" t="n">
-        <v>6880660</v>
+        <v>6048269</v>
       </c>
       <c r="U22" s="40" t="n">
-        <v>10209080</v>
+        <v>9823030</v>
       </c>
       <c r="V22" s="40" t="n">
-        <v>17909229</v>
+        <v>7263590</v>
       </c>
       <c r="W22" s="40" t="n">
-        <v>9500343</v>
+        <v>14940492</v>
       </c>
       <c r="X22" s="40" t="n">
-        <v>19439125</v>
+        <v>8868985</v>
+      </c>
+      <c r="Y22" s="40" t="n">
+        <v>13151700</v>
+      </c>
+      <c r="Z22" s="40" t="n">
+        <v>7846730</v>
+      </c>
+      <c r="AA22" s="40" t="n">
+        <v>5590930</v>
+      </c>
+      <c r="AB22" s="40" t="n">
+        <v>1595128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>2474409</v>
+        <v>0</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>4696696</v>
+        <v>0</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>6991878</v>
+        <v>1339100</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>4060163</v>
+        <v>5579340</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>7685466</v>
+        <v>9518200</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>10141286</v>
+        <v>11747640</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>6393871</v>
+        <v>3885270</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>4534503</v>
+        <v>8765870</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>7579040</v>
+        <v>4571680</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>9679437</v>
+        <v>3911995</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>6102368</v>
+        <v>9234090</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>4294070</v>
+        <v>5390260</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>5589419</v>
+        <v>4645370</v>
       </c>
       <c r="Q23" s="40" t="n">
-        <v>10264941</v>
+        <v>10400980</v>
       </c>
       <c r="R23" s="40" t="n">
-        <v>6114083</v>
+        <v>6123322</v>
       </c>
       <c r="S23" s="40" t="n">
-        <v>10758755</v>
+        <v>5648770</v>
       </c>
       <c r="T23" s="40" t="n">
-        <v>6048269</v>
+        <v>6880660</v>
       </c>
       <c r="U23" s="40" t="n">
-        <v>9823030</v>
+        <v>10209080</v>
       </c>
       <c r="V23" s="40" t="n">
-        <v>7263590</v>
+        <v>17909229</v>
       </c>
       <c r="W23" s="40" t="n">
-        <v>14940492</v>
+        <v>9500343</v>
       </c>
       <c r="X23" s="40" t="n">
-        <v>8868985</v>
+        <v>19439125</v>
+      </c>
+      <c r="Y23" s="40" t="n">
+        <v>9558790</v>
+      </c>
+      <c r="Z23" s="40" t="n">
+        <v>7475060</v>
+      </c>
+      <c r="AA23" s="40" t="n">
+        <v>12183598</v>
+      </c>
+      <c r="AB23" s="40" t="n">
+        <v>390230</v>
       </c>
     </row>
     <row r="24">
@@ -5831,6 +6391,22 @@
       </c>
       <c r="X24" s="41">
         <f>AVERAGE(X6:X23)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="41">
+        <f>AVERAGE(Y6:Y23)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="41">
+        <f>AVERAGE(Z6:Z23)</f>
+        <v/>
+      </c>
+      <c r="AA24" s="41">
+        <f>AVERAGE(AA6:AA23)</f>
+        <v/>
+      </c>
+      <c r="AB24" s="41">
+        <f>AVERAGE(AB6:AB23)</f>
         <v/>
       </c>
     </row>
@@ -5845,7 +6421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:AB24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -5872,6 +6448,10 @@
     <col width="13" customWidth="1" style="20" min="22" max="22"/>
     <col width="13" customWidth="1" style="20" min="23" max="23"/>
     <col width="13" customWidth="1" style="20" min="24" max="24"/>
+    <col width="13" customWidth="1" style="20" min="25" max="25"/>
+    <col width="13" customWidth="1" style="20" min="26" max="26"/>
+    <col width="13" customWidth="1" style="20" min="27" max="27"/>
+    <col width="13" customWidth="1" style="20" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5999,6 +6579,26 @@
           <t>2026-09-21</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -6119,6 +6719,26 @@
       <c r="X4" s="31" t="inlineStr">
         <is>
           <t>21.09–27.09</t>
+        </is>
+      </c>
+      <c r="Y4" s="31" t="inlineStr">
+        <is>
+          <t>28.09–04.10</t>
+        </is>
+      </c>
+      <c r="Z4" s="31" t="inlineStr">
+        <is>
+          <t>05.10–11.10</t>
+        </is>
+      </c>
+      <c r="AA4" s="31" t="inlineStr">
+        <is>
+          <t>12.10–18.10</t>
+        </is>
+      </c>
+      <c r="AB4" s="31" t="inlineStr">
+        <is>
+          <t>19.10–25.10*</t>
         </is>
       </c>
     </row>
@@ -6195,6 +6815,18 @@
       <c r="X5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="Y5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA5" s="34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -6273,6 +6905,18 @@
       <c r="X6" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="Y6" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z6" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA6" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB6" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -6351,6 +6995,18 @@
       <c r="X7" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="Y7" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z7" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA7" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB7" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -6429,23 +7085,35 @@
       <c r="X8" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="Y8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z8" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB8" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
@@ -6506,24 +7174,36 @@
       </c>
       <c r="X9" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="Y9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA9" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB9" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>7</v>
@@ -6584,6 +7264,18 @@
       </c>
       <c r="X10" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="Y10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB10" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -6663,23 +7355,35 @@
       <c r="X11" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="Y11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z11" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA11" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB11" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -6740,99 +7444,123 @@
       </c>
       <c r="X12" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="Y12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB12" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z13" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB13" s="42" t="n">
         <v>1</v>
-      </c>
-      <c r="D13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X13" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="42" t="n">
         <v>7</v>
@@ -6896,24 +7624,36 @@
       </c>
       <c r="X14" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="Y14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB14" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -6974,24 +7714,36 @@
       </c>
       <c r="X15" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="Y15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z15" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB15" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -7052,24 +7804,36 @@
       </c>
       <c r="X16" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="Y16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB16" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -7130,33 +7894,45 @@
       </c>
       <c r="X17" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="Y17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB17" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="42" t="n">
         <v>7</v>
@@ -7208,33 +7984,45 @@
       </c>
       <c r="X18" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="Y18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA18" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB18" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -7286,6 +8074,18 @@
       </c>
       <c r="X19" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="Y19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB19" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -7365,23 +8165,35 @@
       <c r="X20" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="Y20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA20" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB20" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" s="42" t="n">
         <v>7</v>
@@ -7442,30 +8254,42 @@
       </c>
       <c r="X21" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="Y21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA21" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB21" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F22" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G22" s="42" t="n">
         <v>7</v>
@@ -7486,7 +8310,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N22" s="42" t="n">
         <v>7</v>
@@ -7520,30 +8344,42 @@
       </c>
       <c r="X22" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="Y22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA22" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB22" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F23" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G23" s="42" t="n">
         <v>7</v>
@@ -7564,7 +8400,7 @@
         <v>7</v>
       </c>
       <c r="M23" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N23" s="42" t="n">
         <v>7</v>
@@ -7598,6 +8434,18 @@
       </c>
       <c r="X23" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="Y23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB23" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -7695,6 +8543,22 @@
         <f>AVERAGE(X6:X23)</f>
         <v/>
       </c>
+      <c r="Y24" s="43">
+        <f>AVERAGE(Y6:Y23)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="43">
+        <f>AVERAGE(Z6:Z23)</f>
+        <v/>
+      </c>
+      <c r="AA24" s="43">
+        <f>AVERAGE(AA6:AA23)</f>
+        <v/>
+      </c>
+      <c r="AB24" s="43">
+        <f>AVERAGE(AB6:AB23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1555,7 +1555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" style="20" min="1" max="1"/>
@@ -1564,6 +1564,7 @@
     <col width="15" customWidth="1" style="20" min="4" max="4"/>
     <col width="15" customWidth="1" style="20" min="5" max="5"/>
     <col width="15" customWidth="1" style="20" min="6" max="6"/>
+    <col width="15" customWidth="1" style="20" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1581,24 +1582,29 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-08</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -1631,6 +1637,11 @@
       <c r="F4" s="31" t="inlineStr">
         <is>
           <t>август 2026</t>
+        </is>
+      </c>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>сентябрь 2026</t>
         </is>
       </c>
     </row>
@@ -1653,6 +1664,9 @@
       <c r="F5" s="34" t="n">
         <v>31</v>
       </c>
+      <c r="G5" s="34" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -1677,6 +1691,9 @@
       <c r="F6" s="40" t="n">
         <v>20453791</v>
       </c>
+      <c r="G6" s="40" t="n">
+        <v>22046821</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -1701,6 +1718,9 @@
       <c r="F7" s="40" t="n">
         <v>20988887</v>
       </c>
+      <c r="G7" s="40" t="n">
+        <v>27830391</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -1725,6 +1745,9 @@
       <c r="F8" s="40" t="n">
         <v>17400000</v>
       </c>
+      <c r="G8" s="40" t="n">
+        <v>16704000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
@@ -1749,6 +1772,9 @@
       <c r="F9" s="40" t="n">
         <v>17400000</v>
       </c>
+      <c r="G9" s="40" t="n">
+        <v>16680000</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
@@ -1773,6 +1799,9 @@
       <c r="F10" s="40" t="n">
         <v>14000000</v>
       </c>
+      <c r="G10" s="40" t="n">
+        <v>13616000</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
@@ -1797,6 +1826,9 @@
       <c r="F11" s="40" t="n">
         <v>17899610</v>
       </c>
+      <c r="G11" s="40" t="n">
+        <v>17879748</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
@@ -1821,6 +1853,9 @@
       <c r="F12" s="40" t="n">
         <v>17400000</v>
       </c>
+      <c r="G12" s="40" t="n">
+        <v>17040000</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
@@ -1845,6 +1880,9 @@
       <c r="F13" s="40" t="n">
         <v>17400000</v>
       </c>
+      <c r="G13" s="40" t="n">
+        <v>16542000</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
@@ -1869,6 +1907,9 @@
       <c r="F14" s="40" t="n">
         <v>14000000</v>
       </c>
+      <c r="G14" s="40" t="n">
+        <v>13202000</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
@@ -1893,6 +1934,9 @@
       <c r="F15" s="40" t="n">
         <v>14000000</v>
       </c>
+      <c r="G15" s="40" t="n">
+        <v>13646000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
@@ -1917,6 +1961,9 @@
       <c r="F16" s="40" t="n">
         <v>17400000</v>
       </c>
+      <c r="G16" s="40" t="n">
+        <v>16572000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
@@ -1941,6 +1988,9 @@
       <c r="F17" s="40" t="n">
         <v>14000000</v>
       </c>
+      <c r="G17" s="40" t="n">
+        <v>13184000</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
@@ -1965,6 +2015,9 @@
       <c r="F18" s="40" t="n">
         <v>14000000</v>
       </c>
+      <c r="G18" s="40" t="n">
+        <v>13604000</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
@@ -1989,6 +2042,9 @@
       <c r="F19" s="40" t="n">
         <v>14000000</v>
       </c>
+      <c r="G19" s="40" t="n">
+        <v>13556000</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
@@ -2013,6 +2069,9 @@
       <c r="F20" s="40" t="n">
         <v>14000000</v>
       </c>
+      <c r="G20" s="40" t="n">
+        <v>13538000</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
@@ -2037,6 +2096,9 @@
       <c r="F21" s="40" t="n">
         <v>17400000</v>
       </c>
+      <c r="G21" s="40" t="n">
+        <v>17196000</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
@@ -2061,6 +2123,9 @@
       <c r="F22" s="40" t="n">
         <v>11400000</v>
       </c>
+      <c r="G22" s="40" t="n">
+        <v>11100000</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -2084,6 +2149,9 @@
       </c>
       <c r="F23" s="40" t="n">
         <v>14000000</v>
+      </c>
+      <c r="G23" s="40" t="n">
+        <v>13718000</v>
       </c>
     </row>
     <row r="24">
@@ -2107,6 +2175,10 @@
       </c>
       <c r="F24" s="41">
         <f>SUM(F6:F23)</f>
+        <v/>
+      </c>
+      <c r="G24" s="41">
+        <f>SUM(G6:G23)</f>
         <v/>
       </c>
     </row>
@@ -2169,132 +2241,132 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="19" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="19" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="19" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="19" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="19" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="19" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="19" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V3" s="19" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W3" s="19" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X3" s="19" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" s="19" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z3" s="19" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA3" s="19" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB3" s="19" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -4319,132 +4391,132 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="19" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="19" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="19" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="19" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="19" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="19" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="19" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V3" s="19" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W3" s="19" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X3" s="19" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" s="19" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z3" s="19" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA3" s="19" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB3" s="19" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -6469,132 +6541,132 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="19" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="19" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="19" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="19" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="19" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="19" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="19" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="19" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="19" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="19" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" s="19" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="19" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="19" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="19" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V3" s="19" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W3" s="19" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X3" s="19" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" s="19" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z3" s="19" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA3" s="19" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB3" s="19" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -1582,27 +1582,27 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="19" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="19" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
@@ -2241,132 +2241,132 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" s="19" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" s="19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" s="19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" s="19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" s="19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V3" s="19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="W3" s="19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X3" s="19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="Y3" s="19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="Z3" s="19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AA3" s="19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AB3" s="19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -2597,7 +2597,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2687,187 +2687,187 @@
         <v>120</v>
       </c>
       <c r="AB6" s="36" t="n">
-        <v>152</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>29.43</v>
+        <v>7.33</v>
       </c>
       <c r="F7" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G7" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H7" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I7" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J7" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="G7" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="H7" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I7" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J7" s="36" t="n">
-        <v>63</v>
-      </c>
       <c r="K7" s="36" t="n">
-        <v>55.43</v>
+        <v>43.86</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>69.56999999999999</v>
+        <v>50.14</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>59</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>76.86</v>
+        <v>53.71</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>46.57</v>
       </c>
       <c r="P7" s="36" t="n">
-        <v>71.43000000000001</v>
+        <v>49.29</v>
       </c>
       <c r="Q7" s="36" t="n">
-        <v>78.86</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R7" s="36" t="n">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="S7" s="36" t="n">
+        <v>61</v>
+      </c>
+      <c r="T7" s="36" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="U7" s="36" t="n">
+        <v>68</v>
+      </c>
+      <c r="V7" s="36" t="n">
+        <v>77.56999999999999</v>
+      </c>
+      <c r="W7" s="36" t="n">
+        <v>71</v>
+      </c>
+      <c r="X7" s="36" t="n">
+        <v>68.43000000000001</v>
+      </c>
+      <c r="Y7" s="36" t="n">
         <v>78.43000000000001</v>
       </c>
-      <c r="S7" s="36" t="n">
-        <v>72.43000000000001</v>
-      </c>
-      <c r="T7" s="36" t="n">
-        <v>92.14</v>
-      </c>
-      <c r="U7" s="36" t="n">
-        <v>91</v>
-      </c>
-      <c r="V7" s="36" t="n">
-        <v>85.43000000000001</v>
-      </c>
-      <c r="W7" s="36" t="n">
-        <v>88.56999999999999</v>
-      </c>
-      <c r="X7" s="36" t="n">
-        <v>80.70999999999999</v>
-      </c>
-      <c r="Y7" s="36" t="n">
-        <v>101.29</v>
-      </c>
       <c r="Z7" s="36" t="n">
-        <v>76.14</v>
+        <v>78.17</v>
       </c>
       <c r="AA7" s="36" t="n">
-        <v>90.14</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="AB7" s="36" t="n">
-        <v>127</v>
+        <v>95.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>7.33</v>
+        <v>29.43</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>17.86</v>
+        <v>38</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>22.14</v>
+        <v>41.29</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>24.86</v>
+        <v>51.43</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>36.57</v>
+        <v>58.29</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>43.86</v>
+        <v>55.43</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>50.14</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>59</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>53.71</v>
+        <v>76.86</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>46.57</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>49.29</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="Q8" s="36" t="n">
-        <v>65.56999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="R8" s="36" t="n">
-        <v>67.29000000000001</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="S8" s="36" t="n">
-        <v>61</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="T8" s="36" t="n">
-        <v>64.43000000000001</v>
+        <v>92.14</v>
       </c>
       <c r="U8" s="36" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="V8" s="36" t="n">
-        <v>77.56999999999999</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="W8" s="36" t="n">
-        <v>71</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="X8" s="36" t="n">
-        <v>68.43000000000001</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="Y8" s="36" t="n">
-        <v>78.43000000000001</v>
+        <v>101.29</v>
       </c>
       <c r="Z8" s="36" t="n">
-        <v>78.17</v>
+        <v>76.14</v>
       </c>
       <c r="AA8" s="36" t="n">
-        <v>78.56999999999999</v>
+        <v>90.14</v>
       </c>
       <c r="AB8" s="36" t="n">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9">
@@ -2957,907 +2957,907 @@
         <v>57.14</v>
       </c>
       <c r="AB9" s="36" t="n">
-        <v>69</v>
+        <v>67.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>1.67</v>
+        <v>14.29</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>12.14</v>
+        <v>19.14</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>16.57</v>
+        <v>26.71</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>21</v>
+        <v>28.14</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>20.29</v>
+        <v>28.57</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>28.57</v>
+        <v>31.57</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>24.14</v>
+        <v>33</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>27.57</v>
+        <v>34.86</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>28.14</v>
+        <v>41.29</v>
       </c>
       <c r="M10" s="36" t="n">
-        <v>28.86</v>
+        <v>41.43</v>
       </c>
       <c r="N10" s="36" t="n">
-        <v>33.14</v>
+        <v>46.14</v>
       </c>
       <c r="O10" s="36" t="n">
-        <v>30.71</v>
+        <v>41.57</v>
       </c>
       <c r="P10" s="36" t="n">
-        <v>31.14</v>
+        <v>51.86</v>
       </c>
       <c r="Q10" s="36" t="n">
-        <v>40.29</v>
+        <v>48.71</v>
       </c>
       <c r="R10" s="36" t="n">
-        <v>38.71</v>
+        <v>45.14</v>
       </c>
       <c r="S10" s="36" t="n">
-        <v>43.14</v>
+        <v>50.71</v>
       </c>
       <c r="T10" s="36" t="n">
-        <v>37</v>
+        <v>60.71</v>
       </c>
       <c r="U10" s="36" t="n">
-        <v>46.29</v>
+        <v>66.86</v>
       </c>
       <c r="V10" s="36" t="n">
-        <v>43.14</v>
+        <v>63.29</v>
       </c>
       <c r="W10" s="36" t="n">
-        <v>36.86</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="X10" s="36" t="n">
-        <v>33.43</v>
+        <v>61.43</v>
       </c>
       <c r="Y10" s="36" t="n">
-        <v>48</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="Z10" s="36" t="n">
-        <v>39.86</v>
+        <v>50.86</v>
       </c>
       <c r="AA10" s="36" t="n">
-        <v>37.14</v>
+        <v>63.71</v>
       </c>
       <c r="AB10" s="36" t="n">
-        <v>59</v>
+        <v>55.33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>8.43</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>13.43</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>21.71</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>16.57</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>21.29</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>21.14</v>
       </c>
       <c r="J11" s="36" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="K11" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="L11" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="M11" s="36" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="N11" s="36" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="O11" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="P11" s="36" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="Q11" s="36" t="n">
         <v>31.29</v>
       </c>
-      <c r="K11" s="36" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="L11" s="36" t="n">
+      <c r="R11" s="36" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="S11" s="36" t="n">
+        <v>31</v>
+      </c>
+      <c r="T11" s="36" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="U11" s="36" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="V11" s="36" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="W11" s="36" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="X11" s="36" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="Y11" s="36" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z11" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="M11" s="36" t="n">
-        <v>42.43</v>
-      </c>
-      <c r="N11" s="36" t="n">
-        <v>38.57</v>
-      </c>
-      <c r="O11" s="36" t="n">
-        <v>34.29</v>
-      </c>
-      <c r="P11" s="36" t="n">
-        <v>37.86</v>
-      </c>
-      <c r="Q11" s="36" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="R11" s="36" t="n">
-        <v>40.71</v>
-      </c>
-      <c r="S11" s="36" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="T11" s="36" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="U11" s="36" t="n">
-        <v>55.29</v>
-      </c>
-      <c r="V11" s="36" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="W11" s="36" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="X11" s="36" t="n">
-        <v>49.57</v>
-      </c>
-      <c r="Y11" s="36" t="n">
-        <v>47.86</v>
-      </c>
-      <c r="Z11" s="36" t="n">
-        <v>46</v>
-      </c>
       <c r="AA11" s="36" t="n">
-        <v>45.14</v>
+        <v>51.14</v>
       </c>
       <c r="AB11" s="36" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>14.29</v>
+        <v>0</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>19.14</v>
+        <v>8</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>26.71</v>
+        <v>13.14</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>28.14</v>
+        <v>19.43</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>28.57</v>
+        <v>26.43</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>31.57</v>
+        <v>32.29</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>33</v>
+        <v>31.29</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>34.86</v>
+        <v>33.57</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>41.29</v>
+        <v>40</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>41.43</v>
+        <v>42.43</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>46.14</v>
+        <v>38.57</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>41.57</v>
+        <v>34.29</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>51.86</v>
+        <v>37.86</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>48.71</v>
+        <v>42.86</v>
       </c>
       <c r="R12" s="36" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="S12" s="36" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="T12" s="36" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="U12" s="36" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="V12" s="36" t="n">
+        <v>46.29</v>
+      </c>
+      <c r="W12" s="36" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="X12" s="36" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="Y12" s="36" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="Z12" s="36" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA12" s="36" t="n">
         <v>45.14</v>
       </c>
-      <c r="S12" s="36" t="n">
-        <v>50.71</v>
-      </c>
-      <c r="T12" s="36" t="n">
-        <v>60.71</v>
-      </c>
-      <c r="U12" s="36" t="n">
-        <v>66.86</v>
-      </c>
-      <c r="V12" s="36" t="n">
-        <v>63.29</v>
-      </c>
-      <c r="W12" s="36" t="n">
-        <v>65.29000000000001</v>
-      </c>
-      <c r="X12" s="36" t="n">
-        <v>61.43</v>
-      </c>
-      <c r="Y12" s="36" t="n">
-        <v>66.29000000000001</v>
-      </c>
-      <c r="Z12" s="36" t="n">
-        <v>50.86</v>
-      </c>
-      <c r="AA12" s="36" t="n">
-        <v>63.71</v>
-      </c>
       <c r="AB12" s="36" t="n">
-        <v>52</v>
+        <v>46.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>1.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>11</v>
+        <v>12.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>14.43</v>
+        <v>16.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>11.86</v>
+        <v>21</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>18</v>
+        <v>20.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>19.14</v>
+        <v>28.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>21</v>
+        <v>24.14</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>23.43</v>
+        <v>27.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>20.43</v>
+        <v>28.14</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>24.57</v>
+        <v>28.86</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>24.14</v>
+        <v>33.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>24.43</v>
+        <v>30.71</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>22</v>
+        <v>31.14</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>23</v>
+        <v>40.29</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>18.43</v>
+        <v>38.71</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>24.71</v>
+        <v>43.14</v>
       </c>
       <c r="T13" s="36" t="n">
-        <v>27.57</v>
+        <v>37</v>
       </c>
       <c r="U13" s="36" t="n">
-        <v>30</v>
+        <v>46.29</v>
       </c>
       <c r="V13" s="36" t="n">
-        <v>28.57</v>
+        <v>43.14</v>
       </c>
       <c r="W13" s="36" t="n">
-        <v>30.14</v>
+        <v>36.86</v>
       </c>
       <c r="X13" s="36" t="n">
-        <v>34.43</v>
+        <v>33.43</v>
       </c>
       <c r="Y13" s="36" t="n">
-        <v>33.43</v>
+        <v>48</v>
       </c>
       <c r="Z13" s="36" t="n">
-        <v>32</v>
+        <v>39.86</v>
       </c>
       <c r="AA13" s="36" t="n">
-        <v>31.29</v>
+        <v>37.14</v>
       </c>
       <c r="AB13" s="36" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>8.43</v>
+        <v>6.67</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>13.43</v>
+        <v>11.29</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>21.71</v>
+        <v>10.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>16.57</v>
+        <v>11.14</v>
       </c>
       <c r="H14" s="36" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="I14" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="J14" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="K14" s="36" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="L14" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="M14" s="36" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="N14" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="O14" s="36" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="P14" s="36" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="Q14" s="36" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="R14" s="36" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="S14" s="36" t="n">
         <v>21.29</v>
       </c>
-      <c r="I14" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="J14" s="36" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="K14" s="36" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="L14" s="36" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="M14" s="36" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="N14" s="36" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="O14" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="P14" s="36" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="Q14" s="36" t="n">
-        <v>31.29</v>
-      </c>
-      <c r="R14" s="36" t="n">
-        <v>36.14</v>
-      </c>
-      <c r="S14" s="36" t="n">
-        <v>31</v>
-      </c>
       <c r="T14" s="36" t="n">
-        <v>37.71</v>
+        <v>29.14</v>
       </c>
       <c r="U14" s="36" t="n">
-        <v>39.29</v>
+        <v>31.43</v>
       </c>
       <c r="V14" s="36" t="n">
-        <v>45.86</v>
+        <v>35.71</v>
       </c>
       <c r="W14" s="36" t="n">
-        <v>45.14</v>
+        <v>40.71</v>
       </c>
       <c r="X14" s="36" t="n">
-        <v>41.86</v>
+        <v>46.86</v>
       </c>
       <c r="Y14" s="36" t="n">
-        <v>48</v>
+        <v>44.71</v>
       </c>
       <c r="Z14" s="36" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="AA14" s="36" t="n">
-        <v>51.14</v>
+        <v>52.57</v>
       </c>
       <c r="AB14" s="36" t="n">
-        <v>48</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>3</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>7.14</v>
+        <v>11</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13.43</v>
+        <v>14.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>12.71</v>
+        <v>11.86</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>14.43</v>
+        <v>18</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19</v>
+        <v>19.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>21.14</v>
+        <v>21</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>18.57</v>
+        <v>23.43</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>16.57</v>
+        <v>20.43</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>14.71</v>
+        <v>24.57</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>19.14</v>
+        <v>24.14</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>18</v>
+        <v>24.43</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>15.29</v>
+        <v>22</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>15.29</v>
+        <v>23</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>18.71</v>
+        <v>18.43</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>18</v>
+        <v>24.71</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>25.29</v>
+        <v>27.57</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>28.86</v>
+        <v>30</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>24</v>
+        <v>28.57</v>
       </c>
       <c r="W15" s="36" t="n">
-        <v>29.29</v>
+        <v>30.14</v>
       </c>
       <c r="X15" s="36" t="n">
-        <v>31.71</v>
+        <v>34.43</v>
       </c>
       <c r="Y15" s="36" t="n">
-        <v>27</v>
+        <v>33.43</v>
       </c>
       <c r="Z15" s="36" t="n">
-        <v>23.83</v>
+        <v>32</v>
       </c>
       <c r="AA15" s="36" t="n">
-        <v>34.71</v>
+        <v>31.29</v>
       </c>
       <c r="AB15" s="36" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>6.67</v>
+        <v>3</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11.29</v>
+        <v>7.14</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>10.57</v>
+        <v>13.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>11.14</v>
+        <v>12.71</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>13.86</v>
+        <v>14.43</v>
       </c>
       <c r="I16" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="J16" s="36" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K16" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L16" s="36" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="M16" s="36" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="N16" s="36" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="O16" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="J16" s="36" t="n">
+      <c r="P16" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="Q16" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="R16" s="36" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="S16" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="K16" s="36" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="L16" s="36" t="n">
-        <v>15.29</v>
-      </c>
-      <c r="M16" s="36" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="N16" s="36" t="n">
-        <v>24.71</v>
-      </c>
-      <c r="O16" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="P16" s="36" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="Q16" s="36" t="n">
-        <v>25.43</v>
-      </c>
-      <c r="R16" s="36" t="n">
-        <v>22.57</v>
-      </c>
-      <c r="S16" s="36" t="n">
-        <v>21.29</v>
-      </c>
       <c r="T16" s="36" t="n">
-        <v>29.14</v>
+        <v>25.29</v>
       </c>
       <c r="U16" s="36" t="n">
-        <v>31.43</v>
+        <v>28.86</v>
       </c>
       <c r="V16" s="36" t="n">
-        <v>35.71</v>
+        <v>24</v>
       </c>
       <c r="W16" s="36" t="n">
-        <v>40.71</v>
+        <v>29.29</v>
       </c>
       <c r="X16" s="36" t="n">
-        <v>46.86</v>
+        <v>31.71</v>
       </c>
       <c r="Y16" s="36" t="n">
-        <v>44.71</v>
+        <v>27</v>
       </c>
       <c r="Z16" s="36" t="n">
-        <v>37</v>
+        <v>23.83</v>
       </c>
       <c r="AA16" s="36" t="n">
-        <v>52.57</v>
+        <v>34.71</v>
       </c>
       <c r="AB16" s="36" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3.33</v>
+        <v>9.43</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>6.43</v>
+        <v>12.43</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.14</v>
+        <v>19.71</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>16.14</v>
+        <v>17.71</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>18.57</v>
+        <v>19.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.14</v>
+        <v>24.14</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>21.71</v>
+        <v>27.57</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>20.86</v>
+        <v>24.43</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>20.86</v>
+        <v>27.29</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>21.86</v>
+        <v>26.57</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>28.71</v>
+        <v>25.57</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>24.71</v>
+        <v>29</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>24.57</v>
+        <v>27.71</v>
       </c>
       <c r="T17" s="36" t="n">
-        <v>25.29</v>
+        <v>32.57</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>26.71</v>
+        <v>31.57</v>
       </c>
       <c r="V17" s="36" t="n">
-        <v>27.57</v>
+        <v>29.57</v>
       </c>
       <c r="W17" s="36" t="n">
-        <v>28.29</v>
+        <v>29.86</v>
       </c>
       <c r="X17" s="36" t="n">
-        <v>21.29</v>
+        <v>32</v>
       </c>
       <c r="Y17" s="36" t="n">
-        <v>27</v>
+        <v>32.14</v>
       </c>
       <c r="Z17" s="36" t="n">
-        <v>25.43</v>
+        <v>27.14</v>
       </c>
       <c r="AA17" s="36" t="n">
-        <v>30.29</v>
+        <v>36.43</v>
       </c>
       <c r="AB17" s="36" t="n">
-        <v>31</v>
+        <v>33.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>0</v>
+        <v>6.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>0.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>3.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>11.71</v>
+        <v>14</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.57</v>
+        <v>17.14</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>20.43</v>
+        <v>16.14</v>
       </c>
       <c r="K18" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L18" s="36" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="M18" s="36" t="n">
         <v>21.71</v>
       </c>
-      <c r="L18" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="M18" s="36" t="n">
-        <v>22.71</v>
-      </c>
       <c r="N18" s="36" t="n">
-        <v>22.43</v>
+        <v>20.86</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>20.14</v>
+        <v>20.86</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>15.71</v>
+        <v>21.86</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>19.43</v>
+        <v>28.71</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>20.29</v>
+        <v>24.71</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>22.29</v>
+        <v>24.57</v>
       </c>
       <c r="T18" s="36" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="U18" s="36" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="V18" s="36" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="W18" s="36" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="X18" s="36" t="n">
         <v>21.29</v>
       </c>
-      <c r="U18" s="36" t="n">
-        <v>25.14</v>
-      </c>
-      <c r="V18" s="36" t="n">
-        <v>23.57</v>
-      </c>
-      <c r="W18" s="36" t="n">
-        <v>26.29</v>
-      </c>
-      <c r="X18" s="36" t="n">
-        <v>26.43</v>
-      </c>
       <c r="Y18" s="36" t="n">
-        <v>23.71</v>
+        <v>27</v>
       </c>
       <c r="Z18" s="36" t="n">
-        <v>22</v>
+        <v>25.43</v>
       </c>
       <c r="AA18" s="36" t="n">
-        <v>29</v>
+        <v>30.29</v>
       </c>
       <c r="AB18" s="36" t="n">
-        <v>30</v>
+        <v>31.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>12.43</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>13.29</v>
+        <v>0.5</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>14.71</v>
+        <v>3.33</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>17</v>
+        <v>11.71</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>19.71</v>
+        <v>17.57</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>17.71</v>
+        <v>20.43</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>19.57</v>
+        <v>21.71</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>24.14</v>
+        <v>15</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>27.57</v>
+        <v>22.71</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>24.43</v>
+        <v>22.43</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>27.29</v>
+        <v>20.14</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>26.57</v>
+        <v>15.71</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>25.57</v>
+        <v>19.43</v>
       </c>
       <c r="R19" s="36" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="S19" s="36" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="T19" s="36" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="U19" s="36" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="V19" s="36" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="W19" s="36" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="X19" s="36" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="Y19" s="36" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="Z19" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA19" s="36" t="n">
         <v>29</v>
       </c>
-      <c r="S19" s="36" t="n">
-        <v>27.71</v>
-      </c>
-      <c r="T19" s="36" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="U19" s="36" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="V19" s="36" t="n">
-        <v>29.57</v>
-      </c>
-      <c r="W19" s="36" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="X19" s="36" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y19" s="36" t="n">
-        <v>32.14</v>
-      </c>
-      <c r="Z19" s="36" t="n">
-        <v>27.14</v>
-      </c>
-      <c r="AA19" s="36" t="n">
-        <v>36.43</v>
-      </c>
       <c r="AB19" s="36" t="n">
-        <v>28</v>
+        <v>29.67</v>
       </c>
     </row>
     <row r="20">
@@ -3947,7 +3947,7 @@
         <v>25.29</v>
       </c>
       <c r="AB20" s="36" t="n">
-        <v>23</v>
+        <v>28.67</v>
       </c>
     </row>
     <row r="21">
@@ -4037,7 +4037,7 @@
         <v>27.43</v>
       </c>
       <c r="AB21" s="36" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -4127,7 +4127,7 @@
         <v>8</v>
       </c>
       <c r="AB22" s="36" t="n">
-        <v>18</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="23">
@@ -4217,7 +4217,7 @@
         <v>11.43</v>
       </c>
       <c r="AB23" s="36" t="n">
-        <v>6</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="24">
@@ -4391,132 +4391,132 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" s="19" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" s="19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" s="19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" s="19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" s="19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V3" s="19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="W3" s="19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X3" s="19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="Y3" s="19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="Z3" s="19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AA3" s="19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AB3" s="19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -4747,7 +4747,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4837,187 +4837,187 @@
         <v>121486853</v>
       </c>
       <c r="AB6" s="40" t="n">
-        <v>15825840</v>
+        <v>45347415</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>6122227</v>
+        <v>0</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>31792625</v>
+        <v>2886450</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>49374899</v>
+        <v>22932586</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>38585414</v>
+        <v>24764259</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>51458725</v>
+        <v>32268886</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>61835892</v>
+        <v>42977335</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>80551167</v>
+        <v>44364359</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>61490143</v>
+        <v>53225819</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>68619843</v>
+        <v>51621207</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>81742671</v>
+        <v>58204066</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>69757179</v>
+        <v>58190202</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>68198708</v>
+        <v>46275213</v>
       </c>
       <c r="P7" s="40" t="n">
-        <v>67906121</v>
+        <v>51530060</v>
       </c>
       <c r="Q7" s="40" t="n">
-        <v>84229530</v>
+        <v>85043089</v>
       </c>
       <c r="R7" s="40" t="n">
-        <v>92096471</v>
+        <v>67469168</v>
       </c>
       <c r="S7" s="40" t="n">
-        <v>78023476</v>
+        <v>66040134</v>
       </c>
       <c r="T7" s="40" t="n">
-        <v>89918146</v>
+        <v>80004937</v>
       </c>
       <c r="U7" s="40" t="n">
-        <v>94534230</v>
+        <v>67225139</v>
       </c>
       <c r="V7" s="40" t="n">
-        <v>81100625</v>
+        <v>80820230</v>
       </c>
       <c r="W7" s="40" t="n">
-        <v>109654171</v>
+        <v>73904849</v>
       </c>
       <c r="X7" s="40" t="n">
-        <v>99375298</v>
+        <v>73547034</v>
       </c>
       <c r="Y7" s="40" t="n">
-        <v>105623451</v>
+        <v>84513482</v>
       </c>
       <c r="Z7" s="40" t="n">
-        <v>73957610</v>
+        <v>80572023</v>
       </c>
       <c r="AA7" s="40" t="n">
-        <v>96334193</v>
+        <v>88660521</v>
       </c>
       <c r="AB7" s="40" t="n">
-        <v>13660584</v>
+        <v>42888911</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>0</v>
+        <v>6122227</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>2886450</v>
+        <v>31792625</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>22932586</v>
+        <v>49374899</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>24764259</v>
+        <v>38585414</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>32268886</v>
+        <v>51458725</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>42977335</v>
+        <v>61835892</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>44364359</v>
+        <v>80551167</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>53225819</v>
+        <v>61490143</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>51621207</v>
+        <v>68619843</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>58204066</v>
+        <v>81742671</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>58190202</v>
+        <v>69757179</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>46275213</v>
+        <v>68198708</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>51530060</v>
+        <v>67906121</v>
       </c>
       <c r="Q8" s="40" t="n">
-        <v>85043089</v>
+        <v>84229530</v>
       </c>
       <c r="R8" s="40" t="n">
-        <v>67469168</v>
+        <v>92096471</v>
       </c>
       <c r="S8" s="40" t="n">
-        <v>66040134</v>
+        <v>78023476</v>
       </c>
       <c r="T8" s="40" t="n">
-        <v>80004937</v>
+        <v>89918146</v>
       </c>
       <c r="U8" s="40" t="n">
-        <v>67225139</v>
+        <v>94534230</v>
       </c>
       <c r="V8" s="40" t="n">
-        <v>80820230</v>
+        <v>81100625</v>
       </c>
       <c r="W8" s="40" t="n">
-        <v>73904849</v>
+        <v>109654171</v>
       </c>
       <c r="X8" s="40" t="n">
-        <v>73547034</v>
+        <v>99375298</v>
       </c>
       <c r="Y8" s="40" t="n">
-        <v>84513482</v>
+        <v>105623451</v>
       </c>
       <c r="Z8" s="40" t="n">
-        <v>80572023</v>
+        <v>73957610</v>
       </c>
       <c r="AA8" s="40" t="n">
-        <v>88660521</v>
+        <v>96334193</v>
       </c>
       <c r="AB8" s="40" t="n">
-        <v>13233103</v>
+        <v>33879611</v>
       </c>
     </row>
     <row r="9">
@@ -5107,907 +5107,907 @@
         <v>60557072</v>
       </c>
       <c r="AB9" s="40" t="n">
-        <v>10905727</v>
+        <v>35463855</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>536260</v>
+        <v>15808893</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>14403556</v>
+        <v>14209578</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>16216832</v>
+        <v>30449860</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>32622053</v>
+        <v>32603120</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>23929705</v>
+        <v>35552907</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>37214538</v>
+        <v>31069118</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>25375430</v>
+        <v>40525338</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>31500087</v>
+        <v>42402722</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>28078687</v>
+        <v>42012092</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>34472458</v>
+        <v>58722069</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>35343350</v>
+        <v>48135084</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>51225290</v>
+        <v>44293878</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>36142612</v>
+        <v>41613311</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>47488940</v>
+        <v>43739350</v>
       </c>
       <c r="R10" s="40" t="n">
-        <v>44805002</v>
+        <v>78234960</v>
       </c>
       <c r="S10" s="40" t="n">
-        <v>43327432</v>
+        <v>47535640</v>
       </c>
       <c r="T10" s="40" t="n">
-        <v>39637968</v>
+        <v>59241681</v>
       </c>
       <c r="U10" s="40" t="n">
-        <v>55199920</v>
+        <v>65321829</v>
       </c>
       <c r="V10" s="40" t="n">
-        <v>50680631</v>
+        <v>57895664</v>
       </c>
       <c r="W10" s="40" t="n">
-        <v>50163008</v>
+        <v>63196973</v>
       </c>
       <c r="X10" s="40" t="n">
-        <v>38778399</v>
+        <v>51807160</v>
       </c>
       <c r="Y10" s="40" t="n">
-        <v>50996587</v>
+        <v>67644051</v>
       </c>
       <c r="Z10" s="40" t="n">
-        <v>42228986</v>
+        <v>43897626</v>
       </c>
       <c r="AA10" s="40" t="n">
-        <v>32767816</v>
+        <v>68108471</v>
       </c>
       <c r="AB10" s="40" t="n">
-        <v>9982520</v>
+        <v>23066789</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>10351067</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>21091580</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>24243567</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>16381412</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>21591272</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>21904190</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>25438080</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>24614280</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>51983942</v>
+        <v>28889771</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>58935844</v>
+        <v>44250621</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>38454971</v>
+        <v>29608597</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>42939312</v>
+        <v>25219748</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>43650420</v>
+        <v>28515437</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>53954095</v>
+        <v>35235670</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>48898463</v>
+        <v>38511490</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>48011655</v>
+        <v>40935998</v>
       </c>
       <c r="T11" s="40" t="n">
-        <v>72064876</v>
+        <v>58966944</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>59606189</v>
+        <v>43378746</v>
       </c>
       <c r="V11" s="40" t="n">
-        <v>50164748</v>
+        <v>67522298</v>
       </c>
       <c r="W11" s="40" t="n">
-        <v>46095774</v>
+        <v>44905121</v>
       </c>
       <c r="X11" s="40" t="n">
-        <v>57645111</v>
+        <v>43314104</v>
       </c>
       <c r="Y11" s="40" t="n">
-        <v>55172528</v>
+        <v>45152620</v>
       </c>
       <c r="Z11" s="40" t="n">
-        <v>47962010</v>
+        <v>33695914</v>
       </c>
       <c r="AA11" s="40" t="n">
-        <v>43352139</v>
+        <v>56470370</v>
       </c>
       <c r="AB11" s="40" t="n">
-        <v>11340600</v>
+        <v>17677255</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>15808893</v>
+        <v>0</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>14209578</v>
+        <v>8972650</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>30449860</v>
+        <v>18100396</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>32603120</v>
+        <v>23988817</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>35552907</v>
+        <v>22409732</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>31069118</v>
+        <v>37715520</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>40525338</v>
+        <v>35926824</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>42402722</v>
+        <v>39462393</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>42012092</v>
+        <v>51983942</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>58722069</v>
+        <v>58935844</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>48135084</v>
+        <v>38454971</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>44293878</v>
+        <v>42939312</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>41613311</v>
+        <v>43650420</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>43739350</v>
+        <v>53954095</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>78234960</v>
+        <v>48898463</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>47535640</v>
+        <v>48011655</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>59241681</v>
+        <v>72064876</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>65321829</v>
+        <v>59606189</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>57895664</v>
+        <v>50164748</v>
       </c>
       <c r="W12" s="40" t="n">
-        <v>63196973</v>
+        <v>46095774</v>
       </c>
       <c r="X12" s="40" t="n">
-        <v>51807160</v>
+        <v>57645111</v>
       </c>
       <c r="Y12" s="40" t="n">
-        <v>67644051</v>
+        <v>55172528</v>
       </c>
       <c r="Z12" s="40" t="n">
-        <v>43897626</v>
+        <v>47962010</v>
       </c>
       <c r="AA12" s="40" t="n">
-        <v>68108471</v>
+        <v>43352139</v>
       </c>
       <c r="AB12" s="40" t="n">
-        <v>7568429</v>
+        <v>22688450</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>8544625</v>
+        <v>536260</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>8387478</v>
+        <v>14403556</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>10570508</v>
+        <v>16216832</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>11896580</v>
+        <v>32622053</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>19614352</v>
+        <v>23929705</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>20966317</v>
+        <v>37214538</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>20073400</v>
+        <v>25375430</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>23801493</v>
+        <v>31500087</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>27940611</v>
+        <v>28078687</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>27893929</v>
+        <v>34472458</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>29635773</v>
+        <v>35343350</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>19554230</v>
+        <v>51225290</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>23848495</v>
+        <v>36142612</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>24194638</v>
+        <v>47488940</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>20330094</v>
+        <v>44805002</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>26044199</v>
+        <v>43327432</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>24608772</v>
+        <v>39637968</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>28079726</v>
+        <v>55199920</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>20968052</v>
+        <v>50680631</v>
       </c>
       <c r="W13" s="40" t="n">
-        <v>29501132</v>
+        <v>50163008</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>30624981</v>
+        <v>38778399</v>
       </c>
       <c r="Y13" s="40" t="n">
-        <v>28071639</v>
+        <v>50996587</v>
       </c>
       <c r="Z13" s="40" t="n">
-        <v>21021583</v>
+        <v>42228986</v>
       </c>
       <c r="AA13" s="40" t="n">
-        <v>29229414</v>
+        <v>32767816</v>
       </c>
       <c r="AB13" s="40" t="n">
-        <v>6457629</v>
+        <v>22065624</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>10351067</v>
+        <v>5092853</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>21091580</v>
+        <v>11100161</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>24243567</v>
+        <v>14612055</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>16381412</v>
+        <v>20638987</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>21591272</v>
+        <v>14061352</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>21904190</v>
+        <v>31599148</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>25438080</v>
+        <v>18747614</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>24614280</v>
+        <v>19576415</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>28889771</v>
+        <v>14226838</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>44250621</v>
+        <v>23197145</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>29608597</v>
+        <v>25790711</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>25219748</v>
+        <v>27856115</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>28515437</v>
+        <v>20981901</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>35235670</v>
+        <v>25433123</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>38511490</v>
+        <v>19355230</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>40935998</v>
+        <v>24713836</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>58966944</v>
+        <v>20195634</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>43378746</v>
+        <v>32414171</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>67522298</v>
+        <v>42780769</v>
       </c>
       <c r="W14" s="40" t="n">
-        <v>44905121</v>
+        <v>36755122</v>
       </c>
       <c r="X14" s="40" t="n">
-        <v>43314104</v>
+        <v>38071365</v>
       </c>
       <c r="Y14" s="40" t="n">
-        <v>45152620</v>
+        <v>34397222</v>
       </c>
       <c r="Z14" s="40" t="n">
-        <v>33695914</v>
+        <v>32536036</v>
       </c>
       <c r="AA14" s="40" t="n">
-        <v>56470370</v>
+        <v>43911137</v>
       </c>
       <c r="AB14" s="40" t="n">
-        <v>7316350</v>
+        <v>17605235</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>3337146</v>
+        <v>8544625</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>10420206</v>
+        <v>8387478</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>21387685</v>
+        <v>10570508</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>16050448</v>
+        <v>11896580</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>21568794</v>
+        <v>19614352</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>30845816</v>
+        <v>20966317</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>45285935</v>
+        <v>20073400</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>28941455</v>
+        <v>23801493</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>21801828</v>
+        <v>27940611</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>19628570</v>
+        <v>27893929</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>23276090</v>
+        <v>29635773</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>27906254</v>
+        <v>19554230</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>20822247</v>
+        <v>23848495</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>20014322</v>
+        <v>24194638</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>19159625</v>
+        <v>20330094</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>22535696</v>
+        <v>26044199</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>21412810</v>
+        <v>24608772</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>34881782</v>
+        <v>28079726</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>25904024</v>
+        <v>20968052</v>
       </c>
       <c r="W15" s="40" t="n">
-        <v>46961904</v>
+        <v>29501132</v>
       </c>
       <c r="X15" s="40" t="n">
-        <v>42299644</v>
+        <v>30624981</v>
       </c>
       <c r="Y15" s="40" t="n">
-        <v>32109759</v>
+        <v>28071639</v>
       </c>
       <c r="Z15" s="40" t="n">
-        <v>22714393</v>
+        <v>21021583</v>
       </c>
       <c r="AA15" s="40" t="n">
-        <v>52198815</v>
+        <v>29229414</v>
       </c>
       <c r="AB15" s="40" t="n">
-        <v>10446420</v>
+        <v>13272630</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>5092853</v>
+        <v>3337146</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>11100161</v>
+        <v>10420206</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>14612055</v>
+        <v>21387685</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>20638987</v>
+        <v>16050448</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>14061352</v>
+        <v>21568794</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>31599148</v>
+        <v>30845816</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>18747614</v>
+        <v>45285935</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>19576415</v>
+        <v>28941455</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>14226838</v>
+        <v>21801828</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>23197145</v>
+        <v>19628570</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>25790711</v>
+        <v>23276090</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>27856115</v>
+        <v>27906254</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>20981901</v>
+        <v>20822247</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>25433123</v>
+        <v>20014322</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>19355230</v>
+        <v>19159625</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>24713836</v>
+        <v>22535696</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>20195634</v>
+        <v>21412810</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>32414171</v>
+        <v>34881782</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>42780769</v>
+        <v>25904024</v>
       </c>
       <c r="W16" s="40" t="n">
-        <v>36755122</v>
+        <v>46961904</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>38071365</v>
+        <v>42299644</v>
       </c>
       <c r="Y16" s="40" t="n">
-        <v>34397222</v>
+        <v>32109759</v>
       </c>
       <c r="Z16" s="40" t="n">
-        <v>32536036</v>
+        <v>22714393</v>
       </c>
       <c r="AA16" s="40" t="n">
-        <v>43911137</v>
+        <v>52198815</v>
       </c>
       <c r="AB16" s="40" t="n">
-        <v>2335805</v>
+        <v>20882240</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3249588</v>
+        <v>11884771</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>7305524</v>
+        <v>10651216</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>9575225</v>
+        <v>13882033</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>9264589</v>
+        <v>17812948</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>20692424</v>
+        <v>17331854</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>27565767</v>
+        <v>26294756</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>19138015</v>
+        <v>24196222</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>24912292</v>
+        <v>22122847</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>19068954</v>
+        <v>31914115</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>25387051</v>
+        <v>32069521</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>21008637</v>
+        <v>38287475</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>30862574</v>
+        <v>28283704</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>31820447</v>
+        <v>27334091</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>31875986</v>
+        <v>36312415</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>48358034</v>
+        <v>39333565</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>30000524</v>
+        <v>28566119</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>31150016</v>
+        <v>40387845</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>40688796</v>
+        <v>39744111</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>31752550</v>
+        <v>31477917</v>
       </c>
       <c r="W17" s="40" t="n">
-        <v>32778027</v>
+        <v>29910767</v>
       </c>
       <c r="X17" s="40" t="n">
-        <v>21331873</v>
+        <v>44620606</v>
       </c>
       <c r="Y17" s="40" t="n">
-        <v>28676177</v>
+        <v>35679497</v>
       </c>
       <c r="Z17" s="40" t="n">
-        <v>32596511</v>
+        <v>25102609</v>
       </c>
       <c r="AA17" s="40" t="n">
-        <v>53200913</v>
+        <v>39000780</v>
       </c>
       <c r="AB17" s="40" t="n">
-        <v>4088670</v>
+        <v>13381520</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>0</v>
+        <v>3249588</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>0</v>
+        <v>7305524</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>363900</v>
+        <v>9575225</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>3736700</v>
+        <v>9264589</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>17796776</v>
+        <v>20692424</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>42724228</v>
+        <v>27565767</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>33036620</v>
+        <v>19138015</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>29649130</v>
+        <v>24912292</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>13949368</v>
+        <v>19068954</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>24539413</v>
+        <v>25387051</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>19087217</v>
+        <v>21008637</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>17139440</v>
+        <v>30862574</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>17746930</v>
+        <v>31820447</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>21437830</v>
+        <v>31875986</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>17616397</v>
+        <v>48358034</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>19360848</v>
+        <v>30000524</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>25377166</v>
+        <v>31150016</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>24702051</v>
+        <v>40688796</v>
       </c>
       <c r="V18" s="40" t="n">
-        <v>26856647</v>
+        <v>31752550</v>
       </c>
       <c r="W18" s="40" t="n">
-        <v>27122255</v>
+        <v>32778027</v>
       </c>
       <c r="X18" s="40" t="n">
-        <v>30650242</v>
+        <v>21331873</v>
       </c>
       <c r="Y18" s="40" t="n">
-        <v>21101547</v>
+        <v>28676177</v>
       </c>
       <c r="Z18" s="40" t="n">
-        <v>30037062</v>
+        <v>32596511</v>
       </c>
       <c r="AA18" s="40" t="n">
-        <v>22123372</v>
+        <v>53200913</v>
       </c>
       <c r="AB18" s="40" t="n">
-        <v>4001630</v>
+        <v>13451710</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>11884771</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>10651216</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>13882033</v>
+        <v>363900</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>17812948</v>
+        <v>3736700</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>17331854</v>
+        <v>17796776</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>26294756</v>
+        <v>42724228</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>24196222</v>
+        <v>33036620</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>22122847</v>
+        <v>29649130</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>31914115</v>
+        <v>13949368</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>32069521</v>
+        <v>24539413</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>38287475</v>
+        <v>19087217</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>28283704</v>
+        <v>17139440</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>27334091</v>
+        <v>17746930</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>36312415</v>
+        <v>21437830</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>39333565</v>
+        <v>17616397</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>28566119</v>
+        <v>19360848</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>40387845</v>
+        <v>25377166</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>39744111</v>
+        <v>24702051</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>31477917</v>
+        <v>26856647</v>
       </c>
       <c r="W19" s="40" t="n">
-        <v>29910767</v>
+        <v>27122255</v>
       </c>
       <c r="X19" s="40" t="n">
-        <v>44620606</v>
+        <v>30650242</v>
       </c>
       <c r="Y19" s="40" t="n">
-        <v>35679497</v>
+        <v>21101547</v>
       </c>
       <c r="Z19" s="40" t="n">
-        <v>25102609</v>
+        <v>30037062</v>
       </c>
       <c r="AA19" s="40" t="n">
-        <v>39000780</v>
+        <v>22123372</v>
       </c>
       <c r="AB19" s="40" t="n">
-        <v>2897220</v>
+        <v>13201840</v>
       </c>
     </row>
     <row r="20">
@@ -6097,7 +6097,7 @@
         <v>27021110</v>
       </c>
       <c r="AB20" s="40" t="n">
-        <v>3193370</v>
+        <v>11170240</v>
       </c>
     </row>
     <row r="21">
@@ -6187,7 +6187,7 @@
         <v>25564267</v>
       </c>
       <c r="AB21" s="40" t="n">
-        <v>2362507</v>
+        <v>9203127</v>
       </c>
     </row>
     <row r="22">
@@ -6277,7 +6277,7 @@
         <v>5590930</v>
       </c>
       <c r="AB22" s="40" t="n">
-        <v>1595128</v>
+        <v>2937368</v>
       </c>
     </row>
     <row r="23">
@@ -6367,7 +6367,7 @@
         <v>12183598</v>
       </c>
       <c r="AB23" s="40" t="n">
-        <v>390230</v>
+        <v>2924012</v>
       </c>
     </row>
     <row r="24">
@@ -6541,132 +6541,132 @@
       </c>
     </row>
     <row r="3" hidden="1" s="20">
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="L3" s="19" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="Q3" s="19" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="R3" s="19" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="S3" s="19" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="T3" s="19" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="U3" s="19" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V3" s="19" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="W3" s="19" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X3" s="19" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="Y3" s="19" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="Z3" s="19" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="AA3" s="19" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
-      <c r="AB3" s="19" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -6897,7 +6897,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -6987,28 +6987,28 @@
         <v>7</v>
       </c>
       <c r="AB6" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>7</v>
@@ -7071,103 +7071,103 @@
         <v>7</v>
       </c>
       <c r="Z7" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA7" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB7" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB8" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="F8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z8" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB8" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7257,118 +7257,118 @@
         <v>7</v>
       </c>
       <c r="AB9" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA10" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB10" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA10" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB10" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -7431,121 +7431,121 @@
         <v>7</v>
       </c>
       <c r="Z11" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA11" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB11" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z12" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB12" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="D12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB12" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -7611,31 +7611,31 @@
         <v>7</v>
       </c>
       <c r="Z13" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA13" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB13" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="42" t="n">
         <v>7</v>
@@ -7707,25 +7707,25 @@
         <v>7</v>
       </c>
       <c r="AB14" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -7797,214 +7797,214 @@
         <v>7</v>
       </c>
       <c r="AB15" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z16" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="E16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z16" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="AA16" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB16" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB17" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB17" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F18" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G18" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="42" t="n">
         <v>7</v>
@@ -8067,34 +8067,34 @@
         <v>7</v>
       </c>
       <c r="AB18" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F19" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="G19" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -8157,7 +8157,7 @@
         <v>7</v>
       </c>
       <c r="AB19" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -8247,7 +8247,7 @@
         <v>7</v>
       </c>
       <c r="AB20" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -8337,7 +8337,7 @@
         <v>7</v>
       </c>
       <c r="AB21" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -8427,7 +8427,7 @@
         <v>7</v>
       </c>
       <c r="AB22" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -8517,7 +8517,7 @@
         <v>7</v>
       </c>
       <c r="AB23" s="42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2597,7 +2597,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2687,187 +2687,187 @@
         <v>120</v>
       </c>
       <c r="AB6" s="36" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>7.33</v>
+        <v>29.43</v>
       </c>
       <c r="F7" s="36" t="n">
-        <v>17.86</v>
+        <v>38</v>
       </c>
       <c r="G7" s="36" t="n">
-        <v>22.14</v>
+        <v>41.29</v>
       </c>
       <c r="H7" s="36" t="n">
-        <v>24.86</v>
+        <v>51.43</v>
       </c>
       <c r="I7" s="36" t="n">
-        <v>36.57</v>
+        <v>58.29</v>
       </c>
       <c r="J7" s="36" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="K7" s="36" t="n">
-        <v>43.86</v>
+        <v>55.43</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>50.14</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>59</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>53.71</v>
+        <v>76.86</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>46.57</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="P7" s="36" t="n">
-        <v>49.29</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="Q7" s="36" t="n">
-        <v>65.56999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="R7" s="36" t="n">
-        <v>67.29000000000001</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="S7" s="36" t="n">
-        <v>61</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="T7" s="36" t="n">
-        <v>64.43000000000001</v>
+        <v>92.14</v>
       </c>
       <c r="U7" s="36" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="V7" s="36" t="n">
-        <v>77.56999999999999</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="W7" s="36" t="n">
-        <v>71</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="X7" s="36" t="n">
-        <v>68.43000000000001</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="Y7" s="36" t="n">
-        <v>78.43000000000001</v>
+        <v>101.29</v>
       </c>
       <c r="Z7" s="36" t="n">
-        <v>78.17</v>
+        <v>76.14</v>
       </c>
       <c r="AA7" s="36" t="n">
-        <v>78.56999999999999</v>
+        <v>90.14</v>
       </c>
       <c r="AB7" s="36" t="n">
-        <v>95.33</v>
+        <v>82.25</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>29.43</v>
+        <v>7.33</v>
       </c>
       <c r="F8" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G8" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H8" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J8" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="G8" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="H8" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I8" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J8" s="36" t="n">
-        <v>63</v>
-      </c>
       <c r="K8" s="36" t="n">
-        <v>55.43</v>
+        <v>43.86</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>69.56999999999999</v>
+        <v>50.14</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>59</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>76.86</v>
+        <v>53.71</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>46.57</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>71.43000000000001</v>
+        <v>49.29</v>
       </c>
       <c r="Q8" s="36" t="n">
-        <v>78.86</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R8" s="36" t="n">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="S8" s="36" t="n">
+        <v>61</v>
+      </c>
+      <c r="T8" s="36" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="U8" s="36" t="n">
+        <v>68</v>
+      </c>
+      <c r="V8" s="36" t="n">
+        <v>77.56999999999999</v>
+      </c>
+      <c r="W8" s="36" t="n">
+        <v>71</v>
+      </c>
+      <c r="X8" s="36" t="n">
+        <v>68.43000000000001</v>
+      </c>
+      <c r="Y8" s="36" t="n">
         <v>78.43000000000001</v>
       </c>
-      <c r="S8" s="36" t="n">
-        <v>72.43000000000001</v>
-      </c>
-      <c r="T8" s="36" t="n">
-        <v>92.14</v>
-      </c>
-      <c r="U8" s="36" t="n">
-        <v>91</v>
-      </c>
-      <c r="V8" s="36" t="n">
-        <v>85.43000000000001</v>
-      </c>
-      <c r="W8" s="36" t="n">
-        <v>88.56999999999999</v>
-      </c>
-      <c r="X8" s="36" t="n">
-        <v>80.70999999999999</v>
-      </c>
-      <c r="Y8" s="36" t="n">
-        <v>101.29</v>
-      </c>
       <c r="Z8" s="36" t="n">
-        <v>76.14</v>
+        <v>78.17</v>
       </c>
       <c r="AA8" s="36" t="n">
-        <v>90.14</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="AB8" s="36" t="n">
-        <v>92</v>
+        <v>74.75</v>
       </c>
     </row>
     <row r="9">
@@ -2957,7 +2957,7 @@
         <v>57.14</v>
       </c>
       <c r="AB9" s="36" t="n">
-        <v>67.33</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="10">
@@ -3047,277 +3047,277 @@
         <v>63.71</v>
       </c>
       <c r="AB10" s="36" t="n">
-        <v>55.33</v>
+        <v>48.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>8.43</v>
+        <v>1.67</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>13.43</v>
+        <v>12.14</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>21.71</v>
+        <v>16.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>16.57</v>
+        <v>21</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>21.29</v>
+        <v>20.29</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>21.14</v>
+        <v>28.57</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>23.29</v>
+        <v>24.14</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>22.43</v>
+        <v>27.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>22.43</v>
+        <v>28.14</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>28.14</v>
+        <v>28.86</v>
       </c>
       <c r="N11" s="36" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="O11" s="36" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="P11" s="36" t="n">
         <v>31.14</v>
       </c>
-      <c r="O11" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="P11" s="36" t="n">
-        <v>30.43</v>
-      </c>
       <c r="Q11" s="36" t="n">
-        <v>31.29</v>
+        <v>40.29</v>
       </c>
       <c r="R11" s="36" t="n">
-        <v>36.14</v>
+        <v>38.71</v>
       </c>
       <c r="S11" s="36" t="n">
-        <v>31</v>
+        <v>43.14</v>
       </c>
       <c r="T11" s="36" t="n">
-        <v>37.71</v>
+        <v>37</v>
       </c>
       <c r="U11" s="36" t="n">
-        <v>39.29</v>
+        <v>46.29</v>
       </c>
       <c r="V11" s="36" t="n">
-        <v>45.86</v>
+        <v>43.14</v>
       </c>
       <c r="W11" s="36" t="n">
-        <v>45.14</v>
+        <v>36.86</v>
       </c>
       <c r="X11" s="36" t="n">
-        <v>41.86</v>
+        <v>33.43</v>
       </c>
       <c r="Y11" s="36" t="n">
         <v>48</v>
       </c>
       <c r="Z11" s="36" t="n">
-        <v>40</v>
+        <v>39.86</v>
       </c>
       <c r="AA11" s="36" t="n">
-        <v>51.14</v>
+        <v>37.14</v>
       </c>
       <c r="AB11" s="36" t="n">
-        <v>47</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>0</v>
+        <v>8.43</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>8</v>
+        <v>13.43</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>13.14</v>
+        <v>21.71</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>19.43</v>
+        <v>16.57</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>26.43</v>
+        <v>21.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>32.29</v>
+        <v>21.14</v>
       </c>
       <c r="J12" s="36" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="K12" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="L12" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="M12" s="36" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="N12" s="36" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="O12" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="P12" s="36" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="Q12" s="36" t="n">
         <v>31.29</v>
       </c>
-      <c r="K12" s="36" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="L12" s="36" t="n">
+      <c r="R12" s="36" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="S12" s="36" t="n">
+        <v>31</v>
+      </c>
+      <c r="T12" s="36" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="U12" s="36" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="V12" s="36" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="W12" s="36" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="X12" s="36" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="Y12" s="36" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z12" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="M12" s="36" t="n">
-        <v>42.43</v>
-      </c>
-      <c r="N12" s="36" t="n">
-        <v>38.57</v>
-      </c>
-      <c r="O12" s="36" t="n">
-        <v>34.29</v>
-      </c>
-      <c r="P12" s="36" t="n">
-        <v>37.86</v>
-      </c>
-      <c r="Q12" s="36" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="R12" s="36" t="n">
-        <v>40.71</v>
-      </c>
-      <c r="S12" s="36" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="T12" s="36" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="U12" s="36" t="n">
-        <v>55.29</v>
-      </c>
-      <c r="V12" s="36" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="W12" s="36" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="X12" s="36" t="n">
-        <v>49.57</v>
-      </c>
-      <c r="Y12" s="36" t="n">
-        <v>47.86</v>
-      </c>
-      <c r="Z12" s="36" t="n">
-        <v>46</v>
-      </c>
       <c r="AA12" s="36" t="n">
-        <v>45.14</v>
+        <v>51.14</v>
       </c>
       <c r="AB12" s="36" t="n">
-        <v>46.33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>33.14</v>
+        <v>38.57</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>30.71</v>
+        <v>34.29</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>31.14</v>
+        <v>37.86</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>40.29</v>
+        <v>42.86</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>38.71</v>
+        <v>40.71</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>43.14</v>
+        <v>45.43</v>
       </c>
       <c r="T13" s="36" t="n">
-        <v>37</v>
+        <v>44.57</v>
       </c>
       <c r="U13" s="36" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="V13" s="36" t="n">
         <v>46.29</v>
       </c>
-      <c r="V13" s="36" t="n">
-        <v>43.14</v>
-      </c>
       <c r="W13" s="36" t="n">
-        <v>36.86</v>
+        <v>43.71</v>
       </c>
       <c r="X13" s="36" t="n">
-        <v>33.43</v>
+        <v>49.57</v>
       </c>
       <c r="Y13" s="36" t="n">
-        <v>48</v>
+        <v>47.86</v>
       </c>
       <c r="Z13" s="36" t="n">
-        <v>39.86</v>
+        <v>46</v>
       </c>
       <c r="AA13" s="36" t="n">
-        <v>37.14</v>
+        <v>45.14</v>
       </c>
       <c r="AB13" s="36" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -3407,7 +3407,7 @@
         <v>52.57</v>
       </c>
       <c r="AB14" s="36" t="n">
-        <v>44.67</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3497,187 +3497,187 @@
         <v>31.29</v>
       </c>
       <c r="AB15" s="36" t="n">
-        <v>44</v>
+        <v>37.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>3</v>
+        <v>9.43</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>7.14</v>
+        <v>12.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.43</v>
+        <v>13.29</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>12.71</v>
+        <v>14.71</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>14.43</v>
+        <v>17</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>19</v>
+        <v>19.71</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>21.14</v>
+        <v>17.71</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>18.57</v>
+        <v>19.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>16.57</v>
+        <v>24.14</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>14.71</v>
+        <v>27.57</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>19.14</v>
+        <v>24.43</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>18</v>
+        <v>27.29</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>15.29</v>
+        <v>26.57</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>15.29</v>
+        <v>25.57</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>18.71</v>
+        <v>29</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>18</v>
+        <v>27.71</v>
       </c>
       <c r="T16" s="36" t="n">
-        <v>25.29</v>
+        <v>32.57</v>
       </c>
       <c r="U16" s="36" t="n">
-        <v>28.86</v>
+        <v>31.57</v>
       </c>
       <c r="V16" s="36" t="n">
-        <v>24</v>
+        <v>29.57</v>
       </c>
       <c r="W16" s="36" t="n">
-        <v>29.29</v>
+        <v>29.86</v>
       </c>
       <c r="X16" s="36" t="n">
-        <v>31.71</v>
+        <v>32</v>
       </c>
       <c r="Y16" s="36" t="n">
-        <v>27</v>
+        <v>32.14</v>
       </c>
       <c r="Z16" s="36" t="n">
-        <v>23.83</v>
+        <v>27.14</v>
       </c>
       <c r="AA16" s="36" t="n">
-        <v>34.71</v>
+        <v>36.43</v>
       </c>
       <c r="AB16" s="36" t="n">
-        <v>34</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>9.43</v>
+        <v>3</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>12.43</v>
+        <v>7.14</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.29</v>
+        <v>13.43</v>
       </c>
       <c r="G17" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="H17" s="36" t="n">
+        <v>14.43</v>
+      </c>
+      <c r="I17" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="J17" s="36" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K17" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L17" s="36" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="M17" s="36" t="n">
         <v>14.71</v>
       </c>
-      <c r="H17" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="I17" s="36" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="J17" s="36" t="n">
-        <v>17.71</v>
-      </c>
-      <c r="K17" s="36" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="L17" s="36" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="M17" s="36" t="n">
-        <v>27.57</v>
-      </c>
       <c r="N17" s="36" t="n">
-        <v>24.43</v>
+        <v>19.14</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>27.29</v>
+        <v>18</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>26.57</v>
+        <v>15.29</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>25.57</v>
+        <v>15.29</v>
       </c>
       <c r="R17" s="36" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="S17" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="T17" s="36" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="U17" s="36" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="V17" s="36" t="n">
+        <v>24</v>
+      </c>
+      <c r="W17" s="36" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="X17" s="36" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="Y17" s="36" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z17" s="36" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="AA17" s="36" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="AB17" s="36" t="n">
         <v>29</v>
-      </c>
-      <c r="S17" s="36" t="n">
-        <v>27.71</v>
-      </c>
-      <c r="T17" s="36" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="U17" s="36" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="V17" s="36" t="n">
-        <v>29.57</v>
-      </c>
-      <c r="W17" s="36" t="n">
-        <v>29.86</v>
-      </c>
-      <c r="X17" s="36" t="n">
-        <v>32</v>
-      </c>
-      <c r="Y17" s="36" t="n">
-        <v>32.14</v>
-      </c>
-      <c r="Z17" s="36" t="n">
-        <v>27.14</v>
-      </c>
-      <c r="AA17" s="36" t="n">
-        <v>36.43</v>
-      </c>
-      <c r="AB17" s="36" t="n">
-        <v>33.67</v>
       </c>
     </row>
     <row r="18">
@@ -3767,7 +3767,7 @@
         <v>30.29</v>
       </c>
       <c r="AB18" s="36" t="n">
-        <v>31.33</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="19">
@@ -3857,7 +3857,7 @@
         <v>29</v>
       </c>
       <c r="AB19" s="36" t="n">
-        <v>29.67</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="20">
@@ -3947,7 +3947,7 @@
         <v>25.29</v>
       </c>
       <c r="AB20" s="36" t="n">
-        <v>28.67</v>
+        <v>24.75</v>
       </c>
     </row>
     <row r="21">
@@ -4037,7 +4037,7 @@
         <v>27.43</v>
       </c>
       <c r="AB21" s="36" t="n">
-        <v>25</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="22">
@@ -4127,7 +4127,7 @@
         <v>8</v>
       </c>
       <c r="AB22" s="36" t="n">
-        <v>10.33</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="23">
@@ -4217,7 +4217,7 @@
         <v>11.43</v>
       </c>
       <c r="AB23" s="36" t="n">
-        <v>9.33</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="24">
@@ -4747,7 +4747,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -4837,187 +4837,187 @@
         <v>121486853</v>
       </c>
       <c r="AB6" s="40" t="n">
-        <v>45347415</v>
+        <v>48745905</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>0</v>
+        <v>6122227</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>2886450</v>
+        <v>31792625</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>22932586</v>
+        <v>49374899</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>24764259</v>
+        <v>38585414</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>32268886</v>
+        <v>51458725</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>42977335</v>
+        <v>61835892</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>44364359</v>
+        <v>80551167</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>53225819</v>
+        <v>61490143</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>51621207</v>
+        <v>68619843</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>58204066</v>
+        <v>81742671</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>58190202</v>
+        <v>69757179</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>46275213</v>
+        <v>68198708</v>
       </c>
       <c r="P7" s="40" t="n">
-        <v>51530060</v>
+        <v>67906121</v>
       </c>
       <c r="Q7" s="40" t="n">
-        <v>85043089</v>
+        <v>84229530</v>
       </c>
       <c r="R7" s="40" t="n">
-        <v>67469168</v>
+        <v>92096471</v>
       </c>
       <c r="S7" s="40" t="n">
-        <v>66040134</v>
+        <v>78023476</v>
       </c>
       <c r="T7" s="40" t="n">
-        <v>80004937</v>
+        <v>89918146</v>
       </c>
       <c r="U7" s="40" t="n">
-        <v>67225139</v>
+        <v>94534230</v>
       </c>
       <c r="V7" s="40" t="n">
-        <v>80820230</v>
+        <v>81100625</v>
       </c>
       <c r="W7" s="40" t="n">
-        <v>73904849</v>
+        <v>109654171</v>
       </c>
       <c r="X7" s="40" t="n">
-        <v>73547034</v>
+        <v>99375298</v>
       </c>
       <c r="Y7" s="40" t="n">
-        <v>84513482</v>
+        <v>105623451</v>
       </c>
       <c r="Z7" s="40" t="n">
-        <v>80572023</v>
+        <v>73957610</v>
       </c>
       <c r="AA7" s="40" t="n">
-        <v>88660521</v>
+        <v>96334193</v>
       </c>
       <c r="AB7" s="40" t="n">
-        <v>42888911</v>
+        <v>39497971</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>6122227</v>
+        <v>0</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>31792625</v>
+        <v>2886450</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>49374899</v>
+        <v>22932586</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>38585414</v>
+        <v>24764259</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>51458725</v>
+        <v>32268886</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>61835892</v>
+        <v>42977335</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>80551167</v>
+        <v>44364359</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>61490143</v>
+        <v>53225819</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>68619843</v>
+        <v>51621207</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>81742671</v>
+        <v>58204066</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>69757179</v>
+        <v>58190202</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>68198708</v>
+        <v>46275213</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>67906121</v>
+        <v>51530060</v>
       </c>
       <c r="Q8" s="40" t="n">
-        <v>84229530</v>
+        <v>85043089</v>
       </c>
       <c r="R8" s="40" t="n">
-        <v>92096471</v>
+        <v>67469168</v>
       </c>
       <c r="S8" s="40" t="n">
-        <v>78023476</v>
+        <v>66040134</v>
       </c>
       <c r="T8" s="40" t="n">
-        <v>89918146</v>
+        <v>80004937</v>
       </c>
       <c r="U8" s="40" t="n">
-        <v>94534230</v>
+        <v>67225139</v>
       </c>
       <c r="V8" s="40" t="n">
-        <v>81100625</v>
+        <v>80820230</v>
       </c>
       <c r="W8" s="40" t="n">
-        <v>109654171</v>
+        <v>73904849</v>
       </c>
       <c r="X8" s="40" t="n">
-        <v>99375298</v>
+        <v>73547034</v>
       </c>
       <c r="Y8" s="40" t="n">
-        <v>105623451</v>
+        <v>84513482</v>
       </c>
       <c r="Z8" s="40" t="n">
-        <v>73957610</v>
+        <v>80572023</v>
       </c>
       <c r="AA8" s="40" t="n">
-        <v>96334193</v>
+        <v>88660521</v>
       </c>
       <c r="AB8" s="40" t="n">
-        <v>33879611</v>
+        <v>44262521</v>
       </c>
     </row>
     <row r="9">
@@ -5107,7 +5107,7 @@
         <v>60557072</v>
       </c>
       <c r="AB9" s="40" t="n">
-        <v>35463855</v>
+        <v>41511665</v>
       </c>
     </row>
     <row r="10">
@@ -5197,277 +5197,277 @@
         <v>68108471</v>
       </c>
       <c r="AB10" s="40" t="n">
-        <v>23066789</v>
+        <v>28362839</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>10351067</v>
+        <v>536260</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>21091580</v>
+        <v>14403556</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>24243567</v>
+        <v>16216832</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>16381412</v>
+        <v>32622053</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>21591272</v>
+        <v>23929705</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>21904190</v>
+        <v>37214538</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>25438080</v>
+        <v>25375430</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>24614280</v>
+        <v>31500087</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>28889771</v>
+        <v>28078687</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>44250621</v>
+        <v>34472458</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>29608597</v>
+        <v>35343350</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>25219748</v>
+        <v>51225290</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>28515437</v>
+        <v>36142612</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>35235670</v>
+        <v>47488940</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>38511490</v>
+        <v>44805002</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>40935998</v>
+        <v>43327432</v>
       </c>
       <c r="T11" s="40" t="n">
-        <v>58966944</v>
+        <v>39637968</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>43378746</v>
+        <v>55199920</v>
       </c>
       <c r="V11" s="40" t="n">
-        <v>67522298</v>
+        <v>50680631</v>
       </c>
       <c r="W11" s="40" t="n">
-        <v>44905121</v>
+        <v>50163008</v>
       </c>
       <c r="X11" s="40" t="n">
-        <v>43314104</v>
+        <v>38778399</v>
       </c>
       <c r="Y11" s="40" t="n">
-        <v>45152620</v>
+        <v>50996587</v>
       </c>
       <c r="Z11" s="40" t="n">
-        <v>33695914</v>
+        <v>42228986</v>
       </c>
       <c r="AA11" s="40" t="n">
-        <v>56470370</v>
+        <v>32767816</v>
       </c>
       <c r="AB11" s="40" t="n">
-        <v>17677255</v>
+        <v>24295224</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>0</v>
+        <v>10351067</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>8972650</v>
+        <v>21091580</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>18100396</v>
+        <v>24243567</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>23988817</v>
+        <v>16381412</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>22409732</v>
+        <v>21591272</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>37715520</v>
+        <v>21904190</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>35926824</v>
+        <v>25438080</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>39462393</v>
+        <v>24614280</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>51983942</v>
+        <v>28889771</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>58935844</v>
+        <v>44250621</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>38454971</v>
+        <v>29608597</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>42939312</v>
+        <v>25219748</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>43650420</v>
+        <v>28515437</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>53954095</v>
+        <v>35235670</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>48898463</v>
+        <v>38511490</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>48011655</v>
+        <v>40935998</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>72064876</v>
+        <v>58966944</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>59606189</v>
+        <v>43378746</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>50164748</v>
+        <v>67522298</v>
       </c>
       <c r="W12" s="40" t="n">
-        <v>46095774</v>
+        <v>44905121</v>
       </c>
       <c r="X12" s="40" t="n">
-        <v>57645111</v>
+        <v>43314104</v>
       </c>
       <c r="Y12" s="40" t="n">
-        <v>55172528</v>
+        <v>45152620</v>
       </c>
       <c r="Z12" s="40" t="n">
-        <v>47962010</v>
+        <v>33695914</v>
       </c>
       <c r="AA12" s="40" t="n">
-        <v>43352139</v>
+        <v>56470370</v>
       </c>
       <c r="AB12" s="40" t="n">
-        <v>22688450</v>
+        <v>19560715</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>35343350</v>
+        <v>38454971</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>51225290</v>
+        <v>42939312</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>36142612</v>
+        <v>43650420</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>47488940</v>
+        <v>53954095</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>44805002</v>
+        <v>48898463</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>43327432</v>
+        <v>48011655</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>39637968</v>
+        <v>72064876</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>55199920</v>
+        <v>59606189</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>50680631</v>
+        <v>50164748</v>
       </c>
       <c r="W13" s="40" t="n">
-        <v>50163008</v>
+        <v>46095774</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>38778399</v>
+        <v>57645111</v>
       </c>
       <c r="Y13" s="40" t="n">
-        <v>50996587</v>
+        <v>55172528</v>
       </c>
       <c r="Z13" s="40" t="n">
-        <v>42228986</v>
+        <v>47962010</v>
       </c>
       <c r="AA13" s="40" t="n">
-        <v>32767816</v>
+        <v>43352139</v>
       </c>
       <c r="AB13" s="40" t="n">
-        <v>22065624</v>
+        <v>24598150</v>
       </c>
     </row>
     <row r="14">
@@ -5557,7 +5557,7 @@
         <v>43911137</v>
       </c>
       <c r="AB14" s="40" t="n">
-        <v>17605235</v>
+        <v>18794885</v>
       </c>
     </row>
     <row r="15">
@@ -5647,187 +5647,187 @@
         <v>29229414</v>
       </c>
       <c r="AB15" s="40" t="n">
-        <v>13272630</v>
+        <v>16490970</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>3337146</v>
+        <v>11884771</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>10420206</v>
+        <v>10651216</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>21387685</v>
+        <v>13882033</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>16050448</v>
+        <v>17812948</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>21568794</v>
+        <v>17331854</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>30845816</v>
+        <v>26294756</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>45285935</v>
+        <v>24196222</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>28941455</v>
+        <v>22122847</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>21801828</v>
+        <v>31914115</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>19628570</v>
+        <v>32069521</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>23276090</v>
+        <v>38287475</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>27906254</v>
+        <v>28283704</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>20822247</v>
+        <v>27334091</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>20014322</v>
+        <v>36312415</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>19159625</v>
+        <v>39333565</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>22535696</v>
+        <v>28566119</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>21412810</v>
+        <v>40387845</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>34881782</v>
+        <v>39744111</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>25904024</v>
+        <v>31477917</v>
       </c>
       <c r="W16" s="40" t="n">
-        <v>46961904</v>
+        <v>29910767</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>42299644</v>
+        <v>44620606</v>
       </c>
       <c r="Y16" s="40" t="n">
-        <v>32109759</v>
+        <v>35679497</v>
       </c>
       <c r="Z16" s="40" t="n">
-        <v>22714393</v>
+        <v>25102609</v>
       </c>
       <c r="AA16" s="40" t="n">
-        <v>52198815</v>
+        <v>39000780</v>
       </c>
       <c r="AB16" s="40" t="n">
-        <v>20882240</v>
+        <v>18634420</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>11884771</v>
+        <v>3337146</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10651216</v>
+        <v>10420206</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>13882033</v>
+        <v>21387685</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>17812948</v>
+        <v>16050448</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>17331854</v>
+        <v>21568794</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>26294756</v>
+        <v>30845816</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>24196222</v>
+        <v>45285935</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>22122847</v>
+        <v>28941455</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>31914115</v>
+        <v>21801828</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>32069521</v>
+        <v>19628570</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>38287475</v>
+        <v>23276090</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>28283704</v>
+        <v>27906254</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>27334091</v>
+        <v>20822247</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>36312415</v>
+        <v>20014322</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>39333565</v>
+        <v>19159625</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>28566119</v>
+        <v>22535696</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>40387845</v>
+        <v>21412810</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>39744111</v>
+        <v>34881782</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>31477917</v>
+        <v>25904024</v>
       </c>
       <c r="W17" s="40" t="n">
-        <v>29910767</v>
+        <v>46961904</v>
       </c>
       <c r="X17" s="40" t="n">
-        <v>44620606</v>
+        <v>42299644</v>
       </c>
       <c r="Y17" s="40" t="n">
-        <v>35679497</v>
+        <v>32109759</v>
       </c>
       <c r="Z17" s="40" t="n">
-        <v>25102609</v>
+        <v>22714393</v>
       </c>
       <c r="AA17" s="40" t="n">
-        <v>39000780</v>
+        <v>52198815</v>
       </c>
       <c r="AB17" s="40" t="n">
-        <v>13381520</v>
+        <v>23446830</v>
       </c>
     </row>
     <row r="18">
@@ -5917,7 +5917,7 @@
         <v>53200913</v>
       </c>
       <c r="AB18" s="40" t="n">
-        <v>13451710</v>
+        <v>15157200</v>
       </c>
     </row>
     <row r="19">
@@ -6007,7 +6007,7 @@
         <v>22123372</v>
       </c>
       <c r="AB19" s="40" t="n">
-        <v>13201840</v>
+        <v>14758520</v>
       </c>
     </row>
     <row r="20">
@@ -6097,7 +6097,7 @@
         <v>27021110</v>
       </c>
       <c r="AB20" s="40" t="n">
-        <v>11170240</v>
+        <v>14898250</v>
       </c>
     </row>
     <row r="21">
@@ -6187,7 +6187,7 @@
         <v>25564267</v>
       </c>
       <c r="AB21" s="40" t="n">
-        <v>9203127</v>
+        <v>10833129</v>
       </c>
     </row>
     <row r="22">
@@ -6277,7 +6277,7 @@
         <v>5590930</v>
       </c>
       <c r="AB22" s="40" t="n">
-        <v>2937368</v>
+        <v>3444398</v>
       </c>
     </row>
     <row r="23">
@@ -6367,7 +6367,7 @@
         <v>12183598</v>
       </c>
       <c r="AB23" s="40" t="n">
-        <v>2924012</v>
+        <v>3325182</v>
       </c>
     </row>
     <row r="24">
@@ -6897,7 +6897,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -6987,28 +6987,28 @@
         <v>7</v>
       </c>
       <c r="AB6" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>7</v>
@@ -7071,103 +7071,103 @@
         <v>7</v>
       </c>
       <c r="Z7" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA7" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB7" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z8" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA8" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB8" s="42" t="n">
         <v>4</v>
-      </c>
-      <c r="E8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA8" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB8" s="42" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7257,7 +7257,7 @@
         <v>7</v>
       </c>
       <c r="AB9" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -7347,25 +7347,25 @@
         <v>7</v>
       </c>
       <c r="AB10" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>7</v>
@@ -7437,28 +7437,28 @@
         <v>7</v>
       </c>
       <c r="AB11" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E12" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" s="42" t="n">
         <v>7</v>
@@ -7521,34 +7521,34 @@
         <v>7</v>
       </c>
       <c r="Z12" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA12" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB12" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E13" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13" s="42" t="n">
         <v>7</v>
@@ -7611,13 +7611,13 @@
         <v>7</v>
       </c>
       <c r="Z13" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA13" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB13" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -7707,7 +7707,7 @@
         <v>7</v>
       </c>
       <c r="AB14" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -7797,25 +7797,25 @@
         <v>7</v>
       </c>
       <c r="AB15" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -7881,31 +7881,31 @@
         <v>7</v>
       </c>
       <c r="Z16" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB16" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -7971,13 +7971,13 @@
         <v>7</v>
       </c>
       <c r="Z17" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA17" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB17" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -8067,7 +8067,7 @@
         <v>7</v>
       </c>
       <c r="AB18" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -8157,7 +8157,7 @@
         <v>7</v>
       </c>
       <c r="AB19" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -8247,7 +8247,7 @@
         <v>7</v>
       </c>
       <c r="AB20" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -8337,7 +8337,7 @@
         <v>7</v>
       </c>
       <c r="AB21" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -8427,7 +8427,7 @@
         <v>7</v>
       </c>
       <c r="AB22" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -8517,7 +8517,7 @@
         <v>7</v>
       </c>
       <c r="AB23" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2597,7 +2597,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2687,7 +2687,7 @@
         <v>120</v>
       </c>
       <c r="AB6" s="36" t="n">
-        <v>108</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7">
@@ -2777,7 +2777,7 @@
         <v>90.14</v>
       </c>
       <c r="AB7" s="36" t="n">
-        <v>82.25</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="8">
@@ -2867,7 +2867,7 @@
         <v>78.56999999999999</v>
       </c>
       <c r="AB8" s="36" t="n">
-        <v>74.75</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
@@ -2957,7 +2957,7 @@
         <v>57.14</v>
       </c>
       <c r="AB9" s="36" t="n">
-        <v>57.75</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="10">
@@ -3047,97 +3047,97 @@
         <v>63.71</v>
       </c>
       <c r="AB10" s="36" t="n">
-        <v>48.25</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J11" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K11" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L11" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M11" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N11" s="36" t="n">
-        <v>33.14</v>
+        <v>38.57</v>
       </c>
       <c r="O11" s="36" t="n">
-        <v>30.71</v>
+        <v>34.29</v>
       </c>
       <c r="P11" s="36" t="n">
-        <v>31.14</v>
+        <v>37.86</v>
       </c>
       <c r="Q11" s="36" t="n">
-        <v>40.29</v>
+        <v>42.86</v>
       </c>
       <c r="R11" s="36" t="n">
-        <v>38.71</v>
+        <v>40.71</v>
       </c>
       <c r="S11" s="36" t="n">
-        <v>43.14</v>
+        <v>45.43</v>
       </c>
       <c r="T11" s="36" t="n">
-        <v>37</v>
+        <v>44.57</v>
       </c>
       <c r="U11" s="36" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="V11" s="36" t="n">
         <v>46.29</v>
       </c>
-      <c r="V11" s="36" t="n">
-        <v>43.14</v>
-      </c>
       <c r="W11" s="36" t="n">
-        <v>36.86</v>
+        <v>43.71</v>
       </c>
       <c r="X11" s="36" t="n">
-        <v>33.43</v>
+        <v>49.57</v>
       </c>
       <c r="Y11" s="36" t="n">
-        <v>48</v>
+        <v>47.86</v>
       </c>
       <c r="Z11" s="36" t="n">
-        <v>39.86</v>
+        <v>46</v>
       </c>
       <c r="AA11" s="36" t="n">
-        <v>37.14</v>
+        <v>45.14</v>
       </c>
       <c r="AB11" s="36" t="n">
-        <v>40.5</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="12">
@@ -3227,97 +3227,97 @@
         <v>51.14</v>
       </c>
       <c r="AB12" s="36" t="n">
-        <v>40</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>8</v>
+        <v>12.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>13.14</v>
+        <v>16.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>19.43</v>
+        <v>21</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>26.43</v>
+        <v>20.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>32.29</v>
+        <v>28.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>31.29</v>
+        <v>24.14</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>33.57</v>
+        <v>27.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>40</v>
+        <v>28.14</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>42.43</v>
+        <v>28.86</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>38.57</v>
+        <v>33.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>34.29</v>
+        <v>30.71</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>37.86</v>
+        <v>31.14</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>42.86</v>
+        <v>40.29</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>40.71</v>
+        <v>38.71</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>45.43</v>
+        <v>43.14</v>
       </c>
       <c r="T13" s="36" t="n">
-        <v>44.57</v>
+        <v>37</v>
       </c>
       <c r="U13" s="36" t="n">
-        <v>55.29</v>
+        <v>46.29</v>
       </c>
       <c r="V13" s="36" t="n">
-        <v>46.29</v>
+        <v>43.14</v>
       </c>
       <c r="W13" s="36" t="n">
-        <v>43.71</v>
+        <v>36.86</v>
       </c>
       <c r="X13" s="36" t="n">
-        <v>49.57</v>
+        <v>33.43</v>
       </c>
       <c r="Y13" s="36" t="n">
-        <v>47.86</v>
+        <v>48</v>
       </c>
       <c r="Z13" s="36" t="n">
-        <v>46</v>
+        <v>39.86</v>
       </c>
       <c r="AA13" s="36" t="n">
-        <v>45.14</v>
+        <v>37.14</v>
       </c>
       <c r="AB13" s="36" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
@@ -3407,7 +3407,7 @@
         <v>52.57</v>
       </c>
       <c r="AB14" s="36" t="n">
-        <v>38</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="15">
@@ -3497,7 +3497,7 @@
         <v>31.29</v>
       </c>
       <c r="AB15" s="36" t="n">
-        <v>37.25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16">
@@ -3587,7 +3587,7 @@
         <v>36.43</v>
       </c>
       <c r="AB16" s="36" t="n">
-        <v>32.5</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="17">
@@ -3677,7 +3677,7 @@
         <v>34.71</v>
       </c>
       <c r="AB17" s="36" t="n">
-        <v>29</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="18">
@@ -3767,108 +3767,108 @@
         <v>30.29</v>
       </c>
       <c r="AB18" s="36" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>0.5</v>
+        <v>19.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>3.33</v>
+        <v>15.86</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>11.71</v>
+        <v>14.86</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.57</v>
+        <v>16.71</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>20.43</v>
+        <v>19.71</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>21.71</v>
+        <v>16.86</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>15</v>
+        <v>24.86</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>22.71</v>
+        <v>23.43</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>22.43</v>
+        <v>19.43</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>20.14</v>
+        <v>25.57</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>15.71</v>
+        <v>27.43</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>19.43</v>
+        <v>29.14</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>20.29</v>
+        <v>25</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>22.29</v>
+        <v>29.57</v>
       </c>
       <c r="T19" s="36" t="n">
-        <v>21.29</v>
+        <v>29.43</v>
       </c>
       <c r="U19" s="36" t="n">
-        <v>25.14</v>
+        <v>21</v>
       </c>
       <c r="V19" s="36" t="n">
-        <v>23.57</v>
+        <v>27.14</v>
       </c>
       <c r="W19" s="36" t="n">
-        <v>26.29</v>
+        <v>25.57</v>
       </c>
       <c r="X19" s="36" t="n">
-        <v>26.43</v>
+        <v>30.29</v>
       </c>
       <c r="Y19" s="36" t="n">
-        <v>23.71</v>
+        <v>26.57</v>
       </c>
       <c r="Z19" s="36" t="n">
-        <v>22</v>
+        <v>22.86</v>
       </c>
       <c r="AA19" s="36" t="n">
-        <v>29</v>
+        <v>27.43</v>
       </c>
       <c r="AB19" s="36" t="n">
-        <v>25.75</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
@@ -3881,343 +3881,343 @@
         <v>0</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>3.25</v>
+        <v>0.5</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>8</v>
+        <v>3.33</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>9.43</v>
+        <v>11.71</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>12.71</v>
+        <v>17.57</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>11.57</v>
+        <v>20.43</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>21.71</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>11.86</v>
+        <v>15</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>22.71</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>19</v>
+        <v>22.43</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>19.57</v>
+        <v>20.14</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>16.86</v>
+        <v>15.71</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>15</v>
+        <v>19.43</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>14.71</v>
+        <v>20.29</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>15.86</v>
+        <v>22.29</v>
       </c>
       <c r="T20" s="36" t="n">
-        <v>25</v>
+        <v>21.29</v>
       </c>
       <c r="U20" s="36" t="n">
-        <v>27.29</v>
+        <v>25.14</v>
       </c>
       <c r="V20" s="36" t="n">
-        <v>17.14</v>
+        <v>23.57</v>
       </c>
       <c r="W20" s="36" t="n">
-        <v>22.14</v>
+        <v>26.29</v>
       </c>
       <c r="X20" s="36" t="n">
-        <v>23.43</v>
+        <v>26.43</v>
       </c>
       <c r="Y20" s="36" t="n">
-        <v>24.14</v>
+        <v>23.71</v>
       </c>
       <c r="Z20" s="36" t="n">
-        <v>16.43</v>
+        <v>22</v>
       </c>
       <c r="AA20" s="36" t="n">
-        <v>25.29</v>
+        <v>29</v>
       </c>
       <c r="AB20" s="36" t="n">
-        <v>24.75</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>19.43</v>
+        <v>3.25</v>
       </c>
       <c r="G21" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H21" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I21" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="J21" s="36" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="K21" s="36" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L21" s="36" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="M21" s="36" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N21" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="O21" s="36" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="P21" s="36" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="Q21" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="R21" s="36" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="S21" s="36" t="n">
         <v>15.86</v>
       </c>
-      <c r="H21" s="36" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="I21" s="36" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="J21" s="36" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="K21" s="36" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="L21" s="36" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="M21" s="36" t="n">
+      <c r="T21" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="U21" s="36" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="V21" s="36" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="W21" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="X21" s="36" t="n">
         <v>23.43</v>
       </c>
-      <c r="N21" s="36" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="O21" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="P21" s="36" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="Q21" s="36" t="n">
-        <v>29.14</v>
-      </c>
-      <c r="R21" s="36" t="n">
-        <v>25</v>
-      </c>
-      <c r="S21" s="36" t="n">
-        <v>29.57</v>
-      </c>
-      <c r="T21" s="36" t="n">
-        <v>29.43</v>
-      </c>
-      <c r="U21" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="V21" s="36" t="n">
-        <v>27.14</v>
-      </c>
-      <c r="W21" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="X21" s="36" t="n">
-        <v>30.29</v>
-      </c>
       <c r="Y21" s="36" t="n">
-        <v>26.57</v>
+        <v>24.14</v>
       </c>
       <c r="Z21" s="36" t="n">
-        <v>22.86</v>
+        <v>16.43</v>
       </c>
       <c r="AA21" s="36" t="n">
-        <v>27.43</v>
+        <v>25.29</v>
       </c>
       <c r="AB21" s="36" t="n">
-        <v>21.5</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D22" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E22" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G22" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="F22" s="36" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="G22" s="36" t="n">
-        <v>5.29</v>
-      </c>
       <c r="H22" s="36" t="n">
-        <v>7.86</v>
+        <v>6</v>
       </c>
       <c r="I22" s="36" t="n">
-        <v>7.14</v>
+        <v>4.43</v>
       </c>
       <c r="J22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="K22" s="36" t="n">
-        <v>7.14</v>
+        <v>5.86</v>
       </c>
       <c r="L22" s="36" t="n">
-        <v>8.289999999999999</v>
+        <v>5.71</v>
       </c>
       <c r="M22" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>6</v>
       </c>
       <c r="N22" s="36" t="n">
-        <v>8.710000000000001</v>
+        <v>7.43</v>
       </c>
       <c r="O22" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P22" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>7.71</v>
       </c>
       <c r="Q22" s="36" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="R22" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="S22" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="R22" s="36" t="n">
+      <c r="T22" s="36" t="n">
         <v>9.289999999999999</v>
       </c>
-      <c r="S22" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="T22" s="36" t="n">
-        <v>6.86</v>
-      </c>
       <c r="U22" s="36" t="n">
-        <v>12.14</v>
+        <v>12.71</v>
       </c>
       <c r="V22" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>9.57</v>
       </c>
       <c r="W22" s="36" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X22" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>14.86</v>
       </c>
       <c r="Y22" s="36" t="n">
-        <v>11.71</v>
+        <v>11</v>
       </c>
       <c r="Z22" s="36" t="n">
-        <v>8</v>
+        <v>8.57</v>
       </c>
       <c r="AA22" s="36" t="n">
-        <v>8</v>
+        <v>11.43</v>
       </c>
       <c r="AB22" s="36" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F23" s="36" t="n">
-        <v>2.8</v>
+        <v>5.14</v>
       </c>
       <c r="G23" s="36" t="n">
-        <v>4</v>
+        <v>5.29</v>
       </c>
       <c r="H23" s="36" t="n">
-        <v>6</v>
+        <v>7.86</v>
       </c>
       <c r="I23" s="36" t="n">
-        <v>4.43</v>
+        <v>7.14</v>
       </c>
       <c r="J23" s="36" t="n">
-        <v>3.43</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K23" s="36" t="n">
-        <v>5.86</v>
+        <v>7.14</v>
       </c>
       <c r="L23" s="36" t="n">
-        <v>5.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="M23" s="36" t="n">
-        <v>6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N23" s="36" t="n">
-        <v>7.43</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O23" s="36" t="n">
         <v>5</v>
       </c>
       <c r="P23" s="36" t="n">
-        <v>7.71</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q23" s="36" t="n">
-        <v>10.29</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="R23" s="36" t="n">
-        <v>7</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="S23" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="T23" s="36" t="n">
-        <v>9.289999999999999</v>
+        <v>6.86</v>
       </c>
       <c r="U23" s="36" t="n">
-        <v>12.71</v>
+        <v>12.14</v>
       </c>
       <c r="V23" s="36" t="n">
-        <v>9.57</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="W23" s="36" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X23" s="36" t="n">
-        <v>14.86</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="Y23" s="36" t="n">
-        <v>11</v>
+        <v>11.71</v>
       </c>
       <c r="Z23" s="36" t="n">
-        <v>8.57</v>
+        <v>8</v>
       </c>
       <c r="AA23" s="36" t="n">
-        <v>11.43</v>
+        <v>8</v>
       </c>
       <c r="AB23" s="36" t="n">
-        <v>7.75</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -4747,7 +4747,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -4837,7 +4837,7 @@
         <v>121486853</v>
       </c>
       <c r="AB6" s="40" t="n">
-        <v>48745905</v>
+        <v>79631668</v>
       </c>
     </row>
     <row r="7">
@@ -4927,7 +4927,7 @@
         <v>96334193</v>
       </c>
       <c r="AB7" s="40" t="n">
-        <v>39497971</v>
+        <v>54351384</v>
       </c>
     </row>
     <row r="8">
@@ -5017,7 +5017,7 @@
         <v>88660521</v>
       </c>
       <c r="AB8" s="40" t="n">
-        <v>44262521</v>
+        <v>60356978</v>
       </c>
     </row>
     <row r="9">
@@ -5107,7 +5107,7 @@
         <v>60557072</v>
       </c>
       <c r="AB9" s="40" t="n">
-        <v>41511665</v>
+        <v>52363221</v>
       </c>
     </row>
     <row r="10">
@@ -5197,97 +5197,97 @@
         <v>68108471</v>
       </c>
       <c r="AB10" s="40" t="n">
-        <v>28362839</v>
+        <v>42772767</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>35343350</v>
+        <v>38454971</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>51225290</v>
+        <v>42939312</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>36142612</v>
+        <v>43650420</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>47488940</v>
+        <v>53954095</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>44805002</v>
+        <v>48898463</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>43327432</v>
+        <v>48011655</v>
       </c>
       <c r="T11" s="40" t="n">
-        <v>39637968</v>
+        <v>72064876</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>55199920</v>
+        <v>59606189</v>
       </c>
       <c r="V11" s="40" t="n">
-        <v>50680631</v>
+        <v>50164748</v>
       </c>
       <c r="W11" s="40" t="n">
-        <v>50163008</v>
+        <v>46095774</v>
       </c>
       <c r="X11" s="40" t="n">
-        <v>38778399</v>
+        <v>57645111</v>
       </c>
       <c r="Y11" s="40" t="n">
-        <v>50996587</v>
+        <v>55172528</v>
       </c>
       <c r="Z11" s="40" t="n">
-        <v>42228986</v>
+        <v>47962010</v>
       </c>
       <c r="AA11" s="40" t="n">
-        <v>32767816</v>
+        <v>43352139</v>
       </c>
       <c r="AB11" s="40" t="n">
-        <v>24295224</v>
+        <v>32439177</v>
       </c>
     </row>
     <row r="12">
@@ -5377,97 +5377,97 @@
         <v>56470370</v>
       </c>
       <c r="AB12" s="40" t="n">
-        <v>19560715</v>
+        <v>26462475</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>0</v>
+        <v>536260</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>8972650</v>
+        <v>14403556</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>18100396</v>
+        <v>16216832</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>23988817</v>
+        <v>32622053</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>22409732</v>
+        <v>23929705</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37715520</v>
+        <v>37214538</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>35926824</v>
+        <v>25375430</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>39462393</v>
+        <v>31500087</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>51983942</v>
+        <v>28078687</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>58935844</v>
+        <v>34472458</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>38454971</v>
+        <v>35343350</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>42939312</v>
+        <v>51225290</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>43650420</v>
+        <v>36142612</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>53954095</v>
+        <v>47488940</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>48898463</v>
+        <v>44805002</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>48011655</v>
+        <v>43327432</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>72064876</v>
+        <v>39637968</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>59606189</v>
+        <v>55199920</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>50164748</v>
+        <v>50680631</v>
       </c>
       <c r="W13" s="40" t="n">
-        <v>46095774</v>
+        <v>50163008</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>57645111</v>
+        <v>38778399</v>
       </c>
       <c r="Y13" s="40" t="n">
-        <v>55172528</v>
+        <v>50996587</v>
       </c>
       <c r="Z13" s="40" t="n">
-        <v>47962010</v>
+        <v>42228986</v>
       </c>
       <c r="AA13" s="40" t="n">
-        <v>43352139</v>
+        <v>32767816</v>
       </c>
       <c r="AB13" s="40" t="n">
-        <v>24598150</v>
+        <v>31365320</v>
       </c>
     </row>
     <row r="14">
@@ -5557,7 +5557,7 @@
         <v>43911137</v>
       </c>
       <c r="AB14" s="40" t="n">
-        <v>18794885</v>
+        <v>24445515</v>
       </c>
     </row>
     <row r="15">
@@ -5647,7 +5647,7 @@
         <v>29229414</v>
       </c>
       <c r="AB15" s="40" t="n">
-        <v>16490970</v>
+        <v>21143642</v>
       </c>
     </row>
     <row r="16">
@@ -5737,7 +5737,7 @@
         <v>39000780</v>
       </c>
       <c r="AB16" s="40" t="n">
-        <v>18634420</v>
+        <v>27457145</v>
       </c>
     </row>
     <row r="17">
@@ -5827,7 +5827,7 @@
         <v>52198815</v>
       </c>
       <c r="AB17" s="40" t="n">
-        <v>23446830</v>
+        <v>33808770</v>
       </c>
     </row>
     <row r="18">
@@ -5917,108 +5917,108 @@
         <v>53200913</v>
       </c>
       <c r="AB18" s="40" t="n">
-        <v>15157200</v>
+        <v>17597780</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>6239584</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0</v>
+        <v>13803407</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>363900</v>
+        <v>28572076</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>3736700</v>
+        <v>15282581</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>17796776</v>
+        <v>16594572</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>42724228</v>
+        <v>15223898</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>33036620</v>
+        <v>27696695</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>29649130</v>
+        <v>17717888</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>13949368</v>
+        <v>24163432</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>24539413</v>
+        <v>23623477</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>19087217</v>
+        <v>19145601</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>17139440</v>
+        <v>30157601</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>17746930</v>
+        <v>41172333</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>21437830</v>
+        <v>34303423</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>17616397</v>
+        <v>35044850</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>19360848</v>
+        <v>33519824</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>25377166</v>
+        <v>25969876</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>24702051</v>
+        <v>23835106</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>26856647</v>
+        <v>27833047</v>
       </c>
       <c r="W19" s="40" t="n">
-        <v>27122255</v>
+        <v>22815382</v>
       </c>
       <c r="X19" s="40" t="n">
-        <v>30650242</v>
+        <v>28299644</v>
       </c>
       <c r="Y19" s="40" t="n">
-        <v>21101547</v>
+        <v>23130899</v>
       </c>
       <c r="Z19" s="40" t="n">
-        <v>30037062</v>
+        <v>20390472</v>
       </c>
       <c r="AA19" s="40" t="n">
-        <v>22123372</v>
+        <v>25564267</v>
       </c>
       <c r="AB19" s="40" t="n">
-        <v>14758520</v>
+        <v>17219139</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
@@ -6031,343 +6031,343 @@
         <v>0</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>1324510</v>
+        <v>363900</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>10311989</v>
+        <v>3736700</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>19934535</v>
+        <v>17796776</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>13536614</v>
+        <v>42724228</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>22187720</v>
+        <v>33036620</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>11732010</v>
+        <v>29649130</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>21143100</v>
+        <v>13949368</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>14330970</v>
+        <v>24539413</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>38267409</v>
+        <v>19087217</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>46351274</v>
+        <v>17139440</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>37105387</v>
+        <v>17746930</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>19868191</v>
+        <v>21437830</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>15153480</v>
+        <v>17616397</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>19277087</v>
+        <v>19360848</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>34209889</v>
+        <v>25377166</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>33260760</v>
+        <v>24702051</v>
       </c>
       <c r="V20" s="40" t="n">
-        <v>23559262</v>
+        <v>26856647</v>
       </c>
       <c r="W20" s="40" t="n">
-        <v>29206004</v>
+        <v>27122255</v>
       </c>
       <c r="X20" s="40" t="n">
-        <v>26477239</v>
+        <v>30650242</v>
       </c>
       <c r="Y20" s="40" t="n">
-        <v>31392938</v>
+        <v>21101547</v>
       </c>
       <c r="Z20" s="40" t="n">
-        <v>14752034</v>
+        <v>30037062</v>
       </c>
       <c r="AA20" s="40" t="n">
-        <v>27021110</v>
+        <v>22123372</v>
       </c>
       <c r="AB20" s="40" t="n">
-        <v>14898250</v>
+        <v>17770343</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>6239584</v>
+        <v>0</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>13803407</v>
+        <v>0</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>28572076</v>
+        <v>1324510</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>15282581</v>
+        <v>10311989</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>16594572</v>
+        <v>19934535</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>15223898</v>
+        <v>13536614</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>27696695</v>
+        <v>22187720</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>17717888</v>
+        <v>11732010</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>24163432</v>
+        <v>21143100</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>23623477</v>
+        <v>14330970</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>19145601</v>
+        <v>38267409</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>30157601</v>
+        <v>46351274</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>41172333</v>
+        <v>37105387</v>
       </c>
       <c r="Q21" s="40" t="n">
-        <v>34303423</v>
+        <v>19868191</v>
       </c>
       <c r="R21" s="40" t="n">
-        <v>35044850</v>
+        <v>15153480</v>
       </c>
       <c r="S21" s="40" t="n">
-        <v>33519824</v>
+        <v>19277087</v>
       </c>
       <c r="T21" s="40" t="n">
-        <v>25969876</v>
+        <v>34209889</v>
       </c>
       <c r="U21" s="40" t="n">
-        <v>23835106</v>
+        <v>33260760</v>
       </c>
       <c r="V21" s="40" t="n">
-        <v>27833047</v>
+        <v>23559262</v>
       </c>
       <c r="W21" s="40" t="n">
-        <v>22815382</v>
+        <v>29206004</v>
       </c>
       <c r="X21" s="40" t="n">
-        <v>28299644</v>
+        <v>26477239</v>
       </c>
       <c r="Y21" s="40" t="n">
-        <v>23130899</v>
+        <v>31392938</v>
       </c>
       <c r="Z21" s="40" t="n">
-        <v>20390472</v>
+        <v>14752034</v>
       </c>
       <c r="AA21" s="40" t="n">
-        <v>25564267</v>
+        <v>27021110</v>
       </c>
       <c r="AB21" s="40" t="n">
-        <v>10833129</v>
+        <v>18331990</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="40" t="n">
-        <v>862720</v>
+        <v>0</v>
       </c>
       <c r="D22" s="40" t="n">
-        <v>2474409</v>
+        <v>0</v>
       </c>
       <c r="E22" s="40" t="n">
-        <v>4696696</v>
+        <v>0</v>
       </c>
       <c r="F22" s="40" t="n">
-        <v>6991878</v>
+        <v>1339100</v>
       </c>
       <c r="G22" s="40" t="n">
-        <v>4060163</v>
+        <v>5579340</v>
       </c>
       <c r="H22" s="40" t="n">
-        <v>7685466</v>
+        <v>9518200</v>
       </c>
       <c r="I22" s="40" t="n">
-        <v>10141286</v>
+        <v>11747640</v>
       </c>
       <c r="J22" s="40" t="n">
-        <v>6393871</v>
+        <v>3885270</v>
       </c>
       <c r="K22" s="40" t="n">
-        <v>4534503</v>
+        <v>8765870</v>
       </c>
       <c r="L22" s="40" t="n">
-        <v>7579040</v>
+        <v>4571680</v>
       </c>
       <c r="M22" s="40" t="n">
-        <v>9679437</v>
+        <v>3911995</v>
       </c>
       <c r="N22" s="40" t="n">
-        <v>6102368</v>
+        <v>9234090</v>
       </c>
       <c r="O22" s="40" t="n">
-        <v>4294070</v>
+        <v>5390260</v>
       </c>
       <c r="P22" s="40" t="n">
-        <v>5589419</v>
+        <v>4645370</v>
       </c>
       <c r="Q22" s="40" t="n">
-        <v>10264941</v>
+        <v>10400980</v>
       </c>
       <c r="R22" s="40" t="n">
-        <v>6114083</v>
+        <v>6123322</v>
       </c>
       <c r="S22" s="40" t="n">
-        <v>10758755</v>
+        <v>5648770</v>
       </c>
       <c r="T22" s="40" t="n">
-        <v>6048269</v>
+        <v>6880660</v>
       </c>
       <c r="U22" s="40" t="n">
-        <v>9823030</v>
+        <v>10209080</v>
       </c>
       <c r="V22" s="40" t="n">
-        <v>7263590</v>
+        <v>17909229</v>
       </c>
       <c r="W22" s="40" t="n">
-        <v>14940492</v>
+        <v>9500343</v>
       </c>
       <c r="X22" s="40" t="n">
-        <v>8868985</v>
+        <v>19439125</v>
       </c>
       <c r="Y22" s="40" t="n">
-        <v>13151700</v>
+        <v>9558790</v>
       </c>
       <c r="Z22" s="40" t="n">
-        <v>7846730</v>
+        <v>7475060</v>
       </c>
       <c r="AA22" s="40" t="n">
-        <v>5590930</v>
+        <v>12183598</v>
       </c>
       <c r="AB22" s="40" t="n">
-        <v>3444398</v>
+        <v>6201972</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="40" t="n">
-        <v>0</v>
+        <v>862720</v>
       </c>
       <c r="D23" s="40" t="n">
-        <v>0</v>
+        <v>2474409</v>
       </c>
       <c r="E23" s="40" t="n">
-        <v>0</v>
+        <v>4696696</v>
       </c>
       <c r="F23" s="40" t="n">
-        <v>1339100</v>
+        <v>6991878</v>
       </c>
       <c r="G23" s="40" t="n">
-        <v>5579340</v>
+        <v>4060163</v>
       </c>
       <c r="H23" s="40" t="n">
-        <v>9518200</v>
+        <v>7685466</v>
       </c>
       <c r="I23" s="40" t="n">
-        <v>11747640</v>
+        <v>10141286</v>
       </c>
       <c r="J23" s="40" t="n">
-        <v>3885270</v>
+        <v>6393871</v>
       </c>
       <c r="K23" s="40" t="n">
-        <v>8765870</v>
+        <v>4534503</v>
       </c>
       <c r="L23" s="40" t="n">
-        <v>4571680</v>
+        <v>7579040</v>
       </c>
       <c r="M23" s="40" t="n">
-        <v>3911995</v>
+        <v>9679437</v>
       </c>
       <c r="N23" s="40" t="n">
-        <v>9234090</v>
+        <v>6102368</v>
       </c>
       <c r="O23" s="40" t="n">
-        <v>5390260</v>
+        <v>4294070</v>
       </c>
       <c r="P23" s="40" t="n">
-        <v>4645370</v>
+        <v>5589419</v>
       </c>
       <c r="Q23" s="40" t="n">
-        <v>10400980</v>
+        <v>10264941</v>
       </c>
       <c r="R23" s="40" t="n">
-        <v>6123322</v>
+        <v>6114083</v>
       </c>
       <c r="S23" s="40" t="n">
-        <v>5648770</v>
+        <v>10758755</v>
       </c>
       <c r="T23" s="40" t="n">
-        <v>6880660</v>
+        <v>6048269</v>
       </c>
       <c r="U23" s="40" t="n">
-        <v>10209080</v>
+        <v>9823030</v>
       </c>
       <c r="V23" s="40" t="n">
-        <v>17909229</v>
+        <v>7263590</v>
       </c>
       <c r="W23" s="40" t="n">
-        <v>9500343</v>
+        <v>14940492</v>
       </c>
       <c r="X23" s="40" t="n">
-        <v>19439125</v>
+        <v>8868985</v>
       </c>
       <c r="Y23" s="40" t="n">
-        <v>9558790</v>
+        <v>13151700</v>
       </c>
       <c r="Z23" s="40" t="n">
-        <v>7475060</v>
+        <v>7846730</v>
       </c>
       <c r="AA23" s="40" t="n">
-        <v>12183598</v>
+        <v>5590930</v>
       </c>
       <c r="AB23" s="40" t="n">
-        <v>3325182</v>
+        <v>4003358</v>
       </c>
     </row>
     <row r="24">
@@ -6897,7 +6897,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -6987,7 +6987,7 @@
         <v>7</v>
       </c>
       <c r="AB6" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -7077,7 +7077,7 @@
         <v>7</v>
       </c>
       <c r="AB7" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -7167,7 +7167,7 @@
         <v>7</v>
       </c>
       <c r="AB8" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -7257,7 +7257,7 @@
         <v>7</v>
       </c>
       <c r="AB9" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -7347,28 +7347,28 @@
         <v>7</v>
       </c>
       <c r="AB10" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -7431,13 +7431,13 @@
         <v>7</v>
       </c>
       <c r="Z11" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA11" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB11" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -7527,97 +7527,97 @@
         <v>7</v>
       </c>
       <c r="AB12" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB13" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z13" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB13" s="42" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -7707,7 +7707,7 @@
         <v>7</v>
       </c>
       <c r="AB14" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -7797,7 +7797,7 @@
         <v>7</v>
       </c>
       <c r="AB15" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -7887,7 +7887,7 @@
         <v>7</v>
       </c>
       <c r="AB16" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -7977,7 +7977,7 @@
         <v>7</v>
       </c>
       <c r="AB17" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -8067,34 +8067,34 @@
         <v>7</v>
       </c>
       <c r="AB18" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -8157,18 +8157,18 @@
         <v>7</v>
       </c>
       <c r="AB19" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
@@ -8181,10 +8181,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20" s="42" t="n">
         <v>7</v>
@@ -8247,32 +8247,32 @@
         <v>7</v>
       </c>
       <c r="AB20" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F21" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="G21" s="42" t="n">
         <v>7</v>
       </c>
@@ -8337,31 +8337,31 @@
         <v>7</v>
       </c>
       <c r="AB21" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-307</t>
+          <t>FRМРГ-8</t>
         </is>
       </c>
       <c r="B22" s="35" t="inlineStr">
         <is>
-          <t>Крестик</t>
+          <t>Маргилан</t>
         </is>
       </c>
       <c r="C22" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F22" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G22" s="42" t="n">
         <v>7</v>
@@ -8382,7 +8382,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N22" s="42" t="n">
         <v>7</v>
@@ -8427,97 +8427,97 @@
         <v>7</v>
       </c>
       <c r="AB22" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
         <is>
-          <t>FRМРГ-8</t>
+          <t>FRТАШ-307</t>
         </is>
       </c>
       <c r="B23" s="35" t="inlineStr">
         <is>
-          <t>Маргилан</t>
+          <t>Крестик</t>
         </is>
       </c>
       <c r="C23" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D23" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E23" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA23" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB23" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="G23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M23" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="N23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA23" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB23" s="42" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2597,7 +2597,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -2687,7 +2687,7 @@
         <v>120</v>
       </c>
       <c r="AB6" s="36" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7">
@@ -2777,7 +2777,7 @@
         <v>90.14</v>
       </c>
       <c r="AB7" s="36" t="n">
-        <v>87.8</v>
+        <v>90.83</v>
       </c>
     </row>
     <row r="8">
@@ -2867,7 +2867,7 @@
         <v>78.56999999999999</v>
       </c>
       <c r="AB8" s="36" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -2957,7 +2957,7 @@
         <v>57.14</v>
       </c>
       <c r="AB9" s="36" t="n">
-        <v>61.2</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="10">
@@ -3047,7 +3047,7 @@
         <v>63.71</v>
       </c>
       <c r="AB10" s="36" t="n">
-        <v>56</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="11">
@@ -3137,7 +3137,7 @@
         <v>45.14</v>
       </c>
       <c r="AB11" s="36" t="n">
-        <v>45.4</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -3227,367 +3227,367 @@
         <v>51.14</v>
       </c>
       <c r="AB12" s="36" t="n">
-        <v>43.8</v>
+        <v>44.67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>1.67</v>
+        <v>6.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>12.14</v>
+        <v>11.29</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>16.57</v>
+        <v>10.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>21</v>
+        <v>11.14</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>20.29</v>
+        <v>13.86</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>28.57</v>
+        <v>18</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>24.14</v>
+        <v>18</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>27.57</v>
+        <v>17.43</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>28.14</v>
+        <v>15.29</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.86</v>
+        <v>24.43</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>33.14</v>
+        <v>24.71</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>30.71</v>
+        <v>25.57</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>31.14</v>
+        <v>19.29</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>40.29</v>
+        <v>25.43</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>38.71</v>
+        <v>22.57</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>43.14</v>
+        <v>21.29</v>
       </c>
       <c r="T13" s="36" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="U13" s="36" t="n">
+        <v>31.43</v>
+      </c>
+      <c r="V13" s="36" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="W13" s="36" t="n">
+        <v>40.71</v>
+      </c>
+      <c r="X13" s="36" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="Y13" s="36" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="Z13" s="36" t="n">
         <v>37</v>
       </c>
-      <c r="U13" s="36" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="V13" s="36" t="n">
-        <v>43.14</v>
-      </c>
-      <c r="W13" s="36" t="n">
-        <v>36.86</v>
-      </c>
-      <c r="X13" s="36" t="n">
-        <v>33.43</v>
-      </c>
-      <c r="Y13" s="36" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z13" s="36" t="n">
-        <v>39.86</v>
-      </c>
       <c r="AA13" s="36" t="n">
-        <v>37.14</v>
+        <v>52.57</v>
       </c>
       <c r="AB13" s="36" t="n">
-        <v>42</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>6.67</v>
+        <v>1.67</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>11.29</v>
+        <v>12.14</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>10.57</v>
+        <v>16.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>11.14</v>
+        <v>21</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>13.86</v>
+        <v>20.29</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>18</v>
+        <v>28.57</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>18</v>
+        <v>24.14</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>17.43</v>
+        <v>27.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>15.29</v>
+        <v>28.14</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>24.43</v>
+        <v>28.86</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>24.71</v>
+        <v>33.14</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>25.57</v>
+        <v>30.71</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>19.29</v>
+        <v>31.14</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>25.43</v>
+        <v>40.29</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>22.57</v>
+        <v>38.71</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>21.29</v>
+        <v>43.14</v>
       </c>
       <c r="T14" s="36" t="n">
-        <v>29.14</v>
+        <v>37</v>
       </c>
       <c r="U14" s="36" t="n">
-        <v>31.43</v>
+        <v>46.29</v>
       </c>
       <c r="V14" s="36" t="n">
-        <v>35.71</v>
+        <v>43.14</v>
       </c>
       <c r="W14" s="36" t="n">
-        <v>40.71</v>
+        <v>36.86</v>
       </c>
       <c r="X14" s="36" t="n">
-        <v>46.86</v>
+        <v>33.43</v>
       </c>
       <c r="Y14" s="36" t="n">
-        <v>44.71</v>
+        <v>48</v>
       </c>
       <c r="Z14" s="36" t="n">
-        <v>37</v>
+        <v>39.86</v>
       </c>
       <c r="AA14" s="36" t="n">
-        <v>52.57</v>
+        <v>37.14</v>
       </c>
       <c r="AB14" s="36" t="n">
-        <v>39.6</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.43</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>11</v>
+        <v>12.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>14.43</v>
+        <v>13.29</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>11.86</v>
+        <v>14.71</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.14</v>
+        <v>19.71</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>21</v>
+        <v>17.71</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>23.43</v>
+        <v>19.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>20.43</v>
+        <v>24.14</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>24.57</v>
+        <v>27.57</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>24.14</v>
+        <v>24.43</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>24.43</v>
+        <v>27.29</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>22</v>
+        <v>26.57</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>23</v>
+        <v>25.57</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>18.43</v>
+        <v>29</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>24.71</v>
+        <v>27.71</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>27.57</v>
+        <v>32.57</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>30</v>
+        <v>31.57</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>28.57</v>
+        <v>29.57</v>
       </c>
       <c r="W15" s="36" t="n">
-        <v>30.14</v>
+        <v>29.86</v>
       </c>
       <c r="X15" s="36" t="n">
-        <v>34.43</v>
+        <v>32</v>
       </c>
       <c r="Y15" s="36" t="n">
-        <v>33.43</v>
+        <v>32.14</v>
       </c>
       <c r="Z15" s="36" t="n">
-        <v>32</v>
+        <v>27.14</v>
       </c>
       <c r="AA15" s="36" t="n">
-        <v>31.29</v>
+        <v>36.43</v>
       </c>
       <c r="AB15" s="36" t="n">
-        <v>38</v>
+        <v>37.33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.43</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>12.43</v>
+        <v>11</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.29</v>
+        <v>14.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>14.71</v>
+        <v>11.86</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>19.71</v>
+        <v>19.14</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>17.71</v>
+        <v>21</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>19.57</v>
+        <v>23.43</v>
       </c>
       <c r="L16" s="36" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="M16" s="36" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="N16" s="36" t="n">
         <v>24.14</v>
       </c>
-      <c r="M16" s="36" t="n">
+      <c r="O16" s="36" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="P16" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q16" s="36" t="n">
+        <v>23</v>
+      </c>
+      <c r="R16" s="36" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="S16" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="T16" s="36" t="n">
         <v>27.57</v>
       </c>
-      <c r="N16" s="36" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="O16" s="36" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="P16" s="36" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="Q16" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="R16" s="36" t="n">
-        <v>29</v>
-      </c>
-      <c r="S16" s="36" t="n">
-        <v>27.71</v>
-      </c>
-      <c r="T16" s="36" t="n">
-        <v>32.57</v>
-      </c>
       <c r="U16" s="36" t="n">
-        <v>31.57</v>
+        <v>30</v>
       </c>
       <c r="V16" s="36" t="n">
-        <v>29.57</v>
+        <v>28.57</v>
       </c>
       <c r="W16" s="36" t="n">
-        <v>29.86</v>
+        <v>30.14</v>
       </c>
       <c r="X16" s="36" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="Y16" s="36" t="n">
+        <v>33.43</v>
+      </c>
+      <c r="Z16" s="36" t="n">
         <v>32</v>
       </c>
-      <c r="Y16" s="36" t="n">
-        <v>32.14</v>
-      </c>
-      <c r="Z16" s="36" t="n">
-        <v>27.14</v>
-      </c>
       <c r="AA16" s="36" t="n">
-        <v>36.43</v>
+        <v>31.29</v>
       </c>
       <c r="AB16" s="36" t="n">
-        <v>37.6</v>
+        <v>35.33</v>
       </c>
     </row>
     <row r="17">
@@ -3677,7 +3677,7 @@
         <v>34.71</v>
       </c>
       <c r="AB17" s="36" t="n">
-        <v>32.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
@@ -3767,7 +3767,7 @@
         <v>30.29</v>
       </c>
       <c r="AB18" s="36" t="n">
-        <v>27.6</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="19">
@@ -3857,7 +3857,7 @@
         <v>27.43</v>
       </c>
       <c r="AB19" s="36" t="n">
-        <v>27.2</v>
+        <v>27.33</v>
       </c>
     </row>
     <row r="20">
@@ -3947,7 +3947,7 @@
         <v>29</v>
       </c>
       <c r="AB20" s="36" t="n">
-        <v>25.8</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="21">
@@ -4037,7 +4037,7 @@
         <v>25.29</v>
       </c>
       <c r="AB21" s="36" t="n">
-        <v>24.6</v>
+        <v>25.67</v>
       </c>
     </row>
     <row r="22">
@@ -4127,7 +4127,7 @@
         <v>11.43</v>
       </c>
       <c r="AB22" s="36" t="n">
-        <v>10.2</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="23">
@@ -4217,7 +4217,7 @@
         <v>8</v>
       </c>
       <c r="AB23" s="36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="24">
@@ -4747,7 +4747,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -4837,7 +4837,7 @@
         <v>121486853</v>
       </c>
       <c r="AB6" s="40" t="n">
-        <v>79631668</v>
+        <v>93595747</v>
       </c>
     </row>
     <row r="7">
@@ -4927,7 +4927,7 @@
         <v>96334193</v>
       </c>
       <c r="AB7" s="40" t="n">
-        <v>54351384</v>
+        <v>71254033</v>
       </c>
     </row>
     <row r="8">
@@ -5017,7 +5017,7 @@
         <v>88660521</v>
       </c>
       <c r="AB8" s="40" t="n">
-        <v>60356978</v>
+        <v>73138370</v>
       </c>
     </row>
     <row r="9">
@@ -5107,7 +5107,7 @@
         <v>60557072</v>
       </c>
       <c r="AB9" s="40" t="n">
-        <v>52363221</v>
+        <v>62026261</v>
       </c>
     </row>
     <row r="10">
@@ -5197,7 +5197,7 @@
         <v>68108471</v>
       </c>
       <c r="AB10" s="40" t="n">
-        <v>42772767</v>
+        <v>57193725</v>
       </c>
     </row>
     <row r="11">
@@ -5287,7 +5287,7 @@
         <v>43352139</v>
       </c>
       <c r="AB11" s="40" t="n">
-        <v>32439177</v>
+        <v>38912322</v>
       </c>
     </row>
     <row r="12">
@@ -5377,367 +5377,367 @@
         <v>56470370</v>
       </c>
       <c r="AB12" s="40" t="n">
-        <v>26462475</v>
+        <v>30848128</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>536260</v>
+        <v>5092853</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>14403556</v>
+        <v>11100161</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>16216832</v>
+        <v>14612055</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>32622053</v>
+        <v>20638987</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>23929705</v>
+        <v>14061352</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37214538</v>
+        <v>31599148</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25375430</v>
+        <v>18747614</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>31500087</v>
+        <v>19576415</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28078687</v>
+        <v>14226838</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>34472458</v>
+        <v>23197145</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>35343350</v>
+        <v>25790711</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>51225290</v>
+        <v>27856115</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>36142612</v>
+        <v>20981901</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>47488940</v>
+        <v>25433123</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>44805002</v>
+        <v>19355230</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>43327432</v>
+        <v>24713836</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>39637968</v>
+        <v>20195634</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>55199920</v>
+        <v>32414171</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>50680631</v>
+        <v>42780769</v>
       </c>
       <c r="W13" s="40" t="n">
-        <v>50163008</v>
+        <v>36755122</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>38778399</v>
+        <v>38071365</v>
       </c>
       <c r="Y13" s="40" t="n">
-        <v>50996587</v>
+        <v>34397222</v>
       </c>
       <c r="Z13" s="40" t="n">
-        <v>42228986</v>
+        <v>32536036</v>
       </c>
       <c r="AA13" s="40" t="n">
-        <v>32767816</v>
+        <v>43911137</v>
       </c>
       <c r="AB13" s="40" t="n">
-        <v>31365320</v>
+        <v>29624305</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>5092853</v>
+        <v>536260</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>11100161</v>
+        <v>14403556</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>14612055</v>
+        <v>16216832</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>20638987</v>
+        <v>32622053</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>14061352</v>
+        <v>23929705</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>31599148</v>
+        <v>37214538</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>18747614</v>
+        <v>25375430</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>19576415</v>
+        <v>31500087</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>14226838</v>
+        <v>28078687</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>23197145</v>
+        <v>34472458</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>25790711</v>
+        <v>35343350</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>27856115</v>
+        <v>51225290</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>20981901</v>
+        <v>36142612</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>25433123</v>
+        <v>47488940</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>19355230</v>
+        <v>44805002</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>24713836</v>
+        <v>43327432</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>20195634</v>
+        <v>39637968</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>32414171</v>
+        <v>55199920</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>42780769</v>
+        <v>50680631</v>
       </c>
       <c r="W14" s="40" t="n">
-        <v>36755122</v>
+        <v>50163008</v>
       </c>
       <c r="X14" s="40" t="n">
-        <v>38071365</v>
+        <v>38778399</v>
       </c>
       <c r="Y14" s="40" t="n">
-        <v>34397222</v>
+        <v>50996587</v>
       </c>
       <c r="Z14" s="40" t="n">
-        <v>32536036</v>
+        <v>42228986</v>
       </c>
       <c r="AA14" s="40" t="n">
-        <v>43911137</v>
+        <v>32767816</v>
       </c>
       <c r="AB14" s="40" t="n">
-        <v>24445515</v>
+        <v>38696295</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>530238</v>
+        <v>475871</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>8544625</v>
+        <v>11884771</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>8387478</v>
+        <v>10651216</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>10570508</v>
+        <v>13882033</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>11896580</v>
+        <v>17812948</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>19614352</v>
+        <v>17331854</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>20966317</v>
+        <v>26294756</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>20073400</v>
+        <v>24196222</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>23801493</v>
+        <v>22122847</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>27940611</v>
+        <v>31914115</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>27893929</v>
+        <v>32069521</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>29635773</v>
+        <v>38287475</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>19554230</v>
+        <v>28283704</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>23848495</v>
+        <v>27334091</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>24194638</v>
+        <v>36312415</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>20330094</v>
+        <v>39333565</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>26044199</v>
+        <v>28566119</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>24608772</v>
+        <v>40387845</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>28079726</v>
+        <v>39744111</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>20968052</v>
+        <v>31477917</v>
       </c>
       <c r="W15" s="40" t="n">
-        <v>29501132</v>
+        <v>29910767</v>
       </c>
       <c r="X15" s="40" t="n">
-        <v>30624981</v>
+        <v>44620606</v>
       </c>
       <c r="Y15" s="40" t="n">
-        <v>28071639</v>
+        <v>35679497</v>
       </c>
       <c r="Z15" s="40" t="n">
-        <v>21021583</v>
+        <v>25102609</v>
       </c>
       <c r="AA15" s="40" t="n">
-        <v>29229414</v>
+        <v>39000780</v>
       </c>
       <c r="AB15" s="40" t="n">
-        <v>21143642</v>
+        <v>33576555</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>475871</v>
+        <v>530238</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>11884771</v>
+        <v>8544625</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>10651216</v>
+        <v>8387478</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>13882033</v>
+        <v>10570508</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>17812948</v>
+        <v>11896580</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>17331854</v>
+        <v>19614352</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>26294756</v>
+        <v>20966317</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>24196222</v>
+        <v>20073400</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>22122847</v>
+        <v>23801493</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>31914115</v>
+        <v>27940611</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>32069521</v>
+        <v>27893929</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>38287475</v>
+        <v>29635773</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>28283704</v>
+        <v>19554230</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>27334091</v>
+        <v>23848495</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>36312415</v>
+        <v>24194638</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>39333565</v>
+        <v>20330094</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>28566119</v>
+        <v>26044199</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>40387845</v>
+        <v>24608772</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>39744111</v>
+        <v>28079726</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>31477917</v>
+        <v>20968052</v>
       </c>
       <c r="W16" s="40" t="n">
-        <v>29910767</v>
+        <v>29501132</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>44620606</v>
+        <v>30624981</v>
       </c>
       <c r="Y16" s="40" t="n">
-        <v>35679497</v>
+        <v>28071639</v>
       </c>
       <c r="Z16" s="40" t="n">
-        <v>25102609</v>
+        <v>21021583</v>
       </c>
       <c r="AA16" s="40" t="n">
-        <v>39000780</v>
+        <v>29229414</v>
       </c>
       <c r="AB16" s="40" t="n">
-        <v>27457145</v>
+        <v>22834402</v>
       </c>
     </row>
     <row r="17">
@@ -5827,7 +5827,7 @@
         <v>52198815</v>
       </c>
       <c r="AB17" s="40" t="n">
-        <v>33808770</v>
+        <v>46792251</v>
       </c>
     </row>
     <row r="18">
@@ -5917,7 +5917,7 @@
         <v>53200913</v>
       </c>
       <c r="AB18" s="40" t="n">
-        <v>17597780</v>
+        <v>22432829</v>
       </c>
     </row>
     <row r="19">
@@ -6007,7 +6007,7 @@
         <v>25564267</v>
       </c>
       <c r="AB19" s="40" t="n">
-        <v>17219139</v>
+        <v>21703917</v>
       </c>
     </row>
     <row r="20">
@@ -6097,7 +6097,7 @@
         <v>22123372</v>
       </c>
       <c r="AB20" s="40" t="n">
-        <v>17770343</v>
+        <v>21187163</v>
       </c>
     </row>
     <row r="21">
@@ -6187,7 +6187,7 @@
         <v>27021110</v>
       </c>
       <c r="AB21" s="40" t="n">
-        <v>18331990</v>
+        <v>22203030</v>
       </c>
     </row>
     <row r="22">
@@ -6277,7 +6277,7 @@
         <v>12183598</v>
       </c>
       <c r="AB22" s="40" t="n">
-        <v>6201972</v>
+        <v>7462462</v>
       </c>
     </row>
     <row r="23">
@@ -6367,7 +6367,7 @@
         <v>5590930</v>
       </c>
       <c r="AB23" s="40" t="n">
-        <v>4003358</v>
+        <v>4653508</v>
       </c>
     </row>
     <row r="24">
@@ -6897,7 +6897,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -6987,7 +6987,7 @@
         <v>7</v>
       </c>
       <c r="AB6" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -7077,7 +7077,7 @@
         <v>7</v>
       </c>
       <c r="AB7" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -7167,7 +7167,7 @@
         <v>7</v>
       </c>
       <c r="AB8" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -7257,7 +7257,7 @@
         <v>7</v>
       </c>
       <c r="AB9" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -7347,7 +7347,7 @@
         <v>7</v>
       </c>
       <c r="AB10" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -7437,7 +7437,7 @@
         <v>7</v>
       </c>
       <c r="AB11" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -7527,25 +7527,25 @@
         <v>7</v>
       </c>
       <c r="AB12" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -7617,108 +7617,108 @@
         <v>7</v>
       </c>
       <c r="AB13" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA14" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB14" s="42" t="n">
         <v>6</v>
-      </c>
-      <c r="E14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA14" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB14" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
@@ -7791,24 +7791,24 @@
         <v>7</v>
       </c>
       <c r="Z15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA15" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB15" s="42" t="n">
         <v>6</v>
-      </c>
-      <c r="AA15" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB15" s="42" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
@@ -7881,13 +7881,13 @@
         <v>7</v>
       </c>
       <c r="Z16" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA16" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB16" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -7977,7 +7977,7 @@
         <v>7</v>
       </c>
       <c r="AB17" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -8067,7 +8067,7 @@
         <v>7</v>
       </c>
       <c r="AB18" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -8157,7 +8157,7 @@
         <v>7</v>
       </c>
       <c r="AB19" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -8247,7 +8247,7 @@
         <v>7</v>
       </c>
       <c r="AB20" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -8337,7 +8337,7 @@
         <v>7</v>
       </c>
       <c r="AB21" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -8427,7 +8427,7 @@
         <v>7</v>
       </c>
       <c r="AB22" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -8517,7 +8517,7 @@
         <v>7</v>
       </c>
       <c r="AB23" s="42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2510,7 +2510,7 @@
       </c>
       <c r="AB4" s="31" t="inlineStr">
         <is>
-          <t>19.10–25.10*</t>
+          <t>19.10–25.10</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -2687,7 +2687,7 @@
         <v>120</v>
       </c>
       <c r="AB6" s="36" t="n">
-        <v>124</v>
+        <v>123.71</v>
       </c>
     </row>
     <row r="7">
@@ -2777,7 +2777,7 @@
         <v>90.14</v>
       </c>
       <c r="AB7" s="36" t="n">
-        <v>90.83</v>
+        <v>89.86</v>
       </c>
     </row>
     <row r="8">
@@ -2867,7 +2867,7 @@
         <v>78.56999999999999</v>
       </c>
       <c r="AB8" s="36" t="n">
-        <v>80</v>
+        <v>79.29000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -2957,7 +2957,7 @@
         <v>57.14</v>
       </c>
       <c r="AB9" s="36" t="n">
-        <v>62.5</v>
+        <v>62.29</v>
       </c>
     </row>
     <row r="10">
@@ -3047,7 +3047,7 @@
         <v>63.71</v>
       </c>
       <c r="AB10" s="36" t="n">
-        <v>60.5</v>
+        <v>61.86</v>
       </c>
     </row>
     <row r="11">
@@ -3137,7 +3137,7 @@
         <v>45.14</v>
       </c>
       <c r="AB11" s="36" t="n">
-        <v>47</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="12">
@@ -3227,7 +3227,7 @@
         <v>51.14</v>
       </c>
       <c r="AB12" s="36" t="n">
-        <v>44.67</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="13">
@@ -3317,7 +3317,7 @@
         <v>52.57</v>
       </c>
       <c r="AB13" s="36" t="n">
-        <v>43.33</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="14">
@@ -3407,7 +3407,7 @@
         <v>37.14</v>
       </c>
       <c r="AB14" s="36" t="n">
-        <v>41.67</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="15">
@@ -3497,187 +3497,187 @@
         <v>36.43</v>
       </c>
       <c r="AB15" s="36" t="n">
-        <v>37.33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>3</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>11</v>
+        <v>7.14</v>
       </c>
       <c r="F16" s="36" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="G16" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="H16" s="36" t="n">
         <v>14.43</v>
       </c>
-      <c r="G16" s="36" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="H16" s="36" t="n">
+      <c r="I16" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="J16" s="36" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="K16" s="36" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="L16" s="36" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="M16" s="36" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="N16" s="36" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="O16" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="I16" s="36" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="J16" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="K16" s="36" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="L16" s="36" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="M16" s="36" t="n">
-        <v>24.57</v>
-      </c>
-      <c r="N16" s="36" t="n">
-        <v>24.14</v>
-      </c>
-      <c r="O16" s="36" t="n">
-        <v>24.43</v>
-      </c>
       <c r="P16" s="36" t="n">
-        <v>22</v>
+        <v>15.29</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>23</v>
+        <v>15.29</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>18.43</v>
+        <v>18.71</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>24.71</v>
+        <v>18</v>
       </c>
       <c r="T16" s="36" t="n">
-        <v>27.57</v>
+        <v>25.29</v>
       </c>
       <c r="U16" s="36" t="n">
-        <v>30</v>
+        <v>28.86</v>
       </c>
       <c r="V16" s="36" t="n">
-        <v>28.57</v>
+        <v>24</v>
       </c>
       <c r="W16" s="36" t="n">
-        <v>30.14</v>
+        <v>29.29</v>
       </c>
       <c r="X16" s="36" t="n">
-        <v>34.43</v>
+        <v>31.71</v>
       </c>
       <c r="Y16" s="36" t="n">
-        <v>33.43</v>
+        <v>27</v>
       </c>
       <c r="Z16" s="36" t="n">
-        <v>32</v>
+        <v>23.83</v>
       </c>
       <c r="AA16" s="36" t="n">
-        <v>31.29</v>
+        <v>34.71</v>
       </c>
       <c r="AB16" s="36" t="n">
-        <v>35.33</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>7.14</v>
+        <v>11</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.43</v>
+        <v>14.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>12.71</v>
+        <v>11.86</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.43</v>
+        <v>18</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19</v>
+        <v>19.14</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21.14</v>
+        <v>21</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>18.57</v>
+        <v>23.43</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.57</v>
+        <v>20.43</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>14.71</v>
+        <v>24.57</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>19.14</v>
+        <v>24.14</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>18</v>
+        <v>24.43</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>15.29</v>
+        <v>22</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>15.29</v>
+        <v>23</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>18.71</v>
+        <v>18.43</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>18</v>
+        <v>24.71</v>
       </c>
       <c r="T17" s="36" t="n">
-        <v>25.29</v>
+        <v>27.57</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>28.86</v>
+        <v>30</v>
       </c>
       <c r="V17" s="36" t="n">
-        <v>24</v>
+        <v>28.57</v>
       </c>
       <c r="W17" s="36" t="n">
-        <v>29.29</v>
+        <v>30.14</v>
       </c>
       <c r="X17" s="36" t="n">
-        <v>31.71</v>
+        <v>34.43</v>
       </c>
       <c r="Y17" s="36" t="n">
-        <v>27</v>
+        <v>33.43</v>
       </c>
       <c r="Z17" s="36" t="n">
-        <v>23.83</v>
+        <v>32</v>
       </c>
       <c r="AA17" s="36" t="n">
-        <v>34.71</v>
+        <v>31.29</v>
       </c>
       <c r="AB17" s="36" t="n">
-        <v>34</v>
+        <v>35.14</v>
       </c>
     </row>
     <row r="18">
@@ -3767,187 +3767,187 @@
         <v>30.29</v>
       </c>
       <c r="AB18" s="36" t="n">
-        <v>29.17</v>
+        <v>28.57</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="36" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H19" s="36" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="I19" s="36" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="J19" s="36" t="n">
+        <v>20.43</v>
+      </c>
+      <c r="K19" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="L19" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="M19" s="36" t="n">
+        <v>22.71</v>
+      </c>
+      <c r="N19" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="O19" s="36" t="n">
+        <v>20.14</v>
+      </c>
+      <c r="P19" s="36" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="Q19" s="36" t="n">
         <v>19.43</v>
       </c>
-      <c r="G19" s="36" t="n">
-        <v>15.86</v>
-      </c>
-      <c r="H19" s="36" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="I19" s="36" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="J19" s="36" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="K19" s="36" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="L19" s="36" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="M19" s="36" t="n">
-        <v>23.43</v>
-      </c>
-      <c r="N19" s="36" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="O19" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="P19" s="36" t="n">
+      <c r="R19" s="36" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="S19" s="36" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="T19" s="36" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="U19" s="36" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="V19" s="36" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="W19" s="36" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="X19" s="36" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="Y19" s="36" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="Z19" s="36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA19" s="36" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB19" s="36" t="n">
         <v>27.43</v>
-      </c>
-      <c r="Q19" s="36" t="n">
-        <v>29.14</v>
-      </c>
-      <c r="R19" s="36" t="n">
-        <v>25</v>
-      </c>
-      <c r="S19" s="36" t="n">
-        <v>29.57</v>
-      </c>
-      <c r="T19" s="36" t="n">
-        <v>29.43</v>
-      </c>
-      <c r="U19" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="V19" s="36" t="n">
-        <v>27.14</v>
-      </c>
-      <c r="W19" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="X19" s="36" t="n">
-        <v>30.29</v>
-      </c>
-      <c r="Y19" s="36" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="Z19" s="36" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="AA19" s="36" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="AB19" s="36" t="n">
-        <v>27.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>0.5</v>
+        <v>19.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>3.33</v>
+        <v>15.86</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>11.71</v>
+        <v>14.86</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>17.57</v>
+        <v>16.71</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>20.43</v>
+        <v>19.71</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>21.71</v>
+        <v>16.86</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>15</v>
+        <v>24.86</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>22.71</v>
+        <v>23.43</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>22.43</v>
+        <v>19.43</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>20.14</v>
+        <v>25.57</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>15.71</v>
+        <v>27.43</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>19.43</v>
+        <v>29.14</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>20.29</v>
+        <v>25</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>22.29</v>
+        <v>29.57</v>
       </c>
       <c r="T20" s="36" t="n">
-        <v>21.29</v>
+        <v>29.43</v>
       </c>
       <c r="U20" s="36" t="n">
-        <v>25.14</v>
+        <v>21</v>
       </c>
       <c r="V20" s="36" t="n">
-        <v>23.57</v>
+        <v>27.14</v>
       </c>
       <c r="W20" s="36" t="n">
-        <v>26.29</v>
+        <v>25.57</v>
       </c>
       <c r="X20" s="36" t="n">
-        <v>26.43</v>
+        <v>30.29</v>
       </c>
       <c r="Y20" s="36" t="n">
-        <v>23.71</v>
+        <v>26.57</v>
       </c>
       <c r="Z20" s="36" t="n">
-        <v>22</v>
+        <v>22.86</v>
       </c>
       <c r="AA20" s="36" t="n">
-        <v>29</v>
+        <v>27.43</v>
       </c>
       <c r="AB20" s="36" t="n">
-        <v>26.83</v>
+        <v>26.71</v>
       </c>
     </row>
     <row r="21">
@@ -4037,7 +4037,7 @@
         <v>25.29</v>
       </c>
       <c r="AB21" s="36" t="n">
-        <v>25.67</v>
+        <v>25.29</v>
       </c>
     </row>
     <row r="22">
@@ -4127,7 +4127,7 @@
         <v>11.43</v>
       </c>
       <c r="AB22" s="36" t="n">
-        <v>10.67</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="23">
@@ -4217,7 +4217,7 @@
         <v>8</v>
       </c>
       <c r="AB23" s="36" t="n">
-        <v>8.33</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="24">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="AB4" s="31" t="inlineStr">
         <is>
-          <t>19.10–25.10*</t>
+          <t>19.10–25.10</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -4837,7 +4837,7 @@
         <v>121486853</v>
       </c>
       <c r="AB6" s="40" t="n">
-        <v>93595747</v>
+        <v>112485262</v>
       </c>
     </row>
     <row r="7">
@@ -4927,7 +4927,7 @@
         <v>96334193</v>
       </c>
       <c r="AB7" s="40" t="n">
-        <v>71254033</v>
+        <v>84653963</v>
       </c>
     </row>
     <row r="8">
@@ -5017,7 +5017,7 @@
         <v>88660521</v>
       </c>
       <c r="AB8" s="40" t="n">
-        <v>73138370</v>
+        <v>85896590</v>
       </c>
     </row>
     <row r="9">
@@ -5107,7 +5107,7 @@
         <v>60557072</v>
       </c>
       <c r="AB9" s="40" t="n">
-        <v>62026261</v>
+        <v>75839259</v>
       </c>
     </row>
     <row r="10">
@@ -5197,7 +5197,7 @@
         <v>68108471</v>
       </c>
       <c r="AB10" s="40" t="n">
-        <v>57193725</v>
+        <v>65287548</v>
       </c>
     </row>
     <row r="11">
@@ -5287,7 +5287,7 @@
         <v>43352139</v>
       </c>
       <c r="AB11" s="40" t="n">
-        <v>38912322</v>
+        <v>49825299</v>
       </c>
     </row>
     <row r="12">
@@ -5377,7 +5377,7 @@
         <v>56470370</v>
       </c>
       <c r="AB12" s="40" t="n">
-        <v>30848128</v>
+        <v>36092667</v>
       </c>
     </row>
     <row r="13">
@@ -5467,7 +5467,7 @@
         <v>43911137</v>
       </c>
       <c r="AB13" s="40" t="n">
-        <v>29624305</v>
+        <v>33705532</v>
       </c>
     </row>
     <row r="14">
@@ -5557,7 +5557,7 @@
         <v>32767816</v>
       </c>
       <c r="AB14" s="40" t="n">
-        <v>38696295</v>
+        <v>44302861</v>
       </c>
     </row>
     <row r="15">
@@ -5647,187 +5647,187 @@
         <v>39000780</v>
       </c>
       <c r="AB15" s="40" t="n">
-        <v>33576555</v>
+        <v>40583789</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>8544625</v>
+        <v>3337146</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>8387478</v>
+        <v>10420206</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>10570508</v>
+        <v>21387685</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>11896580</v>
+        <v>16050448</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>19614352</v>
+        <v>21568794</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>20966317</v>
+        <v>30845816</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>20073400</v>
+        <v>45285935</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>23801493</v>
+        <v>28941455</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>27940611</v>
+        <v>21801828</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>27893929</v>
+        <v>19628570</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>29635773</v>
+        <v>23276090</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>19554230</v>
+        <v>27906254</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>23848495</v>
+        <v>20822247</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>24194638</v>
+        <v>20014322</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>20330094</v>
+        <v>19159625</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>26044199</v>
+        <v>22535696</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>24608772</v>
+        <v>21412810</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>28079726</v>
+        <v>34881782</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>20968052</v>
+        <v>25904024</v>
       </c>
       <c r="W16" s="40" t="n">
-        <v>29501132</v>
+        <v>46961904</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>30624981</v>
+        <v>42299644</v>
       </c>
       <c r="Y16" s="40" t="n">
-        <v>28071639</v>
+        <v>32109759</v>
       </c>
       <c r="Z16" s="40" t="n">
-        <v>21021583</v>
+        <v>22714393</v>
       </c>
       <c r="AA16" s="40" t="n">
-        <v>29229414</v>
+        <v>52198815</v>
       </c>
       <c r="AB16" s="40" t="n">
-        <v>22834402</v>
+        <v>55359761</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3337146</v>
+        <v>8544625</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10420206</v>
+        <v>8387478</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>21387685</v>
+        <v>10570508</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>16050448</v>
+        <v>11896580</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>21568794</v>
+        <v>19614352</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>30845816</v>
+        <v>20966317</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>45285935</v>
+        <v>20073400</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>28941455</v>
+        <v>23801493</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>21801828</v>
+        <v>27940611</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>19628570</v>
+        <v>27893929</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>23276090</v>
+        <v>29635773</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>27906254</v>
+        <v>19554230</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>20822247</v>
+        <v>23848495</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>20014322</v>
+        <v>24194638</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>19159625</v>
+        <v>20330094</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>22535696</v>
+        <v>26044199</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>21412810</v>
+        <v>24608772</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>34881782</v>
+        <v>28079726</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>25904024</v>
+        <v>20968052</v>
       </c>
       <c r="W17" s="40" t="n">
-        <v>46961904</v>
+        <v>29501132</v>
       </c>
       <c r="X17" s="40" t="n">
-        <v>42299644</v>
+        <v>30624981</v>
       </c>
       <c r="Y17" s="40" t="n">
-        <v>32109759</v>
+        <v>28071639</v>
       </c>
       <c r="Z17" s="40" t="n">
-        <v>22714393</v>
+        <v>21021583</v>
       </c>
       <c r="AA17" s="40" t="n">
-        <v>52198815</v>
+        <v>29229414</v>
       </c>
       <c r="AB17" s="40" t="n">
-        <v>46792251</v>
+        <v>26957117</v>
       </c>
     </row>
     <row r="18">
@@ -5917,187 +5917,187 @@
         <v>53200913</v>
       </c>
       <c r="AB18" s="40" t="n">
-        <v>22432829</v>
+        <v>25830427</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>6239584</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>13803407</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>28572076</v>
+        <v>363900</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>15282581</v>
+        <v>3736700</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>16594572</v>
+        <v>17796776</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>15223898</v>
+        <v>42724228</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>27696695</v>
+        <v>33036620</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>17717888</v>
+        <v>29649130</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>24163432</v>
+        <v>13949368</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>23623477</v>
+        <v>24539413</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>19145601</v>
+        <v>19087217</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>30157601</v>
+        <v>17139440</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>41172333</v>
+        <v>17746930</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>34303423</v>
+        <v>21437830</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>35044850</v>
+        <v>17616397</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>33519824</v>
+        <v>19360848</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>25969876</v>
+        <v>25377166</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>23835106</v>
+        <v>24702051</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>27833047</v>
+        <v>26856647</v>
       </c>
       <c r="W19" s="40" t="n">
-        <v>22815382</v>
+        <v>27122255</v>
       </c>
       <c r="X19" s="40" t="n">
-        <v>28299644</v>
+        <v>30650242</v>
       </c>
       <c r="Y19" s="40" t="n">
-        <v>23130899</v>
+        <v>21101547</v>
       </c>
       <c r="Z19" s="40" t="n">
-        <v>20390472</v>
+        <v>30037062</v>
       </c>
       <c r="AA19" s="40" t="n">
-        <v>25564267</v>
+        <v>22123372</v>
       </c>
       <c r="AB19" s="40" t="n">
-        <v>21703917</v>
+        <v>24293073</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>0</v>
+        <v>6239584</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>0</v>
+        <v>13803407</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>363900</v>
+        <v>28572076</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>3736700</v>
+        <v>15282581</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>17796776</v>
+        <v>16594572</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>42724228</v>
+        <v>15223898</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>33036620</v>
+        <v>27696695</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>29649130</v>
+        <v>17717888</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>13949368</v>
+        <v>24163432</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>24539413</v>
+        <v>23623477</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>19087217</v>
+        <v>19145601</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>17139440</v>
+        <v>30157601</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>17746930</v>
+        <v>41172333</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>21437830</v>
+        <v>34303423</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>17616397</v>
+        <v>35044850</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>19360848</v>
+        <v>33519824</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>25377166</v>
+        <v>25969876</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>24702051</v>
+        <v>23835106</v>
       </c>
       <c r="V20" s="40" t="n">
-        <v>26856647</v>
+        <v>27833047</v>
       </c>
       <c r="W20" s="40" t="n">
-        <v>27122255</v>
+        <v>22815382</v>
       </c>
       <c r="X20" s="40" t="n">
-        <v>30650242</v>
+        <v>28299644</v>
       </c>
       <c r="Y20" s="40" t="n">
-        <v>21101547</v>
+        <v>23130899</v>
       </c>
       <c r="Z20" s="40" t="n">
-        <v>30037062</v>
+        <v>20390472</v>
       </c>
       <c r="AA20" s="40" t="n">
-        <v>22123372</v>
+        <v>25564267</v>
       </c>
       <c r="AB20" s="40" t="n">
-        <v>21187163</v>
+        <v>25453154</v>
       </c>
     </row>
     <row r="21">
@@ -6187,7 +6187,7 @@
         <v>27021110</v>
       </c>
       <c r="AB21" s="40" t="n">
-        <v>22203030</v>
+        <v>26706620</v>
       </c>
     </row>
     <row r="22">
@@ -6277,7 +6277,7 @@
         <v>12183598</v>
       </c>
       <c r="AB22" s="40" t="n">
-        <v>7462462</v>
+        <v>10380052</v>
       </c>
     </row>
     <row r="23">
@@ -6367,7 +6367,7 @@
         <v>5590930</v>
       </c>
       <c r="AB23" s="40" t="n">
-        <v>4653508</v>
+        <v>5406298</v>
       </c>
     </row>
     <row r="24">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="AB4" s="31" t="inlineStr">
         <is>
-          <t>19.10–25.10*</t>
+          <t>19.10–25.10</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
         <v>7</v>
       </c>
       <c r="AB5" s="34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -6987,7 +6987,7 @@
         <v>7</v>
       </c>
       <c r="AB6" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -7077,7 +7077,7 @@
         <v>7</v>
       </c>
       <c r="AB7" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -7167,7 +7167,7 @@
         <v>7</v>
       </c>
       <c r="AB8" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -7257,7 +7257,7 @@
         <v>7</v>
       </c>
       <c r="AB9" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -7347,7 +7347,7 @@
         <v>7</v>
       </c>
       <c r="AB10" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -7437,7 +7437,7 @@
         <v>7</v>
       </c>
       <c r="AB11" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -7527,7 +7527,7 @@
         <v>7</v>
       </c>
       <c r="AB12" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -7617,7 +7617,7 @@
         <v>7</v>
       </c>
       <c r="AB13" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -7707,7 +7707,7 @@
         <v>7</v>
       </c>
       <c r="AB14" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -7797,25 +7797,25 @@
         <v>7</v>
       </c>
       <c r="AB15" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -7887,25 +7887,25 @@
         <v>7</v>
       </c>
       <c r="AB16" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -7977,7 +7977,7 @@
         <v>7</v>
       </c>
       <c r="AB17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -8067,34 +8067,34 @@
         <v>7</v>
       </c>
       <c r="AB18" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G19" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H19" s="42" t="n">
         <v>7</v>
@@ -8157,34 +8157,34 @@
         <v>7</v>
       </c>
       <c r="AB19" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G20" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="42" t="n">
         <v>7</v>
@@ -8247,7 +8247,7 @@
         <v>7</v>
       </c>
       <c r="AB20" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -8337,7 +8337,7 @@
         <v>7</v>
       </c>
       <c r="AB21" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -8427,7 +8427,7 @@
         <v>7</v>
       </c>
       <c r="AB22" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -8517,7 +8517,7 @@
         <v>7</v>
       </c>
       <c r="AB23" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2193,7 +2193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -2224,6 +2224,7 @@
     <col width="13" customWidth="1" style="20" min="26" max="26"/>
     <col width="13" customWidth="1" style="20" min="27" max="27"/>
     <col width="13" customWidth="1" style="20" min="28" max="28"/>
+    <col width="13" customWidth="1" style="20" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2371,6 +2372,11 @@
           <t>2026-10-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -2511,6 +2517,11 @@
       <c r="AB4" s="31" t="inlineStr">
         <is>
           <t>19.10–25.10</t>
+        </is>
+      </c>
+      <c r="AC4" s="31" t="inlineStr">
+        <is>
+          <t>26.10–01.11*</t>
         </is>
       </c>
     </row>
@@ -2599,6 +2610,9 @@
       <c r="AB5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="AC5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -2689,6 +2703,9 @@
       <c r="AB6" s="36" t="n">
         <v>123.71</v>
       </c>
+      <c r="AC6" s="36" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -2779,6 +2796,9 @@
       <c r="AB7" s="36" t="n">
         <v>89.86</v>
       </c>
+      <c r="AC7" s="36" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -2869,455 +2889,473 @@
       <c r="AB8" s="36" t="n">
         <v>79.29000000000001</v>
       </c>
+      <c r="AC8" s="36" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0</v>
+        <v>16.33</v>
       </c>
       <c r="D9" s="36" t="n">
-        <v>7.25</v>
+        <v>14.29</v>
       </c>
       <c r="E9" s="36" t="n">
-        <v>18.71</v>
+        <v>19.14</v>
       </c>
       <c r="F9" s="36" t="n">
-        <v>21.57</v>
+        <v>26.71</v>
       </c>
       <c r="G9" s="36" t="n">
-        <v>30.29</v>
+        <v>28.14</v>
       </c>
       <c r="H9" s="36" t="n">
-        <v>38</v>
+        <v>28.57</v>
       </c>
       <c r="I9" s="36" t="n">
-        <v>39.71</v>
+        <v>31.57</v>
       </c>
       <c r="J9" s="36" t="n">
-        <v>41.71</v>
+        <v>33</v>
       </c>
       <c r="K9" s="36" t="n">
-        <v>35.14</v>
+        <v>34.86</v>
       </c>
       <c r="L9" s="36" t="n">
-        <v>41</v>
+        <v>41.29</v>
       </c>
       <c r="M9" s="36" t="n">
-        <v>48</v>
+        <v>41.43</v>
       </c>
       <c r="N9" s="36" t="n">
-        <v>49.43</v>
+        <v>46.14</v>
       </c>
       <c r="O9" s="36" t="n">
-        <v>45.57</v>
+        <v>41.57</v>
       </c>
       <c r="P9" s="36" t="n">
-        <v>43</v>
+        <v>51.86</v>
       </c>
       <c r="Q9" s="36" t="n">
-        <v>46.57</v>
+        <v>48.71</v>
       </c>
       <c r="R9" s="36" t="n">
-        <v>48.43</v>
+        <v>45.14</v>
       </c>
       <c r="S9" s="36" t="n">
-        <v>38.29</v>
+        <v>50.71</v>
       </c>
       <c r="T9" s="36" t="n">
-        <v>50.14</v>
+        <v>60.71</v>
       </c>
       <c r="U9" s="36" t="n">
-        <v>48.86</v>
+        <v>66.86</v>
       </c>
       <c r="V9" s="36" t="n">
-        <v>49.57</v>
+        <v>63.29</v>
       </c>
       <c r="W9" s="36" t="n">
-        <v>49.86</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="X9" s="36" t="n">
+        <v>61.43</v>
+      </c>
+      <c r="Y9" s="36" t="n">
+        <v>66.29000000000001</v>
+      </c>
+      <c r="Z9" s="36" t="n">
         <v>50.86</v>
       </c>
-      <c r="Y9" s="36" t="n">
-        <v>60.14</v>
-      </c>
-      <c r="Z9" s="36" t="n">
-        <v>41.43</v>
-      </c>
       <c r="AA9" s="36" t="n">
-        <v>57.14</v>
+        <v>63.71</v>
       </c>
       <c r="AB9" s="36" t="n">
-        <v>62.29</v>
+        <v>61.86</v>
+      </c>
+      <c r="AC9" s="36" t="n">
+        <v>83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="36" t="n">
-        <v>16.33</v>
+        <v>0</v>
       </c>
       <c r="D10" s="36" t="n">
-        <v>14.29</v>
+        <v>7.25</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>19.14</v>
+        <v>18.71</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>26.71</v>
+        <v>21.57</v>
       </c>
       <c r="G10" s="36" t="n">
-        <v>28.14</v>
+        <v>30.29</v>
       </c>
       <c r="H10" s="36" t="n">
-        <v>28.57</v>
+        <v>38</v>
       </c>
       <c r="I10" s="36" t="n">
-        <v>31.57</v>
+        <v>39.71</v>
       </c>
       <c r="J10" s="36" t="n">
-        <v>33</v>
+        <v>41.71</v>
       </c>
       <c r="K10" s="36" t="n">
-        <v>34.86</v>
+        <v>35.14</v>
       </c>
       <c r="L10" s="36" t="n">
-        <v>41.29</v>
+        <v>41</v>
       </c>
       <c r="M10" s="36" t="n">
+        <v>48</v>
+      </c>
+      <c r="N10" s="36" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="O10" s="36" t="n">
+        <v>45.57</v>
+      </c>
+      <c r="P10" s="36" t="n">
+        <v>43</v>
+      </c>
+      <c r="Q10" s="36" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="R10" s="36" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="S10" s="36" t="n">
+        <v>38.29</v>
+      </c>
+      <c r="T10" s="36" t="n">
+        <v>50.14</v>
+      </c>
+      <c r="U10" s="36" t="n">
+        <v>48.86</v>
+      </c>
+      <c r="V10" s="36" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="W10" s="36" t="n">
+        <v>49.86</v>
+      </c>
+      <c r="X10" s="36" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="Y10" s="36" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="Z10" s="36" t="n">
         <v>41.43</v>
       </c>
-      <c r="N10" s="36" t="n">
-        <v>46.14</v>
-      </c>
-      <c r="O10" s="36" t="n">
-        <v>41.57</v>
-      </c>
-      <c r="P10" s="36" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="Q10" s="36" t="n">
-        <v>48.71</v>
-      </c>
-      <c r="R10" s="36" t="n">
-        <v>45.14</v>
-      </c>
-      <c r="S10" s="36" t="n">
-        <v>50.71</v>
-      </c>
-      <c r="T10" s="36" t="n">
-        <v>60.71</v>
-      </c>
-      <c r="U10" s="36" t="n">
-        <v>66.86</v>
-      </c>
-      <c r="V10" s="36" t="n">
-        <v>63.29</v>
-      </c>
-      <c r="W10" s="36" t="n">
-        <v>65.29000000000001</v>
-      </c>
-      <c r="X10" s="36" t="n">
-        <v>61.43</v>
-      </c>
-      <c r="Y10" s="36" t="n">
-        <v>66.29000000000001</v>
-      </c>
-      <c r="Z10" s="36" t="n">
-        <v>50.86</v>
-      </c>
       <c r="AA10" s="36" t="n">
-        <v>63.71</v>
+        <v>57.14</v>
       </c>
       <c r="AB10" s="36" t="n">
-        <v>61.86</v>
+        <v>62.29</v>
+      </c>
+      <c r="AC10" s="36" t="n">
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0</v>
+        <v>8.43</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>8</v>
+        <v>13.43</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>13.14</v>
+        <v>21.71</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>19.43</v>
+        <v>16.57</v>
       </c>
       <c r="H11" s="36" t="n">
-        <v>26.43</v>
+        <v>21.29</v>
       </c>
       <c r="I11" s="36" t="n">
-        <v>32.29</v>
+        <v>21.14</v>
       </c>
       <c r="J11" s="36" t="n">
+        <v>23.29</v>
+      </c>
+      <c r="K11" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="L11" s="36" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="M11" s="36" t="n">
+        <v>28.14</v>
+      </c>
+      <c r="N11" s="36" t="n">
+        <v>31.14</v>
+      </c>
+      <c r="O11" s="36" t="n">
+        <v>30</v>
+      </c>
+      <c r="P11" s="36" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="Q11" s="36" t="n">
         <v>31.29</v>
       </c>
-      <c r="K11" s="36" t="n">
-        <v>33.57</v>
-      </c>
-      <c r="L11" s="36" t="n">
+      <c r="R11" s="36" t="n">
+        <v>36.14</v>
+      </c>
+      <c r="S11" s="36" t="n">
+        <v>31</v>
+      </c>
+      <c r="T11" s="36" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="U11" s="36" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="V11" s="36" t="n">
+        <v>45.86</v>
+      </c>
+      <c r="W11" s="36" t="n">
+        <v>45.14</v>
+      </c>
+      <c r="X11" s="36" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="Y11" s="36" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z11" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="M11" s="36" t="n">
-        <v>42.43</v>
-      </c>
-      <c r="N11" s="36" t="n">
-        <v>38.57</v>
-      </c>
-      <c r="O11" s="36" t="n">
-        <v>34.29</v>
-      </c>
-      <c r="P11" s="36" t="n">
-        <v>37.86</v>
-      </c>
-      <c r="Q11" s="36" t="n">
-        <v>42.86</v>
-      </c>
-      <c r="R11" s="36" t="n">
-        <v>40.71</v>
-      </c>
-      <c r="S11" s="36" t="n">
-        <v>45.43</v>
-      </c>
-      <c r="T11" s="36" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="U11" s="36" t="n">
-        <v>55.29</v>
-      </c>
-      <c r="V11" s="36" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="W11" s="36" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="X11" s="36" t="n">
-        <v>49.57</v>
-      </c>
-      <c r="Y11" s="36" t="n">
-        <v>47.86</v>
-      </c>
-      <c r="Z11" s="36" t="n">
-        <v>46</v>
-      </c>
       <c r="AA11" s="36" t="n">
-        <v>45.14</v>
+        <v>51.14</v>
       </c>
       <c r="AB11" s="36" t="n">
-        <v>47.71</v>
+        <v>44.14</v>
+      </c>
+      <c r="AC11" s="36" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>8.43</v>
+        <v>6.67</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>13.43</v>
+        <v>11.29</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>21.71</v>
+        <v>10.57</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>16.57</v>
+        <v>11.14</v>
       </c>
       <c r="H12" s="36" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="I12" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="J12" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="K12" s="36" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="L12" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="M12" s="36" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="N12" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="O12" s="36" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="P12" s="36" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="Q12" s="36" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="R12" s="36" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="S12" s="36" t="n">
         <v>21.29</v>
       </c>
-      <c r="I12" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="J12" s="36" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="K12" s="36" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="L12" s="36" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="M12" s="36" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="N12" s="36" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="O12" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="P12" s="36" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="Q12" s="36" t="n">
-        <v>31.29</v>
-      </c>
-      <c r="R12" s="36" t="n">
-        <v>36.14</v>
-      </c>
-      <c r="S12" s="36" t="n">
-        <v>31</v>
-      </c>
       <c r="T12" s="36" t="n">
-        <v>37.71</v>
+        <v>29.14</v>
       </c>
       <c r="U12" s="36" t="n">
-        <v>39.29</v>
+        <v>31.43</v>
       </c>
       <c r="V12" s="36" t="n">
-        <v>45.86</v>
+        <v>35.71</v>
       </c>
       <c r="W12" s="36" t="n">
-        <v>45.14</v>
+        <v>40.71</v>
       </c>
       <c r="X12" s="36" t="n">
-        <v>41.86</v>
+        <v>46.86</v>
       </c>
       <c r="Y12" s="36" t="n">
-        <v>48</v>
+        <v>44.71</v>
       </c>
       <c r="Z12" s="36" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="AA12" s="36" t="n">
-        <v>51.14</v>
+        <v>52.57</v>
       </c>
       <c r="AB12" s="36" t="n">
-        <v>44.14</v>
+        <v>42.86</v>
+      </c>
+      <c r="AC12" s="36" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>6.67</v>
+        <v>3.33</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>11.29</v>
+        <v>6.43</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>10.57</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>11.14</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>18</v>
+        <v>17.14</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>18</v>
+        <v>16.14</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>17.43</v>
+        <v>18.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>15.29</v>
+        <v>16.14</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>24.43</v>
+        <v>21.71</v>
       </c>
       <c r="N13" s="36" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="O13" s="36" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="P13" s="36" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="Q13" s="36" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="R13" s="36" t="n">
         <v>24.71</v>
       </c>
-      <c r="O13" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="P13" s="36" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="Q13" s="36" t="n">
+      <c r="S13" s="36" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="T13" s="36" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="U13" s="36" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="V13" s="36" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="W13" s="36" t="n">
+        <v>28.29</v>
+      </c>
+      <c r="X13" s="36" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="Y13" s="36" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z13" s="36" t="n">
         <v>25.43</v>
       </c>
-      <c r="R13" s="36" t="n">
-        <v>22.57</v>
-      </c>
-      <c r="S13" s="36" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="T13" s="36" t="n">
-        <v>29.14</v>
-      </c>
-      <c r="U13" s="36" t="n">
-        <v>31.43</v>
-      </c>
-      <c r="V13" s="36" t="n">
-        <v>35.71</v>
-      </c>
-      <c r="W13" s="36" t="n">
-        <v>40.71</v>
-      </c>
-      <c r="X13" s="36" t="n">
-        <v>46.86</v>
-      </c>
-      <c r="Y13" s="36" t="n">
-        <v>44.71</v>
-      </c>
-      <c r="Z13" s="36" t="n">
-        <v>37</v>
-      </c>
       <c r="AA13" s="36" t="n">
-        <v>52.57</v>
+        <v>30.29</v>
       </c>
       <c r="AB13" s="36" t="n">
-        <v>42.86</v>
+        <v>28.57</v>
+      </c>
+      <c r="AC13" s="36" t="n">
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -3409,95 +3447,101 @@
       <c r="AB14" s="36" t="n">
         <v>41.14</v>
       </c>
+      <c r="AC14" s="36" t="n">
+        <v>42</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>9.43</v>
+        <v>0</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>12.43</v>
+        <v>8</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13.29</v>
+        <v>13.14</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>14.71</v>
+        <v>19.43</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>17</v>
+        <v>26.43</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19.71</v>
+        <v>32.29</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>17.71</v>
+        <v>31.29</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>19.57</v>
+        <v>33.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>24.14</v>
+        <v>40</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>27.57</v>
+        <v>42.43</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>24.43</v>
+        <v>38.57</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>27.29</v>
+        <v>34.29</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>26.57</v>
+        <v>37.86</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>25.57</v>
+        <v>42.86</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>29</v>
+        <v>40.71</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>27.71</v>
+        <v>45.43</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>32.57</v>
+        <v>44.57</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>31.57</v>
+        <v>55.29</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>29.57</v>
+        <v>46.29</v>
       </c>
       <c r="W15" s="36" t="n">
-        <v>29.86</v>
+        <v>43.71</v>
       </c>
       <c r="X15" s="36" t="n">
-        <v>32</v>
+        <v>49.57</v>
       </c>
       <c r="Y15" s="36" t="n">
-        <v>32.14</v>
+        <v>47.86</v>
       </c>
       <c r="Z15" s="36" t="n">
-        <v>27.14</v>
+        <v>46</v>
       </c>
       <c r="AA15" s="36" t="n">
-        <v>36.43</v>
+        <v>45.14</v>
       </c>
       <c r="AB15" s="36" t="n">
-        <v>36</v>
+        <v>47.71</v>
+      </c>
+      <c r="AC15" s="36" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -3589,455 +3633,473 @@
       <c r="AB16" s="36" t="n">
         <v>35.86</v>
       </c>
+      <c r="AC16" s="36" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>0</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>14.43</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>11.86</v>
+        <v>3.33</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>18</v>
+        <v>11.71</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19.14</v>
+        <v>17.57</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21</v>
+        <v>20.43</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>23.43</v>
+        <v>21.71</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>20.43</v>
+        <v>15</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>24.57</v>
+        <v>22.71</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>24.14</v>
+        <v>22.43</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>24.43</v>
+        <v>20.14</v>
       </c>
       <c r="P17" s="36" t="n">
+        <v>15.71</v>
+      </c>
+      <c r="Q17" s="36" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="R17" s="36" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="S17" s="36" t="n">
+        <v>22.29</v>
+      </c>
+      <c r="T17" s="36" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="U17" s="36" t="n">
+        <v>25.14</v>
+      </c>
+      <c r="V17" s="36" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="W17" s="36" t="n">
+        <v>26.29</v>
+      </c>
+      <c r="X17" s="36" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="Y17" s="36" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="Z17" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="Q17" s="36" t="n">
-        <v>23</v>
-      </c>
-      <c r="R17" s="36" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="S17" s="36" t="n">
-        <v>24.71</v>
-      </c>
-      <c r="T17" s="36" t="n">
-        <v>27.57</v>
-      </c>
-      <c r="U17" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="V17" s="36" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="W17" s="36" t="n">
-        <v>30.14</v>
-      </c>
-      <c r="X17" s="36" t="n">
-        <v>34.43</v>
-      </c>
-      <c r="Y17" s="36" t="n">
-        <v>33.43</v>
-      </c>
-      <c r="Z17" s="36" t="n">
-        <v>32</v>
-      </c>
       <c r="AA17" s="36" t="n">
-        <v>31.29</v>
+        <v>29</v>
       </c>
       <c r="AB17" s="36" t="n">
-        <v>35.14</v>
+        <v>27.43</v>
+      </c>
+      <c r="AC17" s="36" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>3.33</v>
+        <v>9.43</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>6.43</v>
+        <v>12.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>14.71</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>17.14</v>
+        <v>19.71</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>16.14</v>
+        <v>17.71</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>18.57</v>
+        <v>19.57</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>16.14</v>
+        <v>24.14</v>
       </c>
       <c r="M18" s="36" t="n">
-        <v>21.71</v>
+        <v>27.57</v>
       </c>
       <c r="N18" s="36" t="n">
-        <v>20.86</v>
+        <v>24.43</v>
       </c>
       <c r="O18" s="36" t="n">
-        <v>20.86</v>
+        <v>27.29</v>
       </c>
       <c r="P18" s="36" t="n">
-        <v>21.86</v>
+        <v>26.57</v>
       </c>
       <c r="Q18" s="36" t="n">
-        <v>28.71</v>
+        <v>25.57</v>
       </c>
       <c r="R18" s="36" t="n">
-        <v>24.71</v>
+        <v>29</v>
       </c>
       <c r="S18" s="36" t="n">
-        <v>24.57</v>
+        <v>27.71</v>
       </c>
       <c r="T18" s="36" t="n">
-        <v>25.29</v>
+        <v>32.57</v>
       </c>
       <c r="U18" s="36" t="n">
-        <v>26.71</v>
+        <v>31.57</v>
       </c>
       <c r="V18" s="36" t="n">
-        <v>27.57</v>
+        <v>29.57</v>
       </c>
       <c r="W18" s="36" t="n">
-        <v>28.29</v>
+        <v>29.86</v>
       </c>
       <c r="X18" s="36" t="n">
-        <v>21.29</v>
+        <v>32</v>
       </c>
       <c r="Y18" s="36" t="n">
-        <v>27</v>
+        <v>32.14</v>
       </c>
       <c r="Z18" s="36" t="n">
-        <v>25.43</v>
+        <v>27.14</v>
       </c>
       <c r="AA18" s="36" t="n">
-        <v>30.29</v>
+        <v>36.43</v>
       </c>
       <c r="AB18" s="36" t="n">
-        <v>28.57</v>
+        <v>36</v>
+      </c>
+      <c r="AC18" s="36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>0.5</v>
+        <v>14.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>3.33</v>
+        <v>11.86</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>11.71</v>
+        <v>18</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>17.57</v>
+        <v>19.14</v>
       </c>
       <c r="J19" s="36" t="n">
+        <v>21</v>
+      </c>
+      <c r="K19" s="36" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="L19" s="36" t="n">
         <v>20.43</v>
       </c>
-      <c r="K19" s="36" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="L19" s="36" t="n">
-        <v>15</v>
-      </c>
       <c r="M19" s="36" t="n">
-        <v>22.71</v>
+        <v>24.57</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>22.43</v>
+        <v>24.14</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>20.14</v>
+        <v>24.43</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>15.71</v>
+        <v>22</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>19.43</v>
+        <v>23</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>20.29</v>
+        <v>18.43</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>22.29</v>
+        <v>24.71</v>
       </c>
       <c r="T19" s="36" t="n">
-        <v>21.29</v>
+        <v>27.57</v>
       </c>
       <c r="U19" s="36" t="n">
-        <v>25.14</v>
+        <v>30</v>
       </c>
       <c r="V19" s="36" t="n">
-        <v>23.57</v>
+        <v>28.57</v>
       </c>
       <c r="W19" s="36" t="n">
-        <v>26.29</v>
+        <v>30.14</v>
       </c>
       <c r="X19" s="36" t="n">
-        <v>26.43</v>
+        <v>34.43</v>
       </c>
       <c r="Y19" s="36" t="n">
-        <v>23.71</v>
+        <v>33.43</v>
       </c>
       <c r="Z19" s="36" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AA19" s="36" t="n">
-        <v>29</v>
+        <v>31.29</v>
       </c>
       <c r="AB19" s="36" t="n">
-        <v>27.43</v>
+        <v>35.14</v>
+      </c>
+      <c r="AC19" s="36" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>19.43</v>
+        <v>3.25</v>
       </c>
       <c r="G20" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I20" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="J20" s="36" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="K20" s="36" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L20" s="36" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="M20" s="36" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N20" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="O20" s="36" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="P20" s="36" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="Q20" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="R20" s="36" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="S20" s="36" t="n">
         <v>15.86</v>
       </c>
-      <c r="H20" s="36" t="n">
-        <v>14.86</v>
-      </c>
-      <c r="I20" s="36" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="J20" s="36" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="K20" s="36" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="L20" s="36" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="M20" s="36" t="n">
+      <c r="T20" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="U20" s="36" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="V20" s="36" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="W20" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="X20" s="36" t="n">
         <v>23.43</v>
       </c>
-      <c r="N20" s="36" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="O20" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="P20" s="36" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="Q20" s="36" t="n">
-        <v>29.14</v>
-      </c>
-      <c r="R20" s="36" t="n">
+      <c r="Y20" s="36" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="Z20" s="36" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="AA20" s="36" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="AB20" s="36" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="AC20" s="36" t="n">
         <v>25</v>
-      </c>
-      <c r="S20" s="36" t="n">
-        <v>29.57</v>
-      </c>
-      <c r="T20" s="36" t="n">
-        <v>29.43</v>
-      </c>
-      <c r="U20" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="V20" s="36" t="n">
-        <v>27.14</v>
-      </c>
-      <c r="W20" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="X20" s="36" t="n">
-        <v>30.29</v>
-      </c>
-      <c r="Y20" s="36" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="Z20" s="36" t="n">
-        <v>22.86</v>
-      </c>
-      <c r="AA20" s="36" t="n">
-        <v>27.43</v>
-      </c>
-      <c r="AB20" s="36" t="n">
-        <v>26.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C21" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E21" s="36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F21" s="36" t="n">
-        <v>3.25</v>
+        <v>19.43</v>
       </c>
       <c r="G21" s="36" t="n">
-        <v>8</v>
+        <v>15.86</v>
       </c>
       <c r="H21" s="36" t="n">
-        <v>9.43</v>
+        <v>14.86</v>
       </c>
       <c r="I21" s="36" t="n">
-        <v>12.71</v>
+        <v>16.71</v>
       </c>
       <c r="J21" s="36" t="n">
-        <v>11.57</v>
+        <v>19.71</v>
       </c>
       <c r="K21" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>16.86</v>
       </c>
       <c r="L21" s="36" t="n">
-        <v>11.86</v>
+        <v>24.86</v>
       </c>
       <c r="M21" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>23.43</v>
       </c>
       <c r="N21" s="36" t="n">
-        <v>19</v>
+        <v>19.43</v>
       </c>
       <c r="O21" s="36" t="n">
-        <v>19.57</v>
+        <v>25.57</v>
       </c>
       <c r="P21" s="36" t="n">
-        <v>16.86</v>
+        <v>27.43</v>
       </c>
       <c r="Q21" s="36" t="n">
-        <v>15</v>
+        <v>29.14</v>
       </c>
       <c r="R21" s="36" t="n">
-        <v>14.71</v>
+        <v>25</v>
       </c>
       <c r="S21" s="36" t="n">
-        <v>15.86</v>
+        <v>29.57</v>
       </c>
       <c r="T21" s="36" t="n">
-        <v>25</v>
+        <v>29.43</v>
       </c>
       <c r="U21" s="36" t="n">
-        <v>27.29</v>
+        <v>21</v>
       </c>
       <c r="V21" s="36" t="n">
-        <v>17.14</v>
+        <v>27.14</v>
       </c>
       <c r="W21" s="36" t="n">
-        <v>22.14</v>
+        <v>25.57</v>
       </c>
       <c r="X21" s="36" t="n">
-        <v>23.43</v>
+        <v>30.29</v>
       </c>
       <c r="Y21" s="36" t="n">
-        <v>24.14</v>
+        <v>26.57</v>
       </c>
       <c r="Z21" s="36" t="n">
-        <v>16.43</v>
+        <v>22.86</v>
       </c>
       <c r="AA21" s="36" t="n">
-        <v>25.29</v>
+        <v>27.43</v>
       </c>
       <c r="AB21" s="36" t="n">
-        <v>25.29</v>
+        <v>26.71</v>
+      </c>
+      <c r="AC21" s="36" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -4129,6 +4191,9 @@
       <c r="AB22" s="36" t="n">
         <v>11.86</v>
       </c>
+      <c r="AC22" s="36" t="n">
+        <v>11</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -4218,6 +4283,9 @@
       </c>
       <c r="AB23" s="36" t="n">
         <v>8.57</v>
+      </c>
+      <c r="AC23" s="36" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -4329,6 +4397,10 @@
       </c>
       <c r="AB24" s="39">
         <f>AVERAGE(AB6:AB23)</f>
+        <v/>
+      </c>
+      <c r="AC24" s="39">
+        <f>AVERAGE(AC6:AC23)</f>
         <v/>
       </c>
     </row>
@@ -4343,7 +4415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -4374,6 +4446,7 @@
     <col width="13" customWidth="1" style="20" min="26" max="26"/>
     <col width="13" customWidth="1" style="20" min="27" max="27"/>
     <col width="13" customWidth="1" style="20" min="28" max="28"/>
+    <col width="13" customWidth="1" style="20" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4521,6 +4594,11 @@
           <t>2026-10-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -4661,6 +4739,11 @@
       <c r="AB4" s="31" t="inlineStr">
         <is>
           <t>19.10–25.10</t>
+        </is>
+      </c>
+      <c r="AC4" s="31" t="inlineStr">
+        <is>
+          <t>26.10–01.11*</t>
         </is>
       </c>
     </row>
@@ -4749,6 +4832,9 @@
       <c r="AB5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="AC5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -4839,6 +4925,9 @@
       <c r="AB6" s="40" t="n">
         <v>112485262</v>
       </c>
+      <c r="AC6" s="40" t="n">
+        <v>18599895</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -4929,6 +5018,9 @@
       <c r="AB7" s="40" t="n">
         <v>84653963</v>
       </c>
+      <c r="AC7" s="40" t="n">
+        <v>15193087</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -5019,455 +5111,473 @@
       <c r="AB8" s="40" t="n">
         <v>85896590</v>
       </c>
+      <c r="AC8" s="40" t="n">
+        <v>10875777</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="40" t="n">
-        <v>0</v>
+        <v>9458306</v>
       </c>
       <c r="D9" s="40" t="n">
-        <v>3771593</v>
+        <v>15808893</v>
       </c>
       <c r="E9" s="40" t="n">
-        <v>17664217</v>
+        <v>14209578</v>
       </c>
       <c r="F9" s="40" t="n">
-        <v>21748722</v>
+        <v>30449860</v>
       </c>
       <c r="G9" s="40" t="n">
-        <v>38313932</v>
+        <v>32603120</v>
       </c>
       <c r="H9" s="40" t="n">
-        <v>49313727</v>
+        <v>35552907</v>
       </c>
       <c r="I9" s="40" t="n">
-        <v>41788221</v>
+        <v>31069118</v>
       </c>
       <c r="J9" s="40" t="n">
-        <v>36755638</v>
+        <v>40525338</v>
       </c>
       <c r="K9" s="40" t="n">
-        <v>43259404</v>
+        <v>42402722</v>
       </c>
       <c r="L9" s="40" t="n">
-        <v>68694825</v>
+        <v>42012092</v>
       </c>
       <c r="M9" s="40" t="n">
-        <v>48824266</v>
+        <v>58722069</v>
       </c>
       <c r="N9" s="40" t="n">
-        <v>57556194</v>
+        <v>48135084</v>
       </c>
       <c r="O9" s="40" t="n">
-        <v>38323101</v>
+        <v>44293878</v>
       </c>
       <c r="P9" s="40" t="n">
-        <v>40276838</v>
+        <v>41613311</v>
       </c>
       <c r="Q9" s="40" t="n">
-        <v>45419704</v>
+        <v>43739350</v>
       </c>
       <c r="R9" s="40" t="n">
-        <v>55923182</v>
+        <v>78234960</v>
       </c>
       <c r="S9" s="40" t="n">
-        <v>40248814</v>
+        <v>47535640</v>
       </c>
       <c r="T9" s="40" t="n">
-        <v>50993465</v>
+        <v>59241681</v>
       </c>
       <c r="U9" s="40" t="n">
-        <v>62193580</v>
+        <v>65321829</v>
       </c>
       <c r="V9" s="40" t="n">
-        <v>45202354</v>
+        <v>57895664</v>
       </c>
       <c r="W9" s="40" t="n">
-        <v>45317128</v>
+        <v>63196973</v>
       </c>
       <c r="X9" s="40" t="n">
-        <v>48612400</v>
+        <v>51807160</v>
       </c>
       <c r="Y9" s="40" t="n">
-        <v>64209970</v>
+        <v>67644051</v>
       </c>
       <c r="Z9" s="40" t="n">
-        <v>38948580</v>
+        <v>43897626</v>
       </c>
       <c r="AA9" s="40" t="n">
-        <v>60557072</v>
+        <v>68108471</v>
       </c>
       <c r="AB9" s="40" t="n">
-        <v>75839259</v>
+        <v>65287548</v>
+      </c>
+      <c r="AC9" s="40" t="n">
+        <v>10213235</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="40" t="n">
-        <v>9458306</v>
+        <v>0</v>
       </c>
       <c r="D10" s="40" t="n">
-        <v>15808893</v>
+        <v>3771593</v>
       </c>
       <c r="E10" s="40" t="n">
-        <v>14209578</v>
+        <v>17664217</v>
       </c>
       <c r="F10" s="40" t="n">
-        <v>30449860</v>
+        <v>21748722</v>
       </c>
       <c r="G10" s="40" t="n">
-        <v>32603120</v>
+        <v>38313932</v>
       </c>
       <c r="H10" s="40" t="n">
-        <v>35552907</v>
+        <v>49313727</v>
       </c>
       <c r="I10" s="40" t="n">
-        <v>31069118</v>
+        <v>41788221</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>40525338</v>
+        <v>36755638</v>
       </c>
       <c r="K10" s="40" t="n">
-        <v>42402722</v>
+        <v>43259404</v>
       </c>
       <c r="L10" s="40" t="n">
-        <v>42012092</v>
+        <v>68694825</v>
       </c>
       <c r="M10" s="40" t="n">
-        <v>58722069</v>
+        <v>48824266</v>
       </c>
       <c r="N10" s="40" t="n">
-        <v>48135084</v>
+        <v>57556194</v>
       </c>
       <c r="O10" s="40" t="n">
-        <v>44293878</v>
+        <v>38323101</v>
       </c>
       <c r="P10" s="40" t="n">
-        <v>41613311</v>
+        <v>40276838</v>
       </c>
       <c r="Q10" s="40" t="n">
-        <v>43739350</v>
+        <v>45419704</v>
       </c>
       <c r="R10" s="40" t="n">
-        <v>78234960</v>
+        <v>55923182</v>
       </c>
       <c r="S10" s="40" t="n">
-        <v>47535640</v>
+        <v>40248814</v>
       </c>
       <c r="T10" s="40" t="n">
-        <v>59241681</v>
+        <v>50993465</v>
       </c>
       <c r="U10" s="40" t="n">
-        <v>65321829</v>
+        <v>62193580</v>
       </c>
       <c r="V10" s="40" t="n">
-        <v>57895664</v>
+        <v>45202354</v>
       </c>
       <c r="W10" s="40" t="n">
-        <v>63196973</v>
+        <v>45317128</v>
       </c>
       <c r="X10" s="40" t="n">
-        <v>51807160</v>
+        <v>48612400</v>
       </c>
       <c r="Y10" s="40" t="n">
-        <v>67644051</v>
+        <v>64209970</v>
       </c>
       <c r="Z10" s="40" t="n">
-        <v>43897626</v>
+        <v>38948580</v>
       </c>
       <c r="AA10" s="40" t="n">
-        <v>68108471</v>
+        <v>60557072</v>
       </c>
       <c r="AB10" s="40" t="n">
-        <v>65287548</v>
+        <v>75839259</v>
+      </c>
+      <c r="AC10" s="40" t="n">
+        <v>10558486</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>0</v>
+        <v>10351067</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>8972650</v>
+        <v>21091580</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>18100396</v>
+        <v>24243567</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>23988817</v>
+        <v>16381412</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>22409732</v>
+        <v>21591272</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>37715520</v>
+        <v>21904190</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>35926824</v>
+        <v>25438080</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>39462393</v>
+        <v>24614280</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>51983942</v>
+        <v>28889771</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>58935844</v>
+        <v>44250621</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>38454971</v>
+        <v>29608597</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>42939312</v>
+        <v>25219748</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>43650420</v>
+        <v>28515437</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>53954095</v>
+        <v>35235670</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>48898463</v>
+        <v>38511490</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>48011655</v>
+        <v>40935998</v>
       </c>
       <c r="T11" s="40" t="n">
-        <v>72064876</v>
+        <v>58966944</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>59606189</v>
+        <v>43378746</v>
       </c>
       <c r="V11" s="40" t="n">
-        <v>50164748</v>
+        <v>67522298</v>
       </c>
       <c r="W11" s="40" t="n">
-        <v>46095774</v>
+        <v>44905121</v>
       </c>
       <c r="X11" s="40" t="n">
-        <v>57645111</v>
+        <v>43314104</v>
       </c>
       <c r="Y11" s="40" t="n">
-        <v>55172528</v>
+        <v>45152620</v>
       </c>
       <c r="Z11" s="40" t="n">
-        <v>47962010</v>
+        <v>33695914</v>
       </c>
       <c r="AA11" s="40" t="n">
-        <v>43352139</v>
+        <v>56470370</v>
       </c>
       <c r="AB11" s="40" t="n">
-        <v>49825299</v>
+        <v>36092667</v>
+      </c>
+      <c r="AC11" s="40" t="n">
+        <v>6252898</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>10351067</v>
+        <v>5092853</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>21091580</v>
+        <v>11100161</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>24243567</v>
+        <v>14612055</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>16381412</v>
+        <v>20638987</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>21591272</v>
+        <v>14061352</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>21904190</v>
+        <v>31599148</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>25438080</v>
+        <v>18747614</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>24614280</v>
+        <v>19576415</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>28889771</v>
+        <v>14226838</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>44250621</v>
+        <v>23197145</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>29608597</v>
+        <v>25790711</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>25219748</v>
+        <v>27856115</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>28515437</v>
+        <v>20981901</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>35235670</v>
+        <v>25433123</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>38511490</v>
+        <v>19355230</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>40935998</v>
+        <v>24713836</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>58966944</v>
+        <v>20195634</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>43378746</v>
+        <v>32414171</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>67522298</v>
+        <v>42780769</v>
       </c>
       <c r="W12" s="40" t="n">
-        <v>44905121</v>
+        <v>36755122</v>
       </c>
       <c r="X12" s="40" t="n">
-        <v>43314104</v>
+        <v>38071365</v>
       </c>
       <c r="Y12" s="40" t="n">
-        <v>45152620</v>
+        <v>34397222</v>
       </c>
       <c r="Z12" s="40" t="n">
-        <v>33695914</v>
+        <v>32536036</v>
       </c>
       <c r="AA12" s="40" t="n">
-        <v>56470370</v>
+        <v>43911137</v>
       </c>
       <c r="AB12" s="40" t="n">
-        <v>36092667</v>
+        <v>33705532</v>
+      </c>
+      <c r="AC12" s="40" t="n">
+        <v>6693442</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>5092853</v>
+        <v>3249588</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>11100161</v>
+        <v>7305524</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>14612055</v>
+        <v>9575225</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>20638987</v>
+        <v>9264589</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>14061352</v>
+        <v>20692424</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>31599148</v>
+        <v>27565767</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>18747614</v>
+        <v>19138015</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>19576415</v>
+        <v>24912292</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>14226838</v>
+        <v>19068954</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>23197145</v>
+        <v>25387051</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>25790711</v>
+        <v>21008637</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>27856115</v>
+        <v>30862574</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>20981901</v>
+        <v>31820447</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>25433123</v>
+        <v>31875986</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>19355230</v>
+        <v>48358034</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>24713836</v>
+        <v>30000524</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>20195634</v>
+        <v>31150016</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>32414171</v>
+        <v>40688796</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>42780769</v>
+        <v>31752550</v>
       </c>
       <c r="W13" s="40" t="n">
-        <v>36755122</v>
+        <v>32778027</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>38071365</v>
+        <v>21331873</v>
       </c>
       <c r="Y13" s="40" t="n">
-        <v>34397222</v>
+        <v>28676177</v>
       </c>
       <c r="Z13" s="40" t="n">
-        <v>32536036</v>
+        <v>32596511</v>
       </c>
       <c r="AA13" s="40" t="n">
-        <v>43911137</v>
+        <v>53200913</v>
       </c>
       <c r="AB13" s="40" t="n">
-        <v>33705532</v>
+        <v>25830427</v>
+      </c>
+      <c r="AC13" s="40" t="n">
+        <v>7306468</v>
       </c>
     </row>
     <row r="14">
@@ -5559,95 +5669,101 @@
       <c r="AB14" s="40" t="n">
         <v>44302861</v>
       </c>
+      <c r="AC14" s="40" t="n">
+        <v>6047933</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>11884771</v>
+        <v>0</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>10651216</v>
+        <v>8972650</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>13882033</v>
+        <v>18100396</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>17812948</v>
+        <v>23988817</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>17331854</v>
+        <v>22409732</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>26294756</v>
+        <v>37715520</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>24196222</v>
+        <v>35926824</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>22122847</v>
+        <v>39462393</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>31914115</v>
+        <v>51983942</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>32069521</v>
+        <v>58935844</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>38287475</v>
+        <v>38454971</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>28283704</v>
+        <v>42939312</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>27334091</v>
+        <v>43650420</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>36312415</v>
+        <v>53954095</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>39333565</v>
+        <v>48898463</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>28566119</v>
+        <v>48011655</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>40387845</v>
+        <v>72064876</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>39744111</v>
+        <v>59606189</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>31477917</v>
+        <v>50164748</v>
       </c>
       <c r="W15" s="40" t="n">
-        <v>29910767</v>
+        <v>46095774</v>
       </c>
       <c r="X15" s="40" t="n">
-        <v>44620606</v>
+        <v>57645111</v>
       </c>
       <c r="Y15" s="40" t="n">
-        <v>35679497</v>
+        <v>55172528</v>
       </c>
       <c r="Z15" s="40" t="n">
-        <v>25102609</v>
+        <v>47962010</v>
       </c>
       <c r="AA15" s="40" t="n">
-        <v>39000780</v>
+        <v>43352139</v>
       </c>
       <c r="AB15" s="40" t="n">
-        <v>40583789</v>
+        <v>49825299</v>
+      </c>
+      <c r="AC15" s="40" t="n">
+        <v>8131207</v>
       </c>
     </row>
     <row r="16">
@@ -5739,455 +5855,473 @@
       <c r="AB16" s="40" t="n">
         <v>55359761</v>
       </c>
+      <c r="AC16" s="40" t="n">
+        <v>8148130</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>8544625</v>
+        <v>0</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>8387478</v>
+        <v>0</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>10570508</v>
+        <v>363900</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>11896580</v>
+        <v>3736700</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>19614352</v>
+        <v>17796776</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>20966317</v>
+        <v>42724228</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>20073400</v>
+        <v>33036620</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>23801493</v>
+        <v>29649130</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>27940611</v>
+        <v>13949368</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>27893929</v>
+        <v>24539413</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>29635773</v>
+        <v>19087217</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>19554230</v>
+        <v>17139440</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>23848495</v>
+        <v>17746930</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>24194638</v>
+        <v>21437830</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>20330094</v>
+        <v>17616397</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>26044199</v>
+        <v>19360848</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>24608772</v>
+        <v>25377166</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>28079726</v>
+        <v>24702051</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>20968052</v>
+        <v>26856647</v>
       </c>
       <c r="W17" s="40" t="n">
-        <v>29501132</v>
+        <v>27122255</v>
       </c>
       <c r="X17" s="40" t="n">
-        <v>30624981</v>
+        <v>30650242</v>
       </c>
       <c r="Y17" s="40" t="n">
-        <v>28071639</v>
+        <v>21101547</v>
       </c>
       <c r="Z17" s="40" t="n">
-        <v>21021583</v>
+        <v>30037062</v>
       </c>
       <c r="AA17" s="40" t="n">
-        <v>29229414</v>
+        <v>22123372</v>
       </c>
       <c r="AB17" s="40" t="n">
-        <v>26957117</v>
+        <v>24293073</v>
+      </c>
+      <c r="AC17" s="40" t="n">
+        <v>3681043</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>3249588</v>
+        <v>11884771</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>7305524</v>
+        <v>10651216</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>9575225</v>
+        <v>13882033</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>9264589</v>
+        <v>17812948</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>20692424</v>
+        <v>17331854</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>27565767</v>
+        <v>26294756</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>19138015</v>
+        <v>24196222</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>24912292</v>
+        <v>22122847</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>19068954</v>
+        <v>31914115</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>25387051</v>
+        <v>32069521</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>21008637</v>
+        <v>38287475</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>30862574</v>
+        <v>28283704</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>31820447</v>
+        <v>27334091</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>31875986</v>
+        <v>36312415</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>48358034</v>
+        <v>39333565</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>30000524</v>
+        <v>28566119</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>31150016</v>
+        <v>40387845</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>40688796</v>
+        <v>39744111</v>
       </c>
       <c r="V18" s="40" t="n">
-        <v>31752550</v>
+        <v>31477917</v>
       </c>
       <c r="W18" s="40" t="n">
-        <v>32778027</v>
+        <v>29910767</v>
       </c>
       <c r="X18" s="40" t="n">
-        <v>21331873</v>
+        <v>44620606</v>
       </c>
       <c r="Y18" s="40" t="n">
-        <v>28676177</v>
+        <v>35679497</v>
       </c>
       <c r="Z18" s="40" t="n">
-        <v>32596511</v>
+        <v>25102609</v>
       </c>
       <c r="AA18" s="40" t="n">
-        <v>53200913</v>
+        <v>39000780</v>
       </c>
       <c r="AB18" s="40" t="n">
-        <v>25830427</v>
+        <v>40583789</v>
+      </c>
+      <c r="AC18" s="40" t="n">
+        <v>2620320</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>8544625</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0</v>
+        <v>8387478</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>363900</v>
+        <v>10570508</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>3736700</v>
+        <v>11896580</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>17796776</v>
+        <v>19614352</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>42724228</v>
+        <v>20966317</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>33036620</v>
+        <v>20073400</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>29649130</v>
+        <v>23801493</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>13949368</v>
+        <v>27940611</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>24539413</v>
+        <v>27893929</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>19087217</v>
+        <v>29635773</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>17139440</v>
+        <v>19554230</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>17746930</v>
+        <v>23848495</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>21437830</v>
+        <v>24194638</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>17616397</v>
+        <v>20330094</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>19360848</v>
+        <v>26044199</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>25377166</v>
+        <v>24608772</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>24702051</v>
+        <v>28079726</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>26856647</v>
+        <v>20968052</v>
       </c>
       <c r="W19" s="40" t="n">
-        <v>27122255</v>
+        <v>29501132</v>
       </c>
       <c r="X19" s="40" t="n">
-        <v>30650242</v>
+        <v>30624981</v>
       </c>
       <c r="Y19" s="40" t="n">
-        <v>21101547</v>
+        <v>28071639</v>
       </c>
       <c r="Z19" s="40" t="n">
-        <v>30037062</v>
+        <v>21021583</v>
       </c>
       <c r="AA19" s="40" t="n">
-        <v>22123372</v>
+        <v>29229414</v>
       </c>
       <c r="AB19" s="40" t="n">
-        <v>24293073</v>
+        <v>26957117</v>
+      </c>
+      <c r="AC19" s="40" t="n">
+        <v>4660710</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>6239584</v>
+        <v>0</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>13803407</v>
+        <v>0</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>28572076</v>
+        <v>1324510</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>15282581</v>
+        <v>10311989</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>16594572</v>
+        <v>19934535</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>15223898</v>
+        <v>13536614</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>27696695</v>
+        <v>22187720</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>17717888</v>
+        <v>11732010</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>24163432</v>
+        <v>21143100</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>23623477</v>
+        <v>14330970</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>19145601</v>
+        <v>38267409</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>30157601</v>
+        <v>46351274</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>41172333</v>
+        <v>37105387</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>34303423</v>
+        <v>19868191</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>35044850</v>
+        <v>15153480</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>33519824</v>
+        <v>19277087</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>25969876</v>
+        <v>34209889</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>23835106</v>
+        <v>33260760</v>
       </c>
       <c r="V20" s="40" t="n">
-        <v>27833047</v>
+        <v>23559262</v>
       </c>
       <c r="W20" s="40" t="n">
-        <v>22815382</v>
+        <v>29206004</v>
       </c>
       <c r="X20" s="40" t="n">
-        <v>28299644</v>
+        <v>26477239</v>
       </c>
       <c r="Y20" s="40" t="n">
-        <v>23130899</v>
+        <v>31392938</v>
       </c>
       <c r="Z20" s="40" t="n">
-        <v>20390472</v>
+        <v>14752034</v>
       </c>
       <c r="AA20" s="40" t="n">
-        <v>25564267</v>
+        <v>27021110</v>
       </c>
       <c r="AB20" s="40" t="n">
-        <v>25453154</v>
+        <v>26706620</v>
+      </c>
+      <c r="AC20" s="40" t="n">
+        <v>3914850</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C21" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="40" t="n">
-        <v>0</v>
+        <v>6239584</v>
       </c>
       <c r="E21" s="40" t="n">
-        <v>0</v>
+        <v>13803407</v>
       </c>
       <c r="F21" s="40" t="n">
-        <v>1324510</v>
+        <v>28572076</v>
       </c>
       <c r="G21" s="40" t="n">
-        <v>10311989</v>
+        <v>15282581</v>
       </c>
       <c r="H21" s="40" t="n">
-        <v>19934535</v>
+        <v>16594572</v>
       </c>
       <c r="I21" s="40" t="n">
-        <v>13536614</v>
+        <v>15223898</v>
       </c>
       <c r="J21" s="40" t="n">
-        <v>22187720</v>
+        <v>27696695</v>
       </c>
       <c r="K21" s="40" t="n">
-        <v>11732010</v>
+        <v>17717888</v>
       </c>
       <c r="L21" s="40" t="n">
-        <v>21143100</v>
+        <v>24163432</v>
       </c>
       <c r="M21" s="40" t="n">
-        <v>14330970</v>
+        <v>23623477</v>
       </c>
       <c r="N21" s="40" t="n">
-        <v>38267409</v>
+        <v>19145601</v>
       </c>
       <c r="O21" s="40" t="n">
-        <v>46351274</v>
+        <v>30157601</v>
       </c>
       <c r="P21" s="40" t="n">
-        <v>37105387</v>
+        <v>41172333</v>
       </c>
       <c r="Q21" s="40" t="n">
-        <v>19868191</v>
+        <v>34303423</v>
       </c>
       <c r="R21" s="40" t="n">
-        <v>15153480</v>
+        <v>35044850</v>
       </c>
       <c r="S21" s="40" t="n">
-        <v>19277087</v>
+        <v>33519824</v>
       </c>
       <c r="T21" s="40" t="n">
-        <v>34209889</v>
+        <v>25969876</v>
       </c>
       <c r="U21" s="40" t="n">
-        <v>33260760</v>
+        <v>23835106</v>
       </c>
       <c r="V21" s="40" t="n">
-        <v>23559262</v>
+        <v>27833047</v>
       </c>
       <c r="W21" s="40" t="n">
-        <v>29206004</v>
+        <v>22815382</v>
       </c>
       <c r="X21" s="40" t="n">
-        <v>26477239</v>
+        <v>28299644</v>
       </c>
       <c r="Y21" s="40" t="n">
-        <v>31392938</v>
+        <v>23130899</v>
       </c>
       <c r="Z21" s="40" t="n">
-        <v>14752034</v>
+        <v>20390472</v>
       </c>
       <c r="AA21" s="40" t="n">
-        <v>27021110</v>
+        <v>25564267</v>
       </c>
       <c r="AB21" s="40" t="n">
-        <v>26706620</v>
+        <v>25453154</v>
+      </c>
+      <c r="AC21" s="40" t="n">
+        <v>2593300</v>
       </c>
     </row>
     <row r="22">
@@ -6279,6 +6413,9 @@
       <c r="AB22" s="40" t="n">
         <v>10380052</v>
       </c>
+      <c r="AC22" s="40" t="n">
+        <v>1118710</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -6368,6 +6505,9 @@
       </c>
       <c r="AB23" s="40" t="n">
         <v>5406298</v>
+      </c>
+      <c r="AC23" s="40" t="n">
+        <v>628350</v>
       </c>
     </row>
     <row r="24">
@@ -6479,6 +6619,10 @@
       </c>
       <c r="AB24" s="41">
         <f>AVERAGE(AB6:AB23)</f>
+        <v/>
+      </c>
+      <c r="AC24" s="41">
+        <f>AVERAGE(AC6:AC23)</f>
         <v/>
       </c>
     </row>
@@ -6493,7 +6637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB24"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="20" min="1" max="1"/>
@@ -6524,6 +6668,7 @@
     <col width="13" customWidth="1" style="20" min="26" max="26"/>
     <col width="13" customWidth="1" style="20" min="27" max="27"/>
     <col width="13" customWidth="1" style="20" min="28" max="28"/>
+    <col width="13" customWidth="1" style="20" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6671,6 +6816,11 @@
           <t>2026-10-19</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="31" t="inlineStr">
@@ -6811,6 +6961,11 @@
       <c r="AB4" s="31" t="inlineStr">
         <is>
           <t>19.10–25.10</t>
+        </is>
+      </c>
+      <c r="AC4" s="31" t="inlineStr">
+        <is>
+          <t>26.10–01.11*</t>
         </is>
       </c>
     </row>
@@ -6899,6 +7054,9 @@
       <c r="AB5" s="34" t="n">
         <v>7</v>
       </c>
+      <c r="AC5" s="34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="35" t="inlineStr">
@@ -6989,6 +7147,9 @@
       <c r="AB6" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="AC6" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
@@ -7079,6 +7240,9 @@
       <c r="AB7" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="AC7" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
@@ -7169,23 +7333,26 @@
       <c r="AB8" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="AC8" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-292</t>
+          <t>FRТАШ-294</t>
         </is>
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Спутник</t>
+          <t>Шастри</t>
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E9" s="42" t="n">
         <v>7</v>
@@ -7258,24 +7425,27 @@
       </c>
       <c r="AB9" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="AC9" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-294</t>
+          <t>FRТАШ-292</t>
         </is>
       </c>
       <c r="B10" s="35" t="inlineStr">
         <is>
-          <t>Шастри</t>
+          <t>Спутник</t>
         </is>
       </c>
       <c r="C10" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" s="42" t="n">
         <v>7</v>
@@ -7348,27 +7518,30 @@
       </c>
       <c r="AB10" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="AC10" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E11" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" s="42" t="n">
         <v>7</v>
@@ -7431,121 +7604,127 @@
         <v>7</v>
       </c>
       <c r="Z11" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA11" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB11" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="AC11" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB12" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC12" s="42" t="n">
         <v>1</v>
-      </c>
-      <c r="D12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA12" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB12" s="42" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E13" s="42" t="n">
         <v>7</v>
@@ -7618,6 +7797,9 @@
       </c>
       <c r="AB13" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="AC13" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -7709,26 +7891,29 @@
       <c r="AB14" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="AC14" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E15" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15" s="42" t="n">
         <v>7</v>
@@ -7791,13 +7976,16 @@
         <v>7</v>
       </c>
       <c r="Z15" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA15" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB15" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="AC15" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -7889,32 +8077,35 @@
       <c r="AB16" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="AC16" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="42" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="G17" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H17" s="42" t="n">
         <v>7</v>
@@ -7971,31 +8162,34 @@
         <v>7</v>
       </c>
       <c r="Z17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB17" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="AC17" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -8068,121 +8262,127 @@
       </c>
       <c r="AB18" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="AC18" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z19" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="H19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z19" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="AA19" s="42" t="n">
         <v>7</v>
       </c>
       <c r="AB19" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="AC19" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-319</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Баку</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="42" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F20" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="G20" s="42" t="n">
         <v>7</v>
       </c>
@@ -8248,30 +8448,33 @@
       </c>
       <c r="AB20" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="AC20" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-319</t>
         </is>
       </c>
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Баку</t>
         </is>
       </c>
       <c r="C21" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D21" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E21" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F21" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G21" s="42" t="n">
         <v>7</v>
@@ -8338,6 +8541,9 @@
       </c>
       <c r="AB21" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="AC21" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -8429,6 +8635,9 @@
       <c r="AB22" s="42" t="n">
         <v>7</v>
       </c>
+      <c r="AC22" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="35" t="inlineStr">
@@ -8518,6 +8727,9 @@
       </c>
       <c r="AB23" s="42" t="n">
         <v>7</v>
+      </c>
+      <c r="AC23" s="42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -8631,6 +8843,10 @@
         <f>AVERAGE(AB6:AB23)</f>
         <v/>
       </c>
+      <c r="AC24" s="43">
+        <f>AVERAGE(AC6:AC23)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2611,7 +2611,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2704,193 +2704,193 @@
         <v>123.71</v>
       </c>
       <c r="AC6" s="36" t="n">
-        <v>165</v>
+        <v>152.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E7" s="36" t="n">
-        <v>29.43</v>
+        <v>7.33</v>
       </c>
       <c r="F7" s="36" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="G7" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="H7" s="36" t="n">
+        <v>24.86</v>
+      </c>
+      <c r="I7" s="36" t="n">
+        <v>36.57</v>
+      </c>
+      <c r="J7" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="G7" s="36" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="H7" s="36" t="n">
-        <v>51.43</v>
-      </c>
-      <c r="I7" s="36" t="n">
-        <v>58.29</v>
-      </c>
-      <c r="J7" s="36" t="n">
-        <v>63</v>
-      </c>
       <c r="K7" s="36" t="n">
-        <v>55.43</v>
+        <v>43.86</v>
       </c>
       <c r="L7" s="36" t="n">
-        <v>69.56999999999999</v>
+        <v>50.14</v>
       </c>
       <c r="M7" s="36" t="n">
-        <v>66.43000000000001</v>
+        <v>59</v>
       </c>
       <c r="N7" s="36" t="n">
-        <v>76.86</v>
+        <v>53.71</v>
       </c>
       <c r="O7" s="36" t="n">
-        <v>64.29000000000001</v>
+        <v>46.57</v>
       </c>
       <c r="P7" s="36" t="n">
-        <v>71.43000000000001</v>
+        <v>49.29</v>
       </c>
       <c r="Q7" s="36" t="n">
-        <v>78.86</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="R7" s="36" t="n">
+        <v>67.29000000000001</v>
+      </c>
+      <c r="S7" s="36" t="n">
+        <v>61</v>
+      </c>
+      <c r="T7" s="36" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="U7" s="36" t="n">
+        <v>68</v>
+      </c>
+      <c r="V7" s="36" t="n">
+        <v>77.56999999999999</v>
+      </c>
+      <c r="W7" s="36" t="n">
+        <v>71</v>
+      </c>
+      <c r="X7" s="36" t="n">
+        <v>68.43000000000001</v>
+      </c>
+      <c r="Y7" s="36" t="n">
         <v>78.43000000000001</v>
       </c>
-      <c r="S7" s="36" t="n">
-        <v>72.43000000000001</v>
-      </c>
-      <c r="T7" s="36" t="n">
-        <v>92.14</v>
-      </c>
-      <c r="U7" s="36" t="n">
-        <v>91</v>
-      </c>
-      <c r="V7" s="36" t="n">
-        <v>85.43000000000001</v>
-      </c>
-      <c r="W7" s="36" t="n">
-        <v>88.56999999999999</v>
-      </c>
-      <c r="X7" s="36" t="n">
-        <v>80.70999999999999</v>
-      </c>
-      <c r="Y7" s="36" t="n">
-        <v>101.29</v>
-      </c>
       <c r="Z7" s="36" t="n">
-        <v>76.14</v>
+        <v>78.17</v>
       </c>
       <c r="AA7" s="36" t="n">
-        <v>90.14</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="AB7" s="36" t="n">
-        <v>89.86</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="AC7" s="36" t="n">
-        <v>102</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E8" s="36" t="n">
-        <v>7.33</v>
+        <v>29.43</v>
       </c>
       <c r="F8" s="36" t="n">
-        <v>17.86</v>
+        <v>38</v>
       </c>
       <c r="G8" s="36" t="n">
-        <v>22.14</v>
+        <v>41.29</v>
       </c>
       <c r="H8" s="36" t="n">
-        <v>24.86</v>
+        <v>51.43</v>
       </c>
       <c r="I8" s="36" t="n">
-        <v>36.57</v>
+        <v>58.29</v>
       </c>
       <c r="J8" s="36" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="K8" s="36" t="n">
-        <v>43.86</v>
+        <v>55.43</v>
       </c>
       <c r="L8" s="36" t="n">
-        <v>50.14</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="M8" s="36" t="n">
-        <v>59</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="N8" s="36" t="n">
-        <v>53.71</v>
+        <v>76.86</v>
       </c>
       <c r="O8" s="36" t="n">
-        <v>46.57</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="P8" s="36" t="n">
-        <v>49.29</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="Q8" s="36" t="n">
-        <v>65.56999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="R8" s="36" t="n">
-        <v>67.29000000000001</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="S8" s="36" t="n">
-        <v>61</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="T8" s="36" t="n">
-        <v>64.43000000000001</v>
+        <v>92.14</v>
       </c>
       <c r="U8" s="36" t="n">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="V8" s="36" t="n">
-        <v>77.56999999999999</v>
+        <v>85.43000000000001</v>
       </c>
       <c r="W8" s="36" t="n">
-        <v>71</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="X8" s="36" t="n">
-        <v>68.43000000000001</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="Y8" s="36" t="n">
-        <v>78.43000000000001</v>
+        <v>101.29</v>
       </c>
       <c r="Z8" s="36" t="n">
-        <v>78.17</v>
+        <v>76.14</v>
       </c>
       <c r="AA8" s="36" t="n">
-        <v>78.56999999999999</v>
+        <v>90.14</v>
       </c>
       <c r="AB8" s="36" t="n">
-        <v>79.29000000000001</v>
+        <v>89.86</v>
       </c>
       <c r="AC8" s="36" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -2983,7 +2983,7 @@
         <v>61.86</v>
       </c>
       <c r="AC9" s="36" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -3076,7 +3076,7 @@
         <v>62.29</v>
       </c>
       <c r="AC10" s="36" t="n">
-        <v>72</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="11">
@@ -3169,7 +3169,7 @@
         <v>44.14</v>
       </c>
       <c r="AC11" s="36" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
@@ -3262,379 +3262,379 @@
         <v>42.86</v>
       </c>
       <c r="AC12" s="36" t="n">
-        <v>50</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>3.33</v>
+        <v>1.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>6.43</v>
+        <v>12.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>8.140000000000001</v>
+        <v>16.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>21</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>14</v>
+        <v>20.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>17.14</v>
+        <v>28.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>16.14</v>
+        <v>24.14</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>18.57</v>
+        <v>27.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>16.14</v>
+        <v>28.14</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>21.71</v>
+        <v>28.86</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>20.86</v>
+        <v>33.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>20.86</v>
+        <v>30.71</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>21.86</v>
+        <v>31.14</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>28.71</v>
+        <v>40.29</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>24.71</v>
+        <v>38.71</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>24.57</v>
+        <v>43.14</v>
       </c>
       <c r="T13" s="36" t="n">
-        <v>25.29</v>
+        <v>37</v>
       </c>
       <c r="U13" s="36" t="n">
-        <v>26.71</v>
+        <v>46.29</v>
       </c>
       <c r="V13" s="36" t="n">
-        <v>27.57</v>
+        <v>43.14</v>
       </c>
       <c r="W13" s="36" t="n">
-        <v>28.29</v>
+        <v>36.86</v>
       </c>
       <c r="X13" s="36" t="n">
-        <v>21.29</v>
+        <v>33.43</v>
       </c>
       <c r="Y13" s="36" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="Z13" s="36" t="n">
-        <v>25.43</v>
+        <v>39.86</v>
       </c>
       <c r="AA13" s="36" t="n">
-        <v>30.29</v>
+        <v>37.14</v>
       </c>
       <c r="AB13" s="36" t="n">
-        <v>28.57</v>
+        <v>41.14</v>
       </c>
       <c r="AC13" s="36" t="n">
-        <v>44</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>33.14</v>
+        <v>38.57</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>30.71</v>
+        <v>34.29</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>31.14</v>
+        <v>37.86</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>40.29</v>
+        <v>42.86</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>38.71</v>
+        <v>40.71</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>43.14</v>
+        <v>45.43</v>
       </c>
       <c r="T14" s="36" t="n">
-        <v>37</v>
+        <v>44.57</v>
       </c>
       <c r="U14" s="36" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="V14" s="36" t="n">
         <v>46.29</v>
       </c>
-      <c r="V14" s="36" t="n">
-        <v>43.14</v>
-      </c>
       <c r="W14" s="36" t="n">
-        <v>36.86</v>
+        <v>43.71</v>
       </c>
       <c r="X14" s="36" t="n">
-        <v>33.43</v>
+        <v>49.57</v>
       </c>
       <c r="Y14" s="36" t="n">
-        <v>48</v>
+        <v>47.86</v>
       </c>
       <c r="Z14" s="36" t="n">
-        <v>39.86</v>
+        <v>46</v>
       </c>
       <c r="AA14" s="36" t="n">
-        <v>37.14</v>
+        <v>45.14</v>
       </c>
       <c r="AB14" s="36" t="n">
-        <v>41.14</v>
+        <v>47.71</v>
       </c>
       <c r="AC14" s="36" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>8</v>
+        <v>7.14</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13.14</v>
+        <v>13.43</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>19.43</v>
+        <v>12.71</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>26.43</v>
+        <v>14.43</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>32.29</v>
+        <v>19</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>31.29</v>
+        <v>21.14</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>33.57</v>
+        <v>18.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>40</v>
+        <v>16.57</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>42.43</v>
+        <v>14.71</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>38.57</v>
+        <v>19.14</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>34.29</v>
+        <v>18</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>37.86</v>
+        <v>15.29</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>42.86</v>
+        <v>15.29</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>40.71</v>
+        <v>18.71</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>45.43</v>
+        <v>18</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>44.57</v>
+        <v>25.29</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>55.29</v>
+        <v>28.86</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>46.29</v>
+        <v>24</v>
       </c>
       <c r="W15" s="36" t="n">
-        <v>43.71</v>
+        <v>29.29</v>
       </c>
       <c r="X15" s="36" t="n">
-        <v>49.57</v>
+        <v>31.71</v>
       </c>
       <c r="Y15" s="36" t="n">
-        <v>47.86</v>
+        <v>27</v>
       </c>
       <c r="Z15" s="36" t="n">
-        <v>46</v>
+        <v>23.83</v>
       </c>
       <c r="AA15" s="36" t="n">
-        <v>45.14</v>
+        <v>34.71</v>
       </c>
       <c r="AB15" s="36" t="n">
-        <v>47.71</v>
+        <v>35.86</v>
       </c>
       <c r="AC15" s="36" t="n">
-        <v>40</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>7.14</v>
+        <v>6.43</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>13.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>12.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>14.43</v>
+        <v>14</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>19</v>
+        <v>17.14</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>21.14</v>
+        <v>16.14</v>
       </c>
       <c r="K16" s="36" t="n">
         <v>18.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>16.57</v>
+        <v>16.14</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>14.71</v>
+        <v>21.71</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>19.14</v>
+        <v>20.86</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>18</v>
+        <v>20.86</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>15.29</v>
+        <v>21.86</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>15.29</v>
+        <v>28.71</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>18.71</v>
+        <v>24.71</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>18</v>
+        <v>24.57</v>
       </c>
       <c r="T16" s="36" t="n">
         <v>25.29</v>
       </c>
       <c r="U16" s="36" t="n">
-        <v>28.86</v>
+        <v>26.71</v>
       </c>
       <c r="V16" s="36" t="n">
-        <v>24</v>
+        <v>27.57</v>
       </c>
       <c r="W16" s="36" t="n">
-        <v>29.29</v>
+        <v>28.29</v>
       </c>
       <c r="X16" s="36" t="n">
-        <v>31.71</v>
+        <v>21.29</v>
       </c>
       <c r="Y16" s="36" t="n">
         <v>27</v>
       </c>
       <c r="Z16" s="36" t="n">
-        <v>23.83</v>
+        <v>25.43</v>
       </c>
       <c r="AA16" s="36" t="n">
-        <v>34.71</v>
+        <v>30.29</v>
       </c>
       <c r="AB16" s="36" t="n">
-        <v>35.86</v>
+        <v>28.57</v>
       </c>
       <c r="AC16" s="36" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -3727,7 +3727,7 @@
         <v>27.43</v>
       </c>
       <c r="AC17" s="36" t="n">
-        <v>35</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="18">
@@ -3820,193 +3820,193 @@
         <v>36</v>
       </c>
       <c r="AC18" s="36" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>0</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>14.43</v>
+        <v>3.25</v>
       </c>
       <c r="G19" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H19" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I19" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="J19" s="36" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="K19" s="36" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L19" s="36" t="n">
         <v>11.86</v>
       </c>
-      <c r="H19" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="I19" s="36" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="J19" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="K19" s="36" t="n">
+      <c r="M19" s="36" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N19" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="O19" s="36" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="P19" s="36" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="Q19" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="R19" s="36" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="S19" s="36" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="T19" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="U19" s="36" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="V19" s="36" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="W19" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="X19" s="36" t="n">
         <v>23.43</v>
       </c>
-      <c r="L19" s="36" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="M19" s="36" t="n">
-        <v>24.57</v>
-      </c>
-      <c r="N19" s="36" t="n">
+      <c r="Y19" s="36" t="n">
         <v>24.14</v>
       </c>
-      <c r="O19" s="36" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="P19" s="36" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q19" s="36" t="n">
-        <v>23</v>
-      </c>
-      <c r="R19" s="36" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="S19" s="36" t="n">
-        <v>24.71</v>
-      </c>
-      <c r="T19" s="36" t="n">
-        <v>27.57</v>
-      </c>
-      <c r="U19" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="V19" s="36" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="W19" s="36" t="n">
-        <v>30.14</v>
-      </c>
-      <c r="X19" s="36" t="n">
-        <v>34.43</v>
-      </c>
-      <c r="Y19" s="36" t="n">
-        <v>33.43</v>
-      </c>
       <c r="Z19" s="36" t="n">
-        <v>32</v>
+        <v>16.43</v>
       </c>
       <c r="AA19" s="36" t="n">
-        <v>31.29</v>
+        <v>25.29</v>
       </c>
       <c r="AB19" s="36" t="n">
-        <v>35.14</v>
+        <v>25.29</v>
       </c>
       <c r="AC19" s="36" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>3.25</v>
+        <v>14.43</v>
       </c>
       <c r="G20" s="36" t="n">
-        <v>8</v>
+        <v>11.86</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>9.43</v>
+        <v>18</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>12.71</v>
+        <v>19.14</v>
       </c>
       <c r="J20" s="36" t="n">
-        <v>11.57</v>
+        <v>21</v>
       </c>
       <c r="K20" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>23.43</v>
       </c>
       <c r="L20" s="36" t="n">
-        <v>11.86</v>
+        <v>20.43</v>
       </c>
       <c r="M20" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>24.57</v>
       </c>
       <c r="N20" s="36" t="n">
-        <v>19</v>
+        <v>24.14</v>
       </c>
       <c r="O20" s="36" t="n">
-        <v>19.57</v>
+        <v>24.43</v>
       </c>
       <c r="P20" s="36" t="n">
-        <v>16.86</v>
+        <v>22</v>
       </c>
       <c r="Q20" s="36" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="R20" s="36" t="n">
-        <v>14.71</v>
+        <v>18.43</v>
       </c>
       <c r="S20" s="36" t="n">
-        <v>15.86</v>
+        <v>24.71</v>
       </c>
       <c r="T20" s="36" t="n">
-        <v>25</v>
+        <v>27.57</v>
       </c>
       <c r="U20" s="36" t="n">
-        <v>27.29</v>
+        <v>30</v>
       </c>
       <c r="V20" s="36" t="n">
-        <v>17.14</v>
+        <v>28.57</v>
       </c>
       <c r="W20" s="36" t="n">
-        <v>22.14</v>
+        <v>30.14</v>
       </c>
       <c r="X20" s="36" t="n">
-        <v>23.43</v>
+        <v>34.43</v>
       </c>
       <c r="Y20" s="36" t="n">
-        <v>24.14</v>
+        <v>33.43</v>
       </c>
       <c r="Z20" s="36" t="n">
-        <v>16.43</v>
+        <v>32</v>
       </c>
       <c r="AA20" s="36" t="n">
-        <v>25.29</v>
+        <v>31.29</v>
       </c>
       <c r="AB20" s="36" t="n">
-        <v>25.29</v>
+        <v>35.14</v>
       </c>
       <c r="AC20" s="36" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -4099,7 +4099,7 @@
         <v>26.71</v>
       </c>
       <c r="AC21" s="36" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="22">
@@ -4192,7 +4192,7 @@
         <v>11.86</v>
       </c>
       <c r="AC22" s="36" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="23">
@@ -4285,7 +4285,7 @@
         <v>8.57</v>
       </c>
       <c r="AC23" s="36" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="24">
@@ -4833,7 +4833,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4926,193 +4926,193 @@
         <v>112485262</v>
       </c>
       <c r="AC6" s="40" t="n">
-        <v>18599895</v>
+        <v>36102608</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="40" t="n">
-        <v>6122227</v>
+        <v>0</v>
       </c>
       <c r="E7" s="40" t="n">
-        <v>31792625</v>
+        <v>2886450</v>
       </c>
       <c r="F7" s="40" t="n">
-        <v>49374899</v>
+        <v>22932586</v>
       </c>
       <c r="G7" s="40" t="n">
-        <v>38585414</v>
+        <v>24764259</v>
       </c>
       <c r="H7" s="40" t="n">
-        <v>51458725</v>
+        <v>32268886</v>
       </c>
       <c r="I7" s="40" t="n">
-        <v>61835892</v>
+        <v>42977335</v>
       </c>
       <c r="J7" s="40" t="n">
-        <v>80551167</v>
+        <v>44364359</v>
       </c>
       <c r="K7" s="40" t="n">
-        <v>61490143</v>
+        <v>53225819</v>
       </c>
       <c r="L7" s="40" t="n">
-        <v>68619843</v>
+        <v>51621207</v>
       </c>
       <c r="M7" s="40" t="n">
-        <v>81742671</v>
+        <v>58204066</v>
       </c>
       <c r="N7" s="40" t="n">
-        <v>69757179</v>
+        <v>58190202</v>
       </c>
       <c r="O7" s="40" t="n">
-        <v>68198708</v>
+        <v>46275213</v>
       </c>
       <c r="P7" s="40" t="n">
-        <v>67906121</v>
+        <v>51530060</v>
       </c>
       <c r="Q7" s="40" t="n">
-        <v>84229530</v>
+        <v>85043089</v>
       </c>
       <c r="R7" s="40" t="n">
-        <v>92096471</v>
+        <v>67469168</v>
       </c>
       <c r="S7" s="40" t="n">
-        <v>78023476</v>
+        <v>66040134</v>
       </c>
       <c r="T7" s="40" t="n">
-        <v>89918146</v>
+        <v>80004937</v>
       </c>
       <c r="U7" s="40" t="n">
-        <v>94534230</v>
+        <v>67225139</v>
       </c>
       <c r="V7" s="40" t="n">
-        <v>81100625</v>
+        <v>80820230</v>
       </c>
       <c r="W7" s="40" t="n">
-        <v>109654171</v>
+        <v>73904849</v>
       </c>
       <c r="X7" s="40" t="n">
-        <v>99375298</v>
+        <v>73547034</v>
       </c>
       <c r="Y7" s="40" t="n">
-        <v>105623451</v>
+        <v>84513482</v>
       </c>
       <c r="Z7" s="40" t="n">
-        <v>73957610</v>
+        <v>80572023</v>
       </c>
       <c r="AA7" s="40" t="n">
-        <v>96334193</v>
+        <v>88660521</v>
       </c>
       <c r="AB7" s="40" t="n">
-        <v>84653963</v>
+        <v>85896590</v>
       </c>
       <c r="AC7" s="40" t="n">
-        <v>15193087</v>
+        <v>25781878</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="40" t="n">
-        <v>0</v>
+        <v>6122227</v>
       </c>
       <c r="E8" s="40" t="n">
-        <v>2886450</v>
+        <v>31792625</v>
       </c>
       <c r="F8" s="40" t="n">
-        <v>22932586</v>
+        <v>49374899</v>
       </c>
       <c r="G8" s="40" t="n">
-        <v>24764259</v>
+        <v>38585414</v>
       </c>
       <c r="H8" s="40" t="n">
-        <v>32268886</v>
+        <v>51458725</v>
       </c>
       <c r="I8" s="40" t="n">
-        <v>42977335</v>
+        <v>61835892</v>
       </c>
       <c r="J8" s="40" t="n">
-        <v>44364359</v>
+        <v>80551167</v>
       </c>
       <c r="K8" s="40" t="n">
-        <v>53225819</v>
+        <v>61490143</v>
       </c>
       <c r="L8" s="40" t="n">
-        <v>51621207</v>
+        <v>68619843</v>
       </c>
       <c r="M8" s="40" t="n">
-        <v>58204066</v>
+        <v>81742671</v>
       </c>
       <c r="N8" s="40" t="n">
-        <v>58190202</v>
+        <v>69757179</v>
       </c>
       <c r="O8" s="40" t="n">
-        <v>46275213</v>
+        <v>68198708</v>
       </c>
       <c r="P8" s="40" t="n">
-        <v>51530060</v>
+        <v>67906121</v>
       </c>
       <c r="Q8" s="40" t="n">
-        <v>85043089</v>
+        <v>84229530</v>
       </c>
       <c r="R8" s="40" t="n">
-        <v>67469168</v>
+        <v>92096471</v>
       </c>
       <c r="S8" s="40" t="n">
-        <v>66040134</v>
+        <v>78023476</v>
       </c>
       <c r="T8" s="40" t="n">
-        <v>80004937</v>
+        <v>89918146</v>
       </c>
       <c r="U8" s="40" t="n">
-        <v>67225139</v>
+        <v>94534230</v>
       </c>
       <c r="V8" s="40" t="n">
-        <v>80820230</v>
+        <v>81100625</v>
       </c>
       <c r="W8" s="40" t="n">
-        <v>73904849</v>
+        <v>109654171</v>
       </c>
       <c r="X8" s="40" t="n">
-        <v>73547034</v>
+        <v>99375298</v>
       </c>
       <c r="Y8" s="40" t="n">
-        <v>84513482</v>
+        <v>105623451</v>
       </c>
       <c r="Z8" s="40" t="n">
-        <v>80572023</v>
+        <v>73957610</v>
       </c>
       <c r="AA8" s="40" t="n">
-        <v>88660521</v>
+        <v>96334193</v>
       </c>
       <c r="AB8" s="40" t="n">
-        <v>85896590</v>
+        <v>84653963</v>
       </c>
       <c r="AC8" s="40" t="n">
-        <v>10875777</v>
+        <v>26116333</v>
       </c>
     </row>
     <row r="9">
@@ -5205,7 +5205,7 @@
         <v>65287548</v>
       </c>
       <c r="AC9" s="40" t="n">
-        <v>10213235</v>
+        <v>16991595</v>
       </c>
     </row>
     <row r="10">
@@ -5298,7 +5298,7 @@
         <v>75839259</v>
       </c>
       <c r="AC10" s="40" t="n">
-        <v>10558486</v>
+        <v>17077316</v>
       </c>
     </row>
     <row r="11">
@@ -5391,7 +5391,7 @@
         <v>36092667</v>
       </c>
       <c r="AC11" s="40" t="n">
-        <v>6252898</v>
+        <v>11890348</v>
       </c>
     </row>
     <row r="12">
@@ -5484,379 +5484,379 @@
         <v>33705532</v>
       </c>
       <c r="AC12" s="40" t="n">
-        <v>6693442</v>
+        <v>14173463</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>3249588</v>
+        <v>536260</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>7305524</v>
+        <v>14403556</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>9575225</v>
+        <v>16216832</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>9264589</v>
+        <v>32622053</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>20692424</v>
+        <v>23929705</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>27565767</v>
+        <v>37214538</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>19138015</v>
+        <v>25375430</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>24912292</v>
+        <v>31500087</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>19068954</v>
+        <v>28078687</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>25387051</v>
+        <v>34472458</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>21008637</v>
+        <v>35343350</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>30862574</v>
+        <v>51225290</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>31820447</v>
+        <v>36142612</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>31875986</v>
+        <v>47488940</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>48358034</v>
+        <v>44805002</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>30000524</v>
+        <v>43327432</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>31150016</v>
+        <v>39637968</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>40688796</v>
+        <v>55199920</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>31752550</v>
+        <v>50680631</v>
       </c>
       <c r="W13" s="40" t="n">
-        <v>32778027</v>
+        <v>50163008</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>21331873</v>
+        <v>38778399</v>
       </c>
       <c r="Y13" s="40" t="n">
-        <v>28676177</v>
+        <v>50996587</v>
       </c>
       <c r="Z13" s="40" t="n">
-        <v>32596511</v>
+        <v>42228986</v>
       </c>
       <c r="AA13" s="40" t="n">
-        <v>53200913</v>
+        <v>32767816</v>
       </c>
       <c r="AB13" s="40" t="n">
-        <v>25830427</v>
+        <v>44302861</v>
       </c>
       <c r="AC13" s="40" t="n">
-        <v>7306468</v>
+        <v>14626170</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>35343350</v>
+        <v>38454971</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>51225290</v>
+        <v>42939312</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>36142612</v>
+        <v>43650420</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>47488940</v>
+        <v>53954095</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>44805002</v>
+        <v>48898463</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>43327432</v>
+        <v>48011655</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>39637968</v>
+        <v>72064876</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>55199920</v>
+        <v>59606189</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>50680631</v>
+        <v>50164748</v>
       </c>
       <c r="W14" s="40" t="n">
-        <v>50163008</v>
+        <v>46095774</v>
       </c>
       <c r="X14" s="40" t="n">
-        <v>38778399</v>
+        <v>57645111</v>
       </c>
       <c r="Y14" s="40" t="n">
-        <v>50996587</v>
+        <v>55172528</v>
       </c>
       <c r="Z14" s="40" t="n">
-        <v>42228986</v>
+        <v>47962010</v>
       </c>
       <c r="AA14" s="40" t="n">
-        <v>32767816</v>
+        <v>43352139</v>
       </c>
       <c r="AB14" s="40" t="n">
-        <v>44302861</v>
+        <v>49825299</v>
       </c>
       <c r="AC14" s="40" t="n">
-        <v>6047933</v>
+        <v>16790647</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>8972650</v>
+        <v>10420206</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>18100396</v>
+        <v>21387685</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>23988817</v>
+        <v>16050448</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>22409732</v>
+        <v>21568794</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>37715520</v>
+        <v>30845816</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>35926824</v>
+        <v>45285935</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>39462393</v>
+        <v>28941455</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>51983942</v>
+        <v>21801828</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>58935844</v>
+        <v>19628570</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>38454971</v>
+        <v>23276090</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>42939312</v>
+        <v>27906254</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>43650420</v>
+        <v>20822247</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>53954095</v>
+        <v>20014322</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>48898463</v>
+        <v>19159625</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>48011655</v>
+        <v>22535696</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>72064876</v>
+        <v>21412810</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>59606189</v>
+        <v>34881782</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>50164748</v>
+        <v>25904024</v>
       </c>
       <c r="W15" s="40" t="n">
-        <v>46095774</v>
+        <v>46961904</v>
       </c>
       <c r="X15" s="40" t="n">
-        <v>57645111</v>
+        <v>42299644</v>
       </c>
       <c r="Y15" s="40" t="n">
-        <v>55172528</v>
+        <v>32109759</v>
       </c>
       <c r="Z15" s="40" t="n">
-        <v>47962010</v>
+        <v>22714393</v>
       </c>
       <c r="AA15" s="40" t="n">
-        <v>43352139</v>
+        <v>52198815</v>
       </c>
       <c r="AB15" s="40" t="n">
-        <v>49825299</v>
+        <v>55359761</v>
       </c>
       <c r="AC15" s="40" t="n">
-        <v>8131207</v>
+        <v>16435620</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>3337146</v>
+        <v>3249588</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>10420206</v>
+        <v>7305524</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>21387685</v>
+        <v>9575225</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>16050448</v>
+        <v>9264589</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>21568794</v>
+        <v>20692424</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>30845816</v>
+        <v>27565767</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>45285935</v>
+        <v>19138015</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>28941455</v>
+        <v>24912292</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>21801828</v>
+        <v>19068954</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>19628570</v>
+        <v>25387051</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>23276090</v>
+        <v>21008637</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>27906254</v>
+        <v>30862574</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>20822247</v>
+        <v>31820447</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>20014322</v>
+        <v>31875986</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>19159625</v>
+        <v>48358034</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>22535696</v>
+        <v>30000524</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>21412810</v>
+        <v>31150016</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>34881782</v>
+        <v>40688796</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>25904024</v>
+        <v>31752550</v>
       </c>
       <c r="W16" s="40" t="n">
-        <v>46961904</v>
+        <v>32778027</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>42299644</v>
+        <v>21331873</v>
       </c>
       <c r="Y16" s="40" t="n">
-        <v>32109759</v>
+        <v>28676177</v>
       </c>
       <c r="Z16" s="40" t="n">
-        <v>22714393</v>
+        <v>32596511</v>
       </c>
       <c r="AA16" s="40" t="n">
-        <v>52198815</v>
+        <v>53200913</v>
       </c>
       <c r="AB16" s="40" t="n">
-        <v>55359761</v>
+        <v>25830427</v>
       </c>
       <c r="AC16" s="40" t="n">
-        <v>8148130</v>
+        <v>10722343</v>
       </c>
     </row>
     <row r="17">
@@ -5949,7 +5949,7 @@
         <v>24293073</v>
       </c>
       <c r="AC17" s="40" t="n">
-        <v>3681043</v>
+        <v>7011183</v>
       </c>
     </row>
     <row r="18">
@@ -6042,193 +6042,193 @@
         <v>40583789</v>
       </c>
       <c r="AC18" s="40" t="n">
-        <v>2620320</v>
+        <v>7763544</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>8544625</v>
+        <v>0</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>8387478</v>
+        <v>0</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>10570508</v>
+        <v>1324510</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>11896580</v>
+        <v>10311989</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>19614352</v>
+        <v>19934535</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>20966317</v>
+        <v>13536614</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>20073400</v>
+        <v>22187720</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>23801493</v>
+        <v>11732010</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>27940611</v>
+        <v>21143100</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>27893929</v>
+        <v>14330970</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>29635773</v>
+        <v>38267409</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>19554230</v>
+        <v>46351274</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>23848495</v>
+        <v>37105387</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>24194638</v>
+        <v>19868191</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>20330094</v>
+        <v>15153480</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>26044199</v>
+        <v>19277087</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>24608772</v>
+        <v>34209889</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>28079726</v>
+        <v>33260760</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>20968052</v>
+        <v>23559262</v>
       </c>
       <c r="W19" s="40" t="n">
-        <v>29501132</v>
+        <v>29206004</v>
       </c>
       <c r="X19" s="40" t="n">
-        <v>30624981</v>
+        <v>26477239</v>
       </c>
       <c r="Y19" s="40" t="n">
-        <v>28071639</v>
+        <v>31392938</v>
       </c>
       <c r="Z19" s="40" t="n">
-        <v>21021583</v>
+        <v>14752034</v>
       </c>
       <c r="AA19" s="40" t="n">
-        <v>29229414</v>
+        <v>27021110</v>
       </c>
       <c r="AB19" s="40" t="n">
-        <v>26957117</v>
+        <v>26706620</v>
       </c>
       <c r="AC19" s="40" t="n">
-        <v>4660710</v>
+        <v>9132340</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>0</v>
+        <v>8544625</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>0</v>
+        <v>8387478</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>1324510</v>
+        <v>10570508</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>10311989</v>
+        <v>11896580</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>19934535</v>
+        <v>19614352</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>13536614</v>
+        <v>20966317</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>22187720</v>
+        <v>20073400</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>11732010</v>
+        <v>23801493</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>21143100</v>
+        <v>27940611</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>14330970</v>
+        <v>27893929</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>38267409</v>
+        <v>29635773</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>46351274</v>
+        <v>19554230</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>37105387</v>
+        <v>23848495</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>19868191</v>
+        <v>24194638</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>15153480</v>
+        <v>20330094</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>19277087</v>
+        <v>26044199</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>34209889</v>
+        <v>24608772</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>33260760</v>
+        <v>28079726</v>
       </c>
       <c r="V20" s="40" t="n">
-        <v>23559262</v>
+        <v>20968052</v>
       </c>
       <c r="W20" s="40" t="n">
-        <v>29206004</v>
+        <v>29501132</v>
       </c>
       <c r="X20" s="40" t="n">
-        <v>26477239</v>
+        <v>30624981</v>
       </c>
       <c r="Y20" s="40" t="n">
-        <v>31392938</v>
+        <v>28071639</v>
       </c>
       <c r="Z20" s="40" t="n">
-        <v>14752034</v>
+        <v>21021583</v>
       </c>
       <c r="AA20" s="40" t="n">
-        <v>27021110</v>
+        <v>29229414</v>
       </c>
       <c r="AB20" s="40" t="n">
-        <v>26706620</v>
+        <v>26957117</v>
       </c>
       <c r="AC20" s="40" t="n">
-        <v>3914850</v>
+        <v>5688188</v>
       </c>
     </row>
     <row r="21">
@@ -6321,7 +6321,7 @@
         <v>25453154</v>
       </c>
       <c r="AC21" s="40" t="n">
-        <v>2593300</v>
+        <v>5695487</v>
       </c>
     </row>
     <row r="22">
@@ -6414,7 +6414,7 @@
         <v>10380052</v>
       </c>
       <c r="AC22" s="40" t="n">
-        <v>1118710</v>
+        <v>2416727</v>
       </c>
     </row>
     <row r="23">
@@ -6507,7 +6507,7 @@
         <v>5406298</v>
       </c>
       <c r="AC23" s="40" t="n">
-        <v>628350</v>
+        <v>1116550</v>
       </c>
     </row>
     <row r="24">
@@ -7055,7 +7055,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -7148,28 +7148,28 @@
         <v>7</v>
       </c>
       <c r="AC6" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-290</t>
+          <t>FRТАШ-289</t>
         </is>
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Буз-1</t>
+          <t>Афросиаб</t>
         </is>
       </c>
       <c r="C7" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F7" s="42" t="n">
         <v>7</v>
@@ -7232,7 +7232,7 @@
         <v>7</v>
       </c>
       <c r="Z7" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA7" s="42" t="n">
         <v>7</v>
@@ -7241,28 +7241,28 @@
         <v>7</v>
       </c>
       <c r="AC7" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-289</t>
+          <t>FRТАШ-290</t>
         </is>
       </c>
       <c r="B8" s="35" t="inlineStr">
         <is>
-          <t>Афросиаб</t>
+          <t>Буз-1</t>
         </is>
       </c>
       <c r="C8" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E8" s="42" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F8" s="42" t="n">
         <v>7</v>
@@ -7325,7 +7325,7 @@
         <v>7</v>
       </c>
       <c r="Z8" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA8" s="42" t="n">
         <v>7</v>
@@ -7334,7 +7334,7 @@
         <v>7</v>
       </c>
       <c r="AC8" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -7427,7 +7427,7 @@
         <v>7</v>
       </c>
       <c r="AC9" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -7520,7 +7520,7 @@
         <v>7</v>
       </c>
       <c r="AC10" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -7613,7 +7613,7 @@
         <v>7</v>
       </c>
       <c r="AC11" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -7706,18 +7706,18 @@
         <v>7</v>
       </c>
       <c r="AC12" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
@@ -7799,28 +7799,28 @@
         <v>7</v>
       </c>
       <c r="AC13" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" s="42" t="n">
         <v>7</v>
@@ -7883,7 +7883,7 @@
         <v>7</v>
       </c>
       <c r="Z14" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA14" s="42" t="n">
         <v>7</v>
@@ -7892,28 +7892,28 @@
         <v>7</v>
       </c>
       <c r="AC14" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E15" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" s="42" t="n">
         <v>7</v>
@@ -7985,25 +7985,25 @@
         <v>7</v>
       </c>
       <c r="AC15" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>7</v>
@@ -8069,7 +8069,7 @@
         <v>7</v>
       </c>
       <c r="Z16" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA16" s="42" t="n">
         <v>7</v>
@@ -8078,7 +8078,7 @@
         <v>7</v>
       </c>
       <c r="AC16" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -8171,7 +8171,7 @@
         <v>7</v>
       </c>
       <c r="AC17" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -8264,124 +8264,124 @@
         <v>7</v>
       </c>
       <c r="AC18" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB19" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC19" s="42" t="n">
         <v>2</v>
-      </c>
-      <c r="D19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="E19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z19" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB19" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC19" s="42" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G20" s="42" t="n">
         <v>7</v>
@@ -8441,7 +8441,7 @@
         <v>7</v>
       </c>
       <c r="Z20" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA20" s="42" t="n">
         <v>7</v>
@@ -8450,7 +8450,7 @@
         <v>7</v>
       </c>
       <c r="AC20" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -8543,7 +8543,7 @@
         <v>7</v>
       </c>
       <c r="AC21" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -8636,7 +8636,7 @@
         <v>7</v>
       </c>
       <c r="AC22" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -8729,7 +8729,7 @@
         <v>7</v>
       </c>
       <c r="AC23" s="42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2611,7 +2611,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -2704,7 +2704,7 @@
         <v>123.71</v>
       </c>
       <c r="AC6" s="36" t="n">
-        <v>152.5</v>
+        <v>137.33</v>
       </c>
     </row>
     <row r="7">
@@ -2797,7 +2797,7 @@
         <v>79.29000000000001</v>
       </c>
       <c r="AC7" s="36" t="n">
-        <v>89.5</v>
+        <v>93.67</v>
       </c>
     </row>
     <row r="8">
@@ -2890,7 +2890,7 @@
         <v>89.86</v>
       </c>
       <c r="AC8" s="36" t="n">
-        <v>86</v>
+        <v>71.33</v>
       </c>
     </row>
     <row r="9">
@@ -2983,7 +2983,7 @@
         <v>61.86</v>
       </c>
       <c r="AC9" s="36" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -3076,658 +3076,658 @@
         <v>62.29</v>
       </c>
       <c r="AC10" s="36" t="n">
-        <v>58.5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C11" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D11" s="36" t="n">
-        <v>8.43</v>
+        <v>6.67</v>
       </c>
       <c r="E11" s="36" t="n">
-        <v>13.43</v>
+        <v>11.29</v>
       </c>
       <c r="F11" s="36" t="n">
-        <v>21.71</v>
+        <v>10.57</v>
       </c>
       <c r="G11" s="36" t="n">
-        <v>16.57</v>
+        <v>11.14</v>
       </c>
       <c r="H11" s="36" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="I11" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="J11" s="36" t="n">
+        <v>18</v>
+      </c>
+      <c r="K11" s="36" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="L11" s="36" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="M11" s="36" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="N11" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="O11" s="36" t="n">
+        <v>25.57</v>
+      </c>
+      <c r="P11" s="36" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="Q11" s="36" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="R11" s="36" t="n">
+        <v>22.57</v>
+      </c>
+      <c r="S11" s="36" t="n">
         <v>21.29</v>
       </c>
-      <c r="I11" s="36" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="J11" s="36" t="n">
-        <v>23.29</v>
-      </c>
-      <c r="K11" s="36" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="L11" s="36" t="n">
-        <v>22.43</v>
-      </c>
-      <c r="M11" s="36" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="N11" s="36" t="n">
-        <v>31.14</v>
-      </c>
-      <c r="O11" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="P11" s="36" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="Q11" s="36" t="n">
-        <v>31.29</v>
-      </c>
-      <c r="R11" s="36" t="n">
-        <v>36.14</v>
-      </c>
-      <c r="S11" s="36" t="n">
-        <v>31</v>
-      </c>
       <c r="T11" s="36" t="n">
-        <v>37.71</v>
+        <v>29.14</v>
       </c>
       <c r="U11" s="36" t="n">
-        <v>39.29</v>
+        <v>31.43</v>
       </c>
       <c r="V11" s="36" t="n">
-        <v>45.86</v>
+        <v>35.71</v>
       </c>
       <c r="W11" s="36" t="n">
-        <v>45.14</v>
+        <v>40.71</v>
       </c>
       <c r="X11" s="36" t="n">
-        <v>41.86</v>
+        <v>46.86</v>
       </c>
       <c r="Y11" s="36" t="n">
-        <v>48</v>
+        <v>44.71</v>
       </c>
       <c r="Z11" s="36" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="AA11" s="36" t="n">
-        <v>51.14</v>
+        <v>52.57</v>
       </c>
       <c r="AB11" s="36" t="n">
-        <v>44.14</v>
+        <v>42.86</v>
       </c>
       <c r="AC11" s="36" t="n">
-        <v>58</v>
+        <v>56.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="36" t="n">
-        <v>6.67</v>
+        <v>8.43</v>
       </c>
       <c r="E12" s="36" t="n">
-        <v>11.29</v>
+        <v>13.43</v>
       </c>
       <c r="F12" s="36" t="n">
-        <v>10.57</v>
+        <v>21.71</v>
       </c>
       <c r="G12" s="36" t="n">
-        <v>11.14</v>
+        <v>16.57</v>
       </c>
       <c r="H12" s="36" t="n">
-        <v>13.86</v>
+        <v>21.29</v>
       </c>
       <c r="I12" s="36" t="n">
-        <v>18</v>
+        <v>21.14</v>
       </c>
       <c r="J12" s="36" t="n">
-        <v>18</v>
+        <v>23.29</v>
       </c>
       <c r="K12" s="36" t="n">
-        <v>17.43</v>
+        <v>22.43</v>
       </c>
       <c r="L12" s="36" t="n">
-        <v>15.29</v>
+        <v>22.43</v>
       </c>
       <c r="M12" s="36" t="n">
-        <v>24.43</v>
+        <v>28.14</v>
       </c>
       <c r="N12" s="36" t="n">
-        <v>24.71</v>
+        <v>31.14</v>
       </c>
       <c r="O12" s="36" t="n">
-        <v>25.57</v>
+        <v>30</v>
       </c>
       <c r="P12" s="36" t="n">
-        <v>19.29</v>
+        <v>30.43</v>
       </c>
       <c r="Q12" s="36" t="n">
-        <v>25.43</v>
+        <v>31.29</v>
       </c>
       <c r="R12" s="36" t="n">
-        <v>22.57</v>
+        <v>36.14</v>
       </c>
       <c r="S12" s="36" t="n">
-        <v>21.29</v>
+        <v>31</v>
       </c>
       <c r="T12" s="36" t="n">
-        <v>29.14</v>
+        <v>37.71</v>
       </c>
       <c r="U12" s="36" t="n">
-        <v>31.43</v>
+        <v>39.29</v>
       </c>
       <c r="V12" s="36" t="n">
-        <v>35.71</v>
+        <v>45.86</v>
       </c>
       <c r="W12" s="36" t="n">
-        <v>40.71</v>
+        <v>45.14</v>
       </c>
       <c r="X12" s="36" t="n">
-        <v>46.86</v>
+        <v>41.86</v>
       </c>
       <c r="Y12" s="36" t="n">
-        <v>44.71</v>
+        <v>48</v>
       </c>
       <c r="Z12" s="36" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="AA12" s="36" t="n">
-        <v>52.57</v>
+        <v>51.14</v>
       </c>
       <c r="AB12" s="36" t="n">
-        <v>42.86</v>
+        <v>44.14</v>
       </c>
       <c r="AC12" s="36" t="n">
-        <v>53.5</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>33.14</v>
+        <v>38.57</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>30.71</v>
+        <v>34.29</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>31.14</v>
+        <v>37.86</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>40.29</v>
+        <v>42.86</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>38.71</v>
+        <v>40.71</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>43.14</v>
+        <v>45.43</v>
       </c>
       <c r="T13" s="36" t="n">
-        <v>37</v>
+        <v>44.57</v>
       </c>
       <c r="U13" s="36" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="V13" s="36" t="n">
         <v>46.29</v>
       </c>
-      <c r="V13" s="36" t="n">
-        <v>43.14</v>
-      </c>
       <c r="W13" s="36" t="n">
-        <v>36.86</v>
+        <v>43.71</v>
       </c>
       <c r="X13" s="36" t="n">
-        <v>33.43</v>
+        <v>49.57</v>
       </c>
       <c r="Y13" s="36" t="n">
-        <v>48</v>
+        <v>47.86</v>
       </c>
       <c r="Z13" s="36" t="n">
-        <v>39.86</v>
+        <v>46</v>
       </c>
       <c r="AA13" s="36" t="n">
-        <v>37.14</v>
+        <v>45.14</v>
       </c>
       <c r="AB13" s="36" t="n">
-        <v>41.14</v>
+        <v>47.71</v>
       </c>
       <c r="AC13" s="36" t="n">
-        <v>43.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>8</v>
+        <v>12.14</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>13.14</v>
+        <v>16.57</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>19.43</v>
+        <v>21</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>26.43</v>
+        <v>20.29</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>32.29</v>
+        <v>28.57</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>31.29</v>
+        <v>24.14</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>33.57</v>
+        <v>27.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>40</v>
+        <v>28.14</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>42.43</v>
+        <v>28.86</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>38.57</v>
+        <v>33.14</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>34.29</v>
+        <v>30.71</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>37.86</v>
+        <v>31.14</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>42.86</v>
+        <v>40.29</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>40.71</v>
+        <v>38.71</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>45.43</v>
+        <v>43.14</v>
       </c>
       <c r="T14" s="36" t="n">
-        <v>44.57</v>
+        <v>37</v>
       </c>
       <c r="U14" s="36" t="n">
-        <v>55.29</v>
+        <v>46.29</v>
       </c>
       <c r="V14" s="36" t="n">
-        <v>46.29</v>
+        <v>43.14</v>
       </c>
       <c r="W14" s="36" t="n">
-        <v>43.71</v>
+        <v>36.86</v>
       </c>
       <c r="X14" s="36" t="n">
-        <v>49.57</v>
+        <v>33.43</v>
       </c>
       <c r="Y14" s="36" t="n">
-        <v>47.86</v>
+        <v>48</v>
       </c>
       <c r="Z14" s="36" t="n">
-        <v>46</v>
+        <v>39.86</v>
       </c>
       <c r="AA14" s="36" t="n">
-        <v>45.14</v>
+        <v>37.14</v>
       </c>
       <c r="AB14" s="36" t="n">
-        <v>47.71</v>
+        <v>41.14</v>
       </c>
       <c r="AC14" s="36" t="n">
-        <v>42.5</v>
+        <v>45.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="E15" s="36" t="n">
-        <v>7.14</v>
+        <v>6.43</v>
       </c>
       <c r="F15" s="36" t="n">
-        <v>13.43</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G15" s="36" t="n">
-        <v>12.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H15" s="36" t="n">
-        <v>14.43</v>
+        <v>14</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>19</v>
+        <v>17.14</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>21.14</v>
+        <v>16.14</v>
       </c>
       <c r="K15" s="36" t="n">
         <v>18.57</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>16.57</v>
+        <v>16.14</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>14.71</v>
+        <v>21.71</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>19.14</v>
+        <v>20.86</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>18</v>
+        <v>20.86</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>15.29</v>
+        <v>21.86</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>15.29</v>
+        <v>28.71</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>18.71</v>
+        <v>24.71</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>18</v>
+        <v>24.57</v>
       </c>
       <c r="T15" s="36" t="n">
         <v>25.29</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>28.86</v>
+        <v>26.71</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>24</v>
+        <v>27.57</v>
       </c>
       <c r="W15" s="36" t="n">
-        <v>29.29</v>
+        <v>28.29</v>
       </c>
       <c r="X15" s="36" t="n">
-        <v>31.71</v>
+        <v>21.29</v>
       </c>
       <c r="Y15" s="36" t="n">
         <v>27</v>
       </c>
       <c r="Z15" s="36" t="n">
-        <v>23.83</v>
+        <v>25.43</v>
       </c>
       <c r="AA15" s="36" t="n">
-        <v>34.71</v>
+        <v>30.29</v>
       </c>
       <c r="AB15" s="36" t="n">
-        <v>35.86</v>
+        <v>28.57</v>
       </c>
       <c r="AC15" s="36" t="n">
-        <v>38.5</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G16" s="36" t="n">
         <v>3.33</v>
       </c>
-      <c r="E16" s="36" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F16" s="36" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="G16" s="36" t="n">
-        <v>9.140000000000001</v>
-      </c>
       <c r="H16" s="36" t="n">
-        <v>14</v>
+        <v>11.71</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>17.14</v>
+        <v>17.57</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>16.14</v>
+        <v>20.43</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>18.57</v>
+        <v>21.71</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>16.14</v>
+        <v>15</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>21.71</v>
+        <v>22.71</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>20.86</v>
+        <v>22.43</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>20.86</v>
+        <v>20.14</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>21.86</v>
+        <v>15.71</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>28.71</v>
+        <v>19.43</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>24.71</v>
+        <v>20.29</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>24.57</v>
+        <v>22.29</v>
       </c>
       <c r="T16" s="36" t="n">
-        <v>25.29</v>
+        <v>21.29</v>
       </c>
       <c r="U16" s="36" t="n">
-        <v>26.71</v>
+        <v>25.14</v>
       </c>
       <c r="V16" s="36" t="n">
-        <v>27.57</v>
+        <v>23.57</v>
       </c>
       <c r="W16" s="36" t="n">
-        <v>28.29</v>
+        <v>26.29</v>
       </c>
       <c r="X16" s="36" t="n">
-        <v>21.29</v>
+        <v>26.43</v>
       </c>
       <c r="Y16" s="36" t="n">
-        <v>27</v>
+        <v>23.71</v>
       </c>
       <c r="Z16" s="36" t="n">
-        <v>25.43</v>
+        <v>22</v>
       </c>
       <c r="AA16" s="36" t="n">
-        <v>30.29</v>
+        <v>29</v>
       </c>
       <c r="AB16" s="36" t="n">
-        <v>28.57</v>
+        <v>27.43</v>
       </c>
       <c r="AC16" s="36" t="n">
-        <v>37</v>
+        <v>35.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>0.5</v>
+        <v>13.43</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>3.33</v>
+        <v>12.71</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>11.71</v>
+        <v>14.43</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>17.57</v>
+        <v>19</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>20.43</v>
+        <v>21.14</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>21.71</v>
+        <v>18.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>15</v>
+        <v>16.57</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>22.71</v>
+        <v>14.71</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>22.43</v>
+        <v>19.14</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>20.14</v>
+        <v>18</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>15.71</v>
+        <v>15.29</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>19.43</v>
+        <v>15.29</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>20.29</v>
+        <v>18.71</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>22.29</v>
+        <v>18</v>
       </c>
       <c r="T17" s="36" t="n">
-        <v>21.29</v>
+        <v>25.29</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>25.14</v>
+        <v>28.86</v>
       </c>
       <c r="V17" s="36" t="n">
-        <v>23.57</v>
+        <v>24</v>
       </c>
       <c r="W17" s="36" t="n">
-        <v>26.29</v>
+        <v>29.29</v>
       </c>
       <c r="X17" s="36" t="n">
-        <v>26.43</v>
+        <v>31.71</v>
       </c>
       <c r="Y17" s="36" t="n">
-        <v>23.71</v>
+        <v>27</v>
       </c>
       <c r="Z17" s="36" t="n">
-        <v>22</v>
+        <v>23.83</v>
       </c>
       <c r="AA17" s="36" t="n">
-        <v>29</v>
+        <v>34.71</v>
       </c>
       <c r="AB17" s="36" t="n">
-        <v>27.43</v>
+        <v>35.86</v>
       </c>
       <c r="AC17" s="36" t="n">
-        <v>36.5</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -3820,7 +3820,7 @@
         <v>36</v>
       </c>
       <c r="AC18" s="36" t="n">
-        <v>30.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
@@ -3913,7 +3913,7 @@
         <v>25.29</v>
       </c>
       <c r="AC19" s="36" t="n">
-        <v>27</v>
+        <v>29.33</v>
       </c>
     </row>
     <row r="20">
@@ -4099,7 +4099,7 @@
         <v>26.71</v>
       </c>
       <c r="AC21" s="36" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -4192,7 +4192,7 @@
         <v>11.86</v>
       </c>
       <c r="AC22" s="36" t="n">
-        <v>13.5</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="23">
@@ -4285,7 +4285,7 @@
         <v>8.57</v>
       </c>
       <c r="AC23" s="36" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="24">
@@ -4833,7 +4833,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4926,7 +4926,7 @@
         <v>112485262</v>
       </c>
       <c r="AC6" s="40" t="n">
-        <v>36102608</v>
+        <v>51443913</v>
       </c>
     </row>
     <row r="7">
@@ -5019,7 +5019,7 @@
         <v>85896590</v>
       </c>
       <c r="AC7" s="40" t="n">
-        <v>25781878</v>
+        <v>40287183</v>
       </c>
     </row>
     <row r="8">
@@ -5112,7 +5112,7 @@
         <v>84653963</v>
       </c>
       <c r="AC8" s="40" t="n">
-        <v>26116333</v>
+        <v>32496298</v>
       </c>
     </row>
     <row r="9">
@@ -5205,7 +5205,7 @@
         <v>65287548</v>
       </c>
       <c r="AC9" s="40" t="n">
-        <v>16991595</v>
+        <v>23665128</v>
       </c>
     </row>
     <row r="10">
@@ -5298,658 +5298,658 @@
         <v>75839259</v>
       </c>
       <c r="AC10" s="40" t="n">
-        <v>17077316</v>
+        <v>22311749</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C11" s="40" t="n">
-        <v>251520</v>
+        <v>0</v>
       </c>
       <c r="D11" s="40" t="n">
-        <v>10351067</v>
+        <v>5092853</v>
       </c>
       <c r="E11" s="40" t="n">
-        <v>21091580</v>
+        <v>11100161</v>
       </c>
       <c r="F11" s="40" t="n">
-        <v>24243567</v>
+        <v>14612055</v>
       </c>
       <c r="G11" s="40" t="n">
-        <v>16381412</v>
+        <v>20638987</v>
       </c>
       <c r="H11" s="40" t="n">
-        <v>21591272</v>
+        <v>14061352</v>
       </c>
       <c r="I11" s="40" t="n">
-        <v>21904190</v>
+        <v>31599148</v>
       </c>
       <c r="J11" s="40" t="n">
-        <v>25438080</v>
+        <v>18747614</v>
       </c>
       <c r="K11" s="40" t="n">
-        <v>24614280</v>
+        <v>19576415</v>
       </c>
       <c r="L11" s="40" t="n">
-        <v>28889771</v>
+        <v>14226838</v>
       </c>
       <c r="M11" s="40" t="n">
-        <v>44250621</v>
+        <v>23197145</v>
       </c>
       <c r="N11" s="40" t="n">
-        <v>29608597</v>
+        <v>25790711</v>
       </c>
       <c r="O11" s="40" t="n">
-        <v>25219748</v>
+        <v>27856115</v>
       </c>
       <c r="P11" s="40" t="n">
-        <v>28515437</v>
+        <v>20981901</v>
       </c>
       <c r="Q11" s="40" t="n">
-        <v>35235670</v>
+        <v>25433123</v>
       </c>
       <c r="R11" s="40" t="n">
-        <v>38511490</v>
+        <v>19355230</v>
       </c>
       <c r="S11" s="40" t="n">
-        <v>40935998</v>
+        <v>24713836</v>
       </c>
       <c r="T11" s="40" t="n">
-        <v>58966944</v>
+        <v>20195634</v>
       </c>
       <c r="U11" s="40" t="n">
-        <v>43378746</v>
+        <v>32414171</v>
       </c>
       <c r="V11" s="40" t="n">
-        <v>67522298</v>
+        <v>42780769</v>
       </c>
       <c r="W11" s="40" t="n">
-        <v>44905121</v>
+        <v>36755122</v>
       </c>
       <c r="X11" s="40" t="n">
-        <v>43314104</v>
+        <v>38071365</v>
       </c>
       <c r="Y11" s="40" t="n">
-        <v>45152620</v>
+        <v>34397222</v>
       </c>
       <c r="Z11" s="40" t="n">
-        <v>33695914</v>
+        <v>32536036</v>
       </c>
       <c r="AA11" s="40" t="n">
-        <v>56470370</v>
+        <v>43911137</v>
       </c>
       <c r="AB11" s="40" t="n">
-        <v>36092667</v>
+        <v>33705532</v>
       </c>
       <c r="AC11" s="40" t="n">
-        <v>11890348</v>
+        <v>23345509</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="40" t="n">
-        <v>0</v>
+        <v>251520</v>
       </c>
       <c r="D12" s="40" t="n">
-        <v>5092853</v>
+        <v>10351067</v>
       </c>
       <c r="E12" s="40" t="n">
-        <v>11100161</v>
+        <v>21091580</v>
       </c>
       <c r="F12" s="40" t="n">
-        <v>14612055</v>
+        <v>24243567</v>
       </c>
       <c r="G12" s="40" t="n">
-        <v>20638987</v>
+        <v>16381412</v>
       </c>
       <c r="H12" s="40" t="n">
-        <v>14061352</v>
+        <v>21591272</v>
       </c>
       <c r="I12" s="40" t="n">
-        <v>31599148</v>
+        <v>21904190</v>
       </c>
       <c r="J12" s="40" t="n">
-        <v>18747614</v>
+        <v>25438080</v>
       </c>
       <c r="K12" s="40" t="n">
-        <v>19576415</v>
+        <v>24614280</v>
       </c>
       <c r="L12" s="40" t="n">
-        <v>14226838</v>
+        <v>28889771</v>
       </c>
       <c r="M12" s="40" t="n">
-        <v>23197145</v>
+        <v>44250621</v>
       </c>
       <c r="N12" s="40" t="n">
-        <v>25790711</v>
+        <v>29608597</v>
       </c>
       <c r="O12" s="40" t="n">
-        <v>27856115</v>
+        <v>25219748</v>
       </c>
       <c r="P12" s="40" t="n">
-        <v>20981901</v>
+        <v>28515437</v>
       </c>
       <c r="Q12" s="40" t="n">
-        <v>25433123</v>
+        <v>35235670</v>
       </c>
       <c r="R12" s="40" t="n">
-        <v>19355230</v>
+        <v>38511490</v>
       </c>
       <c r="S12" s="40" t="n">
-        <v>24713836</v>
+        <v>40935998</v>
       </c>
       <c r="T12" s="40" t="n">
-        <v>20195634</v>
+        <v>58966944</v>
       </c>
       <c r="U12" s="40" t="n">
-        <v>32414171</v>
+        <v>43378746</v>
       </c>
       <c r="V12" s="40" t="n">
-        <v>42780769</v>
+        <v>67522298</v>
       </c>
       <c r="W12" s="40" t="n">
-        <v>36755122</v>
+        <v>44905121</v>
       </c>
       <c r="X12" s="40" t="n">
-        <v>38071365</v>
+        <v>43314104</v>
       </c>
       <c r="Y12" s="40" t="n">
-        <v>34397222</v>
+        <v>45152620</v>
       </c>
       <c r="Z12" s="40" t="n">
-        <v>32536036</v>
+        <v>33695914</v>
       </c>
       <c r="AA12" s="40" t="n">
-        <v>43911137</v>
+        <v>56470370</v>
       </c>
       <c r="AB12" s="40" t="n">
-        <v>33705532</v>
+        <v>36092667</v>
       </c>
       <c r="AC12" s="40" t="n">
-        <v>14173463</v>
+        <v>16299181</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>35343350</v>
+        <v>38454971</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>51225290</v>
+        <v>42939312</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>36142612</v>
+        <v>43650420</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>47488940</v>
+        <v>53954095</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>44805002</v>
+        <v>48898463</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>43327432</v>
+        <v>48011655</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>39637968</v>
+        <v>72064876</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>55199920</v>
+        <v>59606189</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>50680631</v>
+        <v>50164748</v>
       </c>
       <c r="W13" s="40" t="n">
-        <v>50163008</v>
+        <v>46095774</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>38778399</v>
+        <v>57645111</v>
       </c>
       <c r="Y13" s="40" t="n">
-        <v>50996587</v>
+        <v>55172528</v>
       </c>
       <c r="Z13" s="40" t="n">
-        <v>42228986</v>
+        <v>47962010</v>
       </c>
       <c r="AA13" s="40" t="n">
-        <v>32767816</v>
+        <v>43352139</v>
       </c>
       <c r="AB13" s="40" t="n">
-        <v>44302861</v>
+        <v>49825299</v>
       </c>
       <c r="AC13" s="40" t="n">
-        <v>14626170</v>
+        <v>24181879</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>0</v>
+        <v>536260</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>8972650</v>
+        <v>14403556</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>18100396</v>
+        <v>16216832</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>23988817</v>
+        <v>32622053</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>22409732</v>
+        <v>23929705</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>37715520</v>
+        <v>37214538</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>35926824</v>
+        <v>25375430</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>39462393</v>
+        <v>31500087</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>51983942</v>
+        <v>28078687</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>58935844</v>
+        <v>34472458</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>38454971</v>
+        <v>35343350</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>42939312</v>
+        <v>51225290</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>43650420</v>
+        <v>36142612</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>53954095</v>
+        <v>47488940</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>48898463</v>
+        <v>44805002</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>48011655</v>
+        <v>43327432</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>72064876</v>
+        <v>39637968</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>59606189</v>
+        <v>55199920</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>50164748</v>
+        <v>50680631</v>
       </c>
       <c r="W14" s="40" t="n">
-        <v>46095774</v>
+        <v>50163008</v>
       </c>
       <c r="X14" s="40" t="n">
-        <v>57645111</v>
+        <v>38778399</v>
       </c>
       <c r="Y14" s="40" t="n">
-        <v>55172528</v>
+        <v>50996587</v>
       </c>
       <c r="Z14" s="40" t="n">
-        <v>47962010</v>
+        <v>42228986</v>
       </c>
       <c r="AA14" s="40" t="n">
-        <v>43352139</v>
+        <v>32767816</v>
       </c>
       <c r="AB14" s="40" t="n">
-        <v>49825299</v>
+        <v>44302861</v>
       </c>
       <c r="AC14" s="40" t="n">
-        <v>16790647</v>
+        <v>25720760</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>3337146</v>
+        <v>3249588</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>10420206</v>
+        <v>7305524</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>21387685</v>
+        <v>9575225</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>16050448</v>
+        <v>9264589</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>21568794</v>
+        <v>20692424</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>30845816</v>
+        <v>27565767</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>45285935</v>
+        <v>19138015</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>28941455</v>
+        <v>24912292</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>21801828</v>
+        <v>19068954</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>19628570</v>
+        <v>25387051</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>23276090</v>
+        <v>21008637</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>27906254</v>
+        <v>30862574</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>20822247</v>
+        <v>31820447</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>20014322</v>
+        <v>31875986</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>19159625</v>
+        <v>48358034</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>22535696</v>
+        <v>30000524</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>21412810</v>
+        <v>31150016</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>34881782</v>
+        <v>40688796</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>25904024</v>
+        <v>31752550</v>
       </c>
       <c r="W15" s="40" t="n">
-        <v>46961904</v>
+        <v>32778027</v>
       </c>
       <c r="X15" s="40" t="n">
-        <v>42299644</v>
+        <v>21331873</v>
       </c>
       <c r="Y15" s="40" t="n">
-        <v>32109759</v>
+        <v>28676177</v>
       </c>
       <c r="Z15" s="40" t="n">
-        <v>22714393</v>
+        <v>32596511</v>
       </c>
       <c r="AA15" s="40" t="n">
-        <v>52198815</v>
+        <v>53200913</v>
       </c>
       <c r="AB15" s="40" t="n">
-        <v>55359761</v>
+        <v>25830427</v>
       </c>
       <c r="AC15" s="40" t="n">
-        <v>16435620</v>
+        <v>16455479</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>7305524</v>
+        <v>0</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>9575225</v>
+        <v>363900</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>9264589</v>
+        <v>3736700</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>20692424</v>
+        <v>17796776</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>27565767</v>
+        <v>42724228</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>19138015</v>
+        <v>33036620</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>24912292</v>
+        <v>29649130</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>19068954</v>
+        <v>13949368</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>25387051</v>
+        <v>24539413</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>21008637</v>
+        <v>19087217</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>30862574</v>
+        <v>17139440</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>31820447</v>
+        <v>17746930</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>31875986</v>
+        <v>21437830</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>48358034</v>
+        <v>17616397</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>30000524</v>
+        <v>19360848</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>31150016</v>
+        <v>25377166</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>40688796</v>
+        <v>24702051</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>31752550</v>
+        <v>26856647</v>
       </c>
       <c r="W16" s="40" t="n">
-        <v>32778027</v>
+        <v>27122255</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>21331873</v>
+        <v>30650242</v>
       </c>
       <c r="Y16" s="40" t="n">
-        <v>28676177</v>
+        <v>21101547</v>
       </c>
       <c r="Z16" s="40" t="n">
-        <v>32596511</v>
+        <v>30037062</v>
       </c>
       <c r="AA16" s="40" t="n">
-        <v>53200913</v>
+        <v>22123372</v>
       </c>
       <c r="AB16" s="40" t="n">
-        <v>25830427</v>
+        <v>24293073</v>
       </c>
       <c r="AC16" s="40" t="n">
-        <v>10722343</v>
+        <v>14172473</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>363900</v>
+        <v>21387685</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>3736700</v>
+        <v>16050448</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>17796776</v>
+        <v>21568794</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>42724228</v>
+        <v>30845816</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>33036620</v>
+        <v>45285935</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>29649130</v>
+        <v>28941455</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>13949368</v>
+        <v>21801828</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>24539413</v>
+        <v>19628570</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>19087217</v>
+        <v>23276090</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>17139440</v>
+        <v>27906254</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>17746930</v>
+        <v>20822247</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>21437830</v>
+        <v>20014322</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>17616397</v>
+        <v>19159625</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>19360848</v>
+        <v>22535696</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>25377166</v>
+        <v>21412810</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>24702051</v>
+        <v>34881782</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>26856647</v>
+        <v>25904024</v>
       </c>
       <c r="W17" s="40" t="n">
-        <v>27122255</v>
+        <v>46961904</v>
       </c>
       <c r="X17" s="40" t="n">
-        <v>30650242</v>
+        <v>42299644</v>
       </c>
       <c r="Y17" s="40" t="n">
-        <v>21101547</v>
+        <v>32109759</v>
       </c>
       <c r="Z17" s="40" t="n">
-        <v>30037062</v>
+        <v>22714393</v>
       </c>
       <c r="AA17" s="40" t="n">
-        <v>22123372</v>
+        <v>52198815</v>
       </c>
       <c r="AB17" s="40" t="n">
-        <v>24293073</v>
+        <v>55359761</v>
       </c>
       <c r="AC17" s="40" t="n">
-        <v>7011183</v>
+        <v>22457510</v>
       </c>
     </row>
     <row r="18">
@@ -6042,7 +6042,7 @@
         <v>40583789</v>
       </c>
       <c r="AC18" s="40" t="n">
-        <v>7763544</v>
+        <v>14371441</v>
       </c>
     </row>
     <row r="19">
@@ -6135,7 +6135,7 @@
         <v>26706620</v>
       </c>
       <c r="AC19" s="40" t="n">
-        <v>9132340</v>
+        <v>15565376</v>
       </c>
     </row>
     <row r="20">
@@ -6228,7 +6228,7 @@
         <v>26957117</v>
       </c>
       <c r="AC20" s="40" t="n">
-        <v>5688188</v>
+        <v>7316345</v>
       </c>
     </row>
     <row r="21">
@@ -6321,7 +6321,7 @@
         <v>25453154</v>
       </c>
       <c r="AC21" s="40" t="n">
-        <v>5695487</v>
+        <v>9326241</v>
       </c>
     </row>
     <row r="22">
@@ -6414,7 +6414,7 @@
         <v>10380052</v>
       </c>
       <c r="AC22" s="40" t="n">
-        <v>2416727</v>
+        <v>4042207</v>
       </c>
     </row>
     <row r="23">
@@ -6507,7 +6507,7 @@
         <v>5406298</v>
       </c>
       <c r="AC23" s="40" t="n">
-        <v>1116550</v>
+        <v>1899290</v>
       </c>
     </row>
     <row r="24">
@@ -7055,7 +7055,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -7148,7 +7148,7 @@
         <v>7</v>
       </c>
       <c r="AC6" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="AC7" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -7334,7 +7334,7 @@
         <v>7</v>
       </c>
       <c r="AC8" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -7427,7 +7427,7 @@
         <v>7</v>
       </c>
       <c r="AC9" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -7520,25 +7520,25 @@
         <v>7</v>
       </c>
       <c r="AC10" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="35" t="inlineStr">
         <is>
-          <t>FRБХР-30</t>
+          <t>FRСМК-52</t>
         </is>
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Бухара</t>
+          <t>Рудаки</t>
         </is>
       </c>
       <c r="C11" s="42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>7</v>
@@ -7613,25 +7613,25 @@
         <v>7</v>
       </c>
       <c r="AC11" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-52</t>
+          <t>FRБХР-30</t>
         </is>
       </c>
       <c r="B12" s="35" t="inlineStr">
         <is>
-          <t>Рудаки</t>
+          <t>Бухара</t>
         </is>
       </c>
       <c r="C12" s="42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" s="42" t="n">
         <v>7</v>
@@ -7706,121 +7706,121 @@
         <v>7</v>
       </c>
       <c r="AC12" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z13" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC13" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC13" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" s="42" t="n">
         <v>7</v>
@@ -7883,7 +7883,7 @@
         <v>7</v>
       </c>
       <c r="Z14" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14" s="42" t="n">
         <v>7</v>
@@ -7892,25 +7892,25 @@
         <v>7</v>
       </c>
       <c r="AC14" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" s="42" t="n">
         <v>7</v>
@@ -7976,7 +7976,7 @@
         <v>7</v>
       </c>
       <c r="Z15" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15" s="42" t="n">
         <v>7</v>
@@ -7985,185 +7985,185 @@
         <v>7</v>
       </c>
       <c r="AC15" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC16" s="42" t="n">
         <v>3</v>
-      </c>
-      <c r="E16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="F16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC16" s="42" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E17" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F17" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y17" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z17" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="H17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y17" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z17" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="AA17" s="42" t="n">
         <v>7</v>
       </c>
@@ -8171,7 +8171,7 @@
         <v>7</v>
       </c>
       <c r="AC17" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -8264,7 +8264,7 @@
         <v>7</v>
       </c>
       <c r="AC18" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -8357,7 +8357,7 @@
         <v>7</v>
       </c>
       <c r="AC19" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -8450,7 +8450,7 @@
         <v>7</v>
       </c>
       <c r="AC20" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -8543,7 +8543,7 @@
         <v>7</v>
       </c>
       <c r="AC21" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -8636,7 +8636,7 @@
         <v>7</v>
       </c>
       <c r="AC22" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -8729,7 +8729,7 @@
         <v>7</v>
       </c>
       <c r="AC23" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2611,7 +2611,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2704,7 +2704,7 @@
         <v>123.71</v>
       </c>
       <c r="AC6" s="36" t="n">
-        <v>137.33</v>
+        <v>134.75</v>
       </c>
     </row>
     <row r="7">
@@ -2797,7 +2797,7 @@
         <v>79.29000000000001</v>
       </c>
       <c r="AC7" s="36" t="n">
-        <v>93.67</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="8">
@@ -2890,7 +2890,7 @@
         <v>89.86</v>
       </c>
       <c r="AC8" s="36" t="n">
-        <v>71.33</v>
+        <v>72.75</v>
       </c>
     </row>
     <row r="9">
@@ -2983,7 +2983,7 @@
         <v>61.86</v>
       </c>
       <c r="AC9" s="36" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -3076,7 +3076,7 @@
         <v>62.29</v>
       </c>
       <c r="AC10" s="36" t="n">
-        <v>59</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="11">
@@ -3169,7 +3169,7 @@
         <v>42.86</v>
       </c>
       <c r="AC11" s="36" t="n">
-        <v>56.33</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="12">
@@ -3262,7 +3262,7 @@
         <v>44.14</v>
       </c>
       <c r="AC12" s="36" t="n">
-        <v>53.33</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="13">
@@ -3355,7 +3355,7 @@
         <v>47.71</v>
       </c>
       <c r="AC13" s="36" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
@@ -3448,379 +3448,379 @@
         <v>41.14</v>
       </c>
       <c r="AC14" s="36" t="n">
-        <v>45.33</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="36" t="n">
         <v>3.33</v>
       </c>
-      <c r="E15" s="36" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="F15" s="36" t="n">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="G15" s="36" t="n">
-        <v>9.140000000000001</v>
-      </c>
       <c r="H15" s="36" t="n">
-        <v>14</v>
+        <v>11.71</v>
       </c>
       <c r="I15" s="36" t="n">
-        <v>17.14</v>
+        <v>17.57</v>
       </c>
       <c r="J15" s="36" t="n">
-        <v>16.14</v>
+        <v>20.43</v>
       </c>
       <c r="K15" s="36" t="n">
-        <v>18.57</v>
+        <v>21.71</v>
       </c>
       <c r="L15" s="36" t="n">
-        <v>16.14</v>
+        <v>15</v>
       </c>
       <c r="M15" s="36" t="n">
-        <v>21.71</v>
+        <v>22.71</v>
       </c>
       <c r="N15" s="36" t="n">
-        <v>20.86</v>
+        <v>22.43</v>
       </c>
       <c r="O15" s="36" t="n">
-        <v>20.86</v>
+        <v>20.14</v>
       </c>
       <c r="P15" s="36" t="n">
-        <v>21.86</v>
+        <v>15.71</v>
       </c>
       <c r="Q15" s="36" t="n">
-        <v>28.71</v>
+        <v>19.43</v>
       </c>
       <c r="R15" s="36" t="n">
-        <v>24.71</v>
+        <v>20.29</v>
       </c>
       <c r="S15" s="36" t="n">
-        <v>24.57</v>
+        <v>22.29</v>
       </c>
       <c r="T15" s="36" t="n">
-        <v>25.29</v>
+        <v>21.29</v>
       </c>
       <c r="U15" s="36" t="n">
-        <v>26.71</v>
+        <v>25.14</v>
       </c>
       <c r="V15" s="36" t="n">
-        <v>27.57</v>
+        <v>23.57</v>
       </c>
       <c r="W15" s="36" t="n">
-        <v>28.29</v>
+        <v>26.29</v>
       </c>
       <c r="X15" s="36" t="n">
-        <v>21.29</v>
+        <v>26.43</v>
       </c>
       <c r="Y15" s="36" t="n">
-        <v>27</v>
+        <v>23.71</v>
       </c>
       <c r="Z15" s="36" t="n">
-        <v>25.43</v>
+        <v>22</v>
       </c>
       <c r="AA15" s="36" t="n">
-        <v>30.29</v>
+        <v>29</v>
       </c>
       <c r="AB15" s="36" t="n">
-        <v>28.57</v>
+        <v>27.43</v>
       </c>
       <c r="AC15" s="36" t="n">
-        <v>35.67</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" s="36" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="F16" s="36" t="n">
-        <v>0.5</v>
+        <v>13.43</v>
       </c>
       <c r="G16" s="36" t="n">
-        <v>3.33</v>
+        <v>12.71</v>
       </c>
       <c r="H16" s="36" t="n">
-        <v>11.71</v>
+        <v>14.43</v>
       </c>
       <c r="I16" s="36" t="n">
-        <v>17.57</v>
+        <v>19</v>
       </c>
       <c r="J16" s="36" t="n">
-        <v>20.43</v>
+        <v>21.14</v>
       </c>
       <c r="K16" s="36" t="n">
-        <v>21.71</v>
+        <v>18.57</v>
       </c>
       <c r="L16" s="36" t="n">
-        <v>15</v>
+        <v>16.57</v>
       </c>
       <c r="M16" s="36" t="n">
-        <v>22.71</v>
+        <v>14.71</v>
       </c>
       <c r="N16" s="36" t="n">
-        <v>22.43</v>
+        <v>19.14</v>
       </c>
       <c r="O16" s="36" t="n">
-        <v>20.14</v>
+        <v>18</v>
       </c>
       <c r="P16" s="36" t="n">
-        <v>15.71</v>
+        <v>15.29</v>
       </c>
       <c r="Q16" s="36" t="n">
-        <v>19.43</v>
+        <v>15.29</v>
       </c>
       <c r="R16" s="36" t="n">
-        <v>20.29</v>
+        <v>18.71</v>
       </c>
       <c r="S16" s="36" t="n">
-        <v>22.29</v>
+        <v>18</v>
       </c>
       <c r="T16" s="36" t="n">
-        <v>21.29</v>
+        <v>25.29</v>
       </c>
       <c r="U16" s="36" t="n">
-        <v>25.14</v>
+        <v>28.86</v>
       </c>
       <c r="V16" s="36" t="n">
-        <v>23.57</v>
+        <v>24</v>
       </c>
       <c r="W16" s="36" t="n">
-        <v>26.29</v>
+        <v>29.29</v>
       </c>
       <c r="X16" s="36" t="n">
-        <v>26.43</v>
+        <v>31.71</v>
       </c>
       <c r="Y16" s="36" t="n">
-        <v>23.71</v>
+        <v>27</v>
       </c>
       <c r="Z16" s="36" t="n">
-        <v>22</v>
+        <v>23.83</v>
       </c>
       <c r="AA16" s="36" t="n">
-        <v>29</v>
+        <v>34.71</v>
       </c>
       <c r="AB16" s="36" t="n">
-        <v>27.43</v>
+        <v>35.86</v>
       </c>
       <c r="AC16" s="36" t="n">
-        <v>35.67</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="D17" s="36" t="n">
-        <v>3</v>
+        <v>9.43</v>
       </c>
       <c r="E17" s="36" t="n">
-        <v>7.14</v>
+        <v>12.43</v>
       </c>
       <c r="F17" s="36" t="n">
-        <v>13.43</v>
+        <v>13.29</v>
       </c>
       <c r="G17" s="36" t="n">
-        <v>12.71</v>
+        <v>14.71</v>
       </c>
       <c r="H17" s="36" t="n">
-        <v>14.43</v>
+        <v>17</v>
       </c>
       <c r="I17" s="36" t="n">
-        <v>19</v>
+        <v>19.71</v>
       </c>
       <c r="J17" s="36" t="n">
-        <v>21.14</v>
+        <v>17.71</v>
       </c>
       <c r="K17" s="36" t="n">
-        <v>18.57</v>
+        <v>19.57</v>
       </c>
       <c r="L17" s="36" t="n">
-        <v>16.57</v>
+        <v>24.14</v>
       </c>
       <c r="M17" s="36" t="n">
-        <v>14.71</v>
+        <v>27.57</v>
       </c>
       <c r="N17" s="36" t="n">
-        <v>19.14</v>
+        <v>24.43</v>
       </c>
       <c r="O17" s="36" t="n">
-        <v>18</v>
+        <v>27.29</v>
       </c>
       <c r="P17" s="36" t="n">
-        <v>15.29</v>
+        <v>26.57</v>
       </c>
       <c r="Q17" s="36" t="n">
-        <v>15.29</v>
+        <v>25.57</v>
       </c>
       <c r="R17" s="36" t="n">
-        <v>18.71</v>
+        <v>29</v>
       </c>
       <c r="S17" s="36" t="n">
-        <v>18</v>
+        <v>27.71</v>
       </c>
       <c r="T17" s="36" t="n">
-        <v>25.29</v>
+        <v>32.57</v>
       </c>
       <c r="U17" s="36" t="n">
-        <v>28.86</v>
+        <v>31.57</v>
       </c>
       <c r="V17" s="36" t="n">
-        <v>24</v>
+        <v>29.57</v>
       </c>
       <c r="W17" s="36" t="n">
-        <v>29.29</v>
+        <v>29.86</v>
       </c>
       <c r="X17" s="36" t="n">
-        <v>31.71</v>
+        <v>32</v>
       </c>
       <c r="Y17" s="36" t="n">
-        <v>27</v>
+        <v>32.14</v>
       </c>
       <c r="Z17" s="36" t="n">
-        <v>23.83</v>
+        <v>27.14</v>
       </c>
       <c r="AA17" s="36" t="n">
-        <v>34.71</v>
+        <v>36.43</v>
       </c>
       <c r="AB17" s="36" t="n">
-        <v>35.86</v>
+        <v>36</v>
       </c>
       <c r="AC17" s="36" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="D18" s="36" t="n">
-        <v>9.43</v>
+        <v>3.33</v>
       </c>
       <c r="E18" s="36" t="n">
-        <v>12.43</v>
+        <v>6.43</v>
       </c>
       <c r="F18" s="36" t="n">
-        <v>13.29</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G18" s="36" t="n">
-        <v>14.71</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H18" s="36" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I18" s="36" t="n">
-        <v>19.71</v>
+        <v>17.14</v>
       </c>
       <c r="J18" s="36" t="n">
-        <v>17.71</v>
+        <v>16.14</v>
       </c>
       <c r="K18" s="36" t="n">
-        <v>19.57</v>
+        <v>18.57</v>
       </c>
       <c r="L18" s="36" t="n">
-        <v>24.14</v>
+        <v>16.14</v>
       </c>
       <c r="M18" s="36" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="N18" s="36" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="O18" s="36" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="P18" s="36" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="Q18" s="36" t="n">
+        <v>28.71</v>
+      </c>
+      <c r="R18" s="36" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="S18" s="36" t="n">
+        <v>24.57</v>
+      </c>
+      <c r="T18" s="36" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="U18" s="36" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="V18" s="36" t="n">
         <v>27.57</v>
       </c>
-      <c r="N18" s="36" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="O18" s="36" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="P18" s="36" t="n">
-        <v>26.57</v>
-      </c>
-      <c r="Q18" s="36" t="n">
-        <v>25.57</v>
-      </c>
-      <c r="R18" s="36" t="n">
-        <v>29</v>
-      </c>
-      <c r="S18" s="36" t="n">
-        <v>27.71</v>
-      </c>
-      <c r="T18" s="36" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="U18" s="36" t="n">
-        <v>31.57</v>
-      </c>
-      <c r="V18" s="36" t="n">
-        <v>29.57</v>
-      </c>
       <c r="W18" s="36" t="n">
-        <v>29.86</v>
+        <v>28.29</v>
       </c>
       <c r="X18" s="36" t="n">
-        <v>32</v>
+        <v>21.29</v>
       </c>
       <c r="Y18" s="36" t="n">
-        <v>32.14</v>
+        <v>27</v>
       </c>
       <c r="Z18" s="36" t="n">
-        <v>27.14</v>
+        <v>25.43</v>
       </c>
       <c r="AA18" s="36" t="n">
-        <v>36.43</v>
+        <v>30.29</v>
       </c>
       <c r="AB18" s="36" t="n">
-        <v>36</v>
+        <v>28.57</v>
       </c>
       <c r="AC18" s="36" t="n">
-        <v>34</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="19">
@@ -3913,7 +3913,7 @@
         <v>25.29</v>
       </c>
       <c r="AC19" s="36" t="n">
-        <v>29.33</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="20">
@@ -4006,7 +4006,7 @@
         <v>35.14</v>
       </c>
       <c r="AC20" s="36" t="n">
-        <v>23</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="21">
@@ -4099,7 +4099,7 @@
         <v>26.71</v>
       </c>
       <c r="AC21" s="36" t="n">
-        <v>20</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="22">
@@ -4192,7 +4192,7 @@
         <v>11.86</v>
       </c>
       <c r="AC22" s="36" t="n">
-        <v>16.67</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="23">
@@ -4285,7 +4285,7 @@
         <v>8.57</v>
       </c>
       <c r="AC23" s="36" t="n">
-        <v>7.33</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="24">
@@ -4833,7 +4833,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -4926,7 +4926,7 @@
         <v>112485262</v>
       </c>
       <c r="AC6" s="40" t="n">
-        <v>51443913</v>
+        <v>64583791</v>
       </c>
     </row>
     <row r="7">
@@ -5019,7 +5019,7 @@
         <v>85896590</v>
       </c>
       <c r="AC7" s="40" t="n">
-        <v>40287183</v>
+        <v>56724253</v>
       </c>
     </row>
     <row r="8">
@@ -5112,7 +5112,7 @@
         <v>84653963</v>
       </c>
       <c r="AC8" s="40" t="n">
-        <v>32496298</v>
+        <v>40708742</v>
       </c>
     </row>
     <row r="9">
@@ -5205,7 +5205,7 @@
         <v>65287548</v>
       </c>
       <c r="AC9" s="40" t="n">
-        <v>23665128</v>
+        <v>27033448</v>
       </c>
     </row>
     <row r="10">
@@ -5298,7 +5298,7 @@
         <v>75839259</v>
       </c>
       <c r="AC10" s="40" t="n">
-        <v>22311749</v>
+        <v>29193079</v>
       </c>
     </row>
     <row r="11">
@@ -5391,7 +5391,7 @@
         <v>33705532</v>
       </c>
       <c r="AC11" s="40" t="n">
-        <v>23345509</v>
+        <v>26385279</v>
       </c>
     </row>
     <row r="12">
@@ -5484,7 +5484,7 @@
         <v>36092667</v>
       </c>
       <c r="AC12" s="40" t="n">
-        <v>16299181</v>
+        <v>28081481</v>
       </c>
     </row>
     <row r="13">
@@ -5577,7 +5577,7 @@
         <v>49825299</v>
       </c>
       <c r="AC13" s="40" t="n">
-        <v>24181879</v>
+        <v>28921839</v>
       </c>
     </row>
     <row r="14">
@@ -5670,379 +5670,379 @@
         <v>44302861</v>
       </c>
       <c r="AC14" s="40" t="n">
-        <v>25720760</v>
+        <v>32688200</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C15" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="40" t="n">
-        <v>3249588</v>
+        <v>0</v>
       </c>
       <c r="E15" s="40" t="n">
-        <v>7305524</v>
+        <v>0</v>
       </c>
       <c r="F15" s="40" t="n">
-        <v>9575225</v>
+        <v>363900</v>
       </c>
       <c r="G15" s="40" t="n">
-        <v>9264589</v>
+        <v>3736700</v>
       </c>
       <c r="H15" s="40" t="n">
-        <v>20692424</v>
+        <v>17796776</v>
       </c>
       <c r="I15" s="40" t="n">
-        <v>27565767</v>
+        <v>42724228</v>
       </c>
       <c r="J15" s="40" t="n">
-        <v>19138015</v>
+        <v>33036620</v>
       </c>
       <c r="K15" s="40" t="n">
-        <v>24912292</v>
+        <v>29649130</v>
       </c>
       <c r="L15" s="40" t="n">
-        <v>19068954</v>
+        <v>13949368</v>
       </c>
       <c r="M15" s="40" t="n">
-        <v>25387051</v>
+        <v>24539413</v>
       </c>
       <c r="N15" s="40" t="n">
-        <v>21008637</v>
+        <v>19087217</v>
       </c>
       <c r="O15" s="40" t="n">
-        <v>30862574</v>
+        <v>17139440</v>
       </c>
       <c r="P15" s="40" t="n">
-        <v>31820447</v>
+        <v>17746930</v>
       </c>
       <c r="Q15" s="40" t="n">
-        <v>31875986</v>
+        <v>21437830</v>
       </c>
       <c r="R15" s="40" t="n">
-        <v>48358034</v>
+        <v>17616397</v>
       </c>
       <c r="S15" s="40" t="n">
-        <v>30000524</v>
+        <v>19360848</v>
       </c>
       <c r="T15" s="40" t="n">
-        <v>31150016</v>
+        <v>25377166</v>
       </c>
       <c r="U15" s="40" t="n">
-        <v>40688796</v>
+        <v>24702051</v>
       </c>
       <c r="V15" s="40" t="n">
-        <v>31752550</v>
+        <v>26856647</v>
       </c>
       <c r="W15" s="40" t="n">
-        <v>32778027</v>
+        <v>27122255</v>
       </c>
       <c r="X15" s="40" t="n">
-        <v>21331873</v>
+        <v>30650242</v>
       </c>
       <c r="Y15" s="40" t="n">
-        <v>28676177</v>
+        <v>21101547</v>
       </c>
       <c r="Z15" s="40" t="n">
-        <v>32596511</v>
+        <v>30037062</v>
       </c>
       <c r="AA15" s="40" t="n">
-        <v>53200913</v>
+        <v>22123372</v>
       </c>
       <c r="AB15" s="40" t="n">
-        <v>25830427</v>
+        <v>24293073</v>
       </c>
       <c r="AC15" s="40" t="n">
-        <v>16455479</v>
+        <v>18313823</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="40" t="n">
-        <v>0</v>
+        <v>3337146</v>
       </c>
       <c r="E16" s="40" t="n">
-        <v>0</v>
+        <v>10420206</v>
       </c>
       <c r="F16" s="40" t="n">
-        <v>363900</v>
+        <v>21387685</v>
       </c>
       <c r="G16" s="40" t="n">
-        <v>3736700</v>
+        <v>16050448</v>
       </c>
       <c r="H16" s="40" t="n">
-        <v>17796776</v>
+        <v>21568794</v>
       </c>
       <c r="I16" s="40" t="n">
-        <v>42724228</v>
+        <v>30845816</v>
       </c>
       <c r="J16" s="40" t="n">
-        <v>33036620</v>
+        <v>45285935</v>
       </c>
       <c r="K16" s="40" t="n">
-        <v>29649130</v>
+        <v>28941455</v>
       </c>
       <c r="L16" s="40" t="n">
-        <v>13949368</v>
+        <v>21801828</v>
       </c>
       <c r="M16" s="40" t="n">
-        <v>24539413</v>
+        <v>19628570</v>
       </c>
       <c r="N16" s="40" t="n">
-        <v>19087217</v>
+        <v>23276090</v>
       </c>
       <c r="O16" s="40" t="n">
-        <v>17139440</v>
+        <v>27906254</v>
       </c>
       <c r="P16" s="40" t="n">
-        <v>17746930</v>
+        <v>20822247</v>
       </c>
       <c r="Q16" s="40" t="n">
-        <v>21437830</v>
+        <v>20014322</v>
       </c>
       <c r="R16" s="40" t="n">
-        <v>17616397</v>
+        <v>19159625</v>
       </c>
       <c r="S16" s="40" t="n">
-        <v>19360848</v>
+        <v>22535696</v>
       </c>
       <c r="T16" s="40" t="n">
-        <v>25377166</v>
+        <v>21412810</v>
       </c>
       <c r="U16" s="40" t="n">
-        <v>24702051</v>
+        <v>34881782</v>
       </c>
       <c r="V16" s="40" t="n">
-        <v>26856647</v>
+        <v>25904024</v>
       </c>
       <c r="W16" s="40" t="n">
-        <v>27122255</v>
+        <v>46961904</v>
       </c>
       <c r="X16" s="40" t="n">
-        <v>30650242</v>
+        <v>42299644</v>
       </c>
       <c r="Y16" s="40" t="n">
-        <v>21101547</v>
+        <v>32109759</v>
       </c>
       <c r="Z16" s="40" t="n">
-        <v>30037062</v>
+        <v>22714393</v>
       </c>
       <c r="AA16" s="40" t="n">
-        <v>22123372</v>
+        <v>52198815</v>
       </c>
       <c r="AB16" s="40" t="n">
-        <v>24293073</v>
+        <v>55359761</v>
       </c>
       <c r="AC16" s="40" t="n">
-        <v>14172473</v>
+        <v>32010030</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="40" t="n">
-        <v>0</v>
+        <v>475871</v>
       </c>
       <c r="D17" s="40" t="n">
-        <v>3337146</v>
+        <v>11884771</v>
       </c>
       <c r="E17" s="40" t="n">
-        <v>10420206</v>
+        <v>10651216</v>
       </c>
       <c r="F17" s="40" t="n">
-        <v>21387685</v>
+        <v>13882033</v>
       </c>
       <c r="G17" s="40" t="n">
-        <v>16050448</v>
+        <v>17812948</v>
       </c>
       <c r="H17" s="40" t="n">
-        <v>21568794</v>
+        <v>17331854</v>
       </c>
       <c r="I17" s="40" t="n">
-        <v>30845816</v>
+        <v>26294756</v>
       </c>
       <c r="J17" s="40" t="n">
-        <v>45285935</v>
+        <v>24196222</v>
       </c>
       <c r="K17" s="40" t="n">
-        <v>28941455</v>
+        <v>22122847</v>
       </c>
       <c r="L17" s="40" t="n">
-        <v>21801828</v>
+        <v>31914115</v>
       </c>
       <c r="M17" s="40" t="n">
-        <v>19628570</v>
+        <v>32069521</v>
       </c>
       <c r="N17" s="40" t="n">
-        <v>23276090</v>
+        <v>38287475</v>
       </c>
       <c r="O17" s="40" t="n">
-        <v>27906254</v>
+        <v>28283704</v>
       </c>
       <c r="P17" s="40" t="n">
-        <v>20822247</v>
+        <v>27334091</v>
       </c>
       <c r="Q17" s="40" t="n">
-        <v>20014322</v>
+        <v>36312415</v>
       </c>
       <c r="R17" s="40" t="n">
-        <v>19159625</v>
+        <v>39333565</v>
       </c>
       <c r="S17" s="40" t="n">
-        <v>22535696</v>
+        <v>28566119</v>
       </c>
       <c r="T17" s="40" t="n">
-        <v>21412810</v>
+        <v>40387845</v>
       </c>
       <c r="U17" s="40" t="n">
-        <v>34881782</v>
+        <v>39744111</v>
       </c>
       <c r="V17" s="40" t="n">
-        <v>25904024</v>
+        <v>31477917</v>
       </c>
       <c r="W17" s="40" t="n">
-        <v>46961904</v>
+        <v>29910767</v>
       </c>
       <c r="X17" s="40" t="n">
-        <v>42299644</v>
+        <v>44620606</v>
       </c>
       <c r="Y17" s="40" t="n">
-        <v>32109759</v>
+        <v>35679497</v>
       </c>
       <c r="Z17" s="40" t="n">
-        <v>22714393</v>
+        <v>25102609</v>
       </c>
       <c r="AA17" s="40" t="n">
-        <v>52198815</v>
+        <v>39000780</v>
       </c>
       <c r="AB17" s="40" t="n">
-        <v>55359761</v>
+        <v>40583789</v>
       </c>
       <c r="AC17" s="40" t="n">
-        <v>22457510</v>
+        <v>19069611</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="40" t="n">
-        <v>475871</v>
+        <v>0</v>
       </c>
       <c r="D18" s="40" t="n">
-        <v>11884771</v>
+        <v>3249588</v>
       </c>
       <c r="E18" s="40" t="n">
-        <v>10651216</v>
+        <v>7305524</v>
       </c>
       <c r="F18" s="40" t="n">
-        <v>13882033</v>
+        <v>9575225</v>
       </c>
       <c r="G18" s="40" t="n">
-        <v>17812948</v>
+        <v>9264589</v>
       </c>
       <c r="H18" s="40" t="n">
-        <v>17331854</v>
+        <v>20692424</v>
       </c>
       <c r="I18" s="40" t="n">
-        <v>26294756</v>
+        <v>27565767</v>
       </c>
       <c r="J18" s="40" t="n">
-        <v>24196222</v>
+        <v>19138015</v>
       </c>
       <c r="K18" s="40" t="n">
-        <v>22122847</v>
+        <v>24912292</v>
       </c>
       <c r="L18" s="40" t="n">
-        <v>31914115</v>
+        <v>19068954</v>
       </c>
       <c r="M18" s="40" t="n">
-        <v>32069521</v>
+        <v>25387051</v>
       </c>
       <c r="N18" s="40" t="n">
-        <v>38287475</v>
+        <v>21008637</v>
       </c>
       <c r="O18" s="40" t="n">
-        <v>28283704</v>
+        <v>30862574</v>
       </c>
       <c r="P18" s="40" t="n">
-        <v>27334091</v>
+        <v>31820447</v>
       </c>
       <c r="Q18" s="40" t="n">
-        <v>36312415</v>
+        <v>31875986</v>
       </c>
       <c r="R18" s="40" t="n">
-        <v>39333565</v>
+        <v>48358034</v>
       </c>
       <c r="S18" s="40" t="n">
-        <v>28566119</v>
+        <v>30000524</v>
       </c>
       <c r="T18" s="40" t="n">
-        <v>40387845</v>
+        <v>31150016</v>
       </c>
       <c r="U18" s="40" t="n">
-        <v>39744111</v>
+        <v>40688796</v>
       </c>
       <c r="V18" s="40" t="n">
-        <v>31477917</v>
+        <v>31752550</v>
       </c>
       <c r="W18" s="40" t="n">
-        <v>29910767</v>
+        <v>32778027</v>
       </c>
       <c r="X18" s="40" t="n">
-        <v>44620606</v>
+        <v>21331873</v>
       </c>
       <c r="Y18" s="40" t="n">
-        <v>35679497</v>
+        <v>28676177</v>
       </c>
       <c r="Z18" s="40" t="n">
-        <v>25102609</v>
+        <v>32596511</v>
       </c>
       <c r="AA18" s="40" t="n">
-        <v>39000780</v>
+        <v>53200913</v>
       </c>
       <c r="AB18" s="40" t="n">
-        <v>40583789</v>
+        <v>25830427</v>
       </c>
       <c r="AC18" s="40" t="n">
-        <v>14371441</v>
+        <v>18883472</v>
       </c>
     </row>
     <row r="19">
@@ -6135,7 +6135,7 @@
         <v>26706620</v>
       </c>
       <c r="AC19" s="40" t="n">
-        <v>15565376</v>
+        <v>16383436</v>
       </c>
     </row>
     <row r="20">
@@ -6228,7 +6228,7 @@
         <v>26957117</v>
       </c>
       <c r="AC20" s="40" t="n">
-        <v>7316345</v>
+        <v>10339305</v>
       </c>
     </row>
     <row r="21">
@@ -6321,7 +6321,7 @@
         <v>25453154</v>
       </c>
       <c r="AC21" s="40" t="n">
-        <v>9326241</v>
+        <v>13561751</v>
       </c>
     </row>
     <row r="22">
@@ -6414,7 +6414,7 @@
         <v>10380052</v>
       </c>
       <c r="AC22" s="40" t="n">
-        <v>4042207</v>
+        <v>5099427</v>
       </c>
     </row>
     <row r="23">
@@ -6507,7 +6507,7 @@
         <v>5406298</v>
       </c>
       <c r="AC23" s="40" t="n">
-        <v>1899290</v>
+        <v>3285548</v>
       </c>
     </row>
     <row r="24">
@@ -7055,7 +7055,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -7148,7 +7148,7 @@
         <v>7</v>
       </c>
       <c r="AC6" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="AC7" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -7334,7 +7334,7 @@
         <v>7</v>
       </c>
       <c r="AC8" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -7427,7 +7427,7 @@
         <v>7</v>
       </c>
       <c r="AC9" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -7520,7 +7520,7 @@
         <v>7</v>
       </c>
       <c r="AC10" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -7613,7 +7613,7 @@
         <v>7</v>
       </c>
       <c r="AC11" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -7706,7 +7706,7 @@
         <v>7</v>
       </c>
       <c r="AC12" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -7799,7 +7799,7 @@
         <v>7</v>
       </c>
       <c r="AC13" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -7892,34 +7892,34 @@
         <v>7</v>
       </c>
       <c r="AC14" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-10</t>
+          <t>FRСМК-53</t>
         </is>
       </c>
       <c r="B15" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Мустакилик</t>
+          <t>Андижанская</t>
         </is>
       </c>
       <c r="C15" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F15" s="42" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G15" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H15" s="42" t="n">
         <v>7</v>
@@ -7985,92 +7985,92 @@
         <v>7</v>
       </c>
       <c r="AC15" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="35" t="inlineStr">
         <is>
-          <t>FRСМК-53</t>
+          <t>FRБУК-2</t>
         </is>
       </c>
       <c r="B16" s="35" t="inlineStr">
         <is>
-          <t>Андижанская</t>
+          <t>Бука</t>
         </is>
       </c>
       <c r="C16" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E16" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F16" s="42" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y16" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z16" s="42" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y16" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z16" s="42" t="n">
-        <v>7</v>
-      </c>
       <c r="AA16" s="42" t="n">
         <v>7</v>
       </c>
@@ -8078,25 +8078,25 @@
         <v>7</v>
       </c>
       <c r="AC16" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="35" t="inlineStr">
         <is>
-          <t>FRБУК-2</t>
+          <t>FRГАЗ-4</t>
         </is>
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Бука</t>
+          <t>Газалкент</t>
         </is>
       </c>
       <c r="C17" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D17" s="42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>7</v>
@@ -8162,7 +8162,7 @@
         <v>7</v>
       </c>
       <c r="Z17" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA17" s="42" t="n">
         <v>7</v>
@@ -8171,25 +8171,25 @@
         <v>7</v>
       </c>
       <c r="AC17" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="35" t="inlineStr">
         <is>
-          <t>FRГАЗ-4</t>
+          <t>FRАЛМ-10</t>
         </is>
       </c>
       <c r="B18" s="35" t="inlineStr">
         <is>
-          <t>Газалкент</t>
+          <t>Алмалык Мустакилик</t>
         </is>
       </c>
       <c r="C18" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" s="42" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>7</v>
@@ -8264,7 +8264,7 @@
         <v>7</v>
       </c>
       <c r="AC18" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -8357,7 +8357,7 @@
         <v>7</v>
       </c>
       <c r="AC19" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -8450,7 +8450,7 @@
         <v>7</v>
       </c>
       <c r="AC20" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -8543,7 +8543,7 @@
         <v>7</v>
       </c>
       <c r="AC21" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -8636,7 +8636,7 @@
         <v>7</v>
       </c>
       <c r="AC22" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -8729,7 +8729,7 @@
         <v>7</v>
       </c>
       <c r="AC23" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">

--- a/Эталон_ПВЗ.xlsx
+++ b/Эталон_ПВЗ.xlsx
@@ -2611,7 +2611,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2704,7 +2704,7 @@
         <v>123.71</v>
       </c>
       <c r="AC6" s="36" t="n">
-        <v>134.75</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="7">
@@ -2797,7 +2797,7 @@
         <v>79.29000000000001</v>
       </c>
       <c r="AC7" s="36" t="n">
-        <v>93.75</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -2890,7 +2890,7 @@
         <v>89.86</v>
       </c>
       <c r="AC8" s="36" t="n">
-        <v>72.75</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2983,7 +2983,7 @@
         <v>61.86</v>
       </c>
       <c r="AC9" s="36" t="n">
-        <v>61</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="10">
@@ -3076,7 +3076,7 @@
         <v>62.29</v>
       </c>
       <c r="AC10" s="36" t="n">
-        <v>58.5</v>
+        <v>57.4</v>
       </c>
     </row>
     <row r="11">
@@ -3169,7 +3169,7 @@
         <v>42.86</v>
       </c>
       <c r="AC11" s="36" t="n">
-        <v>52.75</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="12">
@@ -3262,193 +3262,193 @@
         <v>44.14</v>
       </c>
       <c r="AC12" s="36" t="n">
-        <v>52.5</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="E13" s="36" t="n">
-        <v>8</v>
+        <v>12.14</v>
       </c>
       <c r="F13" s="36" t="n">
-        <v>13.14</v>
+        <v>16.57</v>
       </c>
       <c r="G13" s="36" t="n">
-        <v>19.43</v>
+        <v>21</v>
       </c>
       <c r="H13" s="36" t="n">
-        <v>26.43</v>
+        <v>20.29</v>
       </c>
       <c r="I13" s="36" t="n">
-        <v>32.29</v>
+        <v>28.57</v>
       </c>
       <c r="J13" s="36" t="n">
-        <v>31.29</v>
+        <v>24.14</v>
       </c>
       <c r="K13" s="36" t="n">
-        <v>33.57</v>
+        <v>27.57</v>
       </c>
       <c r="L13" s="36" t="n">
-        <v>40</v>
+        <v>28.14</v>
       </c>
       <c r="M13" s="36" t="n">
-        <v>42.43</v>
+        <v>28.86</v>
       </c>
       <c r="N13" s="36" t="n">
-        <v>38.57</v>
+        <v>33.14</v>
       </c>
       <c r="O13" s="36" t="n">
-        <v>34.29</v>
+        <v>30.71</v>
       </c>
       <c r="P13" s="36" t="n">
-        <v>37.86</v>
+        <v>31.14</v>
       </c>
       <c r="Q13" s="36" t="n">
-        <v>42.86</v>
+        <v>40.29</v>
       </c>
       <c r="R13" s="36" t="n">
-        <v>40.71</v>
+        <v>38.71</v>
       </c>
       <c r="S13" s="36" t="n">
-        <v>45.43</v>
+        <v>43.14</v>
       </c>
       <c r="T13" s="36" t="n">
-        <v>44.57</v>
+        <v>37</v>
       </c>
       <c r="U13" s="36" t="n">
-        <v>55.29</v>
+        <v>46.29</v>
       </c>
       <c r="V13" s="36" t="n">
-        <v>46.29</v>
+        <v>43.14</v>
       </c>
       <c r="W13" s="36" t="n">
-        <v>43.71</v>
+        <v>36.86</v>
       </c>
       <c r="X13" s="36" t="n">
-        <v>49.57</v>
+        <v>33.43</v>
       </c>
       <c r="Y13" s="36" t="n">
-        <v>47.86</v>
+        <v>48</v>
       </c>
       <c r="Z13" s="36" t="n">
-        <v>46</v>
+        <v>39.86</v>
       </c>
       <c r="AA13" s="36" t="n">
-        <v>45.14</v>
+        <v>37.14</v>
       </c>
       <c r="AB13" s="36" t="n">
-        <v>47.71</v>
+        <v>41.14</v>
       </c>
       <c r="AC13" s="36" t="n">
-        <v>43</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C14" s="36" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="E14" s="36" t="n">
-        <v>12.14</v>
+        <v>8</v>
       </c>
       <c r="F14" s="36" t="n">
-        <v>16.57</v>
+        <v>13.14</v>
       </c>
       <c r="G14" s="36" t="n">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="H14" s="36" t="n">
-        <v>20.29</v>
+        <v>26.43</v>
       </c>
       <c r="I14" s="36" t="n">
-        <v>28.57</v>
+        <v>32.29</v>
       </c>
       <c r="J14" s="36" t="n">
-        <v>24.14</v>
+        <v>31.29</v>
       </c>
       <c r="K14" s="36" t="n">
-        <v>27.57</v>
+        <v>33.57</v>
       </c>
       <c r="L14" s="36" t="n">
-        <v>28.14</v>
+        <v>40</v>
       </c>
       <c r="M14" s="36" t="n">
-        <v>28.86</v>
+        <v>42.43</v>
       </c>
       <c r="N14" s="36" t="n">
-        <v>33.14</v>
+        <v>38.57</v>
       </c>
       <c r="O14" s="36" t="n">
-        <v>30.71</v>
+        <v>34.29</v>
       </c>
       <c r="P14" s="36" t="n">
-        <v>31.14</v>
+        <v>37.86</v>
       </c>
       <c r="Q14" s="36" t="n">
-        <v>40.29</v>
+        <v>42.86</v>
       </c>
       <c r="R14" s="36" t="n">
-        <v>38.71</v>
+        <v>40.71</v>
       </c>
       <c r="S14" s="36" t="n">
-        <v>43.14</v>
+        <v>45.43</v>
       </c>
       <c r="T14" s="36" t="n">
-        <v>37</v>
+        <v>44.57</v>
       </c>
       <c r="U14" s="36" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="V14" s="36" t="n">
         <v>46.29</v>
       </c>
-      <c r="V14" s="36" t="n">
-        <v>43.14</v>
-      </c>
       <c r="W14" s="36" t="n">
-        <v>36.86</v>
+        <v>43.71</v>
       </c>
       <c r="X14" s="36" t="n">
-        <v>33.43</v>
+        <v>49.57</v>
       </c>
       <c r="Y14" s="36" t="n">
-        <v>48</v>
+        <v>47.86</v>
       </c>
       <c r="Z14" s="36" t="n">
-        <v>39.86</v>
+        <v>46</v>
       </c>
       <c r="AA14" s="36" t="n">
-        <v>37.14</v>
+        <v>45.14</v>
       </c>
       <c r="AB14" s="36" t="n">
-        <v>41.14</v>
+        <v>47.71</v>
       </c>
       <c r="AC14" s="36" t="n">
-        <v>41.25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -3541,7 +3541,7 @@
         <v>27.43</v>
       </c>
       <c r="AC15" s="36" t="n">
-        <v>36.75</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="16">
@@ -3634,7 +3634,7 @@
         <v>35.86</v>
       </c>
       <c r="AC16" s="36" t="n">
-        <v>36.25</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="17">
@@ -3727,7 +3727,7 @@
         <v>36</v>
       </c>
       <c r="AC17" s="36" t="n">
-        <v>34</v>
+        <v>32.6</v>
       </c>
     </row>
     <row r="18">
@@ -3820,193 +3820,193 @@
         <v>28.57</v>
       </c>
       <c r="AC18" s="36" t="n">
-        <v>32.5</v>
+        <v>31.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E19" s="36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F19" s="36" t="n">
-        <v>3.25</v>
+        <v>14.43</v>
       </c>
       <c r="G19" s="36" t="n">
-        <v>8</v>
+        <v>11.86</v>
       </c>
       <c r="H19" s="36" t="n">
-        <v>9.43</v>
+        <v>18</v>
       </c>
       <c r="I19" s="36" t="n">
-        <v>12.71</v>
+        <v>19.14</v>
       </c>
       <c r="J19" s="36" t="n">
-        <v>11.57</v>
+        <v>21</v>
       </c>
       <c r="K19" s="36" t="n">
-        <v>9.859999999999999</v>
+        <v>23.43</v>
       </c>
       <c r="L19" s="36" t="n">
-        <v>11.86</v>
+        <v>20.43</v>
       </c>
       <c r="M19" s="36" t="n">
-        <v>9.710000000000001</v>
+        <v>24.57</v>
       </c>
       <c r="N19" s="36" t="n">
-        <v>19</v>
+        <v>24.14</v>
       </c>
       <c r="O19" s="36" t="n">
-        <v>19.57</v>
+        <v>24.43</v>
       </c>
       <c r="P19" s="36" t="n">
-        <v>16.86</v>
+        <v>22</v>
       </c>
       <c r="Q19" s="36" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="R19" s="36" t="n">
-        <v>14.71</v>
+        <v>18.43</v>
       </c>
       <c r="S19" s="36" t="n">
-        <v>15.86</v>
+        <v>24.71</v>
       </c>
       <c r="T19" s="36" t="n">
-        <v>25</v>
+        <v>27.57</v>
       </c>
       <c r="U19" s="36" t="n">
-        <v>27.29</v>
+        <v>30</v>
       </c>
       <c r="V19" s="36" t="n">
-        <v>17.14</v>
+        <v>28.57</v>
       </c>
       <c r="W19" s="36" t="n">
-        <v>22.14</v>
+        <v>30.14</v>
       </c>
       <c r="X19" s="36" t="n">
-        <v>23.43</v>
+        <v>34.43</v>
       </c>
       <c r="Y19" s="36" t="n">
-        <v>24.14</v>
+        <v>33.43</v>
       </c>
       <c r="Z19" s="36" t="n">
-        <v>16.43</v>
+        <v>32</v>
       </c>
       <c r="AA19" s="36" t="n">
-        <v>25.29</v>
+        <v>31.29</v>
       </c>
       <c r="AB19" s="36" t="n">
-        <v>25.29</v>
+        <v>35.14</v>
       </c>
       <c r="AC19" s="36" t="n">
-        <v>24.5</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>9.140000000000001</v>
+        <v>0</v>
       </c>
       <c r="E20" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>14.43</v>
+        <v>3.25</v>
       </c>
       <c r="G20" s="36" t="n">
+        <v>8</v>
+      </c>
+      <c r="H20" s="36" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="I20" s="36" t="n">
+        <v>12.71</v>
+      </c>
+      <c r="J20" s="36" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="K20" s="36" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="L20" s="36" t="n">
         <v>11.86</v>
       </c>
-      <c r="H20" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="I20" s="36" t="n">
-        <v>19.14</v>
-      </c>
-      <c r="J20" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="K20" s="36" t="n">
+      <c r="M20" s="36" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="N20" s="36" t="n">
+        <v>19</v>
+      </c>
+      <c r="O20" s="36" t="n">
+        <v>19.57</v>
+      </c>
+      <c r="P20" s="36" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="Q20" s="36" t="n">
+        <v>15</v>
+      </c>
+      <c r="R20" s="36" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="S20" s="36" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="T20" s="36" t="n">
+        <v>25</v>
+      </c>
+      <c r="U20" s="36" t="n">
+        <v>27.29</v>
+      </c>
+      <c r="V20" s="36" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="W20" s="36" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="X20" s="36" t="n">
         <v>23.43</v>
       </c>
-      <c r="L20" s="36" t="n">
-        <v>20.43</v>
-      </c>
-      <c r="M20" s="36" t="n">
-        <v>24.57</v>
-      </c>
-      <c r="N20" s="36" t="n">
+      <c r="Y20" s="36" t="n">
         <v>24.14</v>
       </c>
-      <c r="O20" s="36" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="P20" s="36" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q20" s="36" t="n">
-        <v>23</v>
-      </c>
-      <c r="R20" s="36" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="S20" s="36" t="n">
-        <v>24.71</v>
-      </c>
-      <c r="T20" s="36" t="n">
-        <v>27.57</v>
-      </c>
-      <c r="U20" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="V20" s="36" t="n">
-        <v>28.57</v>
-      </c>
-      <c r="W20" s="36" t="n">
-        <v>30.14</v>
-      </c>
-      <c r="X20" s="36" t="n">
-        <v>34.43</v>
-      </c>
-      <c r="Y20" s="36" t="n">
-        <v>33.43</v>
-      </c>
       <c r="Z20" s="36" t="n">
-        <v>32</v>
+        <v>16.43</v>
       </c>
       <c r="AA20" s="36" t="n">
-        <v>31.29</v>
+        <v>25.29</v>
       </c>
       <c r="AB20" s="36" t="n">
-        <v>35.14</v>
+        <v>25.29</v>
       </c>
       <c r="AC20" s="36" t="n">
-        <v>24.25</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="21">
@@ -4099,7 +4099,7 @@
         <v>26.71</v>
       </c>
       <c r="AC21" s="36" t="n">
-        <v>23.75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -4192,7 +4192,7 @@
         <v>11.86</v>
       </c>
       <c r="AC22" s="36" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="23">
@@ -4285,7 +4285,7 @@
         <v>8.57</v>
       </c>
       <c r="AC23" s="36" t="n">
-        <v>11.25</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -4833,7 +4833,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -4926,7 +4926,7 @@
         <v>112485262</v>
       </c>
       <c r="AC6" s="40" t="n">
-        <v>64583791</v>
+        <v>74172928</v>
       </c>
     </row>
     <row r="7">
@@ -5019,7 +5019,7 @@
         <v>85896590</v>
       </c>
       <c r="AC7" s="40" t="n">
-        <v>56724253</v>
+        <v>72623264</v>
       </c>
     </row>
     <row r="8">
@@ -5112,7 +5112,7 @@
         <v>84653963</v>
       </c>
       <c r="AC8" s="40" t="n">
-        <v>40708742</v>
+        <v>53588541</v>
       </c>
     </row>
     <row r="9">
@@ -5205,7 +5205,7 @@
         <v>65287548</v>
       </c>
       <c r="AC9" s="40" t="n">
-        <v>27033448</v>
+        <v>35102438</v>
       </c>
     </row>
     <row r="10">
@@ -5298,7 +5298,7 @@
         <v>75839259</v>
       </c>
       <c r="AC10" s="40" t="n">
-        <v>29193079</v>
+        <v>38820104</v>
       </c>
     </row>
     <row r="11">
@@ -5391,7 +5391,7 @@
         <v>33705532</v>
       </c>
       <c r="AC11" s="40" t="n">
-        <v>26385279</v>
+        <v>30882755</v>
       </c>
     </row>
     <row r="12">
@@ -5484,193 +5484,193 @@
         <v>36092667</v>
       </c>
       <c r="AC12" s="40" t="n">
-        <v>28081481</v>
+        <v>38351616</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
-        <v>0</v>
+        <v>536260</v>
       </c>
       <c r="E13" s="40" t="n">
-        <v>8972650</v>
+        <v>14403556</v>
       </c>
       <c r="F13" s="40" t="n">
-        <v>18100396</v>
+        <v>16216832</v>
       </c>
       <c r="G13" s="40" t="n">
-        <v>23988817</v>
+        <v>32622053</v>
       </c>
       <c r="H13" s="40" t="n">
-        <v>22409732</v>
+        <v>23929705</v>
       </c>
       <c r="I13" s="40" t="n">
-        <v>37715520</v>
+        <v>37214538</v>
       </c>
       <c r="J13" s="40" t="n">
-        <v>35926824</v>
+        <v>25375430</v>
       </c>
       <c r="K13" s="40" t="n">
-        <v>39462393</v>
+        <v>31500087</v>
       </c>
       <c r="L13" s="40" t="n">
-        <v>51983942</v>
+        <v>28078687</v>
       </c>
       <c r="M13" s="40" t="n">
-        <v>58935844</v>
+        <v>34472458</v>
       </c>
       <c r="N13" s="40" t="n">
-        <v>38454971</v>
+        <v>35343350</v>
       </c>
       <c r="O13" s="40" t="n">
-        <v>42939312</v>
+        <v>51225290</v>
       </c>
       <c r="P13" s="40" t="n">
-        <v>43650420</v>
+        <v>36142612</v>
       </c>
       <c r="Q13" s="40" t="n">
-        <v>53954095</v>
+        <v>47488940</v>
       </c>
       <c r="R13" s="40" t="n">
-        <v>48898463</v>
+        <v>44805002</v>
       </c>
       <c r="S13" s="40" t="n">
-        <v>48011655</v>
+        <v>43327432</v>
       </c>
       <c r="T13" s="40" t="n">
-        <v>72064876</v>
+        <v>39637968</v>
       </c>
       <c r="U13" s="40" t="n">
-        <v>59606189</v>
+        <v>55199920</v>
       </c>
       <c r="V13" s="40" t="n">
-        <v>50164748</v>
+        <v>50680631</v>
       </c>
       <c r="W13" s="40" t="n">
-        <v>46095774</v>
+        <v>50163008</v>
       </c>
       <c r="X13" s="40" t="n">
-        <v>57645111</v>
+        <v>38778399</v>
       </c>
       <c r="Y13" s="40" t="n">
-        <v>55172528</v>
+        <v>50996587</v>
       </c>
       <c r="Z13" s="40" t="n">
-        <v>47962010</v>
+        <v>42228986</v>
       </c>
       <c r="AA13" s="40" t="n">
-        <v>43352139</v>
+        <v>32767816</v>
       </c>
       <c r="AB13" s="40" t="n">
-        <v>49825299</v>
+        <v>44302861</v>
       </c>
       <c r="AC13" s="40" t="n">
-        <v>28921839</v>
+        <v>42214800</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C14" s="40" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="40" t="n">
-        <v>536260</v>
+        <v>0</v>
       </c>
       <c r="E14" s="40" t="n">
-        <v>14403556</v>
+        <v>8972650</v>
       </c>
       <c r="F14" s="40" t="n">
-        <v>16216832</v>
+        <v>18100396</v>
       </c>
       <c r="G14" s="40" t="n">
-        <v>32622053</v>
+        <v>23988817</v>
       </c>
       <c r="H14" s="40" t="n">
-        <v>23929705</v>
+        <v>22409732</v>
       </c>
       <c r="I14" s="40" t="n">
-        <v>37214538</v>
+        <v>37715520</v>
       </c>
       <c r="J14" s="40" t="n">
-        <v>25375430</v>
+        <v>35926824</v>
       </c>
       <c r="K14" s="40" t="n">
-        <v>31500087</v>
+        <v>39462393</v>
       </c>
       <c r="L14" s="40" t="n">
-        <v>28078687</v>
+        <v>51983942</v>
       </c>
       <c r="M14" s="40" t="n">
-        <v>34472458</v>
+        <v>58935844</v>
       </c>
       <c r="N14" s="40" t="n">
-        <v>35343350</v>
+        <v>38454971</v>
       </c>
       <c r="O14" s="40" t="n">
-        <v>51225290</v>
+        <v>42939312</v>
       </c>
       <c r="P14" s="40" t="n">
-        <v>36142612</v>
+        <v>43650420</v>
       </c>
       <c r="Q14" s="40" t="n">
-        <v>47488940</v>
+        <v>53954095</v>
       </c>
       <c r="R14" s="40" t="n">
-        <v>44805002</v>
+        <v>48898463</v>
       </c>
       <c r="S14" s="40" t="n">
-        <v>43327432</v>
+        <v>48011655</v>
       </c>
       <c r="T14" s="40" t="n">
-        <v>39637968</v>
+        <v>72064876</v>
       </c>
       <c r="U14" s="40" t="n">
-        <v>55199920</v>
+        <v>59606189</v>
       </c>
       <c r="V14" s="40" t="n">
-        <v>50680631</v>
+        <v>50164748</v>
       </c>
       <c r="W14" s="40" t="n">
-        <v>50163008</v>
+        <v>46095774</v>
       </c>
       <c r="X14" s="40" t="n">
-        <v>38778399</v>
+        <v>57645111</v>
       </c>
       <c r="Y14" s="40" t="n">
-        <v>50996587</v>
+        <v>55172528</v>
       </c>
       <c r="Z14" s="40" t="n">
-        <v>42228986</v>
+        <v>47962010</v>
       </c>
       <c r="AA14" s="40" t="n">
-        <v>32767816</v>
+        <v>43352139</v>
       </c>
       <c r="AB14" s="40" t="n">
-        <v>44302861</v>
+        <v>49825299</v>
       </c>
       <c r="AC14" s="40" t="n">
-        <v>32688200</v>
+        <v>33591929</v>
       </c>
     </row>
     <row r="15">
@@ -5763,7 +5763,7 @@
         <v>24293073</v>
       </c>
       <c r="AC15" s="40" t="n">
-        <v>18313823</v>
+        <v>22468073</v>
       </c>
     </row>
     <row r="16">
@@ -5856,7 +5856,7 @@
         <v>55359761</v>
       </c>
       <c r="AC16" s="40" t="n">
-        <v>32010030</v>
+        <v>35804660</v>
       </c>
     </row>
     <row r="17">
@@ -5949,7 +5949,7 @@
         <v>40583789</v>
       </c>
       <c r="AC17" s="40" t="n">
-        <v>19069611</v>
+        <v>22292961</v>
       </c>
     </row>
     <row r="18">
@@ -6042,193 +6042,193 @@
         <v>25830427</v>
       </c>
       <c r="AC18" s="40" t="n">
-        <v>18883472</v>
+        <v>21475651</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="40" t="n">
-        <v>0</v>
+        <v>530238</v>
       </c>
       <c r="D19" s="40" t="n">
-        <v>0</v>
+        <v>8544625</v>
       </c>
       <c r="E19" s="40" t="n">
-        <v>0</v>
+        <v>8387478</v>
       </c>
       <c r="F19" s="40" t="n">
-        <v>1324510</v>
+        <v>10570508</v>
       </c>
       <c r="G19" s="40" t="n">
-        <v>10311989</v>
+        <v>11896580</v>
       </c>
       <c r="H19" s="40" t="n">
-        <v>19934535</v>
+        <v>19614352</v>
       </c>
       <c r="I19" s="40" t="n">
-        <v>13536614</v>
+        <v>20966317</v>
       </c>
       <c r="J19" s="40" t="n">
-        <v>22187720</v>
+        <v>20073400</v>
       </c>
       <c r="K19" s="40" t="n">
-        <v>11732010</v>
+        <v>23801493</v>
       </c>
       <c r="L19" s="40" t="n">
-        <v>21143100</v>
+        <v>27940611</v>
       </c>
       <c r="M19" s="40" t="n">
-        <v>14330970</v>
+        <v>27893929</v>
       </c>
       <c r="N19" s="40" t="n">
-        <v>38267409</v>
+        <v>29635773</v>
       </c>
       <c r="O19" s="40" t="n">
-        <v>46351274</v>
+        <v>19554230</v>
       </c>
       <c r="P19" s="40" t="n">
-        <v>37105387</v>
+        <v>23848495</v>
       </c>
       <c r="Q19" s="40" t="n">
-        <v>19868191</v>
+        <v>24194638</v>
       </c>
       <c r="R19" s="40" t="n">
-        <v>15153480</v>
+        <v>20330094</v>
       </c>
       <c r="S19" s="40" t="n">
-        <v>19277087</v>
+        <v>26044199</v>
       </c>
       <c r="T19" s="40" t="n">
-        <v>34209889</v>
+        <v>24608772</v>
       </c>
       <c r="U19" s="40" t="n">
-        <v>33260760</v>
+        <v>28079726</v>
       </c>
       <c r="V19" s="40" t="n">
-        <v>23559262</v>
+        <v>20968052</v>
       </c>
       <c r="W19" s="40" t="n">
-        <v>29206004</v>
+        <v>29501132</v>
       </c>
       <c r="X19" s="40" t="n">
-        <v>26477239</v>
+        <v>30624981</v>
       </c>
       <c r="Y19" s="40" t="n">
-        <v>31392938</v>
+        <v>28071639</v>
       </c>
       <c r="Z19" s="40" t="n">
-        <v>14752034</v>
+        <v>21021583</v>
       </c>
       <c r="AA19" s="40" t="n">
-        <v>27021110</v>
+        <v>29229414</v>
       </c>
       <c r="AB19" s="40" t="n">
-        <v>26706620</v>
+        <v>26957117</v>
       </c>
       <c r="AC19" s="40" t="n">
-        <v>16383436</v>
+        <v>14161920</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="40" t="n">
-        <v>530238</v>
+        <v>0</v>
       </c>
       <c r="D20" s="40" t="n">
-        <v>8544625</v>
+        <v>0</v>
       </c>
       <c r="E20" s="40" t="n">
-        <v>8387478</v>
+        <v>0</v>
       </c>
       <c r="F20" s="40" t="n">
-        <v>10570508</v>
+        <v>1324510</v>
       </c>
       <c r="G20" s="40" t="n">
-        <v>11896580</v>
+        <v>10311989</v>
       </c>
       <c r="H20" s="40" t="n">
-        <v>19614352</v>
+        <v>19934535</v>
       </c>
       <c r="I20" s="40" t="n">
-        <v>20966317</v>
+        <v>13536614</v>
       </c>
       <c r="J20" s="40" t="n">
-        <v>20073400</v>
+        <v>22187720</v>
       </c>
       <c r="K20" s="40" t="n">
-        <v>23801493</v>
+        <v>11732010</v>
       </c>
       <c r="L20" s="40" t="n">
-        <v>27940611</v>
+        <v>21143100</v>
       </c>
       <c r="M20" s="40" t="n">
-        <v>27893929</v>
+        <v>14330970</v>
       </c>
       <c r="N20" s="40" t="n">
-        <v>29635773</v>
+        <v>38267409</v>
       </c>
       <c r="O20" s="40" t="n">
-        <v>19554230</v>
+        <v>46351274</v>
       </c>
       <c r="P20" s="40" t="n">
-        <v>23848495</v>
+        <v>37105387</v>
       </c>
       <c r="Q20" s="40" t="n">
-        <v>24194638</v>
+        <v>19868191</v>
       </c>
       <c r="R20" s="40" t="n">
-        <v>20330094</v>
+        <v>15153480</v>
       </c>
       <c r="S20" s="40" t="n">
-        <v>26044199</v>
+        <v>19277087</v>
       </c>
       <c r="T20" s="40" t="n">
-        <v>24608772</v>
+        <v>34209889</v>
       </c>
       <c r="U20" s="40" t="n">
-        <v>28079726</v>
+        <v>33260760</v>
       </c>
       <c r="V20" s="40" t="n">
-        <v>20968052</v>
+        <v>23559262</v>
       </c>
       <c r="W20" s="40" t="n">
-        <v>29501132</v>
+        <v>29206004</v>
       </c>
       <c r="X20" s="40" t="n">
-        <v>30624981</v>
+        <v>26477239</v>
       </c>
       <c r="Y20" s="40" t="n">
-        <v>28071639</v>
+        <v>31392938</v>
       </c>
       <c r="Z20" s="40" t="n">
-        <v>21021583</v>
+        <v>14752034</v>
       </c>
       <c r="AA20" s="40" t="n">
-        <v>29229414</v>
+        <v>27021110</v>
       </c>
       <c r="AB20" s="40" t="n">
-        <v>26957117</v>
+        <v>26706620</v>
       </c>
       <c r="AC20" s="40" t="n">
-        <v>10339305</v>
+        <v>20754416</v>
       </c>
     </row>
     <row r="21">
@@ -6321,7 +6321,7 @@
         <v>25453154</v>
       </c>
       <c r="AC21" s="40" t="n">
-        <v>13561751</v>
+        <v>18354076</v>
       </c>
     </row>
     <row r="22">
@@ -6414,7 +6414,7 @@
         <v>10380052</v>
       </c>
       <c r="AC22" s="40" t="n">
-        <v>5099427</v>
+        <v>6555417</v>
       </c>
     </row>
     <row r="23">
@@ -6507,7 +6507,7 @@
         <v>5406298</v>
       </c>
       <c r="AC23" s="40" t="n">
-        <v>3285548</v>
+        <v>3434370</v>
       </c>
     </row>
     <row r="24">
@@ -7055,7 +7055,7 @@
         <v>7</v>
       </c>
       <c r="AC5" s="34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -7148,7 +7148,7 @@
         <v>7</v>
       </c>
       <c r="AC6" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -7241,7 +7241,7 @@
         <v>7</v>
       </c>
       <c r="AC7" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -7334,7 +7334,7 @@
         <v>7</v>
       </c>
       <c r="AC8" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -7427,7 +7427,7 @@
         <v>7</v>
       </c>
       <c r="AC9" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -7520,7 +7520,7 @@
         <v>7</v>
       </c>
       <c r="AC10" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -7613,7 +7613,7 @@
         <v>7</v>
       </c>
       <c r="AC11" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -7706,121 +7706,121 @@
         <v>7</v>
       </c>
       <c r="AC12" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-293</t>
+          <t>FRАЛМ-9</t>
         </is>
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>Кургантепа</t>
+          <t>Алмалык Амир Т</t>
         </is>
       </c>
       <c r="C13" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="O13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="P13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="R13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="V13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="W13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="X13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB13" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC13" s="42" t="n">
         <v>5</v>
-      </c>
-      <c r="F13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="I13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="K13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="L13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="M13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="N13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="O13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="S13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="T13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="U13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="V13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="W13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="X13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z13" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB13" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC13" s="42" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="35" t="inlineStr">
         <is>
-          <t>FRАЛМ-9</t>
+          <t>FRТАШ-293</t>
         </is>
       </c>
       <c r="B14" s="35" t="inlineStr">
         <is>
-          <t>Алмалык Амир Т</t>
+          <t>Кургантепа</t>
         </is>
       </c>
       <c r="C14" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" s="42" t="n">
         <v>7</v>
@@ -7883,7 +7883,7 @@
         <v>7</v>
       </c>
       <c r="Z14" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA14" s="42" t="n">
         <v>7</v>
@@ -7892,7 +7892,7 @@
         <v>7</v>
       </c>
       <c r="AC14" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -7985,7 +7985,7 @@
         <v>7</v>
       </c>
       <c r="AC15" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -8078,7 +8078,7 @@
         <v>7</v>
       </c>
       <c r="AC16" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -8171,7 +8171,7 @@
         <v>7</v>
       </c>
       <c r="AC17" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -8264,31 +8264,31 @@
         <v>7</v>
       </c>
       <c r="AC18" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="35" t="inlineStr">
         <is>
-          <t>FRПСК-2</t>
+          <t>FRТАШ-308</t>
         </is>
       </c>
       <c r="B19" s="35" t="inlineStr">
         <is>
-          <t>Пскент</t>
+          <t>Янгиюнусабад</t>
         </is>
       </c>
       <c r="C19" s="42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E19" s="42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="42" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G19" s="42" t="n">
         <v>7</v>
@@ -8348,7 +8348,7 @@
         <v>7</v>
       </c>
       <c r="Z19" s="42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA19" s="42" t="n">
         <v>7</v>
@@ -8357,31 +8357,31 @@
         <v>7</v>
       </c>
       <c r="AC19" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="35" t="inlineStr">
         <is>
-          <t>FRТАШ-308</t>
+          <t>FRПСК-2</t>
         </is>
       </c>
       <c r="B20" s="35" t="inlineStr">
         <is>
-          <t>Янгиюнусабад</t>
+          <t>Пскент</t>
         </is>
       </c>
       <c r="C20" s="42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D20" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E20" s="42" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F20" s="42" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G20" s="42" t="n">
         <v>7</v>
@@ -8441,7 +8441,7 @@
         <v>7</v>
       </c>
       <c r="Z20" s="42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA20" s="42" t="n">
         <v>7</v>
@@ -8450,7 +8450,7 @@
         <v>7</v>
       </c>
       <c r="AC20" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -8543,7 +8543,7 @@
         <v>7</v>
       </c>
       <c r="AC21" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -8636,7 +8636,7 @@
         <v>7</v>
       </c>
       <c r="AC22" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -8729,7 +8729,7 @@
         <v>7</v>
       </c>
       <c r="AC23" s="42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
